--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__PASEO LA PAZ.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__PASEO LA PAZ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="671">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1402" uniqueCount="720">
   <si>
     <t>IDSocio</t>
   </si>
@@ -112,13 +112,19 @@
     <t>322857</t>
   </si>
   <si>
+    <t>332784</t>
+  </si>
+  <si>
+    <t>336694</t>
+  </si>
+  <si>
     <t>227959</t>
   </si>
   <si>
-    <t>332784</t>
-  </si>
-  <si>
-    <t>336694</t>
+    <t>340279</t>
+  </si>
+  <si>
+    <t>340290</t>
   </si>
   <si>
     <t>339939</t>
@@ -127,123 +133,129 @@
     <t>340015</t>
   </si>
   <si>
+    <t>340350</t>
+  </si>
+  <si>
+    <t>340590</t>
+  </si>
+  <si>
+    <t>341119</t>
+  </si>
+  <si>
     <t>339764</t>
   </si>
   <si>
-    <t>340279</t>
-  </si>
-  <si>
-    <t>340290</t>
+    <t>341136</t>
+  </si>
+  <si>
+    <t>341390</t>
   </si>
   <si>
     <t>340286</t>
   </si>
   <si>
-    <t>340590</t>
-  </si>
-  <si>
-    <t>340350</t>
-  </si>
-  <si>
     <t>340215</t>
   </si>
   <si>
+    <t>341783</t>
+  </si>
+  <si>
+    <t>341785</t>
+  </si>
+  <si>
+    <t>341986</t>
+  </si>
+  <si>
+    <t>340554</t>
+  </si>
+  <si>
+    <t>342188</t>
+  </si>
+  <si>
     <t>340353</t>
   </si>
   <si>
-    <t>340554</t>
-  </si>
-  <si>
-    <t>341136</t>
-  </si>
-  <si>
-    <t>341390</t>
+    <t>342302</t>
+  </si>
+  <si>
+    <t>342520</t>
   </si>
   <si>
     <t>341114</t>
   </si>
   <si>
-    <t>341119</t>
-  </si>
-  <si>
-    <t>341783</t>
-  </si>
-  <si>
-    <t>341785</t>
-  </si>
-  <si>
-    <t>341986</t>
+    <t>342230</t>
+  </si>
+  <si>
+    <t>342527</t>
+  </si>
+  <si>
+    <t>343038</t>
+  </si>
+  <si>
+    <t>342701</t>
+  </si>
+  <si>
+    <t>341799</t>
+  </si>
+  <si>
+    <t>342226</t>
+  </si>
+  <si>
+    <t>342920</t>
+  </si>
+  <si>
+    <t>343251</t>
+  </si>
+  <si>
+    <t>343254</t>
+  </si>
+  <si>
+    <t>343379</t>
+  </si>
+  <si>
+    <t>342427</t>
+  </si>
+  <si>
+    <t>343458</t>
+  </si>
+  <si>
+    <t>343509</t>
+  </si>
+  <si>
+    <t>343375</t>
+  </si>
+  <si>
+    <t>342684</t>
   </si>
   <si>
     <t>341797</t>
   </si>
   <si>
-    <t>341799</t>
-  </si>
-  <si>
-    <t>342226</t>
-  </si>
-  <si>
-    <t>342302</t>
-  </si>
-  <si>
-    <t>342188</t>
-  </si>
-  <si>
-    <t>342230</t>
+    <t>343754</t>
+  </si>
+  <si>
+    <t>344321</t>
+  </si>
+  <si>
+    <t>344516</t>
   </si>
   <si>
     <t>342051</t>
   </si>
   <si>
-    <t>342427</t>
-  </si>
-  <si>
-    <t>342520</t>
-  </si>
-  <si>
-    <t>342701</t>
-  </si>
-  <si>
-    <t>343038</t>
+    <t>344366</t>
   </si>
   <si>
     <t>342490</t>
   </si>
   <si>
-    <t>342684</t>
-  </si>
-  <si>
-    <t>342527</t>
-  </si>
-  <si>
-    <t>343754</t>
-  </si>
-  <si>
-    <t>342920</t>
-  </si>
-  <si>
-    <t>343254</t>
-  </si>
-  <si>
-    <t>343458</t>
-  </si>
-  <si>
-    <t>343509</t>
-  </si>
-  <si>
-    <t>343379</t>
+    <t>344316</t>
   </si>
   <si>
     <t>343166</t>
   </si>
   <si>
-    <t>343251</t>
-  </si>
-  <si>
-    <t>343375</t>
-  </si>
-  <si>
     <t>343508</t>
   </si>
   <si>
@@ -259,13 +271,19 @@
     <t>19796</t>
   </si>
   <si>
+    <t>14805</t>
+  </si>
+  <si>
+    <t>22420</t>
+  </si>
+  <si>
     <t>25464</t>
   </si>
   <si>
-    <t>14805</t>
-  </si>
-  <si>
-    <t>22420</t>
+    <t>18097</t>
+  </si>
+  <si>
+    <t>18108</t>
   </si>
   <si>
     <t>17757</t>
@@ -274,123 +292,129 @@
     <t>17833</t>
   </si>
   <si>
+    <t>18168</t>
+  </si>
+  <si>
+    <t>18408</t>
+  </si>
+  <si>
+    <t>18937</t>
+  </si>
+  <si>
     <t>17582</t>
   </si>
   <si>
-    <t>18097</t>
-  </si>
-  <si>
-    <t>18108</t>
+    <t>18954</t>
+  </si>
+  <si>
+    <t>19208</t>
   </si>
   <si>
     <t>18104</t>
   </si>
   <si>
-    <t>18408</t>
-  </si>
-  <si>
-    <t>18168</t>
-  </si>
-  <si>
     <t>18033</t>
   </si>
   <si>
+    <t>19601</t>
+  </si>
+  <si>
+    <t>19603</t>
+  </si>
+  <si>
+    <t>19804</t>
+  </si>
+  <si>
+    <t>18372</t>
+  </si>
+  <si>
+    <t>20006</t>
+  </si>
+  <si>
     <t>18171</t>
   </si>
   <si>
-    <t>18372</t>
-  </si>
-  <si>
-    <t>18954</t>
-  </si>
-  <si>
-    <t>19208</t>
+    <t>20120</t>
+  </si>
+  <si>
+    <t>20337</t>
   </si>
   <si>
     <t>18932</t>
   </si>
   <si>
-    <t>18937</t>
-  </si>
-  <si>
-    <t>19601</t>
-  </si>
-  <si>
-    <t>19603</t>
-  </si>
-  <si>
-    <t>19804</t>
+    <t>20048</t>
+  </si>
+  <si>
+    <t>20344</t>
+  </si>
+  <si>
+    <t>20855</t>
+  </si>
+  <si>
+    <t>20518</t>
+  </si>
+  <si>
+    <t>19617</t>
+  </si>
+  <si>
+    <t>20044</t>
+  </si>
+  <si>
+    <t>20737</t>
+  </si>
+  <si>
+    <t>21068</t>
+  </si>
+  <si>
+    <t>21071</t>
+  </si>
+  <si>
+    <t>21196</t>
+  </si>
+  <si>
+    <t>20244</t>
+  </si>
+  <si>
+    <t>21275</t>
+  </si>
+  <si>
+    <t>21326</t>
+  </si>
+  <si>
+    <t>21192</t>
+  </si>
+  <si>
+    <t>20501</t>
   </si>
   <si>
     <t>19615</t>
   </si>
   <si>
-    <t>19617</t>
-  </si>
-  <si>
-    <t>20044</t>
-  </si>
-  <si>
-    <t>20120</t>
-  </si>
-  <si>
-    <t>20006</t>
-  </si>
-  <si>
-    <t>20048</t>
+    <t>21571</t>
+  </si>
+  <si>
+    <t>22138</t>
+  </si>
+  <si>
+    <t>22333</t>
   </si>
   <si>
     <t>19869</t>
   </si>
   <si>
-    <t>20244</t>
-  </si>
-  <si>
-    <t>20337</t>
-  </si>
-  <si>
-    <t>20518</t>
-  </si>
-  <si>
-    <t>20855</t>
+    <t>22183</t>
   </si>
   <si>
     <t>20307</t>
   </si>
   <si>
-    <t>20501</t>
-  </si>
-  <si>
-    <t>20344</t>
-  </si>
-  <si>
-    <t>21571</t>
-  </si>
-  <si>
-    <t>20737</t>
-  </si>
-  <si>
-    <t>21071</t>
-  </si>
-  <si>
-    <t>21275</t>
-  </si>
-  <si>
-    <t>21326</t>
-  </si>
-  <si>
-    <t>21196</t>
+    <t>22133</t>
   </si>
   <si>
     <t>20983</t>
   </si>
   <si>
-    <t>21068</t>
-  </si>
-  <si>
-    <t>21192</t>
-  </si>
-  <si>
     <t>21325</t>
   </si>
   <si>
@@ -409,13 +433,19 @@
     <t>NAYELI</t>
   </si>
   <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ZULEMA</t>
+  </si>
+  <si>
     <t xml:space="preserve">DANYA MICHELLE AVALOS </t>
   </si>
   <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ZULEMA</t>
+    <t xml:space="preserve">LUZ ANGELICA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHRISTIAN ALEJANDRO </t>
   </si>
   <si>
     <t>GABRIELA</t>
@@ -424,115 +454,121 @@
     <t>MARIA FERNANDA</t>
   </si>
   <si>
+    <t xml:space="preserve">LUIS MANUEL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANA LAURA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HANNIA MARIA </t>
+  </si>
+  <si>
     <t xml:space="preserve">WILIAM ULISES </t>
   </si>
   <si>
-    <t xml:space="preserve">LUZ ANGELICA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHRISTIAN ALEJANDRO </t>
+    <t xml:space="preserve">ROSA ISELA </t>
+  </si>
+  <si>
+    <t>FERNANDA JETSEL</t>
   </si>
   <si>
     <t xml:space="preserve">AMY ANGELINE </t>
   </si>
   <si>
-    <t xml:space="preserve">ANA LAURA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUIS MANUEL </t>
-  </si>
-  <si>
     <t xml:space="preserve">FRANCISCO JAVIER </t>
   </si>
   <si>
+    <t>ERNESTO</t>
+  </si>
+  <si>
+    <t>DENIS ALEJANDRA</t>
+  </si>
+  <si>
+    <t>KARLA ELIZABETH</t>
+  </si>
+  <si>
+    <t>JANNETT</t>
+  </si>
+  <si>
+    <t>EDNA</t>
+  </si>
+  <si>
     <t xml:space="preserve">GIBERTO </t>
   </si>
   <si>
-    <t>JANNETT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROSA ISELA </t>
-  </si>
-  <si>
-    <t>FERNANDA JETSEL</t>
+    <t xml:space="preserve">MELANIE </t>
+  </si>
+  <si>
+    <t>JOSE EDUARDO</t>
   </si>
   <si>
     <t>HANNIA ZULETT GUADALUPE</t>
   </si>
   <si>
-    <t xml:space="preserve">HANNIA MARIA </t>
-  </si>
-  <si>
-    <t>ERNESTO</t>
-  </si>
-  <si>
-    <t>DENIS ALEJANDRA</t>
-  </si>
-  <si>
-    <t>KARLA ELIZABETH</t>
+    <t>ANA ARACELY</t>
+  </si>
+  <si>
+    <t>DIANA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOLORES ITZEL </t>
+  </si>
+  <si>
+    <t>SUMIKO MARIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIGUEL ANGEL </t>
+  </si>
+  <si>
+    <t>ARIANY ROSALIA</t>
+  </si>
+  <si>
+    <t>FERNANDO</t>
+  </si>
+  <si>
+    <t>TAMARA</t>
+  </si>
+  <si>
+    <t>JOUSY ISABELLA</t>
+  </si>
+  <si>
+    <t>SARA BEATRIZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NICOLAS </t>
+  </si>
+  <si>
+    <t>EDUARDO ALEXIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANDRA DELMA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIO ALBERTO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANTIAGO </t>
   </si>
   <si>
     <t>SUSANA</t>
   </si>
   <si>
-    <t xml:space="preserve">MIGUEL ANGEL </t>
-  </si>
-  <si>
-    <t>ARIANY ROSALIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MELANIE </t>
-  </si>
-  <si>
-    <t>EDNA</t>
-  </si>
-  <si>
-    <t>ANA ARACELY</t>
+    <t>NOELIA ANAID</t>
+  </si>
+  <si>
+    <t>GABRIEL MARTIN</t>
   </si>
   <si>
     <t xml:space="preserve">CLAUDIA </t>
   </si>
   <si>
-    <t xml:space="preserve">NICOLAS </t>
-  </si>
-  <si>
-    <t>JOSE EDUARDO</t>
-  </si>
-  <si>
-    <t>SUMIKO MARIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOLORES ITZEL </t>
+    <t>REYNA ICELA</t>
   </si>
   <si>
     <t>RENEE ALESSANDRA</t>
   </si>
   <si>
-    <t xml:space="preserve">SANTIAGO </t>
-  </si>
-  <si>
-    <t>DIANA</t>
-  </si>
-  <si>
-    <t>FERNANDO</t>
-  </si>
-  <si>
-    <t>JOUSY ISABELLA</t>
-  </si>
-  <si>
-    <t>EDUARDO ALEXIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SANDRA DELMA </t>
-  </si>
-  <si>
-    <t>SARA BEATRIZ</t>
-  </si>
-  <si>
-    <t>TAMARA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MARIO ALBERTO </t>
+    <t>MAYTE ANELIZ</t>
   </si>
   <si>
     <t xml:space="preserve">LUISA FERNANDA </t>
@@ -550,13 +586,19 @@
     <t>MARILES</t>
   </si>
   <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>HIGUERA</t>
+  </si>
+  <si>
     <t xml:space="preserve">AVALOS </t>
   </si>
   <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>HIGUERA</t>
+    <t xml:space="preserve">LOA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CERVERA </t>
   </si>
   <si>
     <t>LOPEZ</t>
@@ -565,123 +607,129 @@
     <t>AVILES</t>
   </si>
   <si>
+    <t>CASILLAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEZA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CASTRO </t>
+  </si>
+  <si>
     <t>CASTRO</t>
   </si>
   <si>
-    <t xml:space="preserve">LOA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">CERVERA </t>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAPIZ </t>
   </si>
   <si>
     <t xml:space="preserve">GUZMAN </t>
   </si>
   <si>
-    <t xml:space="preserve">MEZA </t>
-  </si>
-  <si>
-    <t>CASILLAS</t>
-  </si>
-  <si>
     <t xml:space="preserve">SANCHEZ </t>
   </si>
   <si>
+    <t xml:space="preserve">GARZA </t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>BERLANGA</t>
+  </si>
+  <si>
+    <t>CALDERON</t>
+  </si>
+  <si>
+    <t>TAMAYO</t>
+  </si>
+  <si>
     <t xml:space="preserve">MENDEZ </t>
   </si>
   <si>
-    <t>CALDERON</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAPIZ </t>
+    <t>ALBAÑEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
   </si>
   <si>
     <t xml:space="preserve">BURGOIN </t>
   </si>
   <si>
-    <t xml:space="preserve">CASTRO </t>
-  </si>
-  <si>
-    <t xml:space="preserve">GARZA </t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>BERLANGA</t>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>MADRID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUBILLOS </t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>COTA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CASTELLANOS </t>
+  </si>
+  <si>
+    <t>PERPULI</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLIVARES </t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUEN </t>
   </si>
   <si>
     <t>PASALAGUA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>COTA</t>
-  </si>
-  <si>
-    <t>ALBAÑEZ</t>
-  </si>
-  <si>
-    <t>TAMAYO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
+    <t xml:space="preserve">GARCIA </t>
+  </si>
+  <si>
+    <t>ARAIZA</t>
+  </si>
+  <si>
+    <t>GULUARTE</t>
   </si>
   <si>
     <t>AGUAYO</t>
   </si>
   <si>
-    <t>PERPULI</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUBILLOS </t>
+    <t>CADENA MATUS</t>
   </si>
   <si>
     <t xml:space="preserve">CESEÑA </t>
   </si>
   <si>
-    <t xml:space="preserve">CUEN </t>
-  </si>
-  <si>
-    <t>MADRID</t>
-  </si>
-  <si>
-    <t>GARCIA ROSALES</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OLIVARES </t>
-  </si>
-  <si>
-    <t xml:space="preserve">CASTELLANOS </t>
+    <t xml:space="preserve">CUEVAS </t>
   </si>
   <si>
     <t>ACEVEDO</t>
   </si>
   <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
     <t xml:space="preserve">MURILLO </t>
   </si>
   <si>
@@ -703,37 +751,55 @@
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t xml:space="preserve">VEGA </t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
     <t>OVALLE</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t xml:space="preserve">VEGA </t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
+    <t>HALE</t>
   </si>
   <si>
     <t>MUNDO</t>
   </si>
   <si>
-    <t>HALE</t>
-  </si>
-  <si>
     <t>IZAGUIRRE</t>
   </si>
   <si>
+    <t>SANTACRUZ</t>
+  </si>
+  <si>
+    <t>SCHCOLNICK</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
     <t xml:space="preserve">HALE </t>
   </si>
   <si>
-    <t>SCHCOLNICK</t>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>LIMOM</t>
   </si>
   <si>
     <t xml:space="preserve">LUCERO </t>
   </si>
   <si>
-    <t>SANTACRUZ</t>
+    <t>BURQUEZ</t>
+  </si>
+  <si>
+    <t>SILVA</t>
+  </si>
+  <si>
+    <t>AGUIRRE</t>
   </si>
   <si>
     <t>VICENT</t>
@@ -742,57 +808,45 @@
     <t>CARDENAS</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>X</t>
+    <t>ORNELAS</t>
+  </si>
+  <si>
+    <t>AGUIÑAGA</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>VERDUGO</t>
+  </si>
+  <si>
+    <t>VIEYRA</t>
+  </si>
+  <si>
+    <t>VIVAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANRIQUEZ </t>
+  </si>
+  <si>
+    <t>CAMACHO</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>BARAJAS</t>
   </si>
   <si>
     <t>OJEDA</t>
   </si>
   <si>
-    <t>VERDUGO</t>
-  </si>
-  <si>
-    <t>LIMOM</t>
-  </si>
-  <si>
-    <t>AGUIRRE</t>
-  </si>
-  <si>
-    <t>SILVA</t>
-  </si>
-  <si>
     <t xml:space="preserve">DAVIS </t>
   </si>
   <si>
-    <t>CAMACHO</t>
-  </si>
-  <si>
-    <t>BURQUEZ</t>
-  </si>
-  <si>
-    <t>ORNELAS</t>
-  </si>
-  <si>
-    <t>VIEYRA</t>
-  </si>
-  <si>
-    <t>VIVAR</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
     <t>RUVALCABA</t>
   </si>
   <si>
-    <t>AGUIÑAGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANRIQUEZ </t>
-  </si>
-  <si>
     <t>52</t>
   </si>
   <si>
@@ -805,13 +859,19 @@
     <t>6122343921</t>
   </si>
   <si>
+    <t>5585803795</t>
+  </si>
+  <si>
+    <t>6122380771</t>
+  </si>
+  <si>
     <t>6122283257</t>
   </si>
   <si>
-    <t>5585803795</t>
-  </si>
-  <si>
-    <t>6122380771</t>
+    <t>6121042102</t>
+  </si>
+  <si>
+    <t>6122289427</t>
   </si>
   <si>
     <t>6121390387</t>
@@ -820,123 +880,129 @@
     <t>6121058570</t>
   </si>
   <si>
+    <t>6121975782</t>
+  </si>
+  <si>
+    <t>6123520177</t>
+  </si>
+  <si>
+    <t>6121543278</t>
+  </si>
+  <si>
     <t>6691484335</t>
   </si>
   <si>
-    <t>6121042102</t>
-  </si>
-  <si>
-    <t>6122289427</t>
+    <t>6121275515</t>
+  </si>
+  <si>
+    <t>6121007438</t>
   </si>
   <si>
     <t>6121220630</t>
   </si>
   <si>
-    <t>6123520177</t>
-  </si>
-  <si>
-    <t>6121975782</t>
-  </si>
-  <si>
     <t>6121370121</t>
   </si>
   <si>
+    <t>8180747965</t>
+  </si>
+  <si>
+    <t>8120018311</t>
+  </si>
+  <si>
+    <t>5577876880</t>
+  </si>
+  <si>
+    <t>6121042182</t>
+  </si>
+  <si>
+    <t>6123489545</t>
+  </si>
+  <si>
     <t>6121528946</t>
   </si>
   <si>
-    <t>6121042182</t>
-  </si>
-  <si>
-    <t>6121275515</t>
-  </si>
-  <si>
-    <t>6121007438</t>
+    <t>6643640599</t>
+  </si>
+  <si>
+    <t>6121196214</t>
   </si>
   <si>
     <t>6121041819</t>
   </si>
   <si>
-    <t>6121543278</t>
-  </si>
-  <si>
-    <t>8180747965</t>
-  </si>
-  <si>
-    <t>8120018311</t>
-  </si>
-  <si>
-    <t>5577876880</t>
+    <t>6121372111</t>
+  </si>
+  <si>
+    <t>6242249486</t>
+  </si>
+  <si>
+    <t>6121029534</t>
+  </si>
+  <si>
+    <t>6121220205</t>
+  </si>
+  <si>
+    <t>6121590416</t>
+  </si>
+  <si>
+    <t>6121692055</t>
+  </si>
+  <si>
+    <t>6121870554</t>
+  </si>
+  <si>
+    <t>5541288966</t>
+  </si>
+  <si>
+    <t>6391613622</t>
+  </si>
+  <si>
+    <t>6122327477</t>
+  </si>
+  <si>
+    <t>6121614567</t>
+  </si>
+  <si>
+    <t>6121677253</t>
+  </si>
+  <si>
+    <t>6121310729</t>
+  </si>
+  <si>
+    <t>6122343338</t>
+  </si>
+  <si>
+    <t>6122186206</t>
   </si>
   <si>
     <t>6121590135</t>
   </si>
   <si>
-    <t>6121590416</t>
-  </si>
-  <si>
-    <t>6121692055</t>
-  </si>
-  <si>
-    <t>6643640599</t>
-  </si>
-  <si>
-    <t>6123489545</t>
-  </si>
-  <si>
-    <t>6121372111</t>
+    <t>6241578514</t>
+  </si>
+  <si>
+    <t>6121498018</t>
+  </si>
+  <si>
+    <t>6121009849</t>
   </si>
   <si>
     <t>8123512800</t>
   </si>
   <si>
-    <t>6121614567</t>
-  </si>
-  <si>
-    <t>6121196214</t>
-  </si>
-  <si>
-    <t>6121220205</t>
-  </si>
-  <si>
-    <t>6121029534</t>
+    <t>6121971764</t>
   </si>
   <si>
     <t>6122046111</t>
   </si>
   <si>
-    <t>6122186206</t>
-  </si>
-  <si>
-    <t>6242249486</t>
-  </si>
-  <si>
-    <t>6241578514</t>
-  </si>
-  <si>
-    <t>6121870554</t>
-  </si>
-  <si>
-    <t>6391613622</t>
-  </si>
-  <si>
-    <t>6121677253</t>
-  </si>
-  <si>
-    <t>6121310729</t>
-  </si>
-  <si>
-    <t>6122327477</t>
+    <t>6241717643</t>
   </si>
   <si>
     <t>6121068152</t>
   </si>
   <si>
-    <t>5541288966</t>
-  </si>
-  <si>
-    <t>6122343338</t>
-  </si>
-  <si>
     <t>6122290863</t>
   </si>
   <si>
@@ -952,55 +1018,70 @@
     <t>PISTACHE 144</t>
   </si>
   <si>
+    <t xml:space="preserve">PUEBLO NUEVO </t>
+  </si>
+  <si>
+    <t>CENTRO</t>
+  </si>
+  <si>
     <t>C ROSAURA ZAPATA S/N</t>
   </si>
   <si>
-    <t xml:space="preserve">PUEBLO NUEVO </t>
-  </si>
-  <si>
-    <t>CENTRO</t>
+    <t>C MANUEL F MONTAÑO</t>
+  </si>
+  <si>
+    <t>C POSEIDON 666</t>
   </si>
   <si>
     <t>CERRO</t>
   </si>
   <si>
+    <t xml:space="preserve">C GASPAR VELA </t>
+  </si>
+  <si>
+    <t>ANDADOR LAS PALMERAS E 615</t>
+  </si>
+  <si>
     <t xml:space="preserve">C VALTIERRA 324 </t>
   </si>
   <si>
-    <t>C MANUEL F MONTAÑO</t>
-  </si>
-  <si>
-    <t>C POSEIDON 666</t>
+    <t xml:space="preserve">EL CENTENARIO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAN FERNANDO </t>
   </si>
   <si>
     <t xml:space="preserve">C MANUEL F MONTOYA </t>
   </si>
   <si>
-    <t>ANDADOR LAS PALMERAS E 615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C GASPAR VELA </t>
-  </si>
-  <si>
     <t>C ISLA PATO 107</t>
   </si>
   <si>
+    <t>ENCINO #216</t>
+  </si>
+  <si>
+    <t>ENCINO # 216</t>
+  </si>
+  <si>
+    <t>CARRETERA AL NORTE KM 11 PRIV. LAS QUINTAS DEL MAR 7</t>
+  </si>
+  <si>
+    <t>PRIV MARINA CENTRAL 117</t>
+  </si>
+  <si>
     <t>C CERRADA SANTA INES 890</t>
   </si>
   <si>
-    <t>CARRETERA AL NORTE KM 11 PRIV. LAS QUINTAS DEL MAR 7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL CENTENARIO </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAN FERNANDO </t>
-  </si>
-  <si>
-    <t>ENCINO #216</t>
-  </si>
-  <si>
-    <t>ENCINO # 216</t>
+    <t>AGUA DULCE 618</t>
+  </si>
+  <si>
+    <t>DEL ESTRIBO</t>
+  </si>
+  <si>
+    <t>AYENDE #1720</t>
+  </si>
+  <si>
+    <t>C PABLO L. GONZALEZ 235</t>
   </si>
   <si>
     <t>PRIV PALO DE SANTA RITA 9</t>
@@ -1009,31 +1090,22 @@
     <t>CALLE EL TRIUNFO #233</t>
   </si>
   <si>
-    <t>AGUA DULCE 618</t>
-  </si>
-  <si>
-    <t>PRIV MARINA CENTRAL 117</t>
-  </si>
-  <si>
-    <t>DEL ESTRIBO</t>
-  </si>
-  <si>
-    <t>C PABLO L. GONZALEZ 235</t>
-  </si>
-  <si>
-    <t>AYENDE #1720</t>
-  </si>
-  <si>
-    <t>Pedro Matias Goni 353</t>
-  </si>
-  <si>
     <t>LA CIMA</t>
   </si>
   <si>
+    <t>C MELON 121</t>
+  </si>
+  <si>
     <t>C OLMECAS 508</t>
   </si>
   <si>
-    <t>C MELON 121</t>
+    <t>PEDRO MATIAS GONI 353</t>
+  </si>
+  <si>
+    <t>C AGROPECUARIA</t>
+  </si>
+  <si>
+    <t>REGIDORES 113</t>
   </si>
   <si>
     <t>ROMA</t>
@@ -1057,13 +1129,19 @@
     <t>23-12-1992</t>
   </si>
   <si>
+    <t>04-03-1978</t>
+  </si>
+  <si>
+    <t>08-04-1983</t>
+  </si>
+  <si>
     <t>22-03-2007</t>
   </si>
   <si>
-    <t>04-03-1978</t>
-  </si>
-  <si>
-    <t>08-04-1983</t>
+    <t>20-09-1980</t>
+  </si>
+  <si>
+    <t>14-11-2011</t>
   </si>
   <si>
     <t>17-10-1997</t>
@@ -1072,123 +1150,129 @@
     <t>08-12-1997</t>
   </si>
   <si>
+    <t>24-08-1999</t>
+  </si>
+  <si>
+    <t>06-07-2003</t>
+  </si>
+  <si>
+    <t>25-01-2008</t>
+  </si>
+  <si>
     <t>21-09-1990</t>
   </si>
   <si>
-    <t>20-09-1980</t>
-  </si>
-  <si>
-    <t>14-11-2011</t>
+    <t>16-02-1981</t>
+  </si>
+  <si>
+    <t>21-10-1985</t>
   </si>
   <si>
     <t>20-01-2010</t>
   </si>
   <si>
-    <t>06-07-2003</t>
-  </si>
-  <si>
-    <t>24-08-1999</t>
-  </si>
-  <si>
     <t>26-03-1977</t>
   </si>
   <si>
+    <t>27-10-1990</t>
+  </si>
+  <si>
+    <t>01-09-1985</t>
+  </si>
+  <si>
+    <t>22-05-2001</t>
+  </si>
+  <si>
+    <t>22-09-2004</t>
+  </si>
+  <si>
+    <t>02-04-1974</t>
+  </si>
+  <si>
     <t>23-11-2001</t>
   </si>
   <si>
-    <t>22-09-2004</t>
-  </si>
-  <si>
-    <t>16-02-1981</t>
-  </si>
-  <si>
-    <t>21-10-1985</t>
+    <t>01-05-1980</t>
+  </si>
+  <si>
+    <t>03-01-1992</t>
   </si>
   <si>
     <t>01-12-2008</t>
   </si>
   <si>
-    <t>25-01-2008</t>
-  </si>
-  <si>
-    <t>27-10-1990</t>
-  </si>
-  <si>
-    <t>01-09-1985</t>
-  </si>
-  <si>
-    <t>22-05-2001</t>
+    <t>08-10-2008</t>
+  </si>
+  <si>
+    <t>15-05-1995</t>
+  </si>
+  <si>
+    <t>10-12-1994</t>
+  </si>
+  <si>
+    <t>07-04-2013</t>
+  </si>
+  <si>
+    <t>30-10-1955</t>
+  </si>
+  <si>
+    <t>08-10-1981</t>
+  </si>
+  <si>
+    <t>16-09-1975</t>
+  </si>
+  <si>
+    <t>21-12-2004</t>
+  </si>
+  <si>
+    <t>12-10-2003</t>
+  </si>
+  <si>
+    <t>03-06-1981</t>
+  </si>
+  <si>
+    <t>06-03-1973</t>
+  </si>
+  <si>
+    <t>08-04-1991</t>
+  </si>
+  <si>
+    <t>16-04-1976</t>
+  </si>
+  <si>
+    <t>12-12-1977</t>
+  </si>
+  <si>
+    <t>06-10-2008</t>
   </si>
   <si>
     <t>06-02-1966</t>
   </si>
   <si>
-    <t>30-10-1955</t>
-  </si>
-  <si>
-    <t>08-10-1981</t>
-  </si>
-  <si>
-    <t>01-05-1980</t>
-  </si>
-  <si>
-    <t>02-04-1974</t>
-  </si>
-  <si>
-    <t>08-10-2008</t>
+    <t>07-11-1978</t>
+  </si>
+  <si>
+    <t>25-05-2007</t>
+  </si>
+  <si>
+    <t>13-02-2000</t>
   </si>
   <si>
     <t>13-11-2002</t>
   </si>
   <si>
-    <t>06-03-1973</t>
-  </si>
-  <si>
-    <t>03-01-1992</t>
-  </si>
-  <si>
-    <t>07-04-2013</t>
-  </si>
-  <si>
-    <t>10-12-1994</t>
+    <t>22-08-1987</t>
   </si>
   <si>
     <t>20-02-2007</t>
   </si>
   <si>
-    <t>06-10-2008</t>
-  </si>
-  <si>
-    <t>15-05-1995</t>
-  </si>
-  <si>
-    <t>31-12-9999</t>
-  </si>
-  <si>
-    <t>16-09-1975</t>
-  </si>
-  <si>
-    <t>12-10-2003</t>
-  </si>
-  <si>
-    <t>08-04-1991</t>
-  </si>
-  <si>
-    <t>16-04-1976</t>
-  </si>
-  <si>
-    <t>03-06-1981</t>
+    <t>02-01-2007</t>
   </si>
   <si>
     <t>13-09-2003</t>
   </si>
   <si>
-    <t>21-12-2004</t>
-  </si>
-  <si>
-    <t>12-12-1977</t>
-  </si>
-  <si>
     <t>19-12-2004</t>
   </si>
   <si>
@@ -1204,13 +1288,19 @@
     <t>NAYUNOCHO@GMAIL.COM</t>
   </si>
   <si>
+    <t>ALEJANDRO.ROBLESARANDA@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ZULEMA@BAJASURREALTORS.COM</t>
+  </si>
+  <si>
     <t>ALEDANIA22@GMAIL.COM</t>
   </si>
   <si>
-    <t>ALEJANDRO.ROBLESARANDA@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>ZULEMA@BAJASURREALTORS.COM</t>
+    <t>LICLOAVEGA20@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>CHRISTIANCERV777@GMAIL.COM</t>
   </si>
   <si>
     <t>OVALLEGABRIELA97@GMAIL.COM</t>
@@ -1219,123 +1309,129 @@
     <t>AVILESSANCHEZFERNANDA@GMAIL.COM</t>
   </si>
   <si>
+    <t>LUISCASILLAS_19@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>MANALAURA346@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>HANNIATAY13@ICLOUD.COM</t>
+  </si>
+  <si>
     <t>WIL_UCL@HOTMAIL.COM</t>
   </si>
   <si>
-    <t>LICLOAVEGA20@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>CHRISTIANCERV777@GMAIL.COM</t>
+    <t>IVAZQUEZ@CIBNOR.MX</t>
+  </si>
+  <si>
+    <t>SINDICATO.JEC@GMAIL.COM</t>
   </si>
   <si>
     <t>LICLOAVEGA200@GMAIL.COM</t>
   </si>
   <si>
-    <t>MANALAURA346@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>LUISCASILLAS_19@HOTMAIL.COM</t>
-  </si>
-  <si>
     <t>FRANCISCO.SAN.IZA@GMAIL.COM</t>
   </si>
   <si>
+    <t>DRERNESTOGARZA@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ALESSANALESAN85@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>BERLANGACALDERONELIZABETH22@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>JANNETT.22099@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>EDNA_321@HOTMAIL.COM</t>
+  </si>
+  <si>
     <t>GILBERTO.MEN20011@GMAIL.COM</t>
   </si>
   <si>
-    <t>JANNETT.22099@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>IVAZQUEZ@CIBNOR.MX</t>
-  </si>
-  <si>
-    <t>SINDICATO.JEC@GMAIL.COM</t>
+    <t>ANIEALRO2020@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>LIMON.EDUARDO@HOTMAIL.COM</t>
   </si>
   <si>
     <t>HANNIAZULETTBURGOIN@GMAIL.COM</t>
   </si>
   <si>
-    <t>HANNIATAY13@ICLOUD.COM</t>
-  </si>
-  <si>
-    <t>DRERNESTOGARZA@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>ALESSANALESAN85@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>BERLANGACALDERONELIZABETH22@GMAIL.COM</t>
+    <t>ARIANYR2C@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>DIANAMB_@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>CUBILLOSITZEL@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>SUMIJOAGUIRREFISHER@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>MHVICENT@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ARIANY2C@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>FERNANDOCRUZORNELAS@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>TAMARA211204@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ISABELLAMENDOZAVV@OUTLOOK.COM</t>
+  </si>
+  <si>
+    <t>DRA.SARACASTELLANOS@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>NICOLASPERPULIVERDUGO@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>EDUARDOVIEYRA06@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>SANDYPRICES.19@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ROSASCASTELLANOS@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>SANTIAGOCUEN23@GMAIL.COM</t>
   </si>
   <si>
     <t>SIPHITYA@GMAIL.COM</t>
   </si>
   <si>
-    <t>MHVICENT@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>ARIANY2C@HOTMAIL.COM</t>
-  </si>
-  <si>
-    <t>ANIEALRO2020@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>EDNA_321@HOTMAIL.COM</t>
-  </si>
-  <si>
-    <t>ARIANYR2C@HOTMAIL.COM</t>
+    <t>NETOGR78@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>NOELIAANAIDARAIZA@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>MARTINBARAJAS1302@GMAIL.COM</t>
   </si>
   <si>
     <t>CLAUDIABEATRIZ.AGUAYO@GMAIL.COM</t>
   </si>
   <si>
-    <t>NICOLASPERPULIVERDUGO@HOTMAIL.COM</t>
-  </si>
-  <si>
-    <t>LIMON.EDUARDO@HOTMAIL.COM</t>
-  </si>
-  <si>
-    <t>SUMIJOAGUIRREFISHER@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>CUBILLOSITZEL@GMAIL.COM</t>
+    <t>REYNAICELACM@GMAIL.COM</t>
   </si>
   <si>
     <t>RENEEE777111@GMAIL.COM</t>
   </si>
   <si>
-    <t>SANTIAGOCUEN23@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>DIANAMB_@HOTMAIL.COM</t>
-  </si>
-  <si>
-    <t>netogr78@gmail.com</t>
-  </si>
-  <si>
-    <t>FERNANDOCRUZORNELAS@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>ISABELLAMENDOZAVV@OUTLOOK.COM</t>
-  </si>
-  <si>
-    <t>EDUARDOVIEYRA06@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>SANDYPRICES.19@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>DRA.SARACASTELLANOS@GMAIL.COM</t>
+    <t>ANELIZCG07@GMAIL.COM</t>
   </si>
   <si>
     <t>FERNANDAACEV13@GMAIL.COM</t>
   </si>
   <si>
-    <t>TAMARA211204@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>ROSASCASTELLANOS@GMAIL.COM</t>
-  </si>
-  <si>
     <t>ISAFERNAN.19@GMAIL.COM</t>
   </si>
   <si>
@@ -1351,13 +1447,19 @@
     <t>10-11-2025 12:13:22</t>
   </si>
   <si>
+    <t>07-01-2026 09:40:49</t>
+  </si>
+  <si>
+    <t>21-01-2026 10:28:18</t>
+  </si>
+  <si>
     <t>04-04-2024 18:18:59</t>
   </si>
   <si>
-    <t>07-01-2026 09:40:49</t>
-  </si>
-  <si>
-    <t>21-01-2026 10:28:18</t>
+    <t>02-02-2026 16:39:48</t>
+  </si>
+  <si>
+    <t>02-02-2026 16:52:38</t>
   </si>
   <si>
     <t>02-02-2026 09:09:56</t>
@@ -1366,123 +1468,129 @@
     <t>02-02-2026 10:34:28</t>
   </si>
   <si>
+    <t>02-02-2026 18:42:38</t>
+  </si>
+  <si>
+    <t>03-02-2026 14:17:27</t>
+  </si>
+  <si>
+    <t>04-02-2026 17:46:50</t>
+  </si>
+  <si>
     <t>01-02-2026 10:17:19</t>
   </si>
   <si>
-    <t>02-02-2026 16:39:48</t>
-  </si>
-  <si>
-    <t>02-02-2026 16:52:38</t>
+    <t>04-02-2026 18:14:43</t>
+  </si>
+  <si>
+    <t>05-02-2026 17:08:31</t>
   </si>
   <si>
     <t>02-02-2026 16:44:59</t>
   </si>
   <si>
-    <t>03-02-2026 14:17:27</t>
-  </si>
-  <si>
-    <t>02-02-2026 18:42:38</t>
-  </si>
-  <si>
     <t>02-02-2026 15:28:02</t>
   </si>
   <si>
+    <t>07-02-2026 10:19:47</t>
+  </si>
+  <si>
+    <t>07-02-2026 10:21:42</t>
+  </si>
+  <si>
+    <t>09-02-2026 04:13:10</t>
+  </si>
+  <si>
+    <t>03-02-2026 13:02:59</t>
+  </si>
+  <si>
+    <t>09-02-2026 14:43:59</t>
+  </si>
+  <si>
     <t>02-02-2026 18:54:26</t>
   </si>
   <si>
-    <t>03-02-2026 13:02:59</t>
-  </si>
-  <si>
-    <t>04-02-2026 18:14:43</t>
-  </si>
-  <si>
-    <t>05-02-2026 17:08:31</t>
+    <t>09-02-2026 17:06:10</t>
+  </si>
+  <si>
+    <t>10-02-2026 06:36:49</t>
   </si>
   <si>
     <t>04-02-2026 17:38:34</t>
   </si>
   <si>
-    <t>04-02-2026 17:46:50</t>
-  </si>
-  <si>
-    <t>07-02-2026 10:19:47</t>
-  </si>
-  <si>
-    <t>07-02-2026 10:21:42</t>
-  </si>
-  <si>
-    <t>09-02-2026 04:13:10</t>
+    <t>09-02-2026 15:59:56</t>
+  </si>
+  <si>
+    <t>10-02-2026 07:13:24</t>
+  </si>
+  <si>
+    <t>11-02-2026 16:24:22</t>
+  </si>
+  <si>
+    <t>10-02-2026 16:22:22</t>
+  </si>
+  <si>
+    <t>07-02-2026 10:56:26</t>
+  </si>
+  <si>
+    <t>09-02-2026 15:54:22</t>
+  </si>
+  <si>
+    <t>11-02-2026 09:39:30</t>
+  </si>
+  <si>
+    <t>12-02-2026 13:32:17</t>
+  </si>
+  <si>
+    <t>12-02-2026 13:36:03</t>
+  </si>
+  <si>
+    <t>12-02-2026 18:54:35</t>
+  </si>
+  <si>
+    <t>09-02-2026 19:09:18</t>
+  </si>
+  <si>
+    <t>13-02-2026 10:06:29</t>
+  </si>
+  <si>
+    <t>13-02-2026 15:14:31</t>
+  </si>
+  <si>
+    <t>12-02-2026 18:48:15</t>
+  </si>
+  <si>
+    <t>10-02-2026 15:52:34</t>
   </si>
   <si>
     <t>07-02-2026 10:52:31</t>
   </si>
   <si>
-    <t>07-02-2026 10:56:26</t>
-  </si>
-  <si>
-    <t>09-02-2026 15:54:22</t>
-  </si>
-  <si>
-    <t>09-02-2026 17:06:10</t>
-  </si>
-  <si>
-    <t>09-02-2026 14:43:59</t>
-  </si>
-  <si>
-    <t>09-02-2026 15:59:56</t>
+    <t>14-02-2026 18:11:53</t>
+  </si>
+  <si>
+    <t>16-02-2026 18:57:53</t>
+  </si>
+  <si>
+    <t>17-02-2026 15:10:23</t>
   </si>
   <si>
     <t>09-02-2026 08:32:35</t>
   </si>
   <si>
-    <t>09-02-2026 19:09:18</t>
-  </si>
-  <si>
-    <t>10-02-2026 06:36:49</t>
-  </si>
-  <si>
-    <t>10-02-2026 16:22:22</t>
-  </si>
-  <si>
-    <t>11-02-2026 16:24:22</t>
+    <t>16-02-2026 23:34:26</t>
   </si>
   <si>
     <t>09-02-2026 20:30:27</t>
   </si>
   <si>
-    <t>10-02-2026 15:52:34</t>
-  </si>
-  <si>
-    <t>10-02-2026 07:13:24</t>
-  </si>
-  <si>
-    <t>14-02-2026 18:11:53</t>
-  </si>
-  <si>
-    <t>11-02-2026 09:39:30</t>
-  </si>
-  <si>
-    <t>12-02-2026 13:36:03</t>
-  </si>
-  <si>
-    <t>13-02-2026 10:06:29</t>
-  </si>
-  <si>
-    <t>13-02-2026 15:14:31</t>
-  </si>
-  <si>
-    <t>12-02-2026 18:54:35</t>
+    <t>16-02-2026 18:53:41</t>
   </si>
   <si>
     <t>12-02-2026 07:13:35</t>
   </si>
   <si>
-    <t>12-02-2026 13:32:17</t>
-  </si>
-  <si>
-    <t>12-02-2026 18:48:15</t>
-  </si>
-  <si>
     <t>13-02-2026 15:03:03</t>
   </si>
   <si>
@@ -1492,15 +1600,18 @@
     <t>Tarifas 2026 LE</t>
   </si>
   <si>
+    <t>inscripcion promo 199</t>
+  </si>
+  <si>
     <t>Forzoso</t>
   </si>
   <si>
+    <t>Sin contrato</t>
+  </si>
+  <si>
     <t>No Forzoso</t>
   </si>
   <si>
-    <t>Sin contrato</t>
-  </si>
-  <si>
     <t>PROMO FEBRERO 12 MESES</t>
   </si>
   <si>
@@ -1510,12 +1621,12 @@
     <t>PLAN FAMILIA / AMIGOS X $499</t>
   </si>
   <si>
+    <t>CONVENIOS $549</t>
+  </si>
+  <si>
     <t>RECURRENTE $649 LE</t>
   </si>
   <si>
-    <t>CONVENIOS $549</t>
-  </si>
-  <si>
     <t>1 MES $899</t>
   </si>
   <si>
@@ -1525,12 +1636,12 @@
     <t>499</t>
   </si>
   <si>
+    <t>549</t>
+  </si>
+  <si>
     <t>649</t>
   </si>
   <si>
-    <t>549</t>
-  </si>
-  <si>
     <t>899</t>
   </si>
   <si>
@@ -1546,13 +1657,19 @@
     <t>05-02-2026 15:40:20</t>
   </si>
   <si>
+    <t>03-02-2026 14:14:15</t>
+  </si>
+  <si>
+    <t>02-02-2026 09:06:56</t>
+  </si>
+  <si>
     <t>04-02-2026 13:36:51</t>
   </si>
   <si>
-    <t>03-02-2026 14:14:15</t>
-  </si>
-  <si>
-    <t>02-02-2026 09:06:56</t>
+    <t>02-02-2026 16:43:50</t>
+  </si>
+  <si>
+    <t>02-02-2026 16:58:16</t>
   </si>
   <si>
     <t>02-02-2026 09:17:23</t>
@@ -1561,123 +1678,129 @@
     <t>03-02-2026 05:22:36</t>
   </si>
   <si>
+    <t>02-02-2026 18:50:43</t>
+  </si>
+  <si>
+    <t>03-02-2026 14:22:36</t>
+  </si>
+  <si>
+    <t>04-02-2026 17:47:55</t>
+  </si>
+  <si>
     <t>01-02-2026 10:33:00</t>
   </si>
   <si>
-    <t>02-02-2026 16:43:50</t>
-  </si>
-  <si>
-    <t>02-02-2026 16:58:16</t>
+    <t>04-02-2026 18:22:58</t>
+  </si>
+  <si>
+    <t>05-02-2026 17:12:39</t>
   </si>
   <si>
     <t>02-02-2026 16:47:48</t>
   </si>
   <si>
-    <t>03-02-2026 14:22:36</t>
-  </si>
-  <si>
-    <t>02-02-2026 18:50:43</t>
-  </si>
-  <si>
     <t>02-02-2026 15:40:28</t>
   </si>
   <si>
+    <t>11-02-2026 15:26:34</t>
+  </si>
+  <si>
+    <t>11-02-2026 15:32:23</t>
+  </si>
+  <si>
+    <t>09-02-2026 04:15:04</t>
+  </si>
+  <si>
+    <t>03-02-2026 13:08:32</t>
+  </si>
+  <si>
+    <t>11-02-2026 13:12:45</t>
+  </si>
+  <si>
     <t>02-02-2026 18:58:19</t>
   </si>
   <si>
-    <t>03-02-2026 13:08:32</t>
-  </si>
-  <si>
-    <t>04-02-2026 18:22:58</t>
-  </si>
-  <si>
-    <t>05-02-2026 17:12:39</t>
+    <t>09-02-2026 17:08:49</t>
+  </si>
+  <si>
+    <t>10-02-2026 06:41:55</t>
   </si>
   <si>
     <t>04-02-2026 17:42:38</t>
   </si>
   <si>
-    <t>04-02-2026 17:47:55</t>
-  </si>
-  <si>
-    <t>11-02-2026 15:26:34</t>
-  </si>
-  <si>
-    <t>11-02-2026 15:32:23</t>
-  </si>
-  <si>
-    <t>09-02-2026 04:15:04</t>
+    <t>12-02-2026 16:08:25</t>
+  </si>
+  <si>
+    <t>10-02-2026 07:22:03</t>
+  </si>
+  <si>
+    <t>11-02-2026 16:38:56</t>
+  </si>
+  <si>
+    <t>10-02-2026 16:28:08</t>
+  </si>
+  <si>
+    <t>07-02-2026 11:33:16</t>
+  </si>
+  <si>
+    <t>10-02-2026 17:08:18</t>
+  </si>
+  <si>
+    <t>11-02-2026 09:45:27</t>
+  </si>
+  <si>
+    <t>12-02-2026 13:33:36</t>
+  </si>
+  <si>
+    <t>12-02-2026 13:37:01</t>
+  </si>
+  <si>
+    <t>12-02-2026 18:58:52</t>
+  </si>
+  <si>
+    <t>09-02-2026 19:12:38</t>
+  </si>
+  <si>
+    <t>13-02-2026 10:17:33</t>
+  </si>
+  <si>
+    <t>13-02-2026 15:17:56</t>
+  </si>
+  <si>
+    <t>12-02-2026 18:53:02</t>
+  </si>
+  <si>
+    <t>10-02-2026 15:55:25</t>
   </si>
   <si>
     <t>07-02-2026 11:37:55</t>
   </si>
   <si>
-    <t>07-02-2026 11:33:16</t>
-  </si>
-  <si>
-    <t>10-02-2026 17:08:18</t>
-  </si>
-  <si>
-    <t>09-02-2026 17:08:49</t>
-  </si>
-  <si>
-    <t>11-02-2026 13:12:45</t>
-  </si>
-  <si>
-    <t>12-02-2026 16:08:25</t>
+    <t>14-02-2026 18:11:54</t>
+  </si>
+  <si>
+    <t>16-02-2026 18:59:47</t>
+  </si>
+  <si>
+    <t>17-02-2026 15:16:36</t>
   </si>
   <si>
     <t>11-02-2026 09:29:24</t>
   </si>
   <si>
-    <t>09-02-2026 19:12:38</t>
-  </si>
-  <si>
-    <t>10-02-2026 06:41:55</t>
-  </si>
-  <si>
-    <t>10-02-2026 16:28:08</t>
-  </si>
-  <si>
-    <t>11-02-2026 16:38:56</t>
+    <t>16-02-2026 23:34:27</t>
   </si>
   <si>
     <t>09-02-2026 20:32:52</t>
   </si>
   <si>
-    <t>10-02-2026 15:55:25</t>
-  </si>
-  <si>
-    <t>10-02-2026 07:22:03</t>
-  </si>
-  <si>
-    <t>14-02-2026 18:11:54</t>
-  </si>
-  <si>
-    <t>11-02-2026 09:45:27</t>
-  </si>
-  <si>
-    <t>12-02-2026 13:37:01</t>
-  </si>
-  <si>
-    <t>13-02-2026 10:17:33</t>
-  </si>
-  <si>
-    <t>13-02-2026 15:17:56</t>
-  </si>
-  <si>
-    <t>12-02-2026 18:58:52</t>
+    <t>17-02-2026 14:17:50</t>
   </si>
   <si>
     <t>12-02-2026 07:18:27</t>
   </si>
   <si>
-    <t>12-02-2026 13:33:36</t>
-  </si>
-  <si>
-    <t>12-02-2026 18:53:02</t>
-  </si>
-  <si>
     <t>13-02-2026 15:12:55</t>
   </si>
   <si>
@@ -1693,15 +1816,15 @@
     <t>05-03-2026 23:59:59</t>
   </si>
   <si>
+    <t>03-03-2026 23:59:59</t>
+  </si>
+  <si>
+    <t>28-02-2026 23:59:59</t>
+  </si>
+  <si>
     <t>04-03-2026 23:59:59</t>
   </si>
   <si>
-    <t>03-03-2026 23:59:59</t>
-  </si>
-  <si>
-    <t>28-02-2026 23:59:59</t>
-  </si>
-  <si>
     <t>01-03-2026 23:59:59</t>
   </si>
   <si>
@@ -1711,19 +1834,25 @@
     <t>09-03-2026 23:59:59</t>
   </si>
   <si>
+    <t>10-03-2026 23:59:59</t>
+  </si>
+  <si>
     <t>07-03-2026 23:59:59</t>
   </si>
   <si>
-    <t>10-03-2026 23:59:59</t>
-  </si>
-  <si>
     <t>09-05-2026 23:59:59</t>
   </si>
   <si>
+    <t>13-03-2026 23:59:59</t>
+  </si>
+  <si>
     <t>14-03-2026 23:59:59</t>
   </si>
   <si>
-    <t>13-03-2026 23:59:59</t>
+    <t>16-03-2026 23:59:59</t>
+  </si>
+  <si>
+    <t>17-03-2026 23:59:59</t>
   </si>
   <si>
     <t>15-03-2026 23:59:59</t>
@@ -1738,13 +1867,19 @@
     <t>05-02-2026 15:40:02</t>
   </si>
   <si>
+    <t>03-02-2026 13:57:02</t>
+  </si>
+  <si>
+    <t>28-01-2026 09:24:49</t>
+  </si>
+  <si>
     <t>04-02-2026 13:36:16</t>
   </si>
   <si>
-    <t>03-02-2026 13:57:02</t>
-  </si>
-  <si>
-    <t>28-01-2026 09:24:49</t>
+    <t>02-02-2026 16:42:42</t>
+  </si>
+  <si>
+    <t>02-02-2026 16:57:36</t>
   </si>
   <si>
     <t>02-02-2026 09:16:38</t>
@@ -1753,87 +1888,84 @@
     <t>03-02-2026 05:22:05</t>
   </si>
   <si>
+    <t>02-02-2026 18:49:33</t>
+  </si>
+  <si>
+    <t>03-02-2026 14:22:15</t>
+  </si>
+  <si>
     <t>01-02-2026 10:25:23</t>
   </si>
   <si>
-    <t>02-02-2026 16:42:42</t>
-  </si>
-  <si>
-    <t>02-02-2026 16:57:36</t>
+    <t>04-02-2026 18:22:23</t>
+  </si>
+  <si>
+    <t>05-02-2026 17:12:22</t>
   </si>
   <si>
     <t>02-02-2026 16:46:46</t>
   </si>
   <si>
-    <t>03-02-2026 14:22:15</t>
-  </si>
-  <si>
-    <t>02-02-2026 18:49:33</t>
-  </si>
-  <si>
     <t>02-02-2026 15:39:32</t>
   </si>
   <si>
+    <t>11-02-2026 15:25:43</t>
+  </si>
+  <si>
+    <t>11-02-2026 15:31:50</t>
+  </si>
+  <si>
+    <t>03-02-2026 13:07:59</t>
+  </si>
+  <si>
+    <t>11-02-2026 13:12:26</t>
+  </si>
+  <si>
     <t>02-02-2026 18:58:00</t>
   </si>
   <si>
-    <t>03-02-2026 13:07:59</t>
-  </si>
-  <si>
-    <t>04-02-2026 18:22:23</t>
-  </si>
-  <si>
-    <t>05-02-2026 17:12:22</t>
-  </si>
-  <si>
-    <t>11-02-2026 15:25:43</t>
-  </si>
-  <si>
-    <t>11-02-2026 15:31:50</t>
+    <t>09-02-2026 17:08:25</t>
+  </si>
+  <si>
+    <t>10-02-2026 06:41:25</t>
+  </si>
+  <si>
+    <t>10-02-2026 07:20:53</t>
+  </si>
+  <si>
+    <t>11-02-2026 16:38:17</t>
+  </si>
+  <si>
+    <t>07-02-2026 11:32:27</t>
+  </si>
+  <si>
+    <t>10-02-2026 17:07:27</t>
+  </si>
+  <si>
+    <t>11-02-2026 09:45:03</t>
+  </si>
+  <si>
+    <t>12-02-2026 18:58:05</t>
+  </si>
+  <si>
+    <t>13-02-2026 15:17:37</t>
+  </si>
+  <si>
+    <t>12-02-2026 18:52:16</t>
   </si>
   <si>
     <t>07-02-2026 11:37:04</t>
   </si>
   <si>
-    <t>07-02-2026 11:32:27</t>
-  </si>
-  <si>
-    <t>10-02-2026 17:07:27</t>
-  </si>
-  <si>
-    <t>09-02-2026 17:08:25</t>
-  </si>
-  <si>
-    <t>11-02-2026 13:12:26</t>
+    <t>17-02-2026 15:16:14</t>
   </si>
   <si>
     <t>11-02-2026 09:28:31</t>
   </si>
   <si>
-    <t>10-02-2026 06:41:25</t>
-  </si>
-  <si>
-    <t>11-02-2026 16:38:17</t>
-  </si>
-  <si>
-    <t>10-02-2026 07:20:53</t>
-  </si>
-  <si>
-    <t>11-02-2026 09:45:03</t>
-  </si>
-  <si>
-    <t>13-02-2026 15:17:37</t>
-  </si>
-  <si>
-    <t>12-02-2026 18:58:05</t>
-  </si>
-  <si>
     <t>12-02-2026 07:17:45</t>
   </si>
   <si>
-    <t>12-02-2026 18:52:16</t>
-  </si>
-  <si>
     <t>13-02-2026 15:11:55</t>
   </si>
   <si>
@@ -1858,13 +1990,19 @@
     <t>26210522108860002579</t>
   </si>
   <si>
+    <t>26210522040850002349</t>
+  </si>
+  <si>
+    <t>26210522002210002243</t>
+  </si>
+  <si>
     <t>26210522074760002451</t>
   </si>
   <si>
-    <t>26210522040850002349</t>
-  </si>
-  <si>
-    <t>26210522002210002243</t>
+    <t>26210522017090002277</t>
+  </si>
+  <si>
+    <t>26210522017700002281</t>
   </si>
   <si>
     <t>26210522002720002245</t>
@@ -1873,123 +2011,129 @@
     <t>26210522027620002320</t>
   </si>
   <si>
+    <t>26210522021200002303</t>
+  </si>
+  <si>
+    <t>26210522041020002351</t>
+  </si>
+  <si>
+    <t>26210522083460002490</t>
+  </si>
+  <si>
     <t>26210521989080002222</t>
   </si>
   <si>
-    <t>26210522017090002277</t>
-  </si>
-  <si>
-    <t>26210522017700002281</t>
+    <t>26210522085210002502</t>
+  </si>
+  <si>
+    <t>26210522112170002589</t>
   </si>
   <si>
     <t>26210522017270002279</t>
   </si>
   <si>
-    <t>26210522041020002351</t>
-  </si>
-  <si>
-    <t>26210522021200002303</t>
-  </si>
-  <si>
     <t>26210522014940002273</t>
   </si>
   <si>
+    <t>26210522266420003021</t>
+  </si>
+  <si>
+    <t>26210522266660003022</t>
+  </si>
+  <si>
+    <t>26210522174170002753</t>
+  </si>
+  <si>
+    <t>26210522039110002341</t>
+  </si>
+  <si>
+    <t>26210522263830003013</t>
+  </si>
+  <si>
     <t>26210522021420002304</t>
   </si>
   <si>
-    <t>26210522039110002341</t>
-  </si>
-  <si>
-    <t>26210522085210002502</t>
-  </si>
-  <si>
-    <t>26210522112170002589</t>
+    <t>26210522200900002835</t>
+  </si>
+  <si>
+    <t>26210522223420002894</t>
   </si>
   <si>
     <t>26210522083170002489</t>
   </si>
   <si>
-    <t>26210522083460002490</t>
-  </si>
-  <si>
-    <t>26210522266420003021</t>
-  </si>
-  <si>
-    <t>26210522266660003022</t>
-  </si>
-  <si>
-    <t>26210522174170002753</t>
+    <t>26210522296870003118</t>
+  </si>
+  <si>
+    <t>26210522224130002896</t>
+  </si>
+  <si>
+    <t>26210522269110003031</t>
+  </si>
+  <si>
+    <t>26210522236680002929</t>
+  </si>
+  <si>
+    <t>26210522159870002732</t>
+  </si>
+  <si>
+    <t>26210522238630002941</t>
+  </si>
+  <si>
+    <t>26210522260970003000</t>
+  </si>
+  <si>
+    <t>26210522293540003108</t>
+  </si>
+  <si>
+    <t>26210522293680003109</t>
+  </si>
+  <si>
+    <t>26210522303780003149</t>
+  </si>
+  <si>
+    <t>26210522209990002868</t>
+  </si>
+  <si>
+    <t>26210522318120003186</t>
+  </si>
+  <si>
+    <t>26210522322300003205</t>
+  </si>
+  <si>
+    <t>26210522303620003147</t>
+  </si>
+  <si>
+    <t>26210522235410002926</t>
   </si>
   <si>
     <t>26210522160000002733</t>
   </si>
   <si>
-    <t>26210522159870002732</t>
-  </si>
-  <si>
-    <t>26210522238630002941</t>
-  </si>
-  <si>
-    <t>26210522200900002835</t>
-  </si>
-  <si>
-    <t>26210522263830003013</t>
-  </si>
-  <si>
-    <t>26210522296870003118</t>
+    <t>26210522349800003253</t>
+  </si>
+  <si>
+    <t>26210522406620003354</t>
+  </si>
+  <si>
+    <t>26210522431100003417</t>
   </si>
   <si>
     <t>26210522260760002999</t>
   </si>
   <si>
-    <t>26210522209990002868</t>
-  </si>
-  <si>
-    <t>26210522223420002894</t>
-  </si>
-  <si>
-    <t>26210522236680002929</t>
-  </si>
-  <si>
-    <t>26210522269110003031</t>
+    <t>26210522412010003364</t>
   </si>
   <si>
     <t>26210522213810002877</t>
   </si>
   <si>
-    <t>26210522235410002926</t>
-  </si>
-  <si>
-    <t>26210522224130002896</t>
-  </si>
-  <si>
-    <t>26210522349800003253</t>
-  </si>
-  <si>
-    <t>26210522260970003000</t>
-  </si>
-  <si>
-    <t>26210522293680003109</t>
-  </si>
-  <si>
-    <t>26210522318120003186</t>
-  </si>
-  <si>
-    <t>26210522322300003205</t>
-  </si>
-  <si>
-    <t>26210522303780003149</t>
+    <t>26210522429100003408</t>
   </si>
   <si>
     <t>26210522287800003090</t>
   </si>
   <si>
-    <t>26210522293540003108</t>
-  </si>
-  <si>
-    <t>26210522303620003147</t>
-  </si>
-  <si>
     <t>26210522322150003203</t>
   </si>
   <si>
@@ -2011,22 +2155,25 @@
     <t>1899</t>
   </si>
   <si>
+    <t>Juan Pablo Rieke Campoy</t>
+  </si>
+  <si>
+    <t>Cristopher Armando Serrato</t>
+  </si>
+  <si>
+    <t>Guillermo  Garcia De Alba Velazquez</t>
+  </si>
+  <si>
     <t>N/D</t>
   </si>
   <si>
-    <t>Cristopher Armando Serrato</t>
-  </si>
-  <si>
-    <t>Juan Pablo Rieke Campoy</t>
-  </si>
-  <si>
     <t>Christian Jahassiel Castro Navarro</t>
   </si>
   <si>
+    <t>con rutina</t>
+  </si>
+  <si>
     <t>sin rutina</t>
-  </si>
-  <si>
-    <t>con rutina</t>
   </si>
 </sst>
 </file>
@@ -2384,7 +2531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC50"/>
+  <dimension ref="A1:AC54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:29">
@@ -2481,85 +2628,85 @@
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C2" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D2" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="E2" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="F2" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="G2" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H2" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="I2" t="s">
-        <v>309</v>
+        <v>331</v>
       </c>
       <c r="J2" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="K2" t="s">
-        <v>344</v>
+        <v>368</v>
       </c>
       <c r="L2" t="s">
-        <v>393</v>
+        <v>421</v>
       </c>
       <c r="M2" t="s">
-        <v>442</v>
+        <v>474</v>
       </c>
       <c r="O2" t="s">
-        <v>492</v>
+        <v>529</v>
       </c>
       <c r="P2" t="s">
-        <v>495</v>
+        <v>532</v>
       </c>
       <c r="Q2" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="R2" t="s">
-        <v>507</v>
+        <v>544</v>
       </c>
       <c r="S2" t="s">
-        <v>556</v>
+        <v>597</v>
       </c>
       <c r="T2" t="s">
-        <v>571</v>
+        <v>614</v>
       </c>
       <c r="U2" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="V2" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="W2" t="s">
         <v>2</v>
       </c>
       <c r="X2" t="s">
-        <v>611</v>
+        <v>655</v>
       </c>
       <c r="Y2" t="s">
-        <v>660</v>
+        <v>708</v>
       </c>
       <c r="Z2" t="s">
-        <v>662</v>
+        <v>710</v>
       </c>
       <c r="AA2" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="AB2" t="s">
-        <v>665</v>
+        <v>713</v>
       </c>
       <c r="AC2" t="s">
-        <v>669</v>
+        <v>718</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -2567,79 +2714,79 @@
         <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C3" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D3" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="E3" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="F3" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="G3" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H3" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="I3" t="s">
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="J3" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="K3" t="s">
-        <v>345</v>
+        <v>369</v>
       </c>
       <c r="L3" t="s">
-        <v>394</v>
+        <v>422</v>
       </c>
       <c r="M3" t="s">
-        <v>443</v>
+        <v>475</v>
       </c>
       <c r="O3" t="s">
-        <v>492</v>
+        <v>529</v>
       </c>
       <c r="P3" t="s">
-        <v>495</v>
+        <v>532</v>
       </c>
       <c r="Q3" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="R3" t="s">
-        <v>508</v>
+        <v>545</v>
       </c>
       <c r="S3" t="s">
-        <v>557</v>
+        <v>598</v>
       </c>
       <c r="T3" t="s">
-        <v>572</v>
+        <v>615</v>
       </c>
       <c r="U3" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="V3" t="s">
-        <v>609</v>
+        <v>653</v>
       </c>
       <c r="W3" t="s">
         <v>2</v>
       </c>
       <c r="X3" t="s">
-        <v>612</v>
+        <v>656</v>
       </c>
       <c r="AA3" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="AB3" t="s">
-        <v>666</v>
+        <v>714</v>
       </c>
       <c r="AC3" t="s">
-        <v>670</v>
+        <v>718</v>
       </c>
     </row>
     <row r="4" spans="1:29">
@@ -2647,79 +2794,79 @@
         <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D4" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="E4" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="F4" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="G4" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H4" t="s">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="I4" t="s">
-        <v>311</v>
+        <v>333</v>
       </c>
       <c r="J4" t="s">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="K4" t="s">
-        <v>346</v>
+        <v>370</v>
       </c>
       <c r="L4" t="s">
-        <v>395</v>
+        <v>423</v>
       </c>
       <c r="M4" t="s">
-        <v>444</v>
+        <v>476</v>
       </c>
       <c r="O4" t="s">
-        <v>492</v>
+        <v>529</v>
       </c>
       <c r="P4" t="s">
-        <v>495</v>
+        <v>532</v>
       </c>
       <c r="Q4" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="R4" t="s">
-        <v>509</v>
+        <v>546</v>
       </c>
       <c r="S4" t="s">
-        <v>558</v>
+        <v>599</v>
       </c>
       <c r="T4" t="s">
-        <v>573</v>
+        <v>616</v>
       </c>
       <c r="U4" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="V4" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="W4" t="s">
         <v>2</v>
       </c>
       <c r="X4" t="s">
-        <v>613</v>
+        <v>657</v>
       </c>
       <c r="AA4" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="AB4" t="s">
-        <v>665</v>
+        <v>715</v>
       </c>
       <c r="AC4" t="s">
-        <v>669</v>
+        <v>718</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -2727,79 +2874,79 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D5" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E5" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F5" t="s">
-        <v>181</v>
+        <v>243</v>
       </c>
       <c r="G5" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H5" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="I5" t="s">
-        <v>312</v>
+        <v>334</v>
       </c>
       <c r="J5" t="s">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="K5" t="s">
-        <v>347</v>
+        <v>371</v>
       </c>
       <c r="L5" t="s">
-        <v>396</v>
+        <v>424</v>
       </c>
       <c r="M5" t="s">
-        <v>445</v>
+        <v>477</v>
       </c>
       <c r="O5" t="s">
-        <v>492</v>
+        <v>529</v>
       </c>
       <c r="P5" t="s">
-        <v>495</v>
+        <v>532</v>
       </c>
       <c r="Q5" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="R5" t="s">
-        <v>510</v>
+        <v>547</v>
       </c>
       <c r="S5" t="s">
-        <v>559</v>
+        <v>600</v>
       </c>
       <c r="T5" t="s">
-        <v>574</v>
+        <v>617</v>
       </c>
       <c r="U5" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="V5" t="s">
-        <v>609</v>
+        <v>653</v>
       </c>
       <c r="W5" t="s">
         <v>2</v>
       </c>
       <c r="X5" t="s">
-        <v>614</v>
+        <v>658</v>
       </c>
       <c r="AA5" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="AB5" t="s">
-        <v>667</v>
+        <v>716</v>
       </c>
       <c r="AC5" t="s">
-        <v>670</v>
+        <v>719</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -2807,79 +2954,82 @@
         <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D6" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="E6" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="F6" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="G6" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H6" t="s">
-        <v>264</v>
+        <v>282</v>
       </c>
       <c r="I6" t="s">
-        <v>313</v>
+        <v>335</v>
       </c>
       <c r="J6" t="s">
-        <v>342</v>
+        <v>367</v>
       </c>
       <c r="K6" t="s">
-        <v>348</v>
+        <v>372</v>
       </c>
       <c r="L6" t="s">
-        <v>397</v>
+        <v>425</v>
       </c>
       <c r="M6" t="s">
-        <v>446</v>
+        <v>478</v>
       </c>
       <c r="O6" t="s">
-        <v>492</v>
+        <v>529</v>
       </c>
       <c r="P6" t="s">
-        <v>495</v>
+        <v>533</v>
       </c>
       <c r="Q6" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="R6" t="s">
-        <v>511</v>
+        <v>548</v>
       </c>
       <c r="S6" t="s">
-        <v>560</v>
+        <v>601</v>
       </c>
       <c r="T6" t="s">
-        <v>575</v>
+        <v>618</v>
       </c>
       <c r="U6" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="V6" t="s">
-        <v>609</v>
+        <v>653</v>
       </c>
       <c r="W6" t="s">
         <v>2</v>
       </c>
       <c r="X6" t="s">
-        <v>615</v>
+        <v>659</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>708</v>
       </c>
       <c r="AA6" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="AB6" t="s">
-        <v>665</v>
+        <v>717</v>
       </c>
       <c r="AC6" t="s">
-        <v>669</v>
+        <v>718</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -2887,82 +3037,79 @@
         <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D7" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="E7" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="F7" t="s">
-        <v>228</v>
+        <v>195</v>
       </c>
       <c r="G7" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H7" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="I7" t="s">
-        <v>314</v>
+        <v>336</v>
       </c>
       <c r="J7" t="s">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="K7" t="s">
-        <v>349</v>
+        <v>373</v>
       </c>
       <c r="L7" t="s">
-        <v>398</v>
+        <v>426</v>
       </c>
       <c r="M7" t="s">
-        <v>447</v>
+        <v>479</v>
       </c>
       <c r="O7" t="s">
-        <v>492</v>
+        <v>529</v>
       </c>
       <c r="P7" t="s">
-        <v>496</v>
+        <v>532</v>
       </c>
       <c r="Q7" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="R7" t="s">
-        <v>512</v>
+        <v>549</v>
       </c>
       <c r="S7" t="s">
-        <v>561</v>
+        <v>602</v>
       </c>
       <c r="T7" t="s">
-        <v>576</v>
+        <v>619</v>
       </c>
       <c r="U7" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="V7" t="s">
-        <v>609</v>
+        <v>653</v>
       </c>
       <c r="W7" t="s">
         <v>2</v>
       </c>
       <c r="X7" t="s">
-        <v>616</v>
-      </c>
-      <c r="Y7" t="s">
         <v>660</v>
       </c>
       <c r="AA7" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="AB7" t="s">
-        <v>665</v>
+        <v>713</v>
       </c>
       <c r="AC7" t="s">
-        <v>669</v>
+        <v>718</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -2970,79 +3117,79 @@
         <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D8" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="E8" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="F8" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="G8" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H8" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="I8" t="s">
-        <v>315</v>
+        <v>337</v>
       </c>
       <c r="J8" t="s">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="K8" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
       <c r="L8" t="s">
-        <v>399</v>
+        <v>427</v>
       </c>
       <c r="M8" t="s">
-        <v>448</v>
+        <v>480</v>
       </c>
       <c r="O8" t="s">
-        <v>492</v>
+        <v>529</v>
       </c>
       <c r="P8" t="s">
-        <v>495</v>
+        <v>534</v>
       </c>
       <c r="Q8" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="R8" t="s">
-        <v>513</v>
+        <v>550</v>
       </c>
       <c r="S8" t="s">
-        <v>557</v>
+        <v>598</v>
       </c>
       <c r="T8" t="s">
-        <v>577</v>
+        <v>620</v>
       </c>
       <c r="U8" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="V8" t="s">
-        <v>609</v>
+        <v>653</v>
       </c>
       <c r="W8" t="s">
         <v>2</v>
       </c>
       <c r="X8" t="s">
-        <v>617</v>
+        <v>661</v>
       </c>
       <c r="AA8" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="AB8" t="s">
-        <v>665</v>
+        <v>713</v>
       </c>
       <c r="AC8" t="s">
-        <v>669</v>
+        <v>718</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -3050,82 +3197,79 @@
         <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C9" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D9" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="E9" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="F9" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="G9" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H9" t="s">
-        <v>267</v>
+        <v>285</v>
       </c>
       <c r="I9" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="J9" t="s">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="K9" t="s">
-        <v>351</v>
+        <v>375</v>
       </c>
       <c r="L9" t="s">
-        <v>400</v>
+        <v>428</v>
       </c>
       <c r="M9" t="s">
-        <v>449</v>
+        <v>481</v>
       </c>
       <c r="O9" t="s">
-        <v>492</v>
+        <v>529</v>
       </c>
       <c r="P9" t="s">
-        <v>497</v>
+        <v>532</v>
       </c>
       <c r="Q9" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="R9" t="s">
-        <v>514</v>
+        <v>551</v>
       </c>
       <c r="S9" t="s">
-        <v>559</v>
+        <v>598</v>
       </c>
       <c r="T9" t="s">
-        <v>578</v>
+        <v>621</v>
       </c>
       <c r="U9" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="V9" t="s">
-        <v>609</v>
+        <v>653</v>
       </c>
       <c r="W9" t="s">
         <v>2</v>
       </c>
       <c r="X9" t="s">
-        <v>618</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="AA9" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="AB9" t="s">
-        <v>665</v>
+        <v>717</v>
       </c>
       <c r="AC9" t="s">
-        <v>669</v>
+        <v>718</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -3133,79 +3277,79 @@
         <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D10" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E10" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="F10" t="s">
-        <v>181</v>
+        <v>247</v>
       </c>
       <c r="G10" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H10" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="I10" t="s">
-        <v>316</v>
+        <v>339</v>
       </c>
       <c r="J10" t="s">
-        <v>342</v>
+        <v>367</v>
       </c>
       <c r="K10" t="s">
-        <v>352</v>
+        <v>376</v>
       </c>
       <c r="L10" t="s">
-        <v>401</v>
+        <v>429</v>
       </c>
       <c r="M10" t="s">
-        <v>450</v>
+        <v>482</v>
       </c>
       <c r="O10" t="s">
-        <v>492</v>
+        <v>529</v>
       </c>
       <c r="P10" t="s">
-        <v>497</v>
+        <v>532</v>
       </c>
       <c r="Q10" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="R10" t="s">
-        <v>515</v>
+        <v>552</v>
       </c>
       <c r="S10" t="s">
-        <v>562</v>
+        <v>598</v>
       </c>
       <c r="T10" t="s">
-        <v>579</v>
+        <v>622</v>
       </c>
       <c r="U10" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="V10" t="s">
-        <v>609</v>
+        <v>653</v>
       </c>
       <c r="W10" t="s">
         <v>2</v>
       </c>
       <c r="X10" t="s">
-        <v>619</v>
+        <v>663</v>
       </c>
       <c r="AA10" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="AB10" t="s">
-        <v>665</v>
+        <v>716</v>
       </c>
       <c r="AC10" t="s">
-        <v>669</v>
+        <v>719</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -3213,79 +3357,82 @@
         <v>38</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C11" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D11" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="E11" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="F11" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="G11" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H11" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="I11" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="J11" t="s">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="K11" t="s">
-        <v>353</v>
+        <v>377</v>
       </c>
       <c r="L11" t="s">
-        <v>402</v>
+        <v>430</v>
       </c>
       <c r="M11" t="s">
-        <v>451</v>
+        <v>483</v>
       </c>
       <c r="O11" t="s">
-        <v>492</v>
+        <v>529</v>
       </c>
       <c r="P11" t="s">
-        <v>497</v>
+        <v>534</v>
       </c>
       <c r="Q11" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="R11" t="s">
-        <v>516</v>
+        <v>553</v>
       </c>
       <c r="S11" t="s">
-        <v>557</v>
+        <v>602</v>
       </c>
       <c r="T11" t="s">
-        <v>580</v>
+        <v>623</v>
       </c>
       <c r="U11" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="V11" t="s">
-        <v>609</v>
+        <v>653</v>
       </c>
       <c r="W11" t="s">
         <v>2</v>
       </c>
       <c r="X11" t="s">
-        <v>620</v>
+        <v>664</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>708</v>
       </c>
       <c r="AA11" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="AB11" t="s">
-        <v>667</v>
+        <v>716</v>
       </c>
       <c r="AC11" t="s">
-        <v>670</v>
+        <v>719</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -3293,79 +3440,79 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D12" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E12" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="F12" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="G12" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H12" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="I12" t="s">
-        <v>318</v>
+        <v>340</v>
       </c>
       <c r="J12" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="K12" t="s">
-        <v>354</v>
+        <v>378</v>
       </c>
       <c r="L12" t="s">
-        <v>403</v>
+        <v>431</v>
       </c>
       <c r="M12" t="s">
-        <v>452</v>
+        <v>484</v>
       </c>
       <c r="O12" t="s">
-        <v>492</v>
+        <v>529</v>
       </c>
       <c r="P12" t="s">
-        <v>495</v>
+        <v>532</v>
       </c>
       <c r="Q12" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="R12" t="s">
-        <v>517</v>
+        <v>554</v>
       </c>
       <c r="S12" t="s">
-        <v>557</v>
+        <v>598</v>
       </c>
       <c r="T12" t="s">
-        <v>581</v>
+        <v>624</v>
       </c>
       <c r="U12" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="V12" t="s">
-        <v>609</v>
+        <v>653</v>
       </c>
       <c r="W12" t="s">
         <v>2</v>
       </c>
       <c r="X12" t="s">
-        <v>621</v>
+        <v>665</v>
       </c>
       <c r="AA12" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="AB12" t="s">
-        <v>665</v>
+        <v>713</v>
       </c>
       <c r="AC12" t="s">
-        <v>669</v>
+        <v>718</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -3373,79 +3520,79 @@
         <v>40</v>
       </c>
       <c r="B13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D13" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E13" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="F13" t="s">
-        <v>184</v>
+        <v>250</v>
       </c>
       <c r="G13" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H13" t="s">
-        <v>271</v>
+        <v>289</v>
       </c>
       <c r="I13" t="s">
-        <v>319</v>
+        <v>341</v>
       </c>
       <c r="J13" t="s">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="K13" t="s">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="L13" t="s">
-        <v>404</v>
+        <v>432</v>
       </c>
       <c r="M13" t="s">
-        <v>453</v>
+        <v>485</v>
       </c>
       <c r="O13" t="s">
-        <v>492</v>
+        <v>529</v>
       </c>
       <c r="P13" t="s">
-        <v>497</v>
+        <v>532</v>
       </c>
       <c r="Q13" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="R13" t="s">
-        <v>518</v>
+        <v>555</v>
       </c>
       <c r="S13" t="s">
-        <v>557</v>
+        <v>600</v>
       </c>
       <c r="T13" t="s">
-        <v>582</v>
+        <v>625</v>
       </c>
       <c r="U13" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="V13" t="s">
-        <v>609</v>
+        <v>653</v>
       </c>
       <c r="W13" t="s">
         <v>2</v>
       </c>
       <c r="X13" t="s">
-        <v>622</v>
+        <v>666</v>
       </c>
       <c r="AA13" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="AB13" t="s">
-        <v>665</v>
+        <v>713</v>
       </c>
       <c r="AC13" t="s">
-        <v>669</v>
+        <v>718</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -3453,79 +3600,73 @@
         <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C14" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D14" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="E14" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="F14" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="G14" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H14" t="s">
-        <v>272</v>
-      </c>
-      <c r="I14" t="s">
-        <v>320</v>
+        <v>290</v>
       </c>
       <c r="J14" t="s">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="K14" t="s">
-        <v>356</v>
+        <v>380</v>
       </c>
       <c r="L14" t="s">
-        <v>405</v>
+        <v>433</v>
       </c>
       <c r="M14" t="s">
-        <v>454</v>
+        <v>486</v>
+      </c>
+      <c r="N14" t="s">
+        <v>527</v>
       </c>
       <c r="O14" t="s">
-        <v>492</v>
+        <v>530</v>
       </c>
       <c r="P14" t="s">
-        <v>495</v>
+        <v>535</v>
       </c>
       <c r="Q14" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="R14" t="s">
-        <v>519</v>
+        <v>556</v>
       </c>
       <c r="S14" t="s">
-        <v>560</v>
-      </c>
-      <c r="T14" t="s">
-        <v>583</v>
+        <v>602</v>
       </c>
       <c r="U14" t="s">
-        <v>608</v>
-      </c>
-      <c r="V14" t="s">
-        <v>609</v>
+        <v>652</v>
       </c>
       <c r="W14" t="s">
         <v>2</v>
       </c>
       <c r="X14" t="s">
-        <v>623</v>
+        <v>667</v>
       </c>
       <c r="AA14" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="AB14" t="s">
-        <v>665</v>
+        <v>716</v>
       </c>
       <c r="AC14" t="s">
-        <v>669</v>
+        <v>719</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -3533,79 +3674,79 @@
         <v>42</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C15" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D15" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="E15" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="F15" t="s">
-        <v>234</v>
+        <v>195</v>
       </c>
       <c r="G15" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H15" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="I15" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="J15" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="K15" t="s">
-        <v>357</v>
+        <v>381</v>
       </c>
       <c r="L15" t="s">
-        <v>406</v>
+        <v>434</v>
       </c>
       <c r="M15" t="s">
-        <v>455</v>
+        <v>487</v>
       </c>
       <c r="O15" t="s">
-        <v>492</v>
+        <v>529</v>
       </c>
       <c r="P15" t="s">
-        <v>495</v>
+        <v>534</v>
       </c>
       <c r="Q15" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="R15" t="s">
-        <v>520</v>
+        <v>557</v>
       </c>
       <c r="S15" t="s">
-        <v>557</v>
+        <v>603</v>
       </c>
       <c r="T15" t="s">
-        <v>584</v>
+        <v>626</v>
       </c>
       <c r="U15" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="V15" t="s">
-        <v>609</v>
+        <v>653</v>
       </c>
       <c r="W15" t="s">
         <v>2</v>
       </c>
       <c r="X15" t="s">
-        <v>624</v>
+        <v>668</v>
       </c>
       <c r="AA15" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="AB15" t="s">
-        <v>665</v>
+        <v>716</v>
       </c>
       <c r="AC15" t="s">
-        <v>669</v>
+        <v>719</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -3613,79 +3754,82 @@
         <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C16" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D16" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="E16" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="F16" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="G16" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H16" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="I16" t="s">
-        <v>322</v>
+        <v>343</v>
       </c>
       <c r="J16" t="s">
-        <v>342</v>
+        <v>367</v>
       </c>
       <c r="K16" t="s">
-        <v>358</v>
+        <v>382</v>
       </c>
       <c r="L16" t="s">
-        <v>407</v>
+        <v>435</v>
       </c>
       <c r="M16" t="s">
-        <v>456</v>
+        <v>488</v>
+      </c>
+      <c r="N16" t="s">
+        <v>527</v>
       </c>
       <c r="O16" t="s">
-        <v>492</v>
+        <v>531</v>
       </c>
       <c r="P16" t="s">
-        <v>495</v>
+        <v>536</v>
       </c>
       <c r="Q16" t="s">
-        <v>502</v>
+        <v>541</v>
       </c>
       <c r="R16" t="s">
-        <v>521</v>
+        <v>558</v>
       </c>
       <c r="S16" t="s">
-        <v>557</v>
+        <v>602</v>
       </c>
       <c r="T16" t="s">
-        <v>585</v>
+        <v>627</v>
       </c>
       <c r="U16" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="V16" t="s">
-        <v>609</v>
+        <v>652</v>
       </c>
       <c r="W16" t="s">
         <v>2</v>
       </c>
       <c r="X16" t="s">
-        <v>625</v>
+        <v>669</v>
       </c>
       <c r="AA16" t="s">
-        <v>502</v>
+        <v>541</v>
       </c>
       <c r="AB16" t="s">
-        <v>665</v>
+        <v>716</v>
       </c>
       <c r="AC16" t="s">
-        <v>669</v>
+        <v>719</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -3693,79 +3837,79 @@
         <v>44</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C17" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D17" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E17" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="F17" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="G17" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H17" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="I17" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
       <c r="J17" t="s">
-        <v>342</v>
+        <v>367</v>
       </c>
       <c r="K17" t="s">
-        <v>359</v>
+        <v>383</v>
       </c>
       <c r="L17" t="s">
-        <v>408</v>
+        <v>436</v>
       </c>
       <c r="M17" t="s">
-        <v>457</v>
+        <v>489</v>
       </c>
       <c r="O17" t="s">
-        <v>492</v>
+        <v>529</v>
       </c>
       <c r="P17" t="s">
-        <v>495</v>
+        <v>532</v>
       </c>
       <c r="Q17" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="R17" t="s">
-        <v>522</v>
+        <v>559</v>
       </c>
       <c r="S17" t="s">
-        <v>557</v>
+        <v>599</v>
       </c>
       <c r="T17" t="s">
-        <v>586</v>
+        <v>628</v>
       </c>
       <c r="U17" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="V17" t="s">
-        <v>609</v>
+        <v>653</v>
       </c>
       <c r="W17" t="s">
         <v>2</v>
       </c>
       <c r="X17" t="s">
-        <v>626</v>
+        <v>670</v>
       </c>
       <c r="AA17" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="AB17" t="s">
-        <v>665</v>
+        <v>716</v>
       </c>
       <c r="AC17" t="s">
-        <v>669</v>
+        <v>719</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -3773,79 +3917,79 @@
         <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C18" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D18" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="E18" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="F18" t="s">
-        <v>237</v>
+        <v>193</v>
       </c>
       <c r="G18" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H18" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="I18" t="s">
-        <v>324</v>
+        <v>345</v>
       </c>
       <c r="J18" t="s">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="K18" t="s">
-        <v>360</v>
+        <v>384</v>
       </c>
       <c r="L18" t="s">
-        <v>409</v>
+        <v>437</v>
       </c>
       <c r="M18" t="s">
-        <v>458</v>
+        <v>490</v>
       </c>
       <c r="O18" t="s">
-        <v>492</v>
+        <v>529</v>
       </c>
       <c r="P18" t="s">
-        <v>495</v>
+        <v>534</v>
       </c>
       <c r="Q18" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="R18" t="s">
-        <v>523</v>
+        <v>560</v>
       </c>
       <c r="S18" t="s">
-        <v>560</v>
+        <v>598</v>
       </c>
       <c r="T18" t="s">
-        <v>587</v>
+        <v>629</v>
       </c>
       <c r="U18" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="V18" t="s">
-        <v>609</v>
+        <v>653</v>
       </c>
       <c r="W18" t="s">
         <v>2</v>
       </c>
       <c r="X18" t="s">
-        <v>627</v>
+        <v>671</v>
       </c>
       <c r="AA18" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="AB18" t="s">
-        <v>665</v>
+        <v>716</v>
       </c>
       <c r="AC18" t="s">
-        <v>669</v>
+        <v>719</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -3853,82 +3997,79 @@
         <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C19" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D19" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="E19" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="F19" t="s">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="G19" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H19" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="I19" t="s">
-        <v>325</v>
+        <v>346</v>
       </c>
       <c r="J19" t="s">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="K19" t="s">
-        <v>361</v>
+        <v>385</v>
       </c>
       <c r="L19" t="s">
-        <v>410</v>
+        <v>438</v>
       </c>
       <c r="M19" t="s">
-        <v>459</v>
-      </c>
-      <c r="N19" t="s">
         <v>491</v>
       </c>
       <c r="O19" t="s">
-        <v>493</v>
+        <v>529</v>
       </c>
       <c r="P19" t="s">
-        <v>498</v>
+        <v>532</v>
       </c>
       <c r="Q19" t="s">
-        <v>503</v>
+        <v>539</v>
       </c>
       <c r="R19" t="s">
-        <v>524</v>
+        <v>561</v>
       </c>
       <c r="S19" t="s">
-        <v>559</v>
+        <v>598</v>
       </c>
       <c r="T19" t="s">
-        <v>588</v>
+        <v>630</v>
       </c>
       <c r="U19" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="V19" t="s">
-        <v>608</v>
+        <v>653</v>
       </c>
       <c r="W19" t="s">
         <v>2</v>
       </c>
       <c r="X19" t="s">
-        <v>628</v>
+        <v>672</v>
       </c>
       <c r="AA19" t="s">
-        <v>503</v>
+        <v>539</v>
       </c>
       <c r="AB19" t="s">
-        <v>665</v>
+        <v>716</v>
       </c>
       <c r="AC19" t="s">
-        <v>669</v>
+        <v>719</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -3936,79 +4077,85 @@
         <v>47</v>
       </c>
       <c r="B20" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C20" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D20" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="E20" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="F20" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="G20" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H20" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="I20" t="s">
-        <v>326</v>
+        <v>347</v>
       </c>
       <c r="J20" t="s">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="K20" t="s">
-        <v>362</v>
+        <v>386</v>
       </c>
       <c r="L20" t="s">
-        <v>411</v>
+        <v>439</v>
       </c>
       <c r="M20" t="s">
-        <v>460</v>
+        <v>492</v>
       </c>
       <c r="O20" t="s">
-        <v>492</v>
+        <v>529</v>
       </c>
       <c r="P20" t="s">
-        <v>495</v>
+        <v>532</v>
       </c>
       <c r="Q20" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="R20" t="s">
-        <v>525</v>
+        <v>562</v>
       </c>
       <c r="S20" t="s">
-        <v>558</v>
+        <v>604</v>
       </c>
       <c r="T20" t="s">
-        <v>589</v>
+        <v>631</v>
       </c>
       <c r="U20" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="V20" t="s">
-        <v>609</v>
+        <v>652</v>
       </c>
       <c r="W20" t="s">
         <v>2</v>
       </c>
       <c r="X20" t="s">
-        <v>629</v>
+        <v>673</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>708</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>711</v>
       </c>
       <c r="AA20" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="AB20" t="s">
-        <v>665</v>
+        <v>716</v>
       </c>
       <c r="AC20" t="s">
-        <v>669</v>
+        <v>719</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -4016,73 +4163,85 @@
         <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C21" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D21" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="E21" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="F21" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="G21" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H21" t="s">
-        <v>279</v>
+        <v>297</v>
+      </c>
+      <c r="I21" t="s">
+        <v>348</v>
       </c>
       <c r="J21" t="s">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="K21" t="s">
-        <v>363</v>
+        <v>387</v>
       </c>
       <c r="L21" t="s">
-        <v>412</v>
+        <v>440</v>
       </c>
       <c r="M21" t="s">
-        <v>461</v>
-      </c>
-      <c r="N21" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="O21" t="s">
-        <v>494</v>
+        <v>529</v>
       </c>
       <c r="P21" t="s">
-        <v>499</v>
+        <v>532</v>
       </c>
       <c r="Q21" t="s">
-        <v>504</v>
+        <v>539</v>
       </c>
       <c r="R21" t="s">
-        <v>526</v>
+        <v>563</v>
       </c>
       <c r="S21" t="s">
-        <v>559</v>
+        <v>604</v>
+      </c>
+      <c r="T21" t="s">
+        <v>632</v>
       </c>
       <c r="U21" t="s">
-        <v>608</v>
+        <v>652</v>
+      </c>
+      <c r="V21" t="s">
+        <v>652</v>
       </c>
       <c r="W21" t="s">
         <v>2</v>
       </c>
       <c r="X21" t="s">
-        <v>630</v>
+        <v>674</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>708</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>711</v>
       </c>
       <c r="AA21" t="s">
-        <v>504</v>
+        <v>539</v>
       </c>
       <c r="AB21" t="s">
-        <v>665</v>
+        <v>716</v>
       </c>
       <c r="AC21" t="s">
-        <v>669</v>
+        <v>719</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -4090,73 +4249,73 @@
         <v>49</v>
       </c>
       <c r="B22" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C22" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D22" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="E22" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="F22" t="s">
         <v>208</v>
       </c>
       <c r="G22" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H22" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="J22" t="s">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="K22" t="s">
-        <v>364</v>
+        <v>388</v>
       </c>
       <c r="L22" t="s">
-        <v>413</v>
+        <v>441</v>
       </c>
       <c r="M22" t="s">
-        <v>462</v>
+        <v>494</v>
       </c>
       <c r="N22" t="s">
-        <v>491</v>
+        <v>527</v>
       </c>
       <c r="O22" t="s">
-        <v>494</v>
+        <v>530</v>
       </c>
       <c r="P22" t="s">
-        <v>499</v>
+        <v>537</v>
       </c>
       <c r="Q22" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="R22" t="s">
-        <v>527</v>
+        <v>564</v>
       </c>
       <c r="S22" t="s">
-        <v>559</v>
+        <v>605</v>
       </c>
       <c r="U22" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="W22" t="s">
         <v>2</v>
       </c>
       <c r="X22" t="s">
-        <v>631</v>
+        <v>675</v>
       </c>
       <c r="AA22" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
       <c r="AB22" t="s">
-        <v>665</v>
+        <v>716</v>
       </c>
       <c r="AC22" t="s">
-        <v>669</v>
+        <v>719</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -4164,85 +4323,79 @@
         <v>50</v>
       </c>
       <c r="B23" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C23" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D23" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="E23" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="F23" t="s">
-        <v>192</v>
+        <v>253</v>
       </c>
       <c r="G23" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H23" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="I23" t="s">
-        <v>327</v>
+        <v>349</v>
       </c>
       <c r="J23" t="s">
-        <v>342</v>
+        <v>367</v>
       </c>
       <c r="K23" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="L23" t="s">
-        <v>414</v>
+        <v>442</v>
       </c>
       <c r="M23" t="s">
-        <v>463</v>
+        <v>495</v>
       </c>
       <c r="O23" t="s">
-        <v>492</v>
+        <v>529</v>
       </c>
       <c r="P23" t="s">
-        <v>495</v>
+        <v>532</v>
       </c>
       <c r="Q23" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="R23" t="s">
-        <v>528</v>
+        <v>565</v>
       </c>
       <c r="S23" t="s">
-        <v>563</v>
+        <v>600</v>
       </c>
       <c r="T23" t="s">
-        <v>590</v>
+        <v>633</v>
       </c>
       <c r="U23" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="V23" t="s">
-        <v>608</v>
+        <v>653</v>
       </c>
       <c r="W23" t="s">
         <v>2</v>
       </c>
       <c r="X23" t="s">
-        <v>632</v>
-      </c>
-      <c r="Y23" t="s">
-        <v>660</v>
-      </c>
-      <c r="Z23" t="s">
-        <v>663</v>
+        <v>676</v>
       </c>
       <c r="AA23" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="AB23" t="s">
-        <v>665</v>
+        <v>716</v>
       </c>
       <c r="AC23" t="s">
-        <v>669</v>
+        <v>719</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -4250,85 +4403,85 @@
         <v>51</v>
       </c>
       <c r="B24" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C24" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D24" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="E24" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="F24" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="G24" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H24" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="I24" t="s">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="J24" t="s">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="K24" t="s">
-        <v>366</v>
+        <v>390</v>
       </c>
       <c r="L24" t="s">
-        <v>415</v>
+        <v>443</v>
       </c>
       <c r="M24" t="s">
-        <v>464</v>
+        <v>496</v>
       </c>
       <c r="O24" t="s">
-        <v>492</v>
+        <v>529</v>
       </c>
       <c r="P24" t="s">
-        <v>495</v>
+        <v>532</v>
       </c>
       <c r="Q24" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="R24" t="s">
-        <v>529</v>
+        <v>566</v>
       </c>
       <c r="S24" t="s">
-        <v>563</v>
+        <v>604</v>
       </c>
       <c r="T24" t="s">
-        <v>591</v>
+        <v>634</v>
       </c>
       <c r="U24" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="V24" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="W24" t="s">
         <v>2</v>
       </c>
       <c r="X24" t="s">
-        <v>633</v>
+        <v>677</v>
       </c>
       <c r="Y24" t="s">
-        <v>660</v>
+        <v>708</v>
       </c>
       <c r="Z24" t="s">
-        <v>663</v>
+        <v>710</v>
       </c>
       <c r="AA24" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="AB24" t="s">
-        <v>665</v>
+        <v>716</v>
       </c>
       <c r="AC24" t="s">
-        <v>669</v>
+        <v>719</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -4336,73 +4489,79 @@
         <v>52</v>
       </c>
       <c r="B25" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C25" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D25" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="E25" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="F25" t="s">
-        <v>191</v>
+        <v>255</v>
       </c>
       <c r="G25" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H25" t="s">
-        <v>283</v>
+        <v>301</v>
+      </c>
+      <c r="I25" t="s">
+        <v>351</v>
       </c>
       <c r="J25" t="s">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="K25" t="s">
-        <v>367</v>
+        <v>391</v>
       </c>
       <c r="L25" t="s">
-        <v>416</v>
+        <v>444</v>
       </c>
       <c r="M25" t="s">
-        <v>465</v>
-      </c>
-      <c r="N25" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="O25" t="s">
-        <v>494</v>
+        <v>529</v>
       </c>
       <c r="P25" t="s">
-        <v>500</v>
+        <v>532</v>
       </c>
       <c r="Q25" t="s">
-        <v>505</v>
+        <v>539</v>
       </c>
       <c r="R25" t="s">
-        <v>530</v>
+        <v>567</v>
       </c>
       <c r="S25" t="s">
-        <v>564</v>
+        <v>598</v>
+      </c>
+      <c r="T25" t="s">
+        <v>635</v>
       </c>
       <c r="U25" t="s">
-        <v>608</v>
+        <v>652</v>
+      </c>
+      <c r="V25" t="s">
+        <v>653</v>
       </c>
       <c r="W25" t="s">
         <v>2</v>
       </c>
       <c r="X25" t="s">
-        <v>634</v>
+        <v>678</v>
       </c>
       <c r="AA25" t="s">
-        <v>505</v>
+        <v>539</v>
       </c>
       <c r="AB25" t="s">
-        <v>665</v>
+        <v>713</v>
       </c>
       <c r="AC25" t="s">
-        <v>669</v>
+        <v>718</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -4410,82 +4569,79 @@
         <v>53</v>
       </c>
       <c r="B26" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C26" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D26" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="E26" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="F26" t="s">
-        <v>207</v>
+        <v>256</v>
       </c>
       <c r="G26" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H26" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="I26" t="s">
-        <v>329</v>
+        <v>352</v>
       </c>
       <c r="J26" t="s">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="K26" t="s">
-        <v>368</v>
+        <v>392</v>
       </c>
       <c r="L26" t="s">
-        <v>417</v>
+        <v>445</v>
       </c>
       <c r="M26" t="s">
-        <v>466</v>
+        <v>498</v>
       </c>
       <c r="O26" t="s">
-        <v>492</v>
+        <v>529</v>
       </c>
       <c r="P26" t="s">
-        <v>495</v>
+        <v>532</v>
       </c>
       <c r="Q26" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="R26" t="s">
-        <v>531</v>
+        <v>568</v>
       </c>
       <c r="S26" t="s">
-        <v>565</v>
+        <v>605</v>
       </c>
       <c r="T26" t="s">
-        <v>592</v>
+        <v>636</v>
       </c>
       <c r="U26" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="V26" t="s">
-        <v>609</v>
+        <v>652</v>
       </c>
       <c r="W26" t="s">
         <v>2</v>
       </c>
       <c r="X26" t="s">
-        <v>635</v>
-      </c>
-      <c r="Y26" t="s">
-        <v>661</v>
+        <v>679</v>
       </c>
       <c r="AA26" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="AB26" t="s">
-        <v>668</v>
+        <v>716</v>
       </c>
       <c r="AC26" t="s">
-        <v>670</v>
+        <v>719</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -4493,82 +4649,79 @@
         <v>54</v>
       </c>
       <c r="B27" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C27" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D27" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="E27" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="F27" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="G27" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H27" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="I27" t="s">
-        <v>329</v>
+        <v>353</v>
       </c>
       <c r="J27" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="K27" t="s">
-        <v>369</v>
+        <v>393</v>
       </c>
       <c r="L27" t="s">
-        <v>418</v>
+        <v>446</v>
       </c>
       <c r="M27" t="s">
-        <v>467</v>
+        <v>499</v>
       </c>
       <c r="O27" t="s">
-        <v>492</v>
+        <v>529</v>
       </c>
       <c r="P27" t="s">
-        <v>495</v>
+        <v>532</v>
       </c>
       <c r="Q27" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="R27" t="s">
-        <v>532</v>
+        <v>569</v>
       </c>
       <c r="S27" t="s">
-        <v>565</v>
+        <v>606</v>
       </c>
       <c r="T27" t="s">
-        <v>593</v>
+        <v>637</v>
       </c>
       <c r="U27" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="V27" t="s">
-        <v>609</v>
+        <v>653</v>
       </c>
       <c r="W27" t="s">
         <v>2</v>
       </c>
       <c r="X27" t="s">
-        <v>636</v>
-      </c>
-      <c r="Y27" t="s">
-        <v>661</v>
+        <v>680</v>
       </c>
       <c r="AA27" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="AB27" t="s">
-        <v>668</v>
+        <v>716</v>
       </c>
       <c r="AC27" t="s">
-        <v>670</v>
+        <v>719</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -4576,85 +4729,73 @@
         <v>55</v>
       </c>
       <c r="B28" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C28" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D28" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="E28" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="F28" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="G28" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H28" t="s">
-        <v>286</v>
-      </c>
-      <c r="I28" t="s">
-        <v>330</v>
+        <v>304</v>
       </c>
       <c r="J28" t="s">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="K28" t="s">
-        <v>370</v>
+        <v>394</v>
       </c>
       <c r="L28" t="s">
-        <v>419</v>
+        <v>447</v>
       </c>
       <c r="M28" t="s">
-        <v>468</v>
+        <v>500</v>
+      </c>
+      <c r="N28" t="s">
+        <v>527</v>
       </c>
       <c r="O28" t="s">
-        <v>492</v>
+        <v>530</v>
       </c>
       <c r="P28" t="s">
-        <v>495</v>
+        <v>535</v>
       </c>
       <c r="Q28" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="R28" t="s">
-        <v>533</v>
+        <v>570</v>
       </c>
       <c r="S28" t="s">
-        <v>566</v>
-      </c>
-      <c r="T28" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="U28" t="s">
-        <v>608</v>
-      </c>
-      <c r="V28" t="s">
-        <v>609</v>
+        <v>652</v>
       </c>
       <c r="W28" t="s">
         <v>2</v>
       </c>
       <c r="X28" t="s">
-        <v>637</v>
-      </c>
-      <c r="Y28" t="s">
-        <v>660</v>
-      </c>
-      <c r="Z28" t="s">
-        <v>663</v>
+        <v>681</v>
       </c>
       <c r="AA28" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="AB28" t="s">
-        <v>665</v>
+        <v>716</v>
       </c>
       <c r="AC28" t="s">
-        <v>669</v>
+        <v>719</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -4662,79 +4803,79 @@
         <v>56</v>
       </c>
       <c r="B29" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C29" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D29" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E29" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="F29" t="s">
-        <v>242</v>
+        <v>219</v>
       </c>
       <c r="G29" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H29" t="s">
-        <v>287</v>
-      </c>
-      <c r="I29" t="s">
-        <v>331</v>
+        <v>305</v>
       </c>
       <c r="J29" t="s">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="K29" t="s">
-        <v>371</v>
+        <v>395</v>
       </c>
       <c r="L29" t="s">
-        <v>420</v>
+        <v>448</v>
       </c>
       <c r="M29" t="s">
-        <v>469</v>
+        <v>501</v>
+      </c>
+      <c r="N29" t="s">
+        <v>527</v>
       </c>
       <c r="O29" t="s">
-        <v>492</v>
+        <v>530</v>
       </c>
       <c r="P29" t="s">
-        <v>495</v>
+        <v>535</v>
       </c>
       <c r="Q29" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="R29" t="s">
-        <v>534</v>
+        <v>571</v>
       </c>
       <c r="S29" t="s">
-        <v>564</v>
-      </c>
-      <c r="T29" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="U29" t="s">
-        <v>608</v>
-      </c>
-      <c r="V29" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="W29" t="s">
         <v>2</v>
       </c>
       <c r="X29" t="s">
-        <v>638</v>
+        <v>682</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>708</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>711</v>
       </c>
       <c r="AA29" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="AB29" t="s">
-        <v>665</v>
+        <v>716</v>
       </c>
       <c r="AC29" t="s">
-        <v>669</v>
+        <v>719</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -4742,85 +4883,79 @@
         <v>57</v>
       </c>
       <c r="B30" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C30" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D30" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="E30" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="F30" t="s">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="G30" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H30" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="I30" t="s">
-        <v>332</v>
+        <v>354</v>
       </c>
       <c r="J30" t="s">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="K30" t="s">
-        <v>372</v>
+        <v>396</v>
       </c>
       <c r="L30" t="s">
-        <v>421</v>
+        <v>449</v>
       </c>
       <c r="M30" t="s">
-        <v>470</v>
+        <v>502</v>
       </c>
       <c r="O30" t="s">
-        <v>492</v>
+        <v>529</v>
       </c>
       <c r="P30" t="s">
-        <v>495</v>
+        <v>532</v>
       </c>
       <c r="Q30" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="R30" t="s">
-        <v>535</v>
+        <v>572</v>
       </c>
       <c r="S30" t="s">
-        <v>563</v>
+        <v>606</v>
       </c>
       <c r="T30" t="s">
-        <v>596</v>
+        <v>638</v>
       </c>
       <c r="U30" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="V30" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="W30" t="s">
         <v>2</v>
       </c>
       <c r="X30" t="s">
-        <v>639</v>
-      </c>
-      <c r="Y30" t="s">
-        <v>660</v>
-      </c>
-      <c r="Z30" t="s">
-        <v>662</v>
+        <v>683</v>
       </c>
       <c r="AA30" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="AB30" t="s">
-        <v>665</v>
+        <v>716</v>
       </c>
       <c r="AC30" t="s">
-        <v>669</v>
+        <v>719</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -4828,79 +4963,79 @@
         <v>58</v>
       </c>
       <c r="B31" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C31" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D31" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="E31" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="F31" t="s">
-        <v>201</v>
+        <v>260</v>
       </c>
       <c r="G31" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H31" t="s">
-        <v>289</v>
+        <v>307</v>
+      </c>
+      <c r="I31" t="s">
+        <v>355</v>
       </c>
       <c r="J31" t="s">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="K31" t="s">
-        <v>373</v>
+        <v>397</v>
       </c>
       <c r="L31" t="s">
-        <v>422</v>
+        <v>450</v>
       </c>
       <c r="M31" t="s">
-        <v>471</v>
-      </c>
-      <c r="N31" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="O31" t="s">
-        <v>494</v>
+        <v>529</v>
       </c>
       <c r="P31" t="s">
-        <v>499</v>
+        <v>532</v>
       </c>
       <c r="Q31" t="s">
-        <v>504</v>
+        <v>539</v>
       </c>
       <c r="R31" t="s">
-        <v>536</v>
+        <v>573</v>
       </c>
       <c r="S31" t="s">
-        <v>556</v>
+        <v>604</v>
+      </c>
+      <c r="T31" t="s">
+        <v>639</v>
       </c>
       <c r="U31" t="s">
-        <v>608</v>
+        <v>652</v>
+      </c>
+      <c r="V31" t="s">
+        <v>652</v>
       </c>
       <c r="W31" t="s">
         <v>2</v>
       </c>
       <c r="X31" t="s">
-        <v>640</v>
-      </c>
-      <c r="Y31" t="s">
-        <v>660</v>
-      </c>
-      <c r="Z31" t="s">
-        <v>663</v>
+        <v>684</v>
       </c>
       <c r="AA31" t="s">
-        <v>504</v>
+        <v>539</v>
       </c>
       <c r="AB31" t="s">
-        <v>665</v>
+        <v>716</v>
       </c>
       <c r="AC31" t="s">
-        <v>669</v>
+        <v>719</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -4908,85 +5043,73 @@
         <v>59</v>
       </c>
       <c r="B32" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C32" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D32" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="E32" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="F32" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="G32" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H32" t="s">
-        <v>290</v>
-      </c>
-      <c r="I32" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="J32" t="s">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="K32" t="s">
-        <v>374</v>
+        <v>398</v>
       </c>
       <c r="L32" t="s">
-        <v>423</v>
+        <v>451</v>
       </c>
       <c r="M32" t="s">
-        <v>472</v>
+        <v>504</v>
       </c>
       <c r="N32" t="s">
-        <v>491</v>
+        <v>527</v>
       </c>
       <c r="O32" t="s">
-        <v>493</v>
+        <v>530</v>
       </c>
       <c r="P32" t="s">
-        <v>498</v>
+        <v>535</v>
       </c>
       <c r="Q32" t="s">
-        <v>503</v>
+        <v>540</v>
       </c>
       <c r="R32" t="s">
-        <v>537</v>
+        <v>574</v>
       </c>
       <c r="S32" t="s">
-        <v>563</v>
-      </c>
-      <c r="T32" t="s">
-        <v>597</v>
+        <v>606</v>
       </c>
       <c r="U32" t="s">
-        <v>608</v>
-      </c>
-      <c r="V32" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="W32" t="s">
         <v>2</v>
       </c>
       <c r="X32" t="s">
-        <v>641</v>
-      </c>
-      <c r="Y32" t="s">
-        <v>660</v>
+        <v>685</v>
       </c>
       <c r="AA32" t="s">
-        <v>503</v>
+        <v>540</v>
       </c>
       <c r="AB32" t="s">
-        <v>665</v>
+        <v>716</v>
       </c>
       <c r="AC32" t="s">
-        <v>669</v>
+        <v>719</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -4994,73 +5117,82 @@
         <v>60</v>
       </c>
       <c r="B33" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C33" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D33" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="E33" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="F33" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="G33" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H33" t="s">
-        <v>291</v>
+        <v>309</v>
+      </c>
+      <c r="I33" t="s">
+        <v>356</v>
       </c>
       <c r="J33" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="K33" t="s">
-        <v>375</v>
+        <v>399</v>
       </c>
       <c r="L33" t="s">
-        <v>424</v>
+        <v>452</v>
       </c>
       <c r="M33" t="s">
-        <v>473</v>
-      </c>
-      <c r="N33" t="s">
-        <v>491</v>
+        <v>505</v>
       </c>
       <c r="O33" t="s">
-        <v>494</v>
+        <v>529</v>
       </c>
       <c r="P33" t="s">
-        <v>501</v>
+        <v>532</v>
       </c>
       <c r="Q33" t="s">
-        <v>506</v>
+        <v>539</v>
       </c>
       <c r="R33" t="s">
-        <v>538</v>
+        <v>575</v>
       </c>
       <c r="S33" t="s">
-        <v>567</v>
+        <v>607</v>
+      </c>
+      <c r="T33" t="s">
+        <v>640</v>
       </c>
       <c r="U33" t="s">
-        <v>609</v>
+        <v>652</v>
+      </c>
+      <c r="V33" t="s">
+        <v>653</v>
       </c>
       <c r="W33" t="s">
         <v>2</v>
       </c>
       <c r="X33" t="s">
-        <v>642</v>
+        <v>686</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>709</v>
       </c>
       <c r="AA33" t="s">
-        <v>664</v>
+        <v>539</v>
       </c>
       <c r="AB33" t="s">
-        <v>665</v>
+        <v>717</v>
       </c>
       <c r="AC33" t="s">
-        <v>669</v>
+        <v>718</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -5068,79 +5200,85 @@
         <v>61</v>
       </c>
       <c r="B34" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C34" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D34" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="E34" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="F34" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="G34" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H34" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="I34" t="s">
-        <v>333</v>
+        <v>357</v>
       </c>
       <c r="J34" t="s">
-        <v>342</v>
+        <v>367</v>
       </c>
       <c r="K34" t="s">
-        <v>376</v>
+        <v>400</v>
       </c>
       <c r="L34" t="s">
-        <v>425</v>
+        <v>453</v>
       </c>
       <c r="M34" t="s">
-        <v>474</v>
+        <v>506</v>
       </c>
       <c r="O34" t="s">
-        <v>492</v>
+        <v>529</v>
       </c>
       <c r="P34" t="s">
-        <v>495</v>
+        <v>532</v>
       </c>
       <c r="Q34" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="R34" t="s">
-        <v>539</v>
+        <v>576</v>
       </c>
       <c r="S34" t="s">
-        <v>566</v>
+        <v>606</v>
       </c>
       <c r="T34" t="s">
-        <v>598</v>
+        <v>641</v>
       </c>
       <c r="U34" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="V34" t="s">
-        <v>609</v>
+        <v>653</v>
       </c>
       <c r="W34" t="s">
         <v>2</v>
       </c>
       <c r="X34" t="s">
-        <v>643</v>
+        <v>687</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>708</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>711</v>
       </c>
       <c r="AA34" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="AB34" t="s">
-        <v>665</v>
+        <v>716</v>
       </c>
       <c r="AC34" t="s">
-        <v>669</v>
+        <v>719</v>
       </c>
     </row>
     <row r="35" spans="1:29">
@@ -5148,73 +5286,79 @@
         <v>62</v>
       </c>
       <c r="B35" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C35" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D35" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="E35" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="F35" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="G35" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H35" t="s">
-        <v>293</v>
+        <v>311</v>
+      </c>
+      <c r="I35" t="s">
+        <v>358</v>
       </c>
       <c r="J35" t="s">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="K35" t="s">
-        <v>377</v>
+        <v>401</v>
       </c>
       <c r="L35" t="s">
-        <v>426</v>
+        <v>454</v>
       </c>
       <c r="M35" t="s">
-        <v>475</v>
-      </c>
-      <c r="N35" t="s">
-        <v>491</v>
+        <v>507</v>
       </c>
       <c r="O35" t="s">
-        <v>494</v>
+        <v>529</v>
       </c>
       <c r="P35" t="s">
-        <v>499</v>
+        <v>532</v>
       </c>
       <c r="Q35" t="s">
-        <v>504</v>
+        <v>539</v>
       </c>
       <c r="R35" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
       <c r="S35" t="s">
-        <v>566</v>
+        <v>604</v>
+      </c>
+      <c r="T35" t="s">
+        <v>642</v>
       </c>
       <c r="U35" t="s">
-        <v>608</v>
+        <v>652</v>
+      </c>
+      <c r="V35" t="s">
+        <v>653</v>
       </c>
       <c r="W35" t="s">
         <v>2</v>
       </c>
       <c r="X35" t="s">
-        <v>644</v>
+        <v>688</v>
       </c>
       <c r="AA35" t="s">
-        <v>504</v>
+        <v>539</v>
       </c>
       <c r="AB35" t="s">
-        <v>665</v>
+        <v>716</v>
       </c>
       <c r="AC35" t="s">
-        <v>669</v>
+        <v>719</v>
       </c>
     </row>
     <row r="36" spans="1:29">
@@ -5222,79 +5366,73 @@
         <v>63</v>
       </c>
       <c r="B36" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C36" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D36" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="E36" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="F36" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="G36" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H36" t="s">
-        <v>294</v>
-      </c>
-      <c r="I36" t="s">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="J36" t="s">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="K36" t="s">
-        <v>378</v>
+        <v>402</v>
       </c>
       <c r="L36" t="s">
-        <v>427</v>
+        <v>455</v>
       </c>
       <c r="M36" t="s">
-        <v>476</v>
+        <v>508</v>
+      </c>
+      <c r="N36" t="s">
+        <v>527</v>
       </c>
       <c r="O36" t="s">
-        <v>492</v>
+        <v>530</v>
       </c>
       <c r="P36" t="s">
-        <v>495</v>
+        <v>535</v>
       </c>
       <c r="Q36" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="R36" t="s">
-        <v>541</v>
+        <v>578</v>
       </c>
       <c r="S36" t="s">
-        <v>563</v>
-      </c>
-      <c r="T36" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="U36" t="s">
-        <v>608</v>
-      </c>
-      <c r="V36" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="W36" t="s">
         <v>2</v>
       </c>
       <c r="X36" t="s">
-        <v>645</v>
+        <v>689</v>
       </c>
       <c r="AA36" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="AB36" t="s">
-        <v>665</v>
+        <v>716</v>
       </c>
       <c r="AC36" t="s">
-        <v>669</v>
+        <v>719</v>
       </c>
     </row>
     <row r="37" spans="1:29">
@@ -5302,73 +5440,73 @@
         <v>64</v>
       </c>
       <c r="B37" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C37" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D37" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="E37" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="F37" t="s">
-        <v>249</v>
+        <v>201</v>
       </c>
       <c r="G37" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H37" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="J37" t="s">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="K37" t="s">
-        <v>379</v>
+        <v>403</v>
       </c>
       <c r="L37" t="s">
-        <v>428</v>
+        <v>456</v>
       </c>
       <c r="M37" t="s">
-        <v>477</v>
+        <v>509</v>
       </c>
       <c r="N37" t="s">
-        <v>491</v>
+        <v>527</v>
       </c>
       <c r="O37" t="s">
-        <v>494</v>
+        <v>530</v>
       </c>
       <c r="P37" t="s">
-        <v>499</v>
+        <v>535</v>
       </c>
       <c r="Q37" t="s">
-        <v>504</v>
+        <v>540</v>
       </c>
       <c r="R37" t="s">
-        <v>542</v>
+        <v>579</v>
       </c>
       <c r="S37" t="s">
-        <v>564</v>
+        <v>597</v>
       </c>
       <c r="U37" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="W37" t="s">
         <v>2</v>
       </c>
       <c r="X37" t="s">
-        <v>646</v>
+        <v>690</v>
       </c>
       <c r="AA37" t="s">
-        <v>504</v>
+        <v>540</v>
       </c>
       <c r="AB37" t="s">
-        <v>665</v>
+        <v>716</v>
       </c>
       <c r="AC37" t="s">
-        <v>669</v>
+        <v>719</v>
       </c>
     </row>
     <row r="38" spans="1:29">
@@ -5376,73 +5514,79 @@
         <v>65</v>
       </c>
       <c r="B38" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C38" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D38" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="E38" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="F38" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="G38" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H38" t="s">
-        <v>296</v>
+        <v>314</v>
+      </c>
+      <c r="I38" t="s">
+        <v>359</v>
       </c>
       <c r="J38" t="s">
-        <v>342</v>
+        <v>367</v>
       </c>
       <c r="K38" t="s">
-        <v>380</v>
+        <v>404</v>
       </c>
       <c r="L38" t="s">
-        <v>429</v>
+        <v>457</v>
       </c>
       <c r="M38" t="s">
-        <v>478</v>
-      </c>
-      <c r="N38" t="s">
-        <v>491</v>
+        <v>510</v>
       </c>
       <c r="O38" t="s">
-        <v>494</v>
+        <v>529</v>
       </c>
       <c r="P38" t="s">
-        <v>500</v>
+        <v>532</v>
       </c>
       <c r="Q38" t="s">
-        <v>505</v>
+        <v>539</v>
       </c>
       <c r="R38" t="s">
-        <v>543</v>
+        <v>580</v>
       </c>
       <c r="S38" t="s">
-        <v>566</v>
+        <v>597</v>
+      </c>
+      <c r="T38" t="s">
+        <v>643</v>
       </c>
       <c r="U38" t="s">
-        <v>608</v>
+        <v>652</v>
+      </c>
+      <c r="V38" t="s">
+        <v>653</v>
       </c>
       <c r="W38" t="s">
         <v>2</v>
       </c>
       <c r="X38" t="s">
-        <v>647</v>
+        <v>691</v>
       </c>
       <c r="AA38" t="s">
-        <v>505</v>
+        <v>539</v>
       </c>
       <c r="AB38" t="s">
-        <v>665</v>
+        <v>716</v>
       </c>
       <c r="AC38" t="s">
-        <v>669</v>
+        <v>719</v>
       </c>
     </row>
     <row r="39" spans="1:29">
@@ -5450,79 +5594,73 @@
         <v>66</v>
       </c>
       <c r="B39" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C39" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D39" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="E39" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="F39" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="G39" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H39" t="s">
-        <v>297</v>
-      </c>
-      <c r="I39" t="s">
-        <v>335</v>
+        <v>315</v>
       </c>
       <c r="J39" t="s">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="K39" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="L39" t="s">
-        <v>430</v>
+        <v>458</v>
       </c>
       <c r="M39" t="s">
-        <v>479</v>
+        <v>511</v>
+      </c>
+      <c r="N39" t="s">
+        <v>527</v>
       </c>
       <c r="O39" t="s">
-        <v>492</v>
+        <v>530</v>
       </c>
       <c r="P39" t="s">
-        <v>495</v>
+        <v>538</v>
       </c>
       <c r="Q39" t="s">
-        <v>502</v>
+        <v>543</v>
       </c>
       <c r="R39" t="s">
-        <v>544</v>
+        <v>581</v>
       </c>
       <c r="S39" t="s">
-        <v>566</v>
-      </c>
-      <c r="T39" t="s">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="U39" t="s">
-        <v>608</v>
-      </c>
-      <c r="V39" t="s">
-        <v>608</v>
+        <v>653</v>
       </c>
       <c r="W39" t="s">
         <v>2</v>
       </c>
       <c r="X39" t="s">
-        <v>648</v>
+        <v>692</v>
       </c>
       <c r="AA39" t="s">
-        <v>502</v>
+        <v>712</v>
       </c>
       <c r="AB39" t="s">
-        <v>665</v>
+        <v>713</v>
       </c>
       <c r="AC39" t="s">
-        <v>669</v>
+        <v>718</v>
       </c>
     </row>
     <row r="40" spans="1:29">
@@ -5530,70 +5668,73 @@
         <v>67</v>
       </c>
       <c r="B40" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C40" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D40" t="s">
-        <v>149</v>
+        <v>174</v>
       </c>
       <c r="E40" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="F40" t="s">
-        <v>213</v>
+        <v>268</v>
       </c>
       <c r="G40" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H40" t="s">
-        <v>298</v>
-      </c>
-      <c r="I40" t="s">
-        <v>336</v>
+        <v>316</v>
+      </c>
+      <c r="J40" t="s">
+        <v>367</v>
       </c>
       <c r="K40" t="s">
-        <v>382</v>
+        <v>406</v>
       </c>
       <c r="L40" t="s">
-        <v>431</v>
+        <v>459</v>
       </c>
       <c r="M40" t="s">
-        <v>480</v>
+        <v>512</v>
+      </c>
+      <c r="N40" t="s">
+        <v>527</v>
       </c>
       <c r="O40" t="s">
-        <v>494</v>
+        <v>530</v>
       </c>
       <c r="P40" t="s">
-        <v>495</v>
+        <v>537</v>
       </c>
       <c r="Q40" t="s">
-        <v>502</v>
+        <v>542</v>
       </c>
       <c r="R40" t="s">
-        <v>545</v>
+        <v>582</v>
       </c>
       <c r="S40" t="s">
-        <v>568</v>
+        <v>609</v>
       </c>
       <c r="U40" t="s">
-        <v>610</v>
+        <v>652</v>
       </c>
       <c r="W40" t="s">
         <v>2</v>
       </c>
       <c r="X40" t="s">
-        <v>649</v>
+        <v>693</v>
       </c>
       <c r="AA40" t="s">
-        <v>502</v>
+        <v>542</v>
       </c>
       <c r="AB40" t="s">
-        <v>665</v>
+        <v>716</v>
       </c>
       <c r="AC40" t="s">
-        <v>669</v>
+        <v>719</v>
       </c>
     </row>
     <row r="41" spans="1:29">
@@ -5601,79 +5742,79 @@
         <v>68</v>
       </c>
       <c r="B41" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C41" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D41" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="E41" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="F41" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="G41" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H41" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="I41" t="s">
-        <v>337</v>
+        <v>360</v>
       </c>
       <c r="J41" t="s">
-        <v>342</v>
+        <v>367</v>
       </c>
       <c r="K41" t="s">
-        <v>383</v>
+        <v>407</v>
       </c>
       <c r="L41" t="s">
-        <v>432</v>
+        <v>460</v>
       </c>
       <c r="M41" t="s">
-        <v>481</v>
+        <v>513</v>
       </c>
       <c r="O41" t="s">
-        <v>492</v>
+        <v>529</v>
       </c>
       <c r="P41" t="s">
-        <v>495</v>
+        <v>534</v>
       </c>
       <c r="Q41" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="R41" t="s">
-        <v>546</v>
+        <v>583</v>
       </c>
       <c r="S41" t="s">
-        <v>563</v>
+        <v>609</v>
       </c>
       <c r="T41" t="s">
-        <v>601</v>
+        <v>644</v>
       </c>
       <c r="U41" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="V41" t="s">
-        <v>609</v>
+        <v>653</v>
       </c>
       <c r="W41" t="s">
         <v>2</v>
       </c>
       <c r="X41" t="s">
-        <v>650</v>
+        <v>694</v>
       </c>
       <c r="AA41" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="AB41" t="s">
-        <v>665</v>
+        <v>716</v>
       </c>
       <c r="AC41" t="s">
-        <v>669</v>
+        <v>719</v>
       </c>
     </row>
     <row r="42" spans="1:29">
@@ -5681,73 +5822,79 @@
         <v>69</v>
       </c>
       <c r="B42" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C42" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D42" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="E42" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="F42" t="s">
-        <v>192</v>
+        <v>270</v>
       </c>
       <c r="G42" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H42" t="s">
-        <v>300</v>
+        <v>318</v>
+      </c>
+      <c r="I42" t="s">
+        <v>359</v>
       </c>
       <c r="J42" t="s">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="K42" t="s">
-        <v>384</v>
+        <v>408</v>
       </c>
       <c r="L42" t="s">
-        <v>433</v>
+        <v>461</v>
       </c>
       <c r="M42" t="s">
-        <v>482</v>
-      </c>
-      <c r="N42" t="s">
-        <v>491</v>
+        <v>514</v>
       </c>
       <c r="O42" t="s">
-        <v>494</v>
+        <v>529</v>
       </c>
       <c r="P42" t="s">
-        <v>499</v>
+        <v>532</v>
       </c>
       <c r="Q42" t="s">
-        <v>504</v>
+        <v>539</v>
       </c>
       <c r="R42" t="s">
-        <v>547</v>
+        <v>584</v>
       </c>
       <c r="S42" t="s">
-        <v>556</v>
+        <v>597</v>
+      </c>
+      <c r="T42" t="s">
+        <v>645</v>
       </c>
       <c r="U42" t="s">
-        <v>608</v>
+        <v>652</v>
+      </c>
+      <c r="V42" t="s">
+        <v>653</v>
       </c>
       <c r="W42" t="s">
         <v>2</v>
       </c>
       <c r="X42" t="s">
-        <v>651</v>
+        <v>695</v>
       </c>
       <c r="AA42" t="s">
-        <v>504</v>
+        <v>539</v>
       </c>
       <c r="AB42" t="s">
-        <v>665</v>
+        <v>716</v>
       </c>
       <c r="AC42" t="s">
-        <v>669</v>
+        <v>719</v>
       </c>
     </row>
     <row r="43" spans="1:29">
@@ -5755,73 +5902,73 @@
         <v>70</v>
       </c>
       <c r="B43" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C43" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D43" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="E43" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="F43" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="G43" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H43" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="J43" t="s">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="K43" t="s">
-        <v>385</v>
+        <v>409</v>
       </c>
       <c r="L43" t="s">
-        <v>434</v>
+        <v>462</v>
       </c>
       <c r="M43" t="s">
-        <v>483</v>
+        <v>515</v>
       </c>
       <c r="N43" t="s">
-        <v>491</v>
+        <v>527</v>
       </c>
       <c r="O43" t="s">
-        <v>494</v>
+        <v>530</v>
       </c>
       <c r="P43" t="s">
-        <v>500</v>
+        <v>537</v>
       </c>
       <c r="Q43" t="s">
-        <v>505</v>
+        <v>542</v>
       </c>
       <c r="R43" t="s">
-        <v>548</v>
+        <v>585</v>
       </c>
       <c r="S43" t="s">
-        <v>569</v>
+        <v>606</v>
       </c>
       <c r="U43" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="W43" t="s">
         <v>2</v>
       </c>
       <c r="X43" t="s">
-        <v>652</v>
+        <v>696</v>
       </c>
       <c r="AA43" t="s">
-        <v>505</v>
+        <v>542</v>
       </c>
       <c r="AB43" t="s">
-        <v>665</v>
+        <v>713</v>
       </c>
       <c r="AC43" t="s">
-        <v>669</v>
+        <v>718</v>
       </c>
     </row>
     <row r="44" spans="1:29">
@@ -5829,79 +5976,82 @@
         <v>71</v>
       </c>
       <c r="B44" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C44" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D44" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="E44" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="F44" t="s">
-        <v>254</v>
+        <v>212</v>
       </c>
       <c r="G44" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H44" t="s">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="I44" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="J44" t="s">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="K44" t="s">
-        <v>386</v>
+        <v>410</v>
       </c>
       <c r="L44" t="s">
-        <v>435</v>
+        <v>463</v>
       </c>
       <c r="M44" t="s">
-        <v>484</v>
+        <v>516</v>
       </c>
       <c r="O44" t="s">
-        <v>492</v>
+        <v>529</v>
       </c>
       <c r="P44" t="s">
-        <v>497</v>
+        <v>532</v>
       </c>
       <c r="Q44" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="R44" t="s">
-        <v>549</v>
+        <v>586</v>
       </c>
       <c r="S44" t="s">
-        <v>569</v>
+        <v>607</v>
       </c>
       <c r="T44" t="s">
-        <v>602</v>
+        <v>646</v>
       </c>
       <c r="U44" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="V44" t="s">
-        <v>609</v>
+        <v>653</v>
       </c>
       <c r="W44" t="s">
         <v>2</v>
       </c>
       <c r="X44" t="s">
-        <v>653</v>
+        <v>697</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>709</v>
       </c>
       <c r="AA44" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="AB44" t="s">
-        <v>665</v>
+        <v>717</v>
       </c>
       <c r="AC44" t="s">
-        <v>669</v>
+        <v>718</v>
       </c>
     </row>
     <row r="45" spans="1:29">
@@ -5909,79 +6059,79 @@
         <v>72</v>
       </c>
       <c r="B45" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C45" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D45" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="E45" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="F45" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="G45" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H45" t="s">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="I45" t="s">
-        <v>339</v>
+        <v>361</v>
       </c>
       <c r="J45" t="s">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="K45" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="L45" t="s">
-        <v>436</v>
+        <v>464</v>
       </c>
       <c r="M45" t="s">
-        <v>485</v>
+        <v>517</v>
       </c>
       <c r="O45" t="s">
-        <v>492</v>
+        <v>529</v>
       </c>
       <c r="P45" t="s">
-        <v>495</v>
+        <v>532</v>
       </c>
       <c r="Q45" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="R45" t="s">
-        <v>550</v>
+        <v>587</v>
       </c>
       <c r="S45" t="s">
-        <v>556</v>
+        <v>610</v>
       </c>
       <c r="T45" t="s">
-        <v>603</v>
+        <v>587</v>
       </c>
       <c r="U45" t="s">
-        <v>608</v>
+        <v>654</v>
       </c>
       <c r="V45" t="s">
-        <v>609</v>
+        <v>652</v>
       </c>
       <c r="W45" t="s">
         <v>2</v>
       </c>
       <c r="X45" t="s">
-        <v>654</v>
+        <v>698</v>
       </c>
       <c r="AA45" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="AB45" t="s">
-        <v>665</v>
+        <v>713</v>
       </c>
       <c r="AC45" t="s">
-        <v>669</v>
+        <v>718</v>
       </c>
     </row>
     <row r="46" spans="1:29">
@@ -5989,79 +6139,73 @@
         <v>73</v>
       </c>
       <c r="B46" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C46" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D46" t="s">
-        <v>135</v>
+        <v>179</v>
       </c>
       <c r="E46" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="F46" t="s">
-        <v>256</v>
+        <v>211</v>
       </c>
       <c r="G46" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H46" t="s">
-        <v>304</v>
-      </c>
-      <c r="I46" t="s">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="J46" t="s">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="K46" t="s">
-        <v>388</v>
+        <v>412</v>
       </c>
       <c r="L46" t="s">
-        <v>437</v>
+        <v>465</v>
       </c>
       <c r="M46" t="s">
-        <v>486</v>
+        <v>518</v>
+      </c>
+      <c r="N46" t="s">
+        <v>527</v>
       </c>
       <c r="O46" t="s">
-        <v>492</v>
+        <v>530</v>
       </c>
       <c r="P46" t="s">
-        <v>495</v>
+        <v>535</v>
       </c>
       <c r="Q46" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="R46" t="s">
-        <v>551</v>
+        <v>588</v>
       </c>
       <c r="S46" t="s">
-        <v>556</v>
-      </c>
-      <c r="T46" t="s">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="U46" t="s">
-        <v>608</v>
-      </c>
-      <c r="V46" t="s">
-        <v>609</v>
+        <v>652</v>
       </c>
       <c r="W46" t="s">
         <v>2</v>
       </c>
       <c r="X46" t="s">
-        <v>655</v>
+        <v>699</v>
       </c>
       <c r="AA46" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="AB46" t="s">
-        <v>665</v>
+        <v>716</v>
       </c>
       <c r="AC46" t="s">
-        <v>669</v>
+        <v>719</v>
       </c>
     </row>
     <row r="47" spans="1:29">
@@ -6069,73 +6213,82 @@
         <v>74</v>
       </c>
       <c r="B47" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C47" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D47" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="E47" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="F47" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="G47" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H47" t="s">
-        <v>305</v>
+        <v>323</v>
+      </c>
+      <c r="I47" t="s">
+        <v>362</v>
       </c>
       <c r="J47" t="s">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="K47" t="s">
-        <v>389</v>
+        <v>413</v>
       </c>
       <c r="L47" t="s">
-        <v>438</v>
+        <v>466</v>
       </c>
       <c r="M47" t="s">
-        <v>487</v>
+        <v>519</v>
       </c>
       <c r="N47" t="s">
-        <v>491</v>
+        <v>528</v>
       </c>
       <c r="O47" t="s">
-        <v>494</v>
+        <v>529</v>
       </c>
       <c r="P47" t="s">
-        <v>499</v>
+        <v>532</v>
       </c>
       <c r="Q47" t="s">
-        <v>504</v>
+        <v>539</v>
       </c>
       <c r="R47" t="s">
-        <v>552</v>
+        <v>589</v>
       </c>
       <c r="S47" t="s">
-        <v>556</v>
+        <v>612</v>
+      </c>
+      <c r="T47" t="s">
+        <v>647</v>
       </c>
       <c r="U47" t="s">
-        <v>608</v>
+        <v>652</v>
+      </c>
+      <c r="V47" t="s">
+        <v>652</v>
       </c>
       <c r="W47" t="s">
         <v>2</v>
       </c>
       <c r="X47" t="s">
-        <v>656</v>
+        <v>700</v>
       </c>
       <c r="AA47" t="s">
-        <v>504</v>
+        <v>539</v>
       </c>
       <c r="AB47" t="s">
-        <v>665</v>
+        <v>716</v>
       </c>
       <c r="AC47" t="s">
-        <v>669</v>
+        <v>719</v>
       </c>
     </row>
     <row r="48" spans="1:29">
@@ -6143,79 +6296,85 @@
         <v>75</v>
       </c>
       <c r="B48" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C48" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D48" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="E48" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="F48" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="G48" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H48" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="I48" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="J48" t="s">
-        <v>342</v>
+        <v>367</v>
       </c>
       <c r="K48" t="s">
-        <v>390</v>
+        <v>414</v>
       </c>
       <c r="L48" t="s">
-        <v>439</v>
+        <v>467</v>
       </c>
       <c r="M48" t="s">
-        <v>488</v>
+        <v>520</v>
+      </c>
+      <c r="N48" t="s">
+        <v>527</v>
       </c>
       <c r="O48" t="s">
-        <v>492</v>
+        <v>531</v>
       </c>
       <c r="P48" t="s">
-        <v>495</v>
+        <v>536</v>
       </c>
       <c r="Q48" t="s">
-        <v>502</v>
+        <v>541</v>
       </c>
       <c r="R48" t="s">
-        <v>553</v>
+        <v>590</v>
       </c>
       <c r="S48" t="s">
-        <v>556</v>
+        <v>604</v>
       </c>
       <c r="T48" t="s">
-        <v>605</v>
+        <v>648</v>
       </c>
       <c r="U48" t="s">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="V48" t="s">
-        <v>609</v>
+        <v>652</v>
       </c>
       <c r="W48" t="s">
         <v>2</v>
       </c>
       <c r="X48" t="s">
-        <v>657</v>
+        <v>701</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>708</v>
       </c>
       <c r="AA48" t="s">
-        <v>502</v>
+        <v>541</v>
       </c>
       <c r="AB48" t="s">
-        <v>665</v>
+        <v>716</v>
       </c>
       <c r="AC48" t="s">
-        <v>669</v>
+        <v>719</v>
       </c>
     </row>
     <row r="49" spans="1:29">
@@ -6223,79 +6382,82 @@
         <v>76</v>
       </c>
       <c r="B49" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C49" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D49" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="E49" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="F49" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="G49" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H49" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="I49" t="s">
-        <v>338</v>
+        <v>363</v>
       </c>
       <c r="J49" t="s">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="K49" t="s">
-        <v>391</v>
+        <v>415</v>
       </c>
       <c r="L49" t="s">
-        <v>440</v>
+        <v>468</v>
       </c>
       <c r="M49" t="s">
-        <v>489</v>
+        <v>521</v>
+      </c>
+      <c r="N49" t="s">
+        <v>528</v>
       </c>
       <c r="O49" t="s">
-        <v>492</v>
+        <v>529</v>
       </c>
       <c r="P49" t="s">
-        <v>497</v>
+        <v>532</v>
       </c>
       <c r="Q49" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="R49" t="s">
-        <v>554</v>
+        <v>591</v>
       </c>
       <c r="S49" t="s">
-        <v>569</v>
+        <v>611</v>
       </c>
       <c r="T49" t="s">
-        <v>606</v>
+        <v>591</v>
       </c>
       <c r="U49" t="s">
-        <v>608</v>
+        <v>654</v>
       </c>
       <c r="V49" t="s">
-        <v>609</v>
+        <v>653</v>
       </c>
       <c r="W49" t="s">
         <v>2</v>
       </c>
       <c r="X49" t="s">
-        <v>658</v>
+        <v>702</v>
       </c>
       <c r="AA49" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="AB49" t="s">
-        <v>665</v>
+        <v>717</v>
       </c>
       <c r="AC49" t="s">
-        <v>669</v>
+        <v>718</v>
       </c>
     </row>
     <row r="50" spans="1:29">
@@ -6303,79 +6465,387 @@
         <v>77</v>
       </c>
       <c r="B50" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C50" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D50" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="E50" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="F50" t="s">
-        <v>201</v>
+        <v>275</v>
       </c>
       <c r="G50" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="H50" t="s">
-        <v>308</v>
-      </c>
-      <c r="I50" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="J50" t="s">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="K50" t="s">
-        <v>392</v>
+        <v>416</v>
       </c>
       <c r="L50" t="s">
-        <v>441</v>
+        <v>469</v>
       </c>
       <c r="M50" t="s">
-        <v>490</v>
+        <v>522</v>
+      </c>
+      <c r="N50" t="s">
+        <v>527</v>
       </c>
       <c r="O50" t="s">
-        <v>492</v>
+        <v>530</v>
       </c>
       <c r="P50" t="s">
-        <v>495</v>
+        <v>535</v>
       </c>
       <c r="Q50" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="R50" t="s">
-        <v>555</v>
+        <v>592</v>
       </c>
       <c r="S50" t="s">
-        <v>570</v>
-      </c>
-      <c r="T50" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="U50" t="s">
-        <v>608</v>
-      </c>
-      <c r="V50" t="s">
-        <v>609</v>
+        <v>652</v>
       </c>
       <c r="W50" t="s">
         <v>2</v>
       </c>
       <c r="X50" t="s">
-        <v>659</v>
+        <v>703</v>
       </c>
       <c r="AA50" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="AB50" t="s">
-        <v>665</v>
+        <v>716</v>
       </c>
       <c r="AC50" t="s">
-        <v>669</v>
+        <v>719</v>
+      </c>
+    </row>
+    <row r="51" spans="1:29">
+      <c r="A51" t="s">
+        <v>78</v>
+      </c>
+      <c r="B51" t="s">
+        <v>131</v>
+      </c>
+      <c r="C51" t="s">
+        <v>135</v>
+      </c>
+      <c r="D51" t="s">
+        <v>184</v>
+      </c>
+      <c r="E51" t="s">
+        <v>236</v>
+      </c>
+      <c r="F51" t="s">
+        <v>240</v>
+      </c>
+      <c r="G51" t="s">
+        <v>277</v>
+      </c>
+      <c r="H51" t="s">
+        <v>327</v>
+      </c>
+      <c r="J51" t="s">
+        <v>367</v>
+      </c>
+      <c r="K51" t="s">
+        <v>417</v>
+      </c>
+      <c r="L51" t="s">
+        <v>470</v>
+      </c>
+      <c r="M51" t="s">
+        <v>523</v>
+      </c>
+      <c r="N51" t="s">
+        <v>527</v>
+      </c>
+      <c r="O51" t="s">
+        <v>530</v>
+      </c>
+      <c r="P51" t="s">
+        <v>535</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>540</v>
+      </c>
+      <c r="R51" t="s">
+        <v>593</v>
+      </c>
+      <c r="S51" t="s">
+        <v>612</v>
+      </c>
+      <c r="U51" t="s">
+        <v>652</v>
+      </c>
+      <c r="W51" t="s">
+        <v>2</v>
+      </c>
+      <c r="X51" t="s">
+        <v>704</v>
+      </c>
+      <c r="AA51" t="s">
+        <v>540</v>
+      </c>
+      <c r="AB51" t="s">
+        <v>716</v>
+      </c>
+      <c r="AC51" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="52" spans="1:29">
+      <c r="A52" t="s">
+        <v>79</v>
+      </c>
+      <c r="B52" t="s">
+        <v>132</v>
+      </c>
+      <c r="C52" t="s">
+        <v>135</v>
+      </c>
+      <c r="D52" t="s">
+        <v>145</v>
+      </c>
+      <c r="E52" t="s">
+        <v>237</v>
+      </c>
+      <c r="F52" t="s">
+        <v>276</v>
+      </c>
+      <c r="G52" t="s">
+        <v>277</v>
+      </c>
+      <c r="H52" t="s">
+        <v>328</v>
+      </c>
+      <c r="I52" t="s">
+        <v>364</v>
+      </c>
+      <c r="J52" t="s">
+        <v>367</v>
+      </c>
+      <c r="K52" t="s">
+        <v>418</v>
+      </c>
+      <c r="L52" t="s">
+        <v>471</v>
+      </c>
+      <c r="M52" t="s">
+        <v>524</v>
+      </c>
+      <c r="O52" t="s">
+        <v>529</v>
+      </c>
+      <c r="P52" t="s">
+        <v>532</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>539</v>
+      </c>
+      <c r="R52" t="s">
+        <v>594</v>
+      </c>
+      <c r="S52" t="s">
+        <v>597</v>
+      </c>
+      <c r="T52" t="s">
+        <v>649</v>
+      </c>
+      <c r="U52" t="s">
+        <v>652</v>
+      </c>
+      <c r="V52" t="s">
+        <v>653</v>
+      </c>
+      <c r="W52" t="s">
+        <v>2</v>
+      </c>
+      <c r="X52" t="s">
+        <v>705</v>
+      </c>
+      <c r="AA52" t="s">
+        <v>539</v>
+      </c>
+      <c r="AB52" t="s">
+        <v>716</v>
+      </c>
+      <c r="AC52" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="53" spans="1:29">
+      <c r="A53" t="s">
+        <v>80</v>
+      </c>
+      <c r="B53" t="s">
+        <v>133</v>
+      </c>
+      <c r="C53" t="s">
+        <v>135</v>
+      </c>
+      <c r="D53" t="s">
+        <v>185</v>
+      </c>
+      <c r="E53" t="s">
+        <v>238</v>
+      </c>
+      <c r="F53" t="s">
+        <v>226</v>
+      </c>
+      <c r="G53" t="s">
+        <v>277</v>
+      </c>
+      <c r="H53" t="s">
+        <v>329</v>
+      </c>
+      <c r="I53" t="s">
+        <v>360</v>
+      </c>
+      <c r="J53" t="s">
+        <v>367</v>
+      </c>
+      <c r="K53" t="s">
+        <v>419</v>
+      </c>
+      <c r="L53" t="s">
+        <v>472</v>
+      </c>
+      <c r="M53" t="s">
+        <v>525</v>
+      </c>
+      <c r="O53" t="s">
+        <v>529</v>
+      </c>
+      <c r="P53" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>539</v>
+      </c>
+      <c r="R53" t="s">
+        <v>595</v>
+      </c>
+      <c r="S53" t="s">
+        <v>609</v>
+      </c>
+      <c r="T53" t="s">
+        <v>650</v>
+      </c>
+      <c r="U53" t="s">
+        <v>652</v>
+      </c>
+      <c r="V53" t="s">
+        <v>653</v>
+      </c>
+      <c r="W53" t="s">
+        <v>2</v>
+      </c>
+      <c r="X53" t="s">
+        <v>706</v>
+      </c>
+      <c r="AA53" t="s">
+        <v>539</v>
+      </c>
+      <c r="AB53" t="s">
+        <v>716</v>
+      </c>
+      <c r="AC53" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="54" spans="1:29">
+      <c r="A54" t="s">
+        <v>81</v>
+      </c>
+      <c r="B54" t="s">
+        <v>134</v>
+      </c>
+      <c r="C54" t="s">
+        <v>135</v>
+      </c>
+      <c r="D54" t="s">
+        <v>186</v>
+      </c>
+      <c r="E54" t="s">
+        <v>239</v>
+      </c>
+      <c r="F54" t="s">
+        <v>219</v>
+      </c>
+      <c r="G54" t="s">
+        <v>277</v>
+      </c>
+      <c r="H54" t="s">
+        <v>330</v>
+      </c>
+      <c r="I54" t="s">
+        <v>365</v>
+      </c>
+      <c r="J54" t="s">
+        <v>367</v>
+      </c>
+      <c r="K54" t="s">
+        <v>420</v>
+      </c>
+      <c r="L54" t="s">
+        <v>473</v>
+      </c>
+      <c r="M54" t="s">
+        <v>526</v>
+      </c>
+      <c r="O54" t="s">
+        <v>529</v>
+      </c>
+      <c r="P54" t="s">
+        <v>532</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>539</v>
+      </c>
+      <c r="R54" t="s">
+        <v>596</v>
+      </c>
+      <c r="S54" t="s">
+        <v>613</v>
+      </c>
+      <c r="T54" t="s">
+        <v>651</v>
+      </c>
+      <c r="U54" t="s">
+        <v>652</v>
+      </c>
+      <c r="V54" t="s">
+        <v>653</v>
+      </c>
+      <c r="W54" t="s">
+        <v>2</v>
+      </c>
+      <c r="X54" t="s">
+        <v>707</v>
+      </c>
+      <c r="AA54" t="s">
+        <v>539</v>
+      </c>
+      <c r="AB54" t="s">
+        <v>713</v>
+      </c>
+      <c r="AC54" t="s">
+        <v>718</v>
       </c>
     </row>
   </sheetData>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__PASEO LA PAZ.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__PASEO LA PAZ.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC58"/>
+  <dimension ref="A1:AC64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -991,12 +991,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>340353</t>
+          <t>322857</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18171</t>
+          <t>19796</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1006,17 +1006,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">GIBERTO </t>
+          <t>NAYELI</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">MENDEZ </t>
+          <t>MARILES</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HALE </t>
+          <t>CORDERO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1026,32 +1026,32 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6121528946</t>
+          <t>6122343921</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>C CERRADA SANTA INES 890</t>
+          <t>PISTACHE 144</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>23-11-2001</t>
+          <t>23-12-1992</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>GILBERTO.MEN20011@GMAIL.COM</t>
+          <t>NAYUNOCHO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-02-2026 18:54:26</t>
+          <t>10-11-2025 12:13:22</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1072,17 +1072,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-02-2026 18:58:19</t>
+          <t>05-02-2026 15:40:20</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>02-02-2026 18:58:00</t>
+          <t>05-02-2026 15:40:02</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26210522021420002304</t>
+          <t>26210522108860002579</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Guillermo  Garcia De Alba Velazquez</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1126,12 +1126,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>322857</t>
+          <t>340279</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19796</t>
+          <t>18097</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1141,17 +1141,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NAYELI</t>
+          <t xml:space="preserve">LUZ ANGELICA </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MARILES</t>
+          <t xml:space="preserve">LOA </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CORDERO</t>
+          <t xml:space="preserve">VEGA </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6122343921</t>
+          <t>6121042102</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PISTACHE 144</t>
+          <t>C MANUEL F MONTAÑO</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1176,17 +1176,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>23-12-1992</t>
+          <t>20-09-1980</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>NAYUNOCHO@GMAIL.COM</t>
+          <t>LICLOAVEGA20@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>10-11-2025 12:13:22</t>
+          <t>02-02-2026 16:39:48</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1207,17 +1207,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>05-02-2026 15:40:20</t>
+          <t>02-02-2026 16:43:50</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>05-02-2026 15:40:02</t>
+          <t>02-02-2026 16:42:42</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26210522108860002579</t>
+          <t>26210522017090002277</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Guillermo  Garcia De Alba Velazquez</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1261,12 +1261,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>340590</t>
+          <t>340290</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18408</t>
+          <t>18108</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1276,17 +1276,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA LAURA </t>
+          <t xml:space="preserve">CHRISTIAN ALEJANDRO </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEZA </t>
+          <t xml:space="preserve">CERVERA </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MUNDO</t>
+          <t>CERVANTES</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1296,32 +1296,32 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6123520177</t>
+          <t>6122289427</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ANDADOR LAS PALMERAS E 615</t>
+          <t>C POSEIDON 666</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>06-07-2003</t>
+          <t>14-11-2011</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>MANALAURA346@GMAIL.COM</t>
+          <t>CHRISTIANCERV777@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>03-02-2026 14:17:27</t>
+          <t>02-02-2026 16:52:38</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1342,17 +1342,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>03-02-2026 14:22:36</t>
+          <t>02-02-2026 16:58:16</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>03-02-2026 14:22:15</t>
+          <t>02-02-2026 16:57:36</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26210522041020002351</t>
+          <t>26210522017700002281</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1396,12 +1396,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>340279</t>
+          <t>340353</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18097</t>
+          <t>18171</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1411,17 +1411,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUZ ANGELICA </t>
+          <t xml:space="preserve">GIBERTO </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOA </t>
+          <t xml:space="preserve">MENDEZ </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">VEGA </t>
+          <t xml:space="preserve">HALE </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6121042102</t>
+          <t>6121528946</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>C MANUEL F MONTAÑO</t>
+          <t>C CERRADA SANTA INES 890</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>20-09-1980</t>
+          <t>23-11-2001</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>LICLOAVEGA20@GMAIL.COM</t>
+          <t>GILBERTO.MEN20011@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-02-2026 16:39:48</t>
+          <t>02-02-2026 18:54:26</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-02-2026 16:43:50</t>
+          <t>02-02-2026 18:58:19</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>02-02-2026 16:42:42</t>
+          <t>02-02-2026 18:58:00</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26210522017090002277</t>
+          <t>26210522021420002304</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1531,12 +1531,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>340290</t>
+          <t>340215</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18108</t>
+          <t>18033</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHRISTIAN ALEJANDRO </t>
+          <t xml:space="preserve">FRANCISCO JAVIER </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">CERVERA </t>
+          <t xml:space="preserve">SANCHEZ </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CERVANTES</t>
+          <t>IZAGUIRRE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6122289427</t>
+          <t>6121370121</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>C POSEIDON 666</t>
+          <t>C ISLA PATO 107</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1581,17 +1581,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>14-11-2011</t>
+          <t>26-03-1977</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CHRISTIANCERV777@GMAIL.COM</t>
+          <t>FRANCISCO.SAN.IZA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-02-2026 16:52:38</t>
+          <t>02-02-2026 15:28:02</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-02-2026 16:58:16</t>
+          <t>02-02-2026 15:40:28</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>02-02-2026 16:57:36</t>
+          <t>02-02-2026 15:39:32</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26210522017700002281</t>
+          <t>26210522014940002273</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1789,24 +1789,24 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>340215</t>
+          <t>339764</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18033</t>
+          <t>17582</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRANCISCO JAVIER </t>
+          <t xml:space="preserve">WILIAM ULISES </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANCHEZ </t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>IZAGUIRRE</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6121370121</t>
+          <t>6691484335</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>C ISLA PATO 107</t>
+          <t xml:space="preserve">C VALTIERRA 324 </t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1851,17 +1851,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>26-03-1977</t>
+          <t>21-09-1990</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>FRANCISCO.SAN.IZA@GMAIL.COM</t>
+          <t>WIL_UCL@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-02-2026 15:28:02</t>
+          <t>01-02-2026 10:17:19</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1882,17 +1882,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>02-02-2026 15:40:28</t>
+          <t>01-02-2026 10:33:00</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>01-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>02-02-2026 15:39:32</t>
+          <t>01-02-2026 10:25:23</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26210522014940002273</t>
+          <t>26210521989080002222</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
@@ -1924,24 +1924,24 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>339764</t>
+          <t>340015</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>17582</t>
+          <t>17833</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1951,17 +1951,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">WILIAM ULISES </t>
+          <t>MARIA FERNANDA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>AVILES</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1971,32 +1971,32 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6691484335</t>
+          <t>6121058570</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">C VALTIERRA 324 </t>
+          <t>CENTRO</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>21-09-1990</t>
+          <t>08-12-1997</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>WIL_UCL@HOTMAIL.COM</t>
+          <t>AVILESSANCHEZFERNANDA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>01-02-2026 10:17:19</t>
+          <t>02-02-2026 10:34:28</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2017,17 +2017,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>01-02-2026 10:33:00</t>
+          <t>03-02-2026 05:22:36</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>01-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>01-02-2026 10:25:23</t>
+          <t>03-02-2026 05:22:05</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2047,10 +2047,14 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26210521989080002222</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr"/>
+          <t>26210522027620002320</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
@@ -2059,12 +2063,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -2186,24 +2190,24 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>340015</t>
+          <t>340286</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>17833</t>
+          <t>18104</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2213,17 +2217,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA</t>
+          <t xml:space="preserve">AMY ANGELINE </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AVILES</t>
+          <t xml:space="preserve">GUZMAN </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t xml:space="preserve">LOA </t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2233,12 +2237,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6121058570</t>
+          <t>6121220630</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CENTRO</t>
+          <t xml:space="preserve">C MANUEL F MONTOYA </t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2248,17 +2252,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>08-12-1997</t>
+          <t>20-01-2010</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>AVILESSANCHEZFERNANDA@GMAIL.COM</t>
+          <t>LICLOAVEGA200@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-02-2026 10:34:28</t>
+          <t>02-02-2026 16:44:59</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2279,17 +2283,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>03-02-2026 05:22:36</t>
+          <t>02-02-2026 16:47:48</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>03-02-2026 05:22:05</t>
+          <t>02-02-2026 16:46:46</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2309,14 +2313,10 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26210522027620002320</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26210522017270002279</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
@@ -2325,24 +2325,24 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>341783</t>
+          <t>340554</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19601</t>
+          <t>18372</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2352,17 +2352,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ERNESTO</t>
+          <t>JANNETT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARZA </t>
+          <t>CALDERON</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>SCHCOLNICK</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2372,32 +2372,32 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8180747965</t>
+          <t>6121042182</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>ENCINO #216</t>
+          <t>CARRETERA AL NORTE KM 11 PRIV. LAS QUINTAS DEL MAR 7</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>27-10-1990</t>
+          <t>22-09-2004</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>DRERNESTOGARZA@GMAIL.COM</t>
+          <t>JANNETT.22099@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>07-02-2026 10:19:47</t>
+          <t>03-02-2026 13:02:59</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2418,17 +2418,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>11-02-2026 15:26:34</t>
+          <t>03-02-2026 13:08:32</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>11-02-2026 15:25:43</t>
+          <t>03-02-2026 13:07:59</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -2448,19 +2448,11 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26210522266420003021</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>VERONICA VIANEY LOYA CONTRERAS</t>
-        </is>
-      </c>
+          <t>26210522039110002341</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
           <t>499</t>
@@ -2468,24 +2460,24 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>341785</t>
+          <t>341797</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19603</t>
+          <t>19615</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2495,17 +2487,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DENIS ALEJANDRA</t>
+          <t>SUSANA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ESTRADA</t>
+          <t>PASALAGUA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SANTACRUZ</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2515,12 +2507,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8120018311</t>
+          <t>6121590135</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>ENCINO # 216</t>
+          <t>PRIV PALO DE SANTA RITA 9</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2530,17 +2522,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>01-09-1985</t>
+          <t>06-02-1966</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>ALESSANALESAN85@GMAIL.COM</t>
+          <t>SIPHITYA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>07-02-2026 10:21:42</t>
+          <t>07-02-2026 10:52:31</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2561,17 +2553,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>11-02-2026 15:32:23</t>
+          <t>07-02-2026 11:37:55</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>07-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>11-02-2026 15:31:50</t>
+          <t>07-02-2026 11:37:04</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2581,7 +2573,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -2591,19 +2583,15 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26210522266660003022</t>
+          <t>26210522160000002733</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>VERONICA VIANEY LOYA CONTRERAS</t>
-        </is>
-      </c>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
           <t>499</t>
@@ -2611,24 +2599,24 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>340286</t>
+          <t>341799</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>18104</t>
+          <t>19617</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2638,17 +2626,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">AMY ANGELINE </t>
+          <t xml:space="preserve">MIGUEL ANGEL </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUZMAN </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOA </t>
+          <t>VICENT</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2658,32 +2646,32 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6121220630</t>
+          <t>6121590416</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">C MANUEL F MONTOYA </t>
+          <t>PRIV PALO DE SANTA RITA 9</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>20-01-2010</t>
+          <t>30-10-1955</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>LICLOAVEGA200@GMAIL.COM</t>
+          <t>MHVICENT@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>02-02-2026 16:44:59</t>
+          <t>07-02-2026 10:56:26</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2694,7 +2682,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2704,17 +2692,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>02-02-2026 16:47:48</t>
+          <t>07-02-2026 11:33:16</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>07-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>02-02-2026 16:46:46</t>
+          <t>07-02-2026 11:32:27</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2734,10 +2722,14 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26210522017270002279</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr"/>
+          <t>26210522159870002732</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
@@ -2746,24 +2738,24 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>341797</t>
+          <t>341136</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19615</t>
+          <t>18954</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2773,17 +2765,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SUSANA</t>
+          <t xml:space="preserve">ROSA ISELA </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PASALAGUA</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2793,12 +2785,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6121590135</t>
+          <t>6121275515</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>PRIV PALO DE SANTA RITA 9</t>
+          <t xml:space="preserve">EL CENTENARIO </t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2808,48 +2800,52 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>06-02-1966</t>
+          <t>16-02-1981</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>SIPHITYA@GMAIL.COM</t>
+          <t>IVAZQUEZ@CIBNOR.MX</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>07-02-2026 10:52:31</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>04-02-2026 18:14:43</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>07-02-2026 11:37:55</t>
+          <t>04-02-2026 18:22:58</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>07-02-2026 11:37:04</t>
+          <t>04-02-2026 18:22:23</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2859,7 +2855,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2869,23 +2865,19 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26210522160000002733</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26210522085210002502</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2897,12 +2889,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>340554</t>
+          <t>341114</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18372</t>
+          <t>18932</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2912,17 +2904,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>JANNETT</t>
+          <t>HANNIA ZULETT GUADALUPE</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CALDERON</t>
+          <t xml:space="preserve">BURGOIN </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SCHCOLNICK</t>
+          <t xml:space="preserve">LUCERO </t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2932,14 +2924,10 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6121042182</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>CARRETERA AL NORTE KM 11 PRIV. LAS QUINTAS DEL MAR 7</t>
-        </is>
-      </c>
+          <t>6121041819</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2947,60 +2935,56 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>22-09-2004</t>
+          <t>01-12-2008</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>JANNETT.22099@GMAIL.COM</t>
+          <t>HANNIAZULETTBURGOIN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>03-02-2026 13:02:59</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>04-02-2026 17:38:34</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>03-02-2026 13:08:32</t>
+          <t>04-02-2026 17:42:38</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>03-02-2026 13:07:59</t>
-        </is>
-      </c>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3008,36 +2992,36 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26210522039110002341</t>
+          <t>26210522083170002489</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>342051</t>
+          <t>341390</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19869</t>
+          <t>19208</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3047,17 +3031,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLAUDIA </t>
+          <t>FERNANDA JETSEL</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AGUAYO</t>
+          <t xml:space="preserve">TAPIZ </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>OJEDA</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3067,12 +3051,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8123512800</t>
+          <t>6121007438</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CENTRO</t>
+          <t xml:space="preserve">SAN FERNANDO </t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3082,52 +3066,48 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>13-11-2002</t>
+          <t>21-10-1985</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLAUDIABEATRIZ.AGUAYO@GMAIL.COM</t>
+          <t>SINDICATO.JEC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>09-02-2026 08:32:35</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>05-02-2026 17:08:31</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>11-02-2026 09:29:24</t>
+          <t>05-02-2026 17:12:39</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>11-02-2026 09:28:31</t>
+          <t>05-02-2026 17:12:22</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3137,7 +3117,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -3147,40 +3127,36 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26210522260760002999</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26210522112170002589</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>341136</t>
+          <t>342051</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>18954</t>
+          <t>19869</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3190,17 +3166,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROSA ISELA </t>
+          <t xml:space="preserve">CLAUDIA </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>AGUAYO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>OJEDA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3210,12 +3186,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6121275515</t>
+          <t>8123512800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">EL CENTENARIO </t>
+          <t>CENTRO</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3225,17 +3201,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>16-02-1981</t>
+          <t>13-11-2002</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>IVAZQUEZ@CIBNOR.MX</t>
+          <t>CLAUDIABEATRIZ.AGUAYO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>04-02-2026 18:14:43</t>
+          <t>09-02-2026 08:32:35</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3260,17 +3236,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>04-02-2026 18:22:58</t>
+          <t>11-02-2026 09:29:24</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>04-02-2026 18:22:23</t>
+          <t>11-02-2026 09:28:31</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3290,10 +3266,14 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26210522085210002502</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr"/>
+          <t>26210522260760002999</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
@@ -3302,24 +3282,24 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>341390</t>
+          <t>342188</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19208</t>
+          <t>20006</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3329,17 +3309,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FERNANDA JETSEL</t>
+          <t>EDNA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">TAPIZ </t>
+          <t>TAMAYO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3349,12 +3329,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6121007438</t>
+          <t>6123489545</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAN FERNANDO </t>
+          <t>PRIV MARINA CENTRAL 117</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3364,17 +3344,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>21-10-1985</t>
+          <t>02-04-1974</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>SINDICATO.JEC@GMAIL.COM</t>
+          <t>EDNA_321@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>05-02-2026 17:08:31</t>
+          <t>09-02-2026 14:43:59</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3395,17 +3375,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>05-02-2026 17:12:39</t>
+          <t>11-02-2026 13:12:45</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>05-02-2026 17:12:22</t>
+          <t>11-02-2026 13:12:26</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3415,7 +3395,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3425,11 +3405,19 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26210522112170002589</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
+          <t>26210522263830003013</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>CRISTINA AYLIN CHAVEZ GONZALEZ</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>499</t>
@@ -3449,12 +3437,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>342188</t>
+          <t>342427</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20006</t>
+          <t>20244</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3464,17 +3452,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EDNA</t>
+          <t xml:space="preserve">NICOLAS </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>TAMAYO</t>
+          <t>PERPULI</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>VERDUGO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3484,75 +3472,67 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6123489545</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>PRIV MARINA CENTRAL 117</t>
-        </is>
-      </c>
+          <t>6121614567</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>02-04-1974</t>
+          <t>06-03-1973</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>EDNA_321@HOTMAIL.COM</t>
+          <t>NICOLASPERPULIVERDUGO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>09-02-2026 14:43:59</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>09-02-2026 19:09:18</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>11-02-2026 13:12:45</t>
+          <t>09-02-2026 19:12:38</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>11-02-2026 13:12:26</t>
-        </is>
-      </c>
+          <t>09-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3560,44 +3540,36 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26210522263830003013</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>CRISTINA AYLIN CHAVEZ GONZALEZ</t>
-        </is>
-      </c>
+          <t>26210522209990002868</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>341799</t>
+          <t>341986</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>19617</t>
+          <t>19804</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3607,17 +3579,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGUEL ANGEL </t>
+          <t>KARLA ELIZABETH</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>BERLANGA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>VICENT</t>
+          <t>CALDERON</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3627,75 +3599,67 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6121590416</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>PRIV PALO DE SANTA RITA 9</t>
-        </is>
-      </c>
+          <t>5577876880</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>30-10-1955</t>
+          <t>22-05-2001</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>MHVICENT@GMAIL.COM</t>
+          <t>BERLANGACALDERONELIZABETH22@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>07-02-2026 10:56:26</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>09-02-2026 04:13:10</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>07-02-2026 11:33:16</t>
+          <t>09-02-2026 04:15:04</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>07-02-2026 11:32:27</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3703,40 +3667,36 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26210522159870002732</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26210522174170002753</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>341114</t>
+          <t>342226</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>18932</t>
+          <t>20044</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3746,17 +3706,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>HANNIA ZULETT GUADALUPE</t>
+          <t>ARIANY ROSALIA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">BURGOIN </t>
+          <t>COTA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCERO </t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3766,10 +3726,14 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6121041819</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>6121692055</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>CALLE EL TRIUNFO #233</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3777,56 +3741,60 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>01-12-2008</t>
+          <t>08-10-1981</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>HANNIAZULETTBURGOIN@GMAIL.COM</t>
+          <t>ARIANY2C@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>04-02-2026 17:38:34</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 15:54:22</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>04-02-2026 17:42:38</t>
+          <t>10-02-2026 17:08:18</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>10-02-2026 17:07:27</t>
+        </is>
+      </c>
       <c r="U25" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr"/>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W25" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3834,36 +3802,44 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26210522083170002489</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
+          <t>26210522238630002941</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>VERONICA VIANEY LOYA CONTRERAS</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>343038</t>
+          <t>332784</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20855</t>
+          <t>14805</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3873,17 +3849,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">DOLORES ITZEL </t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUBILLOS </t>
+          <t>ROBLES</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>ARANDA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3893,32 +3869,32 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6121029534</t>
+          <t>5585803795</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>C PABLO L. GONZALEZ 235</t>
+          <t xml:space="preserve">PUEBLO NUEVO </t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>10-12-1994</t>
+          <t>04-03-1978</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CUBILLOSITZEL@GMAIL.COM</t>
+          <t>ALEJANDRO.ROBLESARANDA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>11-02-2026 16:24:22</t>
+          <t>07-01-2026 09:40:49</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3939,17 +3915,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>11-02-2026 16:38:56</t>
+          <t>03-02-2026 14:14:15</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>11-02-2026 16:38:17</t>
+          <t>03-02-2026 13:57:02</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3959,7 +3935,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -3969,7 +3945,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26210522269110003031</t>
+          <t>26210522040850002349</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
@@ -3981,24 +3957,24 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>342490</t>
+          <t>336694</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20307</t>
+          <t>22420</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4008,17 +3984,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>RENEE ALESSANDRA</t>
+          <t>ZULEMA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">CESEÑA </t>
+          <t>HIGUERA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAVIS </t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4028,10 +4004,14 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6122046111</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>6122380771</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>CENTRO</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4039,56 +4019,60 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>20-02-2007</t>
+          <t>08-04-1983</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>RENEEE777111@GMAIL.COM</t>
+          <t>ZULEMA@BAJASURREALTORS.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>09-02-2026 20:30:27</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>21-01-2026 10:28:18</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO ENERO 12 MESES</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>09-02-2026 20:32:52</t>
+          <t>02-02-2026 09:06:56</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr"/>
+          <t>28-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>28-01-2026 09:24:49</t>
+        </is>
+      </c>
       <c r="U27" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W27" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4096,36 +4080,40 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26210522213810002877</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr"/>
+          <t>26210522002210002243</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>341986</t>
+          <t>342684</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>19804</t>
+          <t>20501</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4135,17 +4123,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>KARLA ELIZABETH</t>
+          <t xml:space="preserve">SANTIAGO </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>BERLANGA</t>
+          <t xml:space="preserve">CUEN </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CALDERON</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4155,28 +4143,28 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>5577876880</t>
+          <t>6122186206</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>22-05-2001</t>
+          <t>06-10-2008</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>BERLANGACALDERONELIZABETH22@GMAIL.COM</t>
+          <t>SANTIAGOCUEN23@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>09-02-2026 04:13:10</t>
+          <t>10-02-2026 15:52:34</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4201,12 +4189,12 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>09-02-2026 04:15:04</t>
+          <t>10-02-2026 15:55:25</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
@@ -4223,7 +4211,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26210522174170002753</t>
+          <t>26210522235410002926</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
@@ -4235,24 +4223,24 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>342520</t>
+          <t>342490</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20337</t>
+          <t>20307</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4262,17 +4250,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO</t>
+          <t>RENEE ALESSANDRA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t xml:space="preserve">CESEÑA </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>LIMOM</t>
+          <t xml:space="preserve">DAVIS </t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4282,75 +4270,67 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6121196214</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>DEL ESTRIBO</t>
-        </is>
-      </c>
+          <t>6122046111</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>03-01-1992</t>
+          <t>20-02-2007</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>LIMON.EDUARDO@HOTMAIL.COM</t>
+          <t>RENEEE777111@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>10-02-2026 06:36:49</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>09-02-2026 20:30:27</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>10-02-2026 06:41:55</t>
+          <t>09-02-2026 20:32:52</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>10-02-2026 06:41:25</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4358,36 +4338,36 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26210522223420002894</t>
+          <t>26210522213810002877</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>342427</t>
+          <t>340590</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20244</t>
+          <t>18408</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4397,17 +4377,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICOLAS </t>
+          <t xml:space="preserve">ANA LAURA </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PERPULI</t>
+          <t xml:space="preserve">MEZA </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>VERDUGO</t>
+          <t>MUNDO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4417,67 +4397,75 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6121614567</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>6123520177</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ANDADOR LAS PALMERAS E 615</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>06-03-1973</t>
+          <t>06-07-2003</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>NICOLASPERPULIVERDUGO@HOTMAIL.COM</t>
+          <t>MANALAURA346@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>09-02-2026 19:09:18</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>03-02-2026 14:17:27</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>09-02-2026 19:12:38</t>
+          <t>03-02-2026 14:22:36</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>09-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr"/>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>03-02-2026 14:22:15</t>
+        </is>
+      </c>
       <c r="U30" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4485,14 +4473,14 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26210522209990002868</t>
+          <t>26210522041020002351</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -4509,12 +4497,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>342226</t>
+          <t>342520</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20044</t>
+          <t>20337</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4524,17 +4512,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ARIANY ROSALIA</t>
+          <t>JOSE EDUARDO</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>COTA</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>LIMOM</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4544,32 +4532,32 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6121692055</t>
+          <t>6121196214</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>CALLE EL TRIUNFO #233</t>
+          <t>DEL ESTRIBO</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>08-10-1981</t>
+          <t>03-01-1992</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>ARIANY2C@HOTMAIL.COM</t>
+          <t>LIMON.EDUARDO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>09-02-2026 15:54:22</t>
+          <t>10-02-2026 06:36:49</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4590,7 +4578,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>10-02-2026 17:08:18</t>
+          <t>10-02-2026 06:41:55</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -4600,7 +4588,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>10-02-2026 17:07:27</t>
+          <t>10-02-2026 06:41:25</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4620,19 +4608,11 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26210522238630002941</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>VERONICA VIANEY LOYA CONTRERAS</t>
-        </is>
-      </c>
+          <t>26210522223420002894</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
           <t>499</t>
@@ -4775,24 +4755,24 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>332784</t>
+          <t>340350</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>14805</t>
+          <t>18168</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4802,17 +4782,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t xml:space="preserve">LUIS MANUEL </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ROBLES</t>
+          <t>CASILLAS</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ARANDA</t>
+          <t>HALE</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4822,12 +4802,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>5585803795</t>
+          <t>6121975782</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">PUEBLO NUEVO </t>
+          <t xml:space="preserve">C GASPAR VELA </t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4837,17 +4817,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>04-03-1978</t>
+          <t>24-08-1999</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>ALEJANDRO.ROBLESARANDA@GMAIL.COM</t>
+          <t>LUISCASILLAS_19@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>07-01-2026 09:40:49</t>
+          <t>02-02-2026 18:42:38</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4868,17 +4848,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>03-02-2026 14:14:15</t>
+          <t>02-02-2026 18:50:43</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>03-02-2026 13:57:02</t>
+          <t>02-02-2026 18:49:33</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4898,7 +4878,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26210522040850002349</t>
+          <t>26210522021200002303</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
@@ -4910,24 +4890,24 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>336694</t>
+          <t>343254</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>22420</t>
+          <t>21071</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4937,17 +4917,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ZULEMA</t>
+          <t>JOUSY ISABELLA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>HIGUERA</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4957,14 +4937,10 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6122380771</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>CENTRO</t>
-        </is>
-      </c>
+          <t>6391613622</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4972,60 +4948,56 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>08-04-1983</t>
+          <t>12-10-2003</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>ZULEMA@BAJASURREALTORS.COM</t>
+          <t>ISABELLAMENDOZAVV@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>21-01-2026 10:28:18</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>12-02-2026 13:36:03</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>PROMO ENERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>02-02-2026 09:06:56</t>
+          <t>12-02-2026 13:37:01</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>28-02-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>28-01-2026 09:24:49</t>
-        </is>
-      </c>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5033,40 +5005,36 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26210522002210002243</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26210522293680003109</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>342684</t>
+          <t>343458</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20501</t>
+          <t>21275</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5076,17 +5044,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANTIAGO </t>
+          <t>EDUARDO ALEXIS</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUEN </t>
+          <t>VEGA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t>VIEYRA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5096,28 +5064,28 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6122186206</t>
+          <t>6121677253</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>06-10-2008</t>
+          <t>08-04-1991</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>SANTIAGOCUEN23@GMAIL.COM</t>
+          <t>EDUARDOVIEYRA06@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>10-02-2026 15:52:34</t>
+          <t>13-02-2026 10:06:29</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -5142,12 +5110,12 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>10-02-2026 15:55:25</t>
+          <t>13-02-2026 10:17:33</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr"/>
@@ -5164,7 +5132,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26210522235410002926</t>
+          <t>26210522318120003186</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
@@ -5188,12 +5156,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>343166</t>
+          <t>343509</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20983</t>
+          <t>21326</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5203,17 +5171,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA</t>
+          <t xml:space="preserve">SANDRA DELMA </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ACEVEDO</t>
+          <t xml:space="preserve">OLIVARES </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>RUVALCABA</t>
+          <t>VIVAR</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5223,12 +5191,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6121068152</t>
+          <t>6121310729</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>C OLMECAS 508</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5238,17 +5206,17 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>13-09-2003</t>
+          <t>16-04-1976</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>FERNANDAACEV13@GMAIL.COM</t>
+          <t>SANDYPRICES.19@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>12-02-2026 07:13:35</t>
+          <t>13-02-2026 15:14:31</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -5259,7 +5227,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -5269,17 +5237,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>12-02-2026 07:18:27</t>
+          <t>13-02-2026 15:17:56</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>12-02-2026 07:17:45</t>
+          <t>13-02-2026 15:17:37</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -5299,7 +5267,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26210522287800003090</t>
+          <t>26210522322300003205</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
@@ -5311,24 +5279,24 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>343254</t>
+          <t>343166</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>21071</t>
+          <t>20983</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5338,17 +5306,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>JOUSY ISABELLA</t>
+          <t>MARIA FERNANDA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>ACEVEDO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>RUVALCABA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5358,10 +5326,14 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6391613622</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>6121068152</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ROMA</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5369,42 +5341,38 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>12-10-2003</t>
+          <t>13-09-2003</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>ISABELLAMENDOZAVV@OUTLOOK.COM</t>
+          <t>FERNANDAACEV13@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>12-02-2026 13:36:03</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>12-02-2026 07:13:35</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>12-02-2026 13:37:01</t>
+          <t>12-02-2026 07:18:27</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -5412,13 +5380,21 @@
           <t>12-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr"/>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>12-02-2026 07:17:45</t>
+        </is>
+      </c>
       <c r="U37" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr"/>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W37" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5426,14 +5402,14 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26210522293680003109</t>
+          <t>26210522287800003090</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -5450,12 +5426,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>342230</t>
+          <t>343508</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20048</t>
+          <t>21325</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5465,17 +5441,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ANA ARACELY</t>
+          <t xml:space="preserve">LUISA FERNANDA </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t xml:space="preserve">MURILLO </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>COTA</t>
+          <t xml:space="preserve">OLIVARES </t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5485,10 +5461,14 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6121372111</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>6122290863</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>C OLMECAS 508</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5496,56 +5476,60 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>08-10-2008</t>
+          <t>19-12-2004</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>ARIANYR2C@HOTMAIL.COM</t>
+          <t>ISAFERNAN.19@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>09-02-2026 15:59:56</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>13-02-2026 15:03:03</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>12-02-2026 16:08:25</t>
+          <t>13-02-2026 15:12:55</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr"/>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>13-02-2026 15:11:55</t>
+        </is>
+      </c>
       <c r="U38" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr"/>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W38" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5553,44 +5537,36 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26210522296870003118</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>VERONICA VIANEY LOYA CONTRERAS</t>
-        </is>
-      </c>
+          <t>26210522322150003203</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>343508</t>
+          <t>344143</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>21325</t>
+          <t>21960</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5600,17 +5576,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUISA FERNANDA </t>
+          <t xml:space="preserve">ISABELLA </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">MURILLO </t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">OLIVARES </t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5620,14 +5596,10 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6122290863</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>C OLMECAS 508</t>
-        </is>
-      </c>
+          <t>6122133549</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5635,60 +5607,56 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>19-12-2004</t>
+          <t>04-06-2010</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>ISAFERNAN.19@GMAIL.COM</t>
+          <t>CASTROISABELLA600@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>13-02-2026 15:03:03</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>16-02-2026 16:04:56</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>13-02-2026 15:12:55</t>
+          <t>18-02-2026 16:06:37</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>13-02-2026 15:11:55</t>
-        </is>
-      </c>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5696,36 +5664,44 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26210522322150003203</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
+          <t>26210522465650003472</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>VERONICA VIANEY LOYA CONTRERAS</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>343458</t>
+          <t>341783</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21275</t>
+          <t>19601</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5735,17 +5711,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>EDUARDO ALEXIS</t>
+          <t>ERNESTO</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>VEGA</t>
+          <t xml:space="preserve">GARZA </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>VIEYRA</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5755,67 +5731,75 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6121677253</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>8180747965</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ENCINO #216</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>08-04-1991</t>
+          <t>27-10-1990</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>EDUARDOVIEYRA06@GMAIL.COM</t>
+          <t>DRERNESTOGARZA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>13-02-2026 10:06:29</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>07-02-2026 10:19:47</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>13-02-2026 10:17:33</t>
+          <t>11-02-2026 15:26:34</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr"/>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>11-02-2026 15:25:43</t>
+        </is>
+      </c>
       <c r="U40" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr"/>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W40" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5823,14 +5807,22 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26210522318120003186</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
+          <t>26210522266420003021</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>VERONICA VIANEY LOYA CONTRERAS</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
@@ -5847,12 +5839,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>343509</t>
+          <t>341785</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>21326</t>
+          <t>19603</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5862,17 +5854,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANDRA DELMA </t>
+          <t>DENIS ALEJANDRA</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">OLIVARES </t>
+          <t>ESTRADA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>VIVAR</t>
+          <t>SANTACRUZ</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5882,12 +5874,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6121310729</t>
+          <t>8120018311</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>C OLMECAS 508</t>
+          <t>ENCINO # 216</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5897,17 +5889,17 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>16-04-1976</t>
+          <t>01-09-1985</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>SANDYPRICES.19@GMAIL.COM</t>
+          <t>ALESSANALESAN85@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>13-02-2026 15:14:31</t>
+          <t>07-02-2026 10:21:42</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5918,7 +5910,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -5928,17 +5920,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>13-02-2026 15:17:56</t>
+          <t>11-02-2026 15:32:23</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>13-02-2026 15:17:37</t>
+          <t>11-02-2026 15:31:50</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -5948,7 +5940,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -5958,11 +5950,19 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26210522322300003205</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr"/>
+          <t>26210522266660003022</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>VERONICA VIANEY LOYA CONTRERAS</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>499</t>
@@ -5970,24 +5970,24 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>340350</t>
+          <t>343754</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>18168</t>
+          <t>21571</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5997,17 +5997,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIS MANUEL </t>
+          <t>ERNESTO</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>CASILLAS</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>HALE</t>
+          <t>ROSALES</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6121975782</t>
+          <t>6241578514</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">C GASPAR VELA </t>
+          <t>PEDRO MATIAS GONI 353</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -6032,17 +6032,17 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>24-08-1999</t>
+          <t>07-11-1978</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>LUISCASILLAS_19@HOTMAIL.COM</t>
+          <t>NETOGR78@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>02-02-2026 18:42:38</t>
+          <t>14-02-2026 18:11:53</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -6063,29 +6063,29 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>02-02-2026 18:50:43</t>
+          <t>14-02-2026 18:11:54</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>02-02-2026 18:49:33</t>
+          <t>14-02-2026 18:11:54</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="W42" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6093,7 +6093,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26210522021200002303</t>
+          <t>26210522349800003253</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
@@ -6117,12 +6117,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>342701</t>
+          <t>344316</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20518</t>
+          <t>22133</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6132,17 +6132,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SUMIKO MARIA</t>
+          <t>MAYTE ANELIZ</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t xml:space="preserve">CUEVAS </t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AGUIRRE</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6121220205</t>
+          <t>6241717643</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -6163,17 +6163,17 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>07-04-2013</t>
+          <t>02-01-2007</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>SUMIJOAGUIRREFISHER@GMAIL.COM</t>
+          <t>ANELIZCG07@GMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>10-02-2026 16:22:22</t>
+          <t>16-02-2026 18:53:41</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>10-02-2026 16:28:08</t>
+          <t>17-02-2026 14:17:50</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T43" t="inlineStr"/>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26210522236680002929</t>
+          <t>26210522429100003408</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
@@ -6232,12 +6232,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -6379,12 +6379,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>343754</t>
+          <t>342230</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>21571</t>
+          <t>20048</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6394,17 +6394,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ERNESTO</t>
+          <t>ANA ARACELY</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ROSALES</t>
+          <t>COTA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6414,75 +6414,67 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6241578514</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>PEDRO MATIAS GONI 353</t>
-        </is>
-      </c>
+          <t>6121372111</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>07-11-1978</t>
+          <t>08-10-2008</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>NETOGR78@GMAIL.COM</t>
+          <t>ARIANYR2C@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>14-02-2026 18:11:53</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>09-02-2026 15:59:56</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>14-02-2026 18:11:54</t>
+          <t>12-02-2026 16:08:25</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>14-02-2026 18:11:54</t>
-        </is>
-      </c>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
           <t>2</t>
         </is>
       </c>
+      <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6490,14 +6482,22 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26210522349800003253</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr"/>
-      <c r="Z45" t="inlineStr"/>
+          <t>26210522296870003118</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>VERONICA VIANEY LOYA CONTRERAS</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
@@ -6641,24 +6641,24 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>343379</t>
+          <t>344366</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21196</t>
+          <t>22183</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6668,17 +6668,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SARA BEATRIZ</t>
+          <t>REYNA ICELA</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASTELLANOS </t>
+          <t>CADENA MATUS</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>CADENA MATUS</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6122327477</t>
+          <t>6121971764</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>C MELON 121</t>
+          <t>REGIDORES 113</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6703,20 +6703,24 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>03-06-1981</t>
+          <t>22-08-1987</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>DRA.SARACASTELLANOS@GMAIL.COM</t>
+          <t>REYNAICELACM@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>12-02-2026 18:54:35</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+          <t>16-02-2026 23:34:26</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O47" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6734,22 +6738,22 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>12-02-2026 18:58:52</t>
+          <t>16-02-2026 23:34:27</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>12-02-2026 18:58:05</t>
+          <t>16-02-2026 23:34:27</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -6764,7 +6768,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26210522303780003149</t>
+          <t>26210522412010003364</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
@@ -6776,24 +6780,24 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>344143</t>
+          <t>345189</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>21960</t>
+          <t>87354</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6803,17 +6807,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISABELLA </t>
+          <t>MARIA ELISA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>ALAMILLA</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6823,10 +6827,14 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6122133549</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>6121717456</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>C MELITOM ALBAÑEZ 45</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6834,56 +6842,64 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>04-06-2010</t>
+          <t>17-12-2012</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CASTROISABELLA600@GMAIL.COM</t>
+          <t>MARIAELISAHERNANDEZ@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>16-02-2026 16:04:56</t>
+          <t>19-02-2026 19:10:37</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>18-02-2026 16:06:37</t>
+          <t>19-02-2026 19:15:52</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr"/>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>19-02-2026 19:15:15</t>
+        </is>
+      </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W48" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6891,22 +6907,14 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26210522465650003472</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>VERONICA VIANEY LOYA CONTRERAS</t>
-        </is>
-      </c>
+          <t>26210522505670003580</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
@@ -6923,12 +6931,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>344316</t>
+          <t>342701</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>22133</t>
+          <t>20518</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6938,17 +6946,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>MAYTE ANELIZ</t>
+          <t>SUMIKO MARIA</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUEVAS </t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>AGUIRRE</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6958,7 +6966,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6241717643</t>
+          <t>6121220205</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6969,17 +6977,17 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>02-01-2007</t>
+          <t>07-04-2013</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>ANELIZCG07@GMAIL.COM</t>
+          <t>SUMIJOAGUIRREFISHER@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>16-02-2026 18:53:41</t>
+          <t>10-02-2026 16:22:22</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -7004,12 +7012,12 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>17-02-2026 14:17:50</t>
+          <t>10-02-2026 16:28:08</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T49" t="inlineStr"/>
@@ -7026,7 +7034,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26210522429100003408</t>
+          <t>26210522236680002929</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
@@ -7038,24 +7046,24 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>344366</t>
+          <t>344935</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>22183</t>
+          <t>22752</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7065,17 +7073,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>REYNA ICELA</t>
+          <t xml:space="preserve">JESUS ANTONIO </t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CADENA MATUS</t>
+          <t>MADRID</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CADENA MATUS</t>
+          <t>GURROLA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7085,79 +7093,67 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6121971764</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>REGIDORES 113</t>
-        </is>
-      </c>
+          <t>6124408280</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>22-08-1987</t>
+          <t>23-04-1999</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>REYNAICELACM@GMAIL.COM</t>
+          <t>JESUSMG230499@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>16-02-2026 23:34:26</t>
+          <t>18-02-2026 19:00:03</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>16-02-2026 23:34:27</t>
+          <t>18-02-2026 19:01:59</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>16-02-2026 23:34:27</t>
-        </is>
-      </c>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7165,19 +7161,19 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26210522412010003364</t>
+          <t>26210522474020003495</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -7189,12 +7185,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>344935</t>
+          <t>345619</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>22752</t>
+          <t>87784</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7204,17 +7200,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">JESUS ANTONIO </t>
+          <t>AZUL</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MADRID</t>
+          <t>DOMINGUEZ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>GURROLA</t>
+          <t>ESCAMILLA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7224,28 +7220,32 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6124408280</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>6121480447</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>CHAMETLA</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>23-04-1999</t>
+          <t>28-01-1977</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>JESUSMG230499@ICLOUD.COM</t>
+          <t>PLAYAZUL28@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>18-02-2026 19:00:03</t>
+          <t>22-02-2026 13:07:59</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7255,36 +7255,44 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>18-02-2026 19:01:59</t>
+          <t>22-02-2026 13:15:30</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr"/>
+          <t>22-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>22-02-2026 13:13:25</t>
+        </is>
+      </c>
       <c r="U51" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7292,14 +7300,14 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26210522474020003495</t>
+          <t>26210522563650003675</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
@@ -7431,12 +7439,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -7570,24 +7578,24 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>344873</t>
+          <t>343038</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>22690</t>
+          <t>20855</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7597,17 +7605,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>KARLA ROXANA</t>
+          <t xml:space="preserve">DOLORES ITZEL </t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MURILLO</t>
+          <t xml:space="preserve">CUBILLOS </t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7617,12 +7625,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>6121532789</t>
+          <t>6121029534</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD</t>
+          <t>C PABLO L. GONZALEZ 235</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -7632,24 +7640,20 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>18-09-1984</t>
+          <t>10-12-1994</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>KMURILLO@UABCS.MX</t>
+          <t>CUBILLOSITZEL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>18-02-2026 16:45:58</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>11-02-2026 16:24:22</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7667,17 +7671,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>18-02-2026 16:49:17</t>
+          <t>11-02-2026 16:38:56</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>18-02-2026 16:48:16</t>
+          <t>11-02-2026 16:38:17</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -7687,7 +7691,7 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -7697,7 +7701,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26210522467350003478</t>
+          <t>26210522269110003031</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr"/>
@@ -7721,12 +7725,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>342527</t>
+          <t>344873</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>20344</t>
+          <t>22690</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7736,17 +7740,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>DIANA</t>
+          <t>KARLA ROXANA</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MADRID</t>
+          <t>MURILLO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>BURQUEZ</t>
+          <t>VALDEZ</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7756,12 +7760,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6242249486</t>
+          <t>6121532789</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>AYENDE #1720</t>
+          <t>UNIVERSIDAD</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7771,20 +7775,24 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>15-05-1995</t>
+          <t>18-09-1984</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>DIANAMB_@HOTMAIL.COM</t>
+          <t>KMURILLO@UABCS.MX</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>10-02-2026 07:13:24</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+          <t>18-02-2026 16:45:58</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O55" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7802,17 +7810,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>10-02-2026 07:22:03</t>
+          <t>18-02-2026 16:49:17</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>10-02-2026 07:20:53</t>
+          <t>18-02-2026 16:48:16</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -7822,7 +7830,7 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
@@ -7832,7 +7840,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26210522224130002896</t>
+          <t>26210522467350003478</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr"/>
@@ -7844,24 +7852,24 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>342920</t>
+          <t>342527</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>20737</t>
+          <t>20344</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7871,17 +7879,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>FERNANDO</t>
+          <t>DIANA</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>MADRID</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>ORNELAS</t>
+          <t>BURQUEZ</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -7891,32 +7899,32 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6121870554</t>
+          <t>6242249486</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>LA CIMA</t>
+          <t>AYENDE #1720</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>16-09-1975</t>
+          <t>15-05-1995</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>FERNANDOCRUZORNELAS@GMAIL.COM</t>
+          <t>DIANAMB_@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>11-02-2026 09:39:30</t>
+          <t>10-02-2026 07:13:24</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -7937,17 +7945,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>11-02-2026 09:45:27</t>
+          <t>10-02-2026 07:22:03</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>11-02-2026 09:45:03</t>
+          <t>10-02-2026 07:20:53</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -7957,7 +7965,7 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
@@ -7967,7 +7975,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26210522260970003000</t>
+          <t>26210522224130002896</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr"/>
@@ -7979,24 +7987,24 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>343251</t>
+          <t>343379</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>21068</t>
+          <t>21196</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8006,17 +8014,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>TAMARA</t>
+          <t>SARA BEATRIZ</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t xml:space="preserve">CASTELLANOS </t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>AGUIÑAGA</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8026,10 +8034,14 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>5541288966</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>6122327477</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>C MELON 121</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -8037,42 +8049,38 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>21-12-2004</t>
+          <t>03-06-1981</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>TAMARA211204@GMAIL.COM</t>
+          <t>DRA.SARACASTELLANOS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>12-02-2026 13:32:17</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>12-02-2026 18:54:35</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>12-02-2026 13:33:36</t>
+          <t>12-02-2026 18:58:52</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -8080,13 +8088,21 @@
           <t>12-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr"/>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>12-02-2026 18:58:05</t>
+        </is>
+      </c>
       <c r="U57" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr"/>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W57" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8094,36 +8110,36 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26210522293540003108</t>
+          <t>26210522303780003149</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>343375</t>
+          <t>343761</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>21192</t>
+          <t>21578</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8133,17 +8149,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIO ALBERTO </t>
+          <t>OSMAR ALEJANDRO</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ROSAS</t>
+          <t xml:space="preserve"> LIERA </t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANRIQUEZ </t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8153,12 +8169,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>6122343338</t>
+          <t>6151559659</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>C MELON 121</t>
+          <t>CENTRO</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -8168,20 +8184,24 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>12-12-1977</t>
+          <t>26-07-2001</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>ROSASCASTELLANOS@GMAIL.COM</t>
+          <t>LIERAGOMEZOSMARALEJANDRO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>12-02-2026 18:48:15</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
+          <t>14-02-2026 23:55:59</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O58" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8199,17 +8219,17 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>12-02-2026 18:53:02</t>
+          <t>20-02-2026 05:36:59</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>20-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>12-02-2026 18:52:16</t>
+          <t>20-02-2026 05:34:42</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -8229,10 +8249,14 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>26210522303620003147</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr"/>
+          <t>26210522509510003598</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr">
         <is>
@@ -8245,6 +8269,812 @@
         </is>
       </c>
       <c r="AC58" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>342920</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>20737</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>FERNANDO</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>CRUZ</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>ORNELAS</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>6121870554</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>LA CIMA</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>16-09-1975</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>FERNANDOCRUZORNELAS@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>11-02-2026 09:39:30</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>11-02-2026 09:45:27</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>11-02-2026 09:45:03</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>26210522260970003000</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>Christian Jahassiel Castro Navarro</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>343251</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>21068</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>TAMARA</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>AGUIÑAGA</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>5541288966</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>21-12-2004</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>TAMARA211204@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>12-02-2026 13:32:17</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>12-02-2026 13:33:36</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>26210522293540003108</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>Juan Pablo Rieke Campoy</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>343375</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>21192</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARIO ALBERTO </t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>ROSAS</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MANRIQUEZ </t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>6122343338</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>C MELON 121</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>12-12-1977</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>ROSASCASTELLANOS@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>12-02-2026 18:48:15</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>12-02-2026 18:53:02</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>12-02-2026 18:52:16</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>26210522303620003147</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>Juan Pablo Rieke Campoy</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>345136</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>87301</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>FRANCISCA CECILIA</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>BARRETO</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>BARRETO</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>6122148757</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>22-11-1987</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>BARRETOCECILIA925@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>19-02-2026 17:04:50</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>19-02-2026 17:05:35</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>26210522500360003555</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>344727</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>22544</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>MARIA TERESA</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>PEREZ</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>QUEZADA</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>5578843819</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>CENTRO</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>31-05-1969</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>MARIATERESAPEREZQUEZADA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>18-02-2026 05:24:32</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>19-02-2026 06:46:30</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>19-02-2026 06:44:39</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>26210522487370003516</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>345078</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>87243</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANA VICTORIA </t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BARRANCO </t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CASTRO </t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>6123489475</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>C MAGUEY 4551</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>08-02-1994</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>ANACSTRO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>19-02-2026 14:27:10</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>19-02-2026 14:32:01</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>19-02-2026 14:31:19</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>26210522495380003538</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__PASEO LA PAZ.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__PASEO LA PAZ.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC64"/>
+  <dimension ref="A1:AC66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>305773</t>
+          <t>169108</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3272</t>
+          <t>66627</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>IRVIN EMMANUEL</t>
+          <t>CARLOS RENE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>OSUNA</t>
+          <t>MURILLO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6121593169</t>
+          <t>6121170620</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>EMILIANO ZAPATA 2230 D7</t>
+          <t>MISIONES</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -628,17 +628,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>08-01-1989</t>
+          <t>14-11-1996</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>ARKOSUNA@GMAIL.COM</t>
+          <t>CARLOS.MURILLOD96@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>24-07-2025 09:59:08</t>
+          <t>08-05-2023 21:44:32</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -659,17 +659,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>11-02-2026 17:45:12</t>
+          <t>02-02-2026 07:55:34</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>11-02-2026 17:44:35</t>
+          <t>02-02-2026 07:54:27</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -689,19 +689,11 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26210522272210003049</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>CRISTINA AYLIN CHAVEZ GONZALEZ</t>
-        </is>
-      </c>
+          <t>26210522000210002239</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
           <t>499</t>
@@ -709,7 +701,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Cristopher Armando Serrato</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -721,12 +713,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>169108</t>
+          <t>305773</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>66627</t>
+          <t>3272</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -736,17 +728,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CARLOS RENE</t>
+          <t>IRVIN EMMANUEL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MURILLO</t>
+          <t>OSUNA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -756,12 +748,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6121170620</t>
+          <t>6121593169</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MISIONES</t>
+          <t>EMILIANO ZAPATA 2230 D7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -771,17 +763,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>14-11-1996</t>
+          <t>08-01-1989</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CARLOS.MURILLOD96@GMAIL.COM</t>
+          <t>ARKOSUNA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>08-05-2023 21:44:32</t>
+          <t>24-07-2025 09:59:08</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -802,17 +794,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-02-2026 07:55:34</t>
+          <t>11-02-2026 17:45:12</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>02-02-2026 07:54:27</t>
+          <t>11-02-2026 17:44:35</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -822,7 +814,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -832,11 +824,19 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26210522000210002239</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
+          <t>26210522272210003049</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>CRISTINA AYLIN CHAVEZ GONZALEZ</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>499</t>
@@ -844,7 +844,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Cristopher Armando Serrato</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -991,12 +991,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>322857</t>
+          <t>340279</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19796</t>
+          <t>18097</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1006,17 +1006,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NAYELI</t>
+          <t xml:space="preserve">LUZ ANGELICA </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MARILES</t>
+          <t xml:space="preserve">LOA </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CORDERO</t>
+          <t xml:space="preserve">VEGA </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6122343921</t>
+          <t>6121042102</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>PISTACHE 144</t>
+          <t>C MANUEL F MONTAÑO</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1041,17 +1041,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>23-12-1992</t>
+          <t>20-09-1980</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>NAYUNOCHO@GMAIL.COM</t>
+          <t>LICLOAVEGA20@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>10-11-2025 12:13:22</t>
+          <t>02-02-2026 16:39:48</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1072,17 +1072,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>05-02-2026 15:40:20</t>
+          <t>02-02-2026 16:43:50</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>05-02-2026 15:40:02</t>
+          <t>02-02-2026 16:42:42</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26210522108860002579</t>
+          <t>26210522017090002277</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Guillermo  Garcia De Alba Velazquez</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1126,12 +1126,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>340279</t>
+          <t>340290</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18097</t>
+          <t>18108</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1141,17 +1141,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUZ ANGELICA </t>
+          <t xml:space="preserve">CHRISTIAN ALEJANDRO </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOA </t>
+          <t xml:space="preserve">CERVERA </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">VEGA </t>
+          <t>CERVANTES</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6121042102</t>
+          <t>6122289427</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>C MANUEL F MONTAÑO</t>
+          <t>C POSEIDON 666</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>20-09-1980</t>
+          <t>14-11-2011</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>LICLOAVEGA20@GMAIL.COM</t>
+          <t>CHRISTIANCERV777@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-02-2026 16:39:48</t>
+          <t>02-02-2026 16:52:38</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-02-2026 16:43:50</t>
+          <t>02-02-2026 16:58:16</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>02-02-2026 16:42:42</t>
+          <t>02-02-2026 16:57:36</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26210522017090002277</t>
+          <t>26210522017700002281</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1261,12 +1261,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>340290</t>
+          <t>322857</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18108</t>
+          <t>19796</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1276,17 +1276,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHRISTIAN ALEJANDRO </t>
+          <t>NAYELI</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CERVERA </t>
+          <t>MARILES</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CERVANTES</t>
+          <t>CORDERO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1296,32 +1296,32 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6122289427</t>
+          <t>6122343921</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>C POSEIDON 666</t>
+          <t>PISTACHE 144</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>14-11-2011</t>
+          <t>23-12-1992</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CHRISTIANCERV777@GMAIL.COM</t>
+          <t>NAYUNOCHO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-02-2026 16:52:38</t>
+          <t>10-11-2025 12:13:22</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1342,17 +1342,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-02-2026 16:58:16</t>
+          <t>05-02-2026 15:40:20</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>02-02-2026 16:57:36</t>
+          <t>05-02-2026 15:40:02</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26210522017700002281</t>
+          <t>26210522108860002579</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>Guillermo  Garcia De Alba Velazquez</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1531,12 +1531,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>340215</t>
+          <t>339764</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18033</t>
+          <t>17582</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRANCISCO JAVIER </t>
+          <t xml:space="preserve">WILIAM ULISES </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANCHEZ </t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>IZAGUIRRE</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6121370121</t>
+          <t>6691484335</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>C ISLA PATO 107</t>
+          <t xml:space="preserve">C VALTIERRA 324 </t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1581,17 +1581,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>26-03-1977</t>
+          <t>21-09-1990</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>FRANCISCO.SAN.IZA@GMAIL.COM</t>
+          <t>WIL_UCL@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-02-2026 15:28:02</t>
+          <t>01-02-2026 10:17:19</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1612,17 +1612,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-02-2026 15:40:28</t>
+          <t>01-02-2026 10:33:00</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>01-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>02-02-2026 15:39:32</t>
+          <t>01-02-2026 10:25:23</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26210522014940002273</t>
+          <t>26210521989080002222</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1666,12 +1666,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>339939</t>
+          <t>340215</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>17757</t>
+          <t>18033</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1681,17 +1681,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>GABRIELA</t>
+          <t xml:space="preserve">FRANCISCO JAVIER </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t xml:space="preserve">SANCHEZ </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>OVALLE</t>
+          <t>IZAGUIRRE</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1701,32 +1701,32 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6121390387</t>
+          <t>6121370121</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CERRO</t>
+          <t>C ISLA PATO 107</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>17-10-1997</t>
+          <t>26-03-1977</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>OVALLEGABRIELA97@GMAIL.COM</t>
+          <t>FRANCISCO.SAN.IZA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-02-2026 09:09:56</t>
+          <t>02-02-2026 15:28:02</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-02-2026 09:17:23</t>
+          <t>02-02-2026 15:40:28</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>02-02-2026 09:16:38</t>
+          <t>02-02-2026 15:39:32</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26210522002720002245</t>
+          <t>26210522014940002273</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1801,12 +1801,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>339764</t>
+          <t>339939</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>17582</t>
+          <t>17757</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">WILIAM ULISES </t>
+          <t>GABRIELA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>OVALLE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1836,32 +1836,32 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6691484335</t>
+          <t>6121390387</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">C VALTIERRA 324 </t>
+          <t>CERRO</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>21-09-1990</t>
+          <t>17-10-1997</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>WIL_UCL@HOTMAIL.COM</t>
+          <t>OVALLEGABRIELA97@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>01-02-2026 10:17:19</t>
+          <t>02-02-2026 09:09:56</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1882,17 +1882,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>01-02-2026 10:33:00</t>
+          <t>02-02-2026 09:17:23</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>01-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>01-02-2026 10:25:23</t>
+          <t>02-02-2026 09:16:38</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26210521989080002222</t>
+          <t>26210522002720002245</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
@@ -1936,12 +1936,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>340015</t>
+          <t>341119</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>17833</t>
+          <t>18937</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1951,17 +1951,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA</t>
+          <t xml:space="preserve">HANNIA MARIA </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AVILES</t>
+          <t xml:space="preserve">CASTRO </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1971,14 +1971,10 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6121058570</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>CENTRO</t>
-        </is>
-      </c>
+          <t>6121543278</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1986,38 +1982,42 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>08-12-1997</t>
+          <t>25-01-2008</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>AVILESSANCHEZFERNANDA@GMAIL.COM</t>
+          <t>HANNIATAY13@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>02-02-2026 10:34:28</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>04-02-2026 17:46:50</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>03-02-2026 05:22:36</t>
+          <t>04-02-2026 17:47:55</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2025,21 +2025,13 @@
           <t>04-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>03-02-2026 05:22:05</t>
-        </is>
-      </c>
+      <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2047,23 +2039,19 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26210522027620002320</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26210522083460002490</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2075,12 +2063,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>341119</t>
+          <t>340015</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>18937</t>
+          <t>17833</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2090,17 +2078,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">HANNIA MARIA </t>
+          <t>MARIA FERNANDA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASTRO </t>
+          <t>AVILES</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2110,10 +2098,14 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6121543278</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>6121058570</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>CENTRO</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2121,42 +2113,38 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>25-01-2008</t>
+          <t>08-12-1997</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>HANNIATAY13@ICLOUD.COM</t>
+          <t>AVILESSANCHEZFERNANDA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>04-02-2026 17:46:50</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>02-02-2026 10:34:28</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>04-02-2026 17:47:55</t>
+          <t>03-02-2026 05:22:36</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -2164,13 +2152,21 @@
           <t>04-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>03-02-2026 05:22:05</t>
+        </is>
+      </c>
       <c r="U13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W13" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2178,19 +2174,23 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26210522083460002490</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr"/>
+          <t>26210522027620002320</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2472,12 +2472,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>341797</t>
+          <t>342188</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19615</t>
+          <t>20006</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2487,17 +2487,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SUSANA</t>
+          <t>EDNA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PASALAGUA</t>
+          <t>TAMAYO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6121590135</t>
+          <t>6123489545</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>PRIV PALO DE SANTA RITA 9</t>
+          <t>PRIV MARINA CENTRAL 117</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2522,17 +2522,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>06-02-1966</t>
+          <t>02-04-1974</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>SIPHITYA@GMAIL.COM</t>
+          <t>EDNA_321@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>07-02-2026 10:52:31</t>
+          <t>09-02-2026 14:43:59</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2553,17 +2553,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>07-02-2026 11:37:55</t>
+          <t>11-02-2026 13:12:45</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>07-02-2026 11:37:04</t>
+          <t>11-02-2026 13:12:26</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -2583,15 +2583,19 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26210522160000002733</t>
+          <t>26210522263830003013</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>CRISTINA AYLIN CHAVEZ GONZALEZ</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>499</t>
@@ -2611,12 +2615,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>341799</t>
+          <t>341114</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>19617</t>
+          <t>18932</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2626,17 +2630,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGUEL ANGEL </t>
+          <t>HANNIA ZULETT GUADALUPE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t xml:space="preserve">BURGOIN </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>VICENT</t>
+          <t xml:space="preserve">LUCERO </t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2646,75 +2650,67 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6121590416</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>PRIV PALO DE SANTA RITA 9</t>
-        </is>
-      </c>
+          <t>6121041819</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>30-10-1955</t>
+          <t>01-12-2008</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>MHVICENT@GMAIL.COM</t>
+          <t>HANNIAZULETTBURGOIN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>07-02-2026 10:56:26</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>04-02-2026 17:38:34</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>07-02-2026 11:33:16</t>
+          <t>04-02-2026 17:42:38</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>07-02-2026 11:32:27</t>
-        </is>
-      </c>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2722,23 +2718,19 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26210522159870002732</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26210522083170002489</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2750,12 +2742,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>341136</t>
+          <t>341797</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>18954</t>
+          <t>19615</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2765,17 +2757,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROSA ISELA </t>
+          <t>SUSANA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>PASALAGUA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2785,12 +2777,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6121275515</t>
+          <t>6121590135</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">EL CENTENARIO </t>
+          <t>PRIV PALO DE SANTA RITA 9</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2800,52 +2792,48 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>16-02-1981</t>
+          <t>06-02-1966</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>IVAZQUEZ@CIBNOR.MX</t>
+          <t>SIPHITYA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>04-02-2026 18:14:43</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>07-02-2026 10:52:31</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>04-02-2026 18:22:58</t>
+          <t>07-02-2026 11:37:55</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>07-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>04-02-2026 18:22:23</t>
+          <t>07-02-2026 11:37:04</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2855,7 +2843,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2865,19 +2853,23 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26210522085210002502</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr"/>
+          <t>26210522160000002733</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2889,12 +2881,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>341114</t>
+          <t>341799</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18932</t>
+          <t>19617</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2904,17 +2896,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HANNIA ZULETT GUADALUPE</t>
+          <t xml:space="preserve">MIGUEL ANGEL </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">BURGOIN </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCERO </t>
+          <t>VICENT</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2924,67 +2916,75 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6121041819</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>6121590416</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>PRIV PALO DE SANTA RITA 9</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>01-12-2008</t>
+          <t>30-10-1955</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>HANNIAZULETTBURGOIN@GMAIL.COM</t>
+          <t>MHVICENT@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>04-02-2026 17:38:34</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>07-02-2026 10:56:26</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>04-02-2026 17:42:38</t>
+          <t>07-02-2026 11:33:16</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr"/>
+          <t>07-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>07-02-2026 11:32:27</t>
+        </is>
+      </c>
       <c r="U19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W19" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2992,19 +2992,23 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26210522083170002489</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr"/>
+          <t>26210522159870002732</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3016,12 +3020,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>341390</t>
+          <t>341136</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19208</t>
+          <t>18954</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3031,17 +3035,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FERNANDA JETSEL</t>
+          <t xml:space="preserve">ROSA ISELA </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">TAPIZ </t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3051,12 +3055,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6121007438</t>
+          <t>6121275515</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAN FERNANDO </t>
+          <t xml:space="preserve">EL CENTENARIO </t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3066,48 +3070,52 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>21-10-1985</t>
+          <t>16-02-1981</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>SINDICATO.JEC@GMAIL.COM</t>
+          <t>IVAZQUEZ@CIBNOR.MX</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>05-02-2026 17:08:31</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>04-02-2026 18:14:43</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>05-02-2026 17:12:39</t>
+          <t>04-02-2026 18:22:58</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>05-02-2026 17:12:22</t>
+          <t>04-02-2026 18:22:23</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3117,7 +3125,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -3127,14 +3135,14 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26210522112170002589</t>
+          <t>26210522085210002502</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -3294,12 +3302,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>342188</t>
+          <t>341390</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20006</t>
+          <t>19208</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3309,17 +3317,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EDNA</t>
+          <t>FERNANDA JETSEL</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>TAMAYO</t>
+          <t xml:space="preserve">TAPIZ </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3329,12 +3337,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6123489545</t>
+          <t>6121007438</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>PRIV MARINA CENTRAL 117</t>
+          <t xml:space="preserve">SAN FERNANDO </t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3344,17 +3352,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>02-04-1974</t>
+          <t>21-10-1985</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>EDNA_321@HOTMAIL.COM</t>
+          <t>SINDICATO.JEC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>09-02-2026 14:43:59</t>
+          <t>05-02-2026 17:08:31</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3375,17 +3383,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>11-02-2026 13:12:45</t>
+          <t>05-02-2026 17:12:39</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>11-02-2026 13:12:26</t>
+          <t>05-02-2026 17:12:22</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3395,7 +3403,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3405,19 +3413,11 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26210522263830003013</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>CRISTINA AYLIN CHAVEZ GONZALEZ</t>
-        </is>
-      </c>
+          <t>26210522112170002589</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
           <t>499</t>
@@ -3425,24 +3425,24 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>342427</t>
+          <t>342520</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20244</t>
+          <t>20337</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3452,17 +3452,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICOLAS </t>
+          <t>JOSE EDUARDO</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PERPULI</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>VERDUGO</t>
+          <t>LIMOM</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3472,10 +3472,14 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6121614567</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>6121196214</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>DEL ESTRIBO</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3483,56 +3487,60 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>06-03-1973</t>
+          <t>03-01-1992</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>NICOLASPERPULIVERDUGO@HOTMAIL.COM</t>
+          <t>LIMON.EDUARDO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>09-02-2026 19:09:18</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 06:36:49</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>09-02-2026 19:12:38</t>
+          <t>10-02-2026 06:41:55</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>09-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>10-02-2026 06:41:25</t>
+        </is>
+      </c>
       <c r="U23" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3540,19 +3548,19 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26210522209990002868</t>
+          <t>26210522223420002894</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Cristopher Armando Serrato</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3564,12 +3572,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>341986</t>
+          <t>342427</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>19804</t>
+          <t>20244</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3579,17 +3587,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>KARLA ELIZABETH</t>
+          <t xml:space="preserve">NICOLAS </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>BERLANGA</t>
+          <t>PERPULI</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CALDERON</t>
+          <t>VERDUGO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3599,28 +3607,28 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>5577876880</t>
+          <t>6121614567</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>22-05-2001</t>
+          <t>06-03-1973</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>BERLANGACALDERONELIZABETH22@GMAIL.COM</t>
+          <t>NICOLASPERPULIVERDUGO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>09-02-2026 04:13:10</t>
+          <t>09-02-2026 19:09:18</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3635,28 +3643,28 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>09-02-2026 04:15:04</t>
+          <t>09-02-2026 19:12:38</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>09-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V24" t="inlineStr"/>
@@ -3667,36 +3675,36 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26210522174170002753</t>
+          <t>26210522209990002868</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>342226</t>
+          <t>341986</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20044</t>
+          <t>19804</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3706,17 +3714,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ARIANY ROSALIA</t>
+          <t>KARLA ELIZABETH</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>COTA</t>
+          <t>BERLANGA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>CALDERON</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3726,14 +3734,10 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6121692055</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>CALLE EL TRIUNFO #233</t>
-        </is>
-      </c>
+          <t>5577876880</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3741,60 +3745,56 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>08-10-1981</t>
+          <t>22-05-2001</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>ARIANY2C@HOTMAIL.COM</t>
+          <t>BERLANGACALDERONELIZABETH22@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>09-02-2026 15:54:22</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>09-02-2026 04:13:10</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>10-02-2026 17:08:18</t>
+          <t>09-02-2026 04:15:04</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>10-02-2026 17:07:27</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3802,32 +3802,24 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26210522238630002941</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>VERONICA VIANEY LOYA CONTRERAS</t>
-        </is>
-      </c>
+          <t>26210522174170002753</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -4108,12 +4100,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>342684</t>
+          <t>342226</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20501</t>
+          <t>20044</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4123,17 +4115,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANTIAGO </t>
+          <t>ARIANY ROSALIA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUEN </t>
+          <t>COTA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4143,53 +4135,53 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6122186206</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>6121692055</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>CALLE EL TRIUNFO #233</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>06-10-2008</t>
+          <t>08-10-1981</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>SANTIAGOCUEN23@GMAIL.COM</t>
+          <t>ARIANY2C@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>10-02-2026 15:52:34</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 15:54:22</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>10-02-2026 15:55:25</t>
+          <t>10-02-2026 17:08:18</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -4197,13 +4189,21 @@
           <t>10-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr"/>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>10-02-2026 17:07:27</t>
+        </is>
+      </c>
       <c r="U28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr"/>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W28" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4211,14 +4211,22 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26210522235410002926</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
+          <t>26210522238630002941</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>VERONICA VIANEY LOYA CONTRERAS</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -4235,12 +4243,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>342490</t>
+          <t>342684</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20307</t>
+          <t>20501</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4250,17 +4258,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>RENEE ALESSANDRA</t>
+          <t xml:space="preserve">SANTIAGO </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">CESEÑA </t>
+          <t xml:space="preserve">CUEN </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAVIS </t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4270,28 +4278,28 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6122046111</t>
+          <t>6122186206</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>20-02-2007</t>
+          <t>06-10-2008</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>RENEEE777111@GMAIL.COM</t>
+          <t>SANTIAGOCUEN23@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>09-02-2026 20:30:27</t>
+          <t>10-02-2026 15:52:34</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4306,22 +4314,22 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>09-02-2026 20:32:52</t>
+          <t>10-02-2026 15:55:25</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
@@ -4338,14 +4346,14 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26210522213810002877</t>
+          <t>26210522235410002926</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -4362,12 +4370,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>340590</t>
+          <t>342490</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>18408</t>
+          <t>20307</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4377,17 +4385,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA LAURA </t>
+          <t>RENEE ALESSANDRA</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEZA </t>
+          <t xml:space="preserve">CESEÑA </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MUNDO</t>
+          <t xml:space="preserve">DAVIS </t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4397,14 +4405,10 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6123520177</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>ANDADOR LAS PALMERAS E 615</t>
-        </is>
-      </c>
+          <t>6122046111</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4412,60 +4416,56 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>06-07-2003</t>
+          <t>20-02-2007</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>MANALAURA346@GMAIL.COM</t>
+          <t>RENEEE777111@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>03-02-2026 14:17:27</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+          <t>09-02-2026 20:30:27</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>03-02-2026 14:22:36</t>
+          <t>09-02-2026 20:32:52</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>03-02-2026 14:22:15</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4473,14 +4473,14 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26210522041020002351</t>
+          <t>26210522213810002877</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -4497,12 +4497,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>342520</t>
+          <t>340590</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20337</t>
+          <t>18408</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4512,17 +4512,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO</t>
+          <t xml:space="preserve">ANA LAURA </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t xml:space="preserve">MEZA </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>LIMOM</t>
+          <t>MUNDO</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4532,32 +4532,32 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6121196214</t>
+          <t>6123520177</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>DEL ESTRIBO</t>
+          <t>ANDADOR LAS PALMERAS E 615</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>03-01-1992</t>
+          <t>06-07-2003</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>LIMON.EDUARDO@HOTMAIL.COM</t>
+          <t>MANALAURA346@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>10-02-2026 06:36:49</t>
+          <t>03-02-2026 14:17:27</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4578,17 +4578,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>10-02-2026 06:41:55</t>
+          <t>03-02-2026 14:22:36</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>10-02-2026 06:41:25</t>
+          <t>03-02-2026 14:22:15</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26210522223420002894</t>
+          <t>26210522041020002351</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
@@ -4620,24 +4620,24 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>342302</t>
+          <t>343254</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20120</t>
+          <t>21071</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4647,17 +4647,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">MELANIE </t>
+          <t>JOUSY ISABELLA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ALBAÑEZ</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4667,14 +4667,10 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6643640599</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>AGUA DULCE 618</t>
-        </is>
-      </c>
+          <t>6391613622</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4682,60 +4678,56 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>01-05-1980</t>
+          <t>12-10-2003</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>ANIEALRO2020@GMAIL.COM</t>
+          <t>ISABELLAMENDOZAVV@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>09-02-2026 17:06:10</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>12-02-2026 13:36:03</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>09-02-2026 17:08:49</t>
+          <t>12-02-2026 13:37:01</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>09-02-2026 17:08:25</t>
-        </is>
-      </c>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4743,19 +4735,19 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26210522200900002835</t>
+          <t>26210522293680003109</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Cristopher Armando Serrato</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4767,12 +4759,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>340350</t>
+          <t>343458</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>18168</t>
+          <t>21275</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4782,17 +4774,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIS MANUEL </t>
+          <t>EDUARDO ALEXIS</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CASILLAS</t>
+          <t>VEGA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>HALE</t>
+          <t>VIEYRA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4802,75 +4794,67 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6121975782</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C GASPAR VELA </t>
-        </is>
-      </c>
+          <t>6121677253</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>24-08-1999</t>
+          <t>08-04-1991</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>LUISCASILLAS_19@HOTMAIL.COM</t>
+          <t>EDUARDOVIEYRA06@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>02-02-2026 18:42:38</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>13-02-2026 10:06:29</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>02-02-2026 18:50:43</t>
+          <t>13-02-2026 10:17:33</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>02-02-2026 18:49:33</t>
-        </is>
-      </c>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4878,14 +4862,14 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26210522021200002303</t>
+          <t>26210522318120003186</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -4902,12 +4886,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>343254</t>
+          <t>343509</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21071</t>
+          <t>21326</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4917,17 +4901,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>JOUSY ISABELLA</t>
+          <t xml:space="preserve">SANDRA DELMA </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t xml:space="preserve">OLIVARES </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>VIVAR</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4937,10 +4921,14 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6391613622</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>6121310729</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>C OLMECAS 508</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4948,56 +4936,60 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>12-10-2003</t>
+          <t>16-04-1976</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>ISABELLAMENDOZAVV@OUTLOOK.COM</t>
+          <t>SANDYPRICES.19@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>12-02-2026 13:36:03</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>13-02-2026 15:14:31</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>12-02-2026 13:37:01</t>
+          <t>13-02-2026 15:17:56</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr"/>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>13-02-2026 15:17:37</t>
+        </is>
+      </c>
       <c r="U34" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr"/>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W34" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5005,36 +4997,36 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26210522293680003109</t>
+          <t>26210522322300003205</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>343458</t>
+          <t>342302</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21275</t>
+          <t>20120</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5044,17 +5036,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>EDUARDO ALEXIS</t>
+          <t xml:space="preserve">MELANIE </t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>VEGA</t>
+          <t>ALBAÑEZ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>VIEYRA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5064,10 +5056,14 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6121677253</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>6643640599</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>AGUA DULCE 618</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5075,56 +5071,60 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>08-04-1991</t>
+          <t>01-05-1980</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>EDUARDOVIEYRA06@GMAIL.COM</t>
+          <t>ANIEALRO2020@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>13-02-2026 10:06:29</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 17:06:10</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>13-02-2026 10:17:33</t>
+          <t>09-02-2026 17:08:49</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>09-02-2026 17:08:25</t>
+        </is>
+      </c>
       <c r="U35" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr"/>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W35" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5132,14 +5132,14 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26210522318120003186</t>
+          <t>26210522200900002835</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -5156,12 +5156,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>343509</t>
+          <t>340350</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21326</t>
+          <t>18168</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5171,17 +5171,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANDRA DELMA </t>
+          <t xml:space="preserve">LUIS MANUEL </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">OLIVARES </t>
+          <t>CASILLAS</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>VIVAR</t>
+          <t>HALE</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6121310729</t>
+          <t>6121975782</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>C OLMECAS 508</t>
+          <t xml:space="preserve">C GASPAR VELA </t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>16-04-1976</t>
+          <t>24-08-1999</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>SANDYPRICES.19@GMAIL.COM</t>
+          <t>LUISCASILLAS_19@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>13-02-2026 15:14:31</t>
+          <t>02-02-2026 18:42:38</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -5237,17 +5237,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>13-02-2026 15:17:56</t>
+          <t>02-02-2026 18:50:43</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>13-02-2026 15:17:37</t>
+          <t>02-02-2026 18:49:33</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26210522322300003205</t>
+          <t>26210522021200002303</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
@@ -5414,12 +5414,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Cristopher Armando Serrato</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -5561,12 +5561,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>344143</t>
+          <t>343754</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>21960</t>
+          <t>21571</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5576,17 +5576,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISABELLA </t>
+          <t>ERNESTO</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>ROSALES</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5596,67 +5596,75 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6122133549</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>6241578514</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>PEDRO MATIAS GONI 353</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>04-06-2010</t>
+          <t>07-11-1978</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CASTROISABELLA600@GMAIL.COM</t>
+          <t>NETOGR78@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>16-02-2026 16:04:56</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>14-02-2026 18:11:53</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>18-02-2026 16:06:37</t>
+          <t>14-02-2026 18:11:54</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr"/>
+          <t>14-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>14-02-2026 18:11:54</t>
+        </is>
+      </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W39" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5664,22 +5672,14 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26210522465650003472</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>VERONICA VIANEY LOYA CONTRERAS</t>
-        </is>
-      </c>
+          <t>26210522349800003253</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -5982,12 +5982,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>343754</t>
+          <t>344965</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>21571</t>
+          <t>22782</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5997,17 +5997,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ERNESTO</t>
+          <t xml:space="preserve">JOSE LUIS </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t>SERRANO</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ROSALES</t>
+          <t>TELLEZ</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6241578514</t>
+          <t>6241750961</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>PEDRO MATIAS GONI 353</t>
+          <t>C HORBLENDA 918</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -6032,20 +6032,24 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>07-11-1978</t>
+          <t>31-03-1997</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>NETOGR78@GMAIL.COM</t>
+          <t>IAJOSELUIS@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>14-02-2026 18:11:53</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+          <t>18-02-2026 20:42:50</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O42" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6063,22 +6067,22 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>14-02-2026 18:11:54</t>
+          <t>18-02-2026 20:49:56</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>14-02-2026 18:11:54</t>
+          <t>18-02-2026 20:48:57</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -6093,7 +6097,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26210522349800003253</t>
+          <t>26210522477060003507</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
@@ -6117,12 +6121,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>344316</t>
+          <t>345189</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>22133</t>
+          <t>87354</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6132,17 +6136,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>MAYTE ANELIZ</t>
+          <t>MARIA ELISA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUEVAS </t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>ALAMILLA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6152,10 +6156,14 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6241717643</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>6121717456</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>C MELITOM ALBAÑEZ 45</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6163,56 +6171,64 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>02-01-2007</t>
+          <t>17-12-2012</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>ANELIZCG07@GMAIL.COM</t>
+          <t>MARIAELISAHERNANDEZ@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>16-02-2026 18:53:41</t>
+          <t>19-02-2026 19:10:37</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>17-02-2026 14:17:50</t>
+          <t>19-02-2026 19:15:52</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr"/>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>19-02-2026 19:15:15</t>
+        </is>
+      </c>
       <c r="U43" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr"/>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W43" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6220,24 +6236,24 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26210522429100003408</t>
+          <t>26210522505670003580</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -6379,12 +6395,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>342230</t>
+          <t>344143</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20048</t>
+          <t>21960</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6394,17 +6410,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ANA ARACELY</t>
+          <t xml:space="preserve">ISABELLA </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>COTA</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6414,7 +6430,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6121372111</t>
+          <t>6122133549</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -6425,17 +6441,17 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>08-10-2008</t>
+          <t>04-06-2010</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>ARIANYR2C@HOTMAIL.COM</t>
+          <t>CASTROISABELLA600@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>09-02-2026 15:59:56</t>
+          <t>16-02-2026 16:04:56</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -6460,18 +6476,18 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>12-02-2026 16:08:25</t>
+          <t>18-02-2026 16:06:37</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V45" t="inlineStr"/>
@@ -6482,7 +6498,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26210522296870003118</t>
+          <t>26210522465650003472</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -6514,12 +6530,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>344965</t>
+          <t>344316</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>22782</t>
+          <t>22133</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6529,17 +6545,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE LUIS </t>
+          <t>MAYTE ANELIZ</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SERRANO</t>
+          <t xml:space="preserve">CUEVAS </t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>TELLEZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6549,79 +6565,67 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6241750961</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>C HORBLENDA 918</t>
-        </is>
-      </c>
+          <t>6241717643</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>31-03-1997</t>
+          <t>02-01-2007</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>IAJOSELUIS@OUTLOOK.COM</t>
+          <t>ANELIZCG07@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>18-02-2026 20:42:50</t>
+          <t>16-02-2026 18:53:41</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>18-02-2026 20:49:56</t>
+          <t>17-02-2026 14:17:50</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>18-02-2026 20:48:57</t>
-        </is>
-      </c>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6629,14 +6633,14 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26210522477060003507</t>
+          <t>26210522429100003408</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
@@ -6792,12 +6796,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>345189</t>
+          <t>344935</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>87354</t>
+          <t>22752</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6807,17 +6811,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>MARIA ELISA</t>
+          <t xml:space="preserve">JESUS ANTONIO </t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>MADRID</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ALAMILLA</t>
+          <t>GURROLA</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6827,79 +6831,67 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6121717456</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>C MELITOM ALBAÑEZ 45</t>
-        </is>
-      </c>
+          <t>6124408280</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>17-12-2012</t>
+          <t>23-04-1999</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>MARIAELISAHERNANDEZ@ICLOUD.COM</t>
+          <t>JESUSMG230499@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>19-02-2026 19:10:37</t>
+          <t>18-02-2026 19:00:03</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>19-02-2026 19:15:52</t>
+          <t>18-02-2026 19:01:59</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>19-02-2026 19:15:15</t>
-        </is>
-      </c>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6907,36 +6899,36 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26210522505670003580</t>
+          <t>26210522474020003495</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>342701</t>
+          <t>344321</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20518</t>
+          <t>22138</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6946,17 +6938,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>SUMIKO MARIA</t>
+          <t>NOELIA ANAID</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>ARAIZA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>AGUIRRE</t>
+          <t>ALBAÑEZ</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6966,7 +6958,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6121220205</t>
+          <t>6121498018</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6977,17 +6969,17 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>07-04-2013</t>
+          <t>25-05-2007</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>SUMIJOAGUIRREFISHER@GMAIL.COM</t>
+          <t>NOELIAANAIDARAIZA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>10-02-2026 16:22:22</t>
+          <t>16-02-2026 18:57:53</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -7012,12 +7004,12 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>10-02-2026 16:28:08</t>
+          <t>16-02-2026 18:59:47</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T49" t="inlineStr"/>
@@ -7034,7 +7026,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26210522236680002929</t>
+          <t>26210522406620003354</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
@@ -7058,12 +7050,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>344935</t>
+          <t>345619</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>22752</t>
+          <t>87784</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7073,17 +7065,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">JESUS ANTONIO </t>
+          <t>AZUL</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>MADRID</t>
+          <t>DOMINGUEZ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>GURROLA</t>
+          <t>ESCAMILLA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7093,28 +7085,32 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6124408280</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>6121480447</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>CHAMETLA</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>23-04-1999</t>
+          <t>28-01-1977</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>JESUSMG230499@ICLOUD.COM</t>
+          <t>PLAYAZUL28@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>18-02-2026 19:00:03</t>
+          <t>22-02-2026 13:07:59</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -7124,36 +7120,44 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>18-02-2026 19:01:59</t>
+          <t>22-02-2026 13:15:30</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr"/>
+          <t>22-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>22-02-2026 13:13:25</t>
+        </is>
+      </c>
       <c r="U50" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7161,19 +7165,19 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26210522474020003495</t>
+          <t>26210522563650003675</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Cristopher Armando Serrato</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -7185,12 +7189,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>345619</t>
+          <t>342230</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>87784</t>
+          <t>20048</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7200,17 +7204,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>AZUL</t>
+          <t>ANA ARACELY</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>DOMINGUEZ</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>ESCAMILLA</t>
+          <t>COTA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7220,14 +7224,10 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6121480447</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>CHAMETLA</t>
-        </is>
-      </c>
+          <t>6121372111</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7235,17 +7235,17 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>28-01-1977</t>
+          <t>08-10-2008</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>PLAYAZUL28@HOTMAIL.COM</t>
+          <t>ARIANYR2C@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>22-02-2026 13:07:59</t>
+          <t>09-02-2026 15:59:56</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7255,44 +7255,36 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>22-02-2026 13:15:30</t>
+          <t>12-02-2026 16:08:25</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>22-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>22-02-2026 13:13:25</t>
-        </is>
-      </c>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7300,36 +7292,44 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26210522563650003675</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="inlineStr"/>
+          <t>26210522296870003118</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>VERONICA VIANEY LOYA CONTRERAS</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>344321</t>
+          <t>343038</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>22138</t>
+          <t>20855</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7339,17 +7339,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NOELIA ANAID</t>
+          <t xml:space="preserve">DOLORES ITZEL </t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ARAIZA</t>
+          <t xml:space="preserve">CUBILLOS </t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>ALBAÑEZ</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7359,10 +7359,14 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6121498018</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>6121029534</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>C PABLO L. GONZALEZ 235</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7370,56 +7374,60 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>25-05-2007</t>
+          <t>10-12-1994</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>NOELIAANAIDARAIZA@GMAIL.COM</t>
+          <t>CUBILLOSITZEL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>16-02-2026 18:57:53</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>11-02-2026 16:24:22</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>16-02-2026 18:59:47</t>
+          <t>11-02-2026 16:38:56</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr"/>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>11-02-2026 16:38:17</t>
+        </is>
+      </c>
       <c r="U52" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr"/>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W52" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7427,14 +7435,14 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26210522406620003354</t>
+          <t>26210522269110003031</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
@@ -7590,12 +7598,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>343038</t>
+          <t>343761</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20855</t>
+          <t>21578</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7605,17 +7613,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">DOLORES ITZEL </t>
+          <t>OSMAR ALEJANDRO</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUBILLOS </t>
+          <t xml:space="preserve"> LIERA </t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7625,35 +7633,39 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>6121029534</t>
+          <t>6151559659</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>C PABLO L. GONZALEZ 235</t>
+          <t>CENTRO</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>10-12-1994</t>
+          <t>26-07-2001</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>CUBILLOSITZEL@GMAIL.COM</t>
+          <t>LIERAGOMEZOSMARALEJANDRO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>11-02-2026 16:24:22</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+          <t>14-02-2026 23:55:59</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O54" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7671,17 +7683,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>11-02-2026 16:38:56</t>
+          <t>20-02-2026 05:36:59</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>20-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>11-02-2026 16:38:17</t>
+          <t>20-02-2026 05:34:42</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -7691,7 +7703,7 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -7701,10 +7713,14 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26210522269110003031</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr"/>
+          <t>26210522509510003598</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr">
         <is>
@@ -7713,24 +7729,24 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>344873</t>
+          <t>342527</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>22690</t>
+          <t>20344</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7740,17 +7756,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>KARLA ROXANA</t>
+          <t>DIANA</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MURILLO</t>
+          <t>MADRID</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t>BURQUEZ</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7760,12 +7776,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6121532789</t>
+          <t>6242249486</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD</t>
+          <t>AYENDE #1720</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7775,24 +7791,20 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>18-09-1984</t>
+          <t>15-05-1995</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>KMURILLO@UABCS.MX</t>
+          <t>DIANAMB_@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>18-02-2026 16:45:58</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>10-02-2026 07:13:24</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7810,17 +7822,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>18-02-2026 16:49:17</t>
+          <t>10-02-2026 07:22:03</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>18-02-2026 16:48:16</t>
+          <t>10-02-2026 07:20:53</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -7830,7 +7842,7 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
@@ -7840,7 +7852,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26210522467350003478</t>
+          <t>26210522224130002896</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr"/>
@@ -7852,7 +7864,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -7864,12 +7876,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>342527</t>
+          <t>346048</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>20344</t>
+          <t>88213</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7879,17 +7891,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>DIANA</t>
+          <t xml:space="preserve">ADALBERTO ABIMAEL </t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MADRID</t>
+          <t>ZAZUETA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>BURQUEZ</t>
+          <t>VEGA</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -7899,35 +7911,39 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6242249486</t>
+          <t>6122191467</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>AYENDE #1720</t>
+          <t>C MANUEL ENCINAS 1353</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>15-05-1995</t>
+          <t>21-10-1992</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>DIANAMB_@HOTMAIL.COM</t>
+          <t>REBUILDNERVE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>10-02-2026 07:13:24</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
+          <t>23-02-2026 20:33:49</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O56" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7945,17 +7961,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>10-02-2026 07:22:03</t>
+          <t>23-02-2026 20:38:02</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>10-02-2026 07:20:53</t>
+          <t>23-02-2026 20:37:01</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -7965,7 +7981,7 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
@@ -7975,7 +7991,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26210522224130002896</t>
+          <t>26210522601920003802</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr"/>
@@ -7987,24 +8003,24 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>343379</t>
+          <t>344873</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>21196</t>
+          <t>22690</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8014,17 +8030,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SARA BEATRIZ</t>
+          <t>KARLA ROXANA</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASTELLANOS </t>
+          <t>MURILLO</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>VALDEZ</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8034,12 +8050,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>6122327477</t>
+          <t>6121532789</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>C MELON 121</t>
+          <t>UNIVERSIDAD</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -8049,20 +8065,24 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>03-06-1981</t>
+          <t>18-09-1984</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>DRA.SARACASTELLANOS@GMAIL.COM</t>
+          <t>KMURILLO@UABCS.MX</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>12-02-2026 18:54:35</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>18-02-2026 16:45:58</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O57" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8080,17 +8100,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>12-02-2026 18:58:52</t>
+          <t>18-02-2026 16:49:17</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>12-02-2026 18:58:05</t>
+          <t>18-02-2026 16:48:16</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -8110,7 +8130,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26210522303780003149</t>
+          <t>26210522467350003478</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr"/>
@@ -8134,12 +8154,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>343761</t>
+          <t>342701</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>21578</t>
+          <t>20518</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8149,17 +8169,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>OSMAR ALEJANDRO</t>
+          <t>SUMIKO MARIA</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LIERA </t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>AGUIRRE</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8169,79 +8189,67 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>6151559659</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>CENTRO</t>
-        </is>
-      </c>
+          <t>6121220205</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>26-07-2001</t>
+          <t>07-04-2013</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>LIERAGOMEZOSMARALEJANDRO@GMAIL.COM</t>
+          <t>SUMIJOAGUIRREFISHER@GMAIL.COM</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>14-02-2026 23:55:59</t>
+          <t>10-02-2026 16:22:22</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>20-02-2026 05:36:59</t>
+          <t>10-02-2026 16:28:08</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>20-02-2026 05:34:42</t>
-        </is>
-      </c>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V58" t="inlineStr"/>
       <c r="W58" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8249,28 +8257,24 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>26210522509510003598</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26210522236680002929</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -8412,12 +8416,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>343251</t>
+          <t>346045</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>21068</t>
+          <t>88210</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8427,17 +8431,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>TAMARA</t>
+          <t xml:space="preserve">LIZBETH </t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>PIÑUELAS</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AGUIÑAGA</t>
+          <t xml:space="preserve">SANTIAGO </t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -8447,10 +8451,14 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>5541288966</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>6121701231</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>C MANUEL ENCINAS 1353</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -8458,56 +8466,64 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>21-12-2004</t>
+          <t>10-12-1997</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>TAMARA211204@GMAIL.COM</t>
+          <t>LIZPISA94@GMAIL.COM</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>12-02-2026 13:32:17</t>
+          <t>23-02-2026 20:23:38</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>12-02-2026 13:33:36</t>
+          <t>23-02-2026 20:32:15</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>23-02-2026 20:31:30</t>
+        </is>
+      </c>
       <c r="U60" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr"/>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W60" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8515,36 +8531,36 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>26210522293540003108</t>
+          <t>26210522601760003801</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="inlineStr"/>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>343375</t>
+          <t>343251</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>21192</t>
+          <t>21068</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8554,17 +8570,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIO ALBERTO </t>
+          <t>TAMARA</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ROSAS</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANRIQUEZ </t>
+          <t>AGUIÑAGA</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -8574,53 +8590,53 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>6122343338</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>C MELON 121</t>
-        </is>
-      </c>
+          <t>5541288966</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>12-12-1977</t>
+          <t>21-12-2004</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>ROSASCASTELLANOS@GMAIL.COM</t>
+          <t>TAMARA211204@GMAIL.COM</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>12-02-2026 18:48:15</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
+          <t>12-02-2026 13:32:17</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>12-02-2026 18:53:02</t>
+          <t>12-02-2026 13:33:36</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -8628,21 +8644,13 @@
           <t>12-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>12-02-2026 18:52:16</t>
-        </is>
-      </c>
+      <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V61" t="inlineStr"/>
       <c r="W61" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8650,14 +8658,14 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>26210522303620003147</t>
+          <t>26210522293540003108</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="inlineStr"/>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
@@ -8674,12 +8682,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>345136</t>
+          <t>343379</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>87301</t>
+          <t>21196</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8689,17 +8697,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>FRANCISCA CECILIA</t>
+          <t>SARA BEATRIZ</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>BARRETO</t>
+          <t xml:space="preserve">CASTELLANOS </t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>BARRETO</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -8709,10 +8717,14 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>6122148757</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>6122327477</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>C MELON 121</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -8720,56 +8732,60 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>22-11-1987</t>
+          <t>03-06-1981</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>BARRETOCECILIA925@GMAIL.COM</t>
+          <t>DRA.SARACASTELLANOS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>19-02-2026 17:04:50</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>12-02-2026 18:54:35</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>19-02-2026 17:05:35</t>
+          <t>12-02-2026 18:58:52</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T62" t="inlineStr"/>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>12-02-2026 18:58:05</t>
+        </is>
+      </c>
       <c r="U62" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr"/>
       <c r="W62" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8777,36 +8793,36 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>26210522500360003555</t>
+          <t>26210522303780003149</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>344727</t>
+          <t>343375</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>22544</t>
+          <t>21192</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8816,17 +8832,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>MARIA TERESA</t>
+          <t xml:space="preserve">MARIO ALBERTO </t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>ROSAS</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>QUEZADA</t>
+          <t xml:space="preserve">MANRIQUEZ </t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -8836,67 +8852,63 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>5578843819</t>
+          <t>6122343338</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>CENTRO</t>
+          <t>C MELON 121</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>31-05-1969</t>
+          <t>12-12-1977</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>MARIATERESAPEREZQUEZADA@GMAIL.COM</t>
+          <t>ROSASCASTELLANOS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>18-02-2026 05:24:32</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>12-02-2026 18:48:15</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>19-02-2026 06:46:30</t>
+          <t>12-02-2026 18:53:02</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>19-02-2026 06:44:39</t>
+          <t>12-02-2026 18:52:16</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -8916,40 +8928,36 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>26210522487370003516</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26210522303620003147</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="inlineStr"/>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>345078</t>
+          <t>344727</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>87243</t>
+          <t>22544</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -8959,17 +8967,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA VICTORIA </t>
+          <t>MARIA TERESA</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">BARRANCO </t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASTRO </t>
+          <t>QUEZADA</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -8979,12 +8987,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>6123489475</t>
+          <t>5578843819</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>C MAGUEY 4551</t>
+          <t>CENTRO</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -8994,42 +9002,42 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>08-02-1994</t>
+          <t>31-05-1969</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>ANACSTRO@GMAIL.COM</t>
+          <t>MARIATERESAPEREZQUEZADA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>19-02-2026 14:27:10</t>
+          <t>18-02-2026 05:24:32</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>19-02-2026 14:32:01</t>
+          <t>19-02-2026 06:46:30</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -9039,7 +9047,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>19-02-2026 14:31:19</t>
+          <t>19-02-2026 06:44:39</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -9059,22 +9067,292 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>26210522495380003538</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr"/>
+          <t>26210522487370003516</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z64" t="inlineStr"/>
       <c r="AA64" t="inlineStr">
         <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>Christian Jahassiel Castro Navarro</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>345078</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>87243</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANA VICTORIA </t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BARRANCO </t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CASTRO </t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>6123489475</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>C MAGUEY 4551</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>08-02-1994</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>ANACSTRO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>19-02-2026 14:27:10</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
           <t>499</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>19-02-2026 14:32:01</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>19-02-2026 14:31:19</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>26210522495380003538</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>345136</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>87301</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>FRANCISCA CECILIA</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>BARRETO</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>BARRETO</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>6122148757</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>22-11-1987</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>BARRETOCECILIA925@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>19-02-2026 17:04:50</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>19-02-2026 17:05:35</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>26210522500360003555</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__PASEO LA PAZ.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__PASEO LA PAZ.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC66"/>
+  <dimension ref="A1:AC70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -991,12 +991,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>340279</t>
+          <t>336249</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18097</t>
+          <t>21975</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1006,17 +1006,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUZ ANGELICA </t>
+          <t xml:space="preserve">ITZEL PAMELA </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOA </t>
+          <t>OJEDA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">VEGA </t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6121042102</t>
+          <t>6122145378</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>C MANUEL F MONTAÑO</t>
+          <t>C BAHIA SALINAS 89</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1041,48 +1041,52 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>20-09-1980</t>
+          <t>06-02-1992</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>LICLOAVEGA20@GMAIL.COM</t>
+          <t>OERI920602@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-02-2026 16:39:48</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>19-01-2026 21:41:41</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-02-2026 16:43:50</t>
+          <t>25-02-2026 15:40:17</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>25-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>02-02-2026 16:42:42</t>
+          <t>25-02-2026 15:39:58</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1092,7 +1096,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1102,14 +1106,22 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26210522017090002277</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+          <t>26210522655810003953</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>VERONICA VIANEY LOYA CONTRERAS</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1126,12 +1138,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>340290</t>
+          <t>340279</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18108</t>
+          <t>18097</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1141,17 +1153,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHRISTIAN ALEJANDRO </t>
+          <t xml:space="preserve">LUZ ANGELICA </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CERVERA </t>
+          <t xml:space="preserve">LOA </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CERVANTES</t>
+          <t xml:space="preserve">VEGA </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1161,32 +1173,32 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6122289427</t>
+          <t>6121042102</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>C POSEIDON 666</t>
+          <t>C MANUEL F MONTAÑO</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>14-11-2011</t>
+          <t>20-09-1980</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CHRISTIANCERV777@GMAIL.COM</t>
+          <t>LICLOAVEGA20@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-02-2026 16:52:38</t>
+          <t>02-02-2026 16:39:48</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1197,7 +1209,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1207,7 +1219,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-02-2026 16:58:16</t>
+          <t>02-02-2026 16:43:50</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1217,7 +1229,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>02-02-2026 16:57:36</t>
+          <t>02-02-2026 16:42:42</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1237,7 +1249,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26210522017700002281</t>
+          <t>26210522017090002277</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -1249,7 +1261,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1261,12 +1273,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>322857</t>
+          <t>340290</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19796</t>
+          <t>18108</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1276,17 +1288,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NAYELI</t>
+          <t xml:space="preserve">CHRISTIAN ALEJANDRO </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MARILES</t>
+          <t xml:space="preserve">CERVERA </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CORDERO</t>
+          <t>CERVANTES</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1296,32 +1308,32 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6122343921</t>
+          <t>6122289427</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PISTACHE 144</t>
+          <t>C POSEIDON 666</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>23-12-1992</t>
+          <t>14-11-2011</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>NAYUNOCHO@GMAIL.COM</t>
+          <t>CHRISTIANCERV777@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>10-11-2025 12:13:22</t>
+          <t>02-02-2026 16:52:38</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1342,17 +1354,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>05-02-2026 15:40:20</t>
+          <t>02-02-2026 16:58:16</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>05-02-2026 15:40:02</t>
+          <t>02-02-2026 16:57:36</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1362,7 +1374,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1372,7 +1384,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26210522108860002579</t>
+          <t>26210522017700002281</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
@@ -1384,7 +1396,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Guillermo  Garcia De Alba Velazquez</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1396,12 +1408,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>340353</t>
+          <t>322857</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18171</t>
+          <t>19796</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1411,17 +1423,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">GIBERTO </t>
+          <t>NAYELI</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">MENDEZ </t>
+          <t>MARILES</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">HALE </t>
+          <t>CORDERO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1431,32 +1443,32 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6121528946</t>
+          <t>6122343921</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>C CERRADA SANTA INES 890</t>
+          <t>PISTACHE 144</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>23-11-2001</t>
+          <t>23-12-1992</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>GILBERTO.MEN20011@GMAIL.COM</t>
+          <t>NAYUNOCHO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-02-2026 18:54:26</t>
+          <t>10-11-2025 12:13:22</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1477,17 +1489,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-02-2026 18:58:19</t>
+          <t>05-02-2026 15:40:20</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>02-02-2026 18:58:00</t>
+          <t>05-02-2026 15:40:02</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1497,7 +1509,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1507,7 +1519,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26210522021420002304</t>
+          <t>26210522108860002579</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1519,7 +1531,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Guillermo  Garcia De Alba Velazquez</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1531,12 +1543,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>339764</t>
+          <t>340215</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>17582</t>
+          <t>18033</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1546,17 +1558,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">WILIAM ULISES </t>
+          <t xml:space="preserve">FRANCISCO JAVIER </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t xml:space="preserve">SANCHEZ </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>IZAGUIRRE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1566,12 +1578,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6691484335</t>
+          <t>6121370121</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">C VALTIERRA 324 </t>
+          <t>C ISLA PATO 107</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1581,17 +1593,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>21-09-1990</t>
+          <t>26-03-1977</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>WIL_UCL@HOTMAIL.COM</t>
+          <t>FRANCISCO.SAN.IZA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>01-02-2026 10:17:19</t>
+          <t>02-02-2026 15:28:02</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1602,7 +1614,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1612,17 +1624,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>01-02-2026 10:33:00</t>
+          <t>02-02-2026 15:40:28</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>01-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>01-02-2026 10:25:23</t>
+          <t>02-02-2026 15:39:32</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1642,7 +1654,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26210521989080002222</t>
+          <t>26210522014940002273</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
@@ -1654,7 +1666,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1666,12 +1678,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>340215</t>
+          <t>341119</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18033</t>
+          <t>18937</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1681,17 +1693,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRANCISCO JAVIER </t>
+          <t xml:space="preserve">HANNIA MARIA </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANCHEZ </t>
+          <t xml:space="preserve">CASTRO </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>IZAGUIRRE</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1701,75 +1713,67 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6121370121</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>C ISLA PATO 107</t>
-        </is>
-      </c>
+          <t>6121543278</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>26-03-1977</t>
+          <t>25-01-2008</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>FRANCISCO.SAN.IZA@GMAIL.COM</t>
+          <t>HANNIATAY13@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-02-2026 15:28:02</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>04-02-2026 17:46:50</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-02-2026 15:40:28</t>
+          <t>04-02-2026 17:47:55</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>02-02-2026 15:39:32</t>
-        </is>
-      </c>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1777,14 +1781,14 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26210522014940002273</t>
+          <t>26210522083460002490</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1936,12 +1940,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>341119</t>
+          <t>340015</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>18937</t>
+          <t>17833</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1951,17 +1955,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HANNIA MARIA </t>
+          <t>MARIA FERNANDA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASTRO </t>
+          <t>AVILES</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1971,10 +1975,14 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6121543278</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>6121058570</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>CENTRO</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1982,42 +1990,38 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>25-01-2008</t>
+          <t>08-12-1997</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>HANNIATAY13@ICLOUD.COM</t>
+          <t>AVILESSANCHEZFERNANDA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>04-02-2026 17:46:50</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>02-02-2026 10:34:28</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>04-02-2026 17:47:55</t>
+          <t>03-02-2026 05:22:36</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2025,13 +2029,21 @@
           <t>04-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>03-02-2026 05:22:05</t>
+        </is>
+      </c>
       <c r="U12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2039,19 +2051,23 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26210522083460002490</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr"/>
+          <t>26210522027620002320</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2063,12 +2079,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>340015</t>
+          <t>295801</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>17833</t>
+          <t>93299</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2078,17 +2094,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA</t>
+          <t>MARIBEL</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AVILES</t>
+          <t xml:space="preserve">PEREZ </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2098,12 +2114,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6121058570</t>
+          <t>6122147740</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CENTRO</t>
+          <t>CADIZ #367</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2113,20 +2129,24 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>08-12-1997</t>
+          <t>05-02-1982</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>AVILESSANCHEZFERNANDA@GMAIL.COM</t>
+          <t>MARIBEPZNZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>02-02-2026 10:34:28</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>02-06-2025 07:55:35</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -2134,7 +2154,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2144,17 +2164,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>03-02-2026 05:22:36</t>
+          <t>24-02-2026 10:40:21</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>24-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>03-02-2026 05:22:05</t>
+          <t>24-02-2026 10:38:54</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2164,7 +2184,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2174,14 +2194,10 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26210522027620002320</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26210522615770003833</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
@@ -2190,24 +2206,24 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>340286</t>
+          <t>340353</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18104</t>
+          <t>18171</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2217,17 +2233,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">AMY ANGELINE </t>
+          <t xml:space="preserve">GIBERTO </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUZMAN </t>
+          <t xml:space="preserve">MENDEZ </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOA </t>
+          <t xml:space="preserve">HALE </t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2237,32 +2253,32 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6121220630</t>
+          <t>6121528946</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">C MANUEL F MONTOYA </t>
+          <t>C CERRADA SANTA INES 890</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>20-01-2010</t>
+          <t>23-11-2001</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>LICLOAVEGA200@GMAIL.COM</t>
+          <t>GILBERTO.MEN20011@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-02-2026 16:44:59</t>
+          <t>02-02-2026 18:54:26</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2273,7 +2289,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -2283,7 +2299,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>02-02-2026 16:47:48</t>
+          <t>02-02-2026 18:58:19</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2293,7 +2309,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>02-02-2026 16:46:46</t>
+          <t>02-02-2026 18:58:00</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2313,7 +2329,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26210522017270002279</t>
+          <t>26210522021420002304</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
@@ -2337,12 +2353,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>340554</t>
+          <t>342188</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>18372</t>
+          <t>20006</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2352,17 +2368,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>JANNETT</t>
+          <t>EDNA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CALDERON</t>
+          <t>TAMAYO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SCHCOLNICK</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2372,12 +2388,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6121042182</t>
+          <t>6123489545</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>CARRETERA AL NORTE KM 11 PRIV. LAS QUINTAS DEL MAR 7</t>
+          <t>PRIV MARINA CENTRAL 117</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2387,17 +2403,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>22-09-2004</t>
+          <t>02-04-1974</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>JANNETT.22099@GMAIL.COM</t>
+          <t>EDNA_321@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>03-02-2026 13:02:59</t>
+          <t>09-02-2026 14:43:59</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2418,17 +2434,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>03-02-2026 13:08:32</t>
+          <t>11-02-2026 13:12:45</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>03-02-2026 13:07:59</t>
+          <t>11-02-2026 13:12:26</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2438,7 +2454,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -2448,11 +2464,19 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26210522039110002341</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
+          <t>26210522263830003013</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>CRISTINA AYLIN CHAVEZ GONZALEZ</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>499</t>
@@ -2472,12 +2496,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>342188</t>
+          <t>341136</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20006</t>
+          <t>18954</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2487,17 +2511,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EDNA</t>
+          <t xml:space="preserve">ROSA ISELA </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TAMAYO</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2507,12 +2531,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6123489545</t>
+          <t>6121275515</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>PRIV MARINA CENTRAL 117</t>
+          <t xml:space="preserve">EL CENTENARIO </t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2522,48 +2546,52 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>02-04-1974</t>
+          <t>16-02-1981</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>EDNA_321@HOTMAIL.COM</t>
+          <t>IVAZQUEZ@CIBNOR.MX</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>09-02-2026 14:43:59</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>04-02-2026 18:14:43</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>11-02-2026 13:12:45</t>
+          <t>04-02-2026 18:22:58</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>11-02-2026 13:12:26</t>
+          <t>04-02-2026 18:22:23</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2583,27 +2611,19 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26210522263830003013</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>CRISTINA AYLIN CHAVEZ GONZALEZ</t>
-        </is>
-      </c>
+          <t>26210522085210002502</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2615,12 +2635,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>341114</t>
+          <t>341799</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>18932</t>
+          <t>19617</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2630,17 +2650,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HANNIA ZULETT GUADALUPE</t>
+          <t xml:space="preserve">MIGUEL ANGEL </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">BURGOIN </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCERO </t>
+          <t>VICENT</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2650,67 +2670,75 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6121041819</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>6121590416</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>PRIV PALO DE SANTA RITA 9</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>01-12-2008</t>
+          <t>30-10-1955</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>HANNIAZULETTBURGOIN@GMAIL.COM</t>
+          <t>MHVICENT@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>04-02-2026 17:38:34</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>07-02-2026 10:56:26</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>04-02-2026 17:42:38</t>
+          <t>07-02-2026 11:33:16</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr"/>
+          <t>07-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>07-02-2026 11:32:27</t>
+        </is>
+      </c>
       <c r="U17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W17" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2718,19 +2746,23 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26210522083170002489</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr"/>
+          <t>26210522159870002732</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2742,12 +2774,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>341797</t>
+          <t>341390</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19615</t>
+          <t>19208</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2757,17 +2789,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SUSANA</t>
+          <t>FERNANDA JETSEL</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PASALAGUA</t>
+          <t xml:space="preserve">TAPIZ </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2777,12 +2809,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6121590135</t>
+          <t>6121007438</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>PRIV PALO DE SANTA RITA 9</t>
+          <t xml:space="preserve">SAN FERNANDO </t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2792,17 +2824,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>06-02-1966</t>
+          <t>21-10-1985</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>SIPHITYA@GMAIL.COM</t>
+          <t>SINDICATO.JEC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>07-02-2026 10:52:31</t>
+          <t>05-02-2026 17:08:31</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2823,17 +2855,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>07-02-2026 11:37:55</t>
+          <t>05-02-2026 17:12:39</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>07-02-2026 11:37:04</t>
+          <t>05-02-2026 17:12:22</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2853,14 +2885,10 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26210522160000002733</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26210522112170002589</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
@@ -2869,7 +2897,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2881,12 +2909,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>341799</t>
+          <t>342520</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19617</t>
+          <t>20337</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2896,17 +2924,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGUEL ANGEL </t>
+          <t>JOSE EDUARDO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VICENT</t>
+          <t>LIMOM</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2916,12 +2944,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6121590416</t>
+          <t>6121196214</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>PRIV PALO DE SANTA RITA 9</t>
+          <t>DEL ESTRIBO</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2931,17 +2959,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>30-10-1955</t>
+          <t>03-01-1992</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>MHVICENT@GMAIL.COM</t>
+          <t>LIMON.EDUARDO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>07-02-2026 10:56:26</t>
+          <t>10-02-2026 06:36:49</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2962,17 +2990,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>07-02-2026 11:33:16</t>
+          <t>10-02-2026 06:41:55</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>07-02-2026 11:32:27</t>
+          <t>10-02-2026 06:41:25</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2992,14 +3020,10 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26210522159870002732</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26210522223420002894</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
@@ -3008,7 +3032,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>Cristopher Armando Serrato</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3020,12 +3044,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>341136</t>
+          <t>341986</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>18954</t>
+          <t>19804</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3035,17 +3059,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROSA ISELA </t>
+          <t>KARLA ELIZABETH</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>BERLANGA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>CALDERON</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3055,14 +3079,10 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6121275515</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EL CENTENARIO </t>
-        </is>
-      </c>
+          <t>5577876880</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3070,17 +3090,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>16-02-1981</t>
+          <t>22-05-2001</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>IVAZQUEZ@CIBNOR.MX</t>
+          <t>BERLANGACALDERONELIZABETH22@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>04-02-2026 18:14:43</t>
+          <t>09-02-2026 04:13:10</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3090,44 +3110,36 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>04-02-2026 18:22:58</t>
+          <t>09-02-2026 04:15:04</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>04-02-2026 18:22:23</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3135,36 +3147,36 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26210522085210002502</t>
+          <t>26210522174170002753</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>342051</t>
+          <t>341797</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19869</t>
+          <t>19615</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3174,17 +3186,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLAUDIA </t>
+          <t>SUSANA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AGUAYO</t>
+          <t>PASALAGUA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>OJEDA</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3194,12 +3206,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>8123512800</t>
+          <t>6121590135</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>CENTRO</t>
+          <t>PRIV PALO DE SANTA RITA 9</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3209,52 +3221,48 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>13-11-2002</t>
+          <t>06-02-1966</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLAUDIABEATRIZ.AGUAYO@GMAIL.COM</t>
+          <t>SIPHITYA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>09-02-2026 08:32:35</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>07-02-2026 10:52:31</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>11-02-2026 09:29:24</t>
+          <t>07-02-2026 11:37:55</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>07-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>11-02-2026 09:28:31</t>
+          <t>07-02-2026 11:37:04</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3264,7 +3272,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -3274,18 +3282,18 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26210522260760002999</t>
+          <t>26210522160000002733</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+          <t>PASE RECORRIDO</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -3302,12 +3310,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>341390</t>
+          <t>342427</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19208</t>
+          <t>20244</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3317,17 +3325,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FERNANDA JETSEL</t>
+          <t xml:space="preserve">NICOLAS </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">TAPIZ </t>
+          <t>PERPULI</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>VERDUGO</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3337,75 +3345,67 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6121007438</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SAN FERNANDO </t>
-        </is>
-      </c>
+          <t>6121614567</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>21-10-1985</t>
+          <t>06-03-1973</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>SINDICATO.JEC@GMAIL.COM</t>
+          <t>NICOLASPERPULIVERDUGO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>05-02-2026 17:08:31</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>09-02-2026 19:09:18</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>05-02-2026 17:12:39</t>
+          <t>09-02-2026 19:12:38</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>05-02-2026 17:12:22</t>
-        </is>
-      </c>
+          <t>09-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3413,14 +3413,14 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26210522112170002589</t>
+          <t>26210522209990002868</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3437,12 +3437,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>342520</t>
+          <t>342684</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20337</t>
+          <t>20501</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3452,17 +3452,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO</t>
+          <t xml:space="preserve">SANTIAGO </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t xml:space="preserve">CUEN </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>LIMOM</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3472,14 +3472,10 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6121196214</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>DEL ESTRIBO</t>
-        </is>
-      </c>
+          <t>6122186206</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -3487,38 +3483,42 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>03-01-1992</t>
+          <t>06-10-2008</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>LIMON.EDUARDO@HOTMAIL.COM</t>
+          <t>SANTIAGOCUEN23@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>10-02-2026 06:36:49</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>10-02-2026 15:52:34</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>10-02-2026 06:41:55</t>
+          <t>10-02-2026 15:55:25</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3526,21 +3526,13 @@
           <t>10-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>10-02-2026 06:41:25</t>
-        </is>
-      </c>
+      <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3548,19 +3540,19 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26210522223420002894</t>
+          <t>26210522235410002926</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Cristopher Armando Serrato</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3572,12 +3564,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>342427</t>
+          <t>343254</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20244</t>
+          <t>21071</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3587,17 +3579,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICOLAS </t>
+          <t>JOUSY ISABELLA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PERPULI</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>VERDUGO</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3607,28 +3599,28 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6121614567</t>
+          <t>6391613622</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>06-03-1973</t>
+          <t>12-10-2003</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>NICOLASPERPULIVERDUGO@HOTMAIL.COM</t>
+          <t>ISABELLAMENDOZAVV@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>09-02-2026 19:09:18</t>
+          <t>12-02-2026 13:36:03</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3643,28 +3635,28 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>09-02-2026 19:12:38</t>
+          <t>12-02-2026 13:37:01</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>09-05-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V24" t="inlineStr"/>
@@ -3675,19 +3667,19 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26210522209990002868</t>
+          <t>26210522293680003109</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Cristopher Armando Serrato</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3699,12 +3691,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>341986</t>
+          <t>343458</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>19804</t>
+          <t>21275</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3714,17 +3706,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>KARLA ELIZABETH</t>
+          <t>EDUARDO ALEXIS</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>BERLANGA</t>
+          <t>VEGA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CALDERON</t>
+          <t>VIEYRA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3734,7 +3726,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>5577876880</t>
+          <t>6121677253</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3745,17 +3737,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>22-05-2001</t>
+          <t>08-04-1991</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>BERLANGACALDERONELIZABETH22@GMAIL.COM</t>
+          <t>EDUARDOVIEYRA06@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>09-02-2026 04:13:10</t>
+          <t>13-02-2026 10:06:29</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3780,12 +3772,12 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>09-02-2026 04:15:04</t>
+          <t>13-02-2026 10:17:33</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -3802,7 +3794,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26210522174170002753</t>
+          <t>26210522318120003186</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
@@ -3814,24 +3806,24 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>332784</t>
+          <t>343509</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14805</t>
+          <t>21326</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3841,17 +3833,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t xml:space="preserve">SANDRA DELMA </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ROBLES</t>
+          <t xml:space="preserve">OLIVARES </t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ARANDA</t>
+          <t>VIVAR</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3861,32 +3853,32 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>5585803795</t>
+          <t>6121310729</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">PUEBLO NUEVO </t>
+          <t>C OLMECAS 508</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>04-03-1978</t>
+          <t>16-04-1976</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>ALEJANDRO.ROBLESARANDA@GMAIL.COM</t>
+          <t>SANDYPRICES.19@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>07-01-2026 09:40:49</t>
+          <t>13-02-2026 15:14:31</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3897,7 +3889,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -3907,17 +3899,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>03-02-2026 14:14:15</t>
+          <t>13-02-2026 15:17:56</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>03-02-2026 13:57:02</t>
+          <t>13-02-2026 15:17:37</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3937,7 +3929,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26210522040850002349</t>
+          <t>26210522322300003205</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
@@ -3961,12 +3953,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>336694</t>
+          <t>332784</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>22420</t>
+          <t>14805</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3976,17 +3968,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ZULEMA</t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>HIGUERA</t>
+          <t>ROBLES</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>ARANDA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3996,32 +3988,32 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6122380771</t>
+          <t>5585803795</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>CENTRO</t>
+          <t xml:space="preserve">PUEBLO NUEVO </t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>08-04-1983</t>
+          <t>04-03-1978</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>ZULEMA@BAJASURREALTORS.COM</t>
+          <t>ALEJANDRO.ROBLESARANDA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>21-01-2026 10:28:18</t>
+          <t>07-01-2026 09:40:49</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -4032,7 +4024,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>PROMO ENERO 12 MESES</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -4042,17 +4034,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>02-02-2026 09:06:56</t>
+          <t>03-02-2026 14:14:15</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>28-02-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>28-01-2026 09:24:49</t>
+          <t>03-02-2026 13:57:02</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4072,14 +4064,10 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26210522002210002243</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26210522040850002349</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
@@ -4088,7 +4076,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4100,12 +4088,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>342226</t>
+          <t>336694</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20044</t>
+          <t>22420</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4115,17 +4103,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ARIANY ROSALIA</t>
+          <t>ZULEMA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>COTA</t>
+          <t>HIGUERA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4135,12 +4123,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6121692055</t>
+          <t>6122380771</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>CALLE EL TRIUNFO #233</t>
+          <t>CENTRO</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4150,17 +4138,17 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>08-10-1981</t>
+          <t>08-04-1983</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>ARIANY2C@HOTMAIL.COM</t>
+          <t>ZULEMA@BAJASURREALTORS.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>09-02-2026 15:54:22</t>
+          <t>21-01-2026 10:28:18</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4171,7 +4159,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PROMO ENERO 12 MESES</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -4181,17 +4169,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>10-02-2026 17:08:18</t>
+          <t>02-02-2026 09:06:56</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>28-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>10-02-2026 17:07:27</t>
+          <t>28-01-2026 09:24:49</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -4211,7 +4199,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26210522238630002941</t>
+          <t>26210522002210002243</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -4219,11 +4207,7 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>VERONICA VIANEY LOYA CONTRERAS</t>
-        </is>
-      </c>
+      <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
           <t>499</t>
@@ -4231,7 +4215,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4243,12 +4227,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>342684</t>
+          <t>342051</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20501</t>
+          <t>19869</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4258,17 +4242,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANTIAGO </t>
+          <t xml:space="preserve">CLAUDIA </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUEN </t>
+          <t>AGUAYO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t>OJEDA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4278,28 +4262,32 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6122186206</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>8123512800</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>CENTRO</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>06-10-2008</t>
+          <t>13-11-2002</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>SANTIAGOCUEN23@GMAIL.COM</t>
+          <t>CLAUDIABEATRIZ.AGUAYO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>10-02-2026 15:52:34</t>
+          <t>09-02-2026 08:32:35</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4309,36 +4297,44 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>10-02-2026 15:55:25</t>
+          <t>11-02-2026 09:29:24</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr"/>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>11-02-2026 09:28:31</t>
+        </is>
+      </c>
       <c r="U29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr"/>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W29" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4346,19 +4342,23 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26210522235410002926</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr"/>
+          <t>26210522260760002999</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4370,12 +4370,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>342490</t>
+          <t>342302</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20307</t>
+          <t>20120</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4385,17 +4385,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>RENEE ALESSANDRA</t>
+          <t xml:space="preserve">MELANIE </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">CESEÑA </t>
+          <t>ALBAÑEZ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAVIS </t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4405,10 +4405,14 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6122046111</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>6643640599</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>AGUA DULCE 618</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4416,42 +4420,38 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>20-02-2007</t>
+          <t>01-05-1980</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>RENEEE777111@GMAIL.COM</t>
+          <t>ANIEALRO2020@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>09-02-2026 20:30:27</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 17:06:10</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>09-02-2026 20:32:52</t>
+          <t>09-02-2026 17:08:49</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -4459,13 +4459,21 @@
           <t>09-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr"/>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>09-02-2026 17:08:25</t>
+        </is>
+      </c>
       <c r="U30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr"/>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W30" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4473,14 +4481,14 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26210522213810002877</t>
+          <t>26210522200900002835</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -4632,12 +4640,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>343254</t>
+          <t>339764</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21071</t>
+          <t>17582</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4647,17 +4655,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>JOUSY ISABELLA</t>
+          <t xml:space="preserve">WILIAM ULISES </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4667,67 +4675,75 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6391613622</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>6691484335</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C VALTIERRA 324 </t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>12-10-2003</t>
+          <t>21-09-1990</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>ISABELLAMENDOZAVV@OUTLOOK.COM</t>
+          <t>WIL_UCL@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>12-02-2026 13:36:03</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>01-02-2026 10:17:19</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>12-02-2026 13:37:01</t>
+          <t>01-02-2026 10:33:00</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr"/>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>01-02-2026 10:25:23</t>
+        </is>
+      </c>
       <c r="U32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr"/>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W32" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4735,19 +4751,19 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26210522293680003109</t>
+          <t>26210521989080002222</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Cristopher Armando Serrato</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4759,12 +4775,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>343458</t>
+          <t>340286</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21275</t>
+          <t>18104</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4774,17 +4790,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>EDUARDO ALEXIS</t>
+          <t xml:space="preserve">AMY ANGELINE </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>VEGA</t>
+          <t xml:space="preserve">GUZMAN </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>VIEYRA</t>
+          <t xml:space="preserve">LOA </t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4794,10 +4810,14 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6121677253</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>6121220630</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C MANUEL F MONTOYA </t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4805,56 +4825,60 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>08-04-1991</t>
+          <t>20-01-2010</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>EDUARDOVIEYRA06@GMAIL.COM</t>
+          <t>LICLOAVEGA200@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>13-02-2026 10:06:29</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>02-02-2026 16:44:59</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>13-02-2026 10:17:33</t>
+          <t>02-02-2026 16:47:48</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>02-02-2026 16:46:46</t>
+        </is>
+      </c>
       <c r="U33" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr"/>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W33" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4862,14 +4886,14 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26210522318120003186</t>
+          <t>26210522017270002279</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -4886,12 +4910,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>343509</t>
+          <t>342490</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21326</t>
+          <t>20307</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4901,17 +4925,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANDRA DELMA </t>
+          <t>RENEE ALESSANDRA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">OLIVARES </t>
+          <t xml:space="preserve">CESEÑA </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>VIVAR</t>
+          <t xml:space="preserve">DAVIS </t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4921,14 +4945,10 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6121310729</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>C OLMECAS 508</t>
-        </is>
-      </c>
+          <t>6122046111</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4936,60 +4956,56 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>16-04-1976</t>
+          <t>20-02-2007</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>SANDYPRICES.19@GMAIL.COM</t>
+          <t>RENEEE777111@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>13-02-2026 15:14:31</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>09-02-2026 20:30:27</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>13-02-2026 15:17:56</t>
+          <t>09-02-2026 20:32:52</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>13-02-2026 15:17:37</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4997,14 +5013,14 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26210522322300003205</t>
+          <t>26210522213810002877</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -5021,12 +5037,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>342302</t>
+          <t>340554</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20120</t>
+          <t>18372</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5036,17 +5052,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">MELANIE </t>
+          <t>JANNETT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ALBAÑEZ</t>
+          <t>CALDERON</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>SCHCOLNICK</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5056,12 +5072,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6643640599</t>
+          <t>6121042182</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>AGUA DULCE 618</t>
+          <t>CARRETERA AL NORTE KM 11 PRIV. LAS QUINTAS DEL MAR 7</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5071,17 +5087,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>01-05-1980</t>
+          <t>22-09-2004</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>ANIEALRO2020@GMAIL.COM</t>
+          <t>JANNETT.22099@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>09-02-2026 17:06:10</t>
+          <t>03-02-2026 13:02:59</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -5102,17 +5118,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>09-02-2026 17:08:49</t>
+          <t>03-02-2026 13:08:32</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>09-02-2026 17:08:25</t>
+          <t>03-02-2026 13:07:59</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5122,7 +5138,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -5132,7 +5148,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26210522200900002835</t>
+          <t>26210522039110002341</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
@@ -5144,7 +5160,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5291,12 +5307,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>343166</t>
+          <t>341783</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20983</t>
+          <t>19601</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5306,17 +5322,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA</t>
+          <t>ERNESTO</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ACEVEDO</t>
+          <t xml:space="preserve">GARZA </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>RUVALCABA</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5326,32 +5342,32 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6121068152</t>
+          <t>8180747965</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>ENCINO #216</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>13-09-2003</t>
+          <t>27-10-1990</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>FERNANDAACEV13@GMAIL.COM</t>
+          <t>DRERNESTOGARZA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>12-02-2026 07:13:35</t>
+          <t>07-02-2026 10:19:47</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5372,17 +5388,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>12-02-2026 07:18:27</t>
+          <t>11-02-2026 15:26:34</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>12-02-2026 07:17:45</t>
+          <t>11-02-2026 15:25:43</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -5392,7 +5408,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -5402,11 +5418,19 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26210522287800003090</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
+          <t>26210522266420003021</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>VERONICA VIANEY LOYA CONTRERAS</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>499</t>
@@ -5414,7 +5438,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Cristopher Armando Serrato</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -5426,12 +5450,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>343508</t>
+          <t>341785</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>21325</t>
+          <t>19603</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5441,17 +5465,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUISA FERNANDA </t>
+          <t>DENIS ALEJANDRA</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">MURILLO </t>
+          <t>ESTRADA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">OLIVARES </t>
+          <t>SANTACRUZ</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5461,12 +5485,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6122290863</t>
+          <t>8120018311</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>C OLMECAS 508</t>
+          <t>ENCINO # 216</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5476,17 +5500,17 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>19-12-2004</t>
+          <t>01-09-1985</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>ISAFERNAN.19@GMAIL.COM</t>
+          <t>ALESSANALESAN85@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>13-02-2026 15:03:03</t>
+          <t>07-02-2026 10:21:42</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5497,7 +5521,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -5507,17 +5531,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>13-02-2026 15:12:55</t>
+          <t>11-02-2026 15:32:23</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>13-02-2026 15:11:55</t>
+          <t>11-02-2026 15:31:50</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -5527,7 +5551,7 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
@@ -5537,11 +5561,19 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26210522322150003203</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
+          <t>26210522266660003022</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>VERONICA VIANEY LOYA CONTRERAS</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>499</t>
@@ -5561,12 +5593,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>343754</t>
+          <t>344965</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>21571</t>
+          <t>22782</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5576,17 +5608,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ERNESTO</t>
+          <t xml:space="preserve">JOSE LUIS </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t>SERRANO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ROSALES</t>
+          <t>TELLEZ</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5596,12 +5628,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6241578514</t>
+          <t>6241750961</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>PEDRO MATIAS GONI 353</t>
+          <t>C HORBLENDA 918</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5611,20 +5643,24 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>07-11-1978</t>
+          <t>31-03-1997</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>NETOGR78@GMAIL.COM</t>
+          <t>IAJOSELUIS@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>14-02-2026 18:11:53</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>18-02-2026 20:42:50</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O39" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5642,22 +5678,22 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>14-02-2026 18:11:54</t>
+          <t>18-02-2026 20:49:56</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>14-02-2026 18:11:54</t>
+          <t>18-02-2026 20:48:57</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -5672,7 +5708,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26210522349800003253</t>
+          <t>26210522477060003507</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
@@ -5696,12 +5732,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>341783</t>
+          <t>345189</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>19601</t>
+          <t>87354</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5711,17 +5747,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ERNESTO</t>
+          <t>MARIA ELISA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARZA </t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>ALAMILLA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5731,35 +5767,39 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>8180747965</t>
+          <t>6121717456</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>ENCINO #216</t>
+          <t>C MELITOM ALBAÑEZ 45</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>27-10-1990</t>
+          <t>17-12-2012</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>DRERNESTOGARZA@GMAIL.COM</t>
+          <t>MARIAELISAHERNANDEZ@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>07-02-2026 10:19:47</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>19-02-2026 19:10:37</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O40" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -5777,17 +5817,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>11-02-2026 15:26:34</t>
+          <t>19-02-2026 19:15:52</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>11-02-2026 15:25:43</t>
+          <t>19-02-2026 19:15:15</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5807,19 +5847,11 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26210522266420003021</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>VERONICA VIANEY LOYA CONTRERAS</t>
-        </is>
-      </c>
+          <t>26210522505670003580</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
           <t>499</t>
@@ -5827,24 +5859,24 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>341785</t>
+          <t>341114</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>19603</t>
+          <t>18932</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5854,17 +5886,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>DENIS ALEJANDRA</t>
+          <t>HANNIA ZULETT GUADALUPE</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ESTRADA</t>
+          <t xml:space="preserve">BURGOIN </t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SANTACRUZ</t>
+          <t xml:space="preserve">LUCERO </t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5874,14 +5906,10 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>8120018311</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>ENCINO # 216</t>
-        </is>
-      </c>
+          <t>6121041819</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5889,60 +5917,56 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>01-09-1985</t>
+          <t>01-12-2008</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>ALESSANALESAN85@GMAIL.COM</t>
+          <t>HANNIAZULETTBURGOIN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>07-02-2026 10:21:42</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+          <t>04-02-2026 17:38:34</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>11-02-2026 15:32:23</t>
+          <t>04-02-2026 17:42:38</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>11-02-2026 15:31:50</t>
-        </is>
-      </c>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5950,22 +5974,14 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26210522266660003022</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>VERONICA VIANEY LOYA CONTRERAS</t>
-        </is>
-      </c>
+          <t>26210522083170002489</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
@@ -5982,12 +5998,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>344965</t>
+          <t>344143</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>22782</t>
+          <t>21960</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5997,17 +6013,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE LUIS </t>
+          <t xml:space="preserve">ISABELLA </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SERRANO</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>TELLEZ</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6017,57 +6033,53 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6241750961</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>C HORBLENDA 918</t>
-        </is>
-      </c>
+          <t>6122133549</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>31-03-1997</t>
+          <t>04-06-2010</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>IAJOSELUIS@OUTLOOK.COM</t>
+          <t>CASTROISABELLA600@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>18-02-2026 20:42:50</t>
+          <t>16-02-2026 16:04:56</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>18-02-2026 20:49:56</t>
+          <t>18-02-2026 16:06:37</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -6075,21 +6087,13 @@
           <t>18-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>18-02-2026 20:48:57</t>
-        </is>
-      </c>
+      <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6097,14 +6101,22 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26210522477060003507</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
+          <t>26210522465650003472</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>VERONICA VIANEY LOYA CONTRERAS</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
@@ -6121,12 +6133,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>345189</t>
+          <t>344316</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>87354</t>
+          <t>22133</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6136,17 +6148,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>MARIA ELISA</t>
+          <t>MAYTE ANELIZ</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t xml:space="preserve">CUEVAS </t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>ALAMILLA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6156,14 +6168,10 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6121717456</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>C MELITOM ALBAÑEZ 45</t>
-        </is>
-      </c>
+          <t>6241717643</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6171,64 +6179,56 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>17-12-2012</t>
+          <t>02-01-2007</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>MARIAELISAHERNANDEZ@ICLOUD.COM</t>
+          <t>ANELIZCG07@GMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>19-02-2026 19:10:37</t>
+          <t>16-02-2026 18:53:41</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>19-02-2026 19:15:52</t>
+          <t>17-02-2026 14:17:50</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>19-02-2026 19:15:15</t>
-        </is>
-      </c>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6236,36 +6236,36 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26210522505670003580</t>
+          <t>26210522429100003408</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>343827</t>
+          <t>343166</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>21644</t>
+          <t>20983</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6275,17 +6275,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">KARLA ADRIANA </t>
+          <t>MARIA FERNANDA</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>MAYORAL</t>
+          <t>ACEVEDO</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>COTA</t>
+          <t>RUVALCABA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6122145835</t>
+          <t>6121068152</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>C JUAN SARABIA 725</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6310,17 +6310,17 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>04-11-1987</t>
+          <t>13-09-2003</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>KARLAMC4.87@GMAIL.COM</t>
+          <t>FERNANDAACEV13@GMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>15-02-2026 12:11:56</t>
+          <t>12-02-2026 07:13:35</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -6341,17 +6341,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>15-02-2026 12:17:37</t>
+          <t>12-02-2026 07:18:27</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>15-02-2026 12:16:16</t>
+          <t>12-02-2026 07:17:45</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26210522365310003259</t>
+          <t>26210522287800003090</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr"/>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Cristopher Armando Serrato</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -6395,12 +6395,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>344143</t>
+          <t>343508</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>21960</t>
+          <t>21325</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6410,17 +6410,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISABELLA </t>
+          <t xml:space="preserve">LUISA FERNANDA </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t xml:space="preserve">MURILLO </t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t xml:space="preserve">OLIVARES </t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6430,10 +6430,14 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6122133549</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>6122290863</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>C OLMECAS 508</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6441,56 +6445,60 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>04-06-2010</t>
+          <t>19-12-2004</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CASTROISABELLA600@GMAIL.COM</t>
+          <t>ISAFERNAN.19@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>16-02-2026 16:04:56</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>13-02-2026 15:03:03</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>18-02-2026 16:06:37</t>
+          <t>13-02-2026 15:12:55</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr"/>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>13-02-2026 15:11:55</t>
+        </is>
+      </c>
       <c r="U45" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6498,22 +6506,14 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26210522465650003472</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>VERONICA VIANEY LOYA CONTRERAS</t>
-        </is>
-      </c>
+          <t>26210522322150003203</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
@@ -6530,12 +6530,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>344316</t>
+          <t>344321</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>22133</t>
+          <t>22138</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6545,17 +6545,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>MAYTE ANELIZ</t>
+          <t>NOELIA ANAID</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUEVAS </t>
+          <t>ARAIZA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>ALBAÑEZ</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6241717643</t>
+          <t>6121498018</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6576,17 +6576,17 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>02-01-2007</t>
+          <t>25-05-2007</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>ANELIZCG07@GMAIL.COM</t>
+          <t>NOELIAANAIDARAIZA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>16-02-2026 18:53:41</t>
+          <t>16-02-2026 18:57:53</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>17-02-2026 14:17:50</t>
+          <t>16-02-2026 18:59:47</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T46" t="inlineStr"/>
@@ -6633,7 +6633,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26210522429100003408</t>
+          <t>26210522406620003354</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr"/>
@@ -6657,12 +6657,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>344366</t>
+          <t>342226</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>22183</t>
+          <t>20044</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6672,17 +6672,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>REYNA ICELA</t>
+          <t>ARIANY ROSALIA</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CADENA MATUS</t>
+          <t>COTA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CADENA MATUS</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6121971764</t>
+          <t>6121692055</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>REGIDORES 113</t>
+          <t>CALLE EL TRIUNFO #233</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6707,24 +6707,20 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>22-08-1987</t>
+          <t>08-10-1981</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>REYNAICELACM@GMAIL.COM</t>
+          <t>ARIANY2C@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>16-02-2026 23:34:26</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>09-02-2026 15:54:22</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6742,22 +6738,22 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>16-02-2026 23:34:27</t>
+          <t>10-02-2026 17:08:18</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>16-02-2026 23:34:27</t>
+          <t>10-02-2026 17:07:27</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -6772,11 +6768,19 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26210522412010003364</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr"/>
-      <c r="Z47" t="inlineStr"/>
+          <t>26210522238630002941</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>VERONICA VIANEY LOYA CONTRERAS</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>499</t>
@@ -6784,7 +6788,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -6923,12 +6927,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>344321</t>
+          <t>343827</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>22138</t>
+          <t>21644</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6938,17 +6942,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NOELIA ANAID</t>
+          <t xml:space="preserve">KARLA ADRIANA </t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ARAIZA</t>
+          <t>MAYORAL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ALBAÑEZ</t>
+          <t>COTA</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6958,10 +6962,14 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6121498018</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>6122145835</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>C JUAN SARABIA 725</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6969,56 +6977,60 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>25-05-2007</t>
+          <t>04-11-1987</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>NOELIAANAIDARAIZA@GMAIL.COM</t>
+          <t>KARLAMC4.87@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>16-02-2026 18:57:53</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>15-02-2026 12:11:56</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>16-02-2026 18:59:47</t>
+          <t>15-02-2026 12:17:37</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr"/>
+          <t>15-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>15-02-2026 12:16:16</t>
+        </is>
+      </c>
       <c r="U49" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr"/>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W49" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7026,14 +7038,14 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26210522406620003354</t>
+          <t>26210522365310003259</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
@@ -7050,12 +7062,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>345619</t>
+          <t>344516</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>87784</t>
+          <t>22333</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7065,17 +7077,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>AZUL</t>
+          <t>GABRIEL MARTIN</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>DOMINGUEZ</t>
+          <t>GULUARTE</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>ESCAMILLA</t>
+          <t>BARAJAS</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7085,67 +7097,67 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6121480447</t>
+          <t>6121009849</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>CHAMETLA</t>
+          <t>C AGROPECUARIA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>28-01-1977</t>
+          <t>13-02-2000</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>PLAYAZUL28@HOTMAIL.COM</t>
+          <t>MARTINBARAJAS1302@GMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>22-02-2026 13:07:59</t>
+          <t>17-02-2026 15:10:23</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>22-02-2026 13:15:30</t>
+          <t>17-02-2026 15:16:36</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>22-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>22-02-2026 13:13:25</t>
+          <t>17-02-2026 15:16:14</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -7155,7 +7167,7 @@
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
@@ -7165,19 +7177,19 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26210522563650003675</t>
+          <t>26210522431100003417</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>Cristopher Armando Serrato</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -7324,12 +7336,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>343038</t>
+          <t>344873</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20855</t>
+          <t>22690</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7339,17 +7351,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">DOLORES ITZEL </t>
+          <t>KARLA ROXANA</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUBILLOS </t>
+          <t>MURILLO</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>VALDEZ</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7359,12 +7371,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6121029534</t>
+          <t>6121532789</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>C PABLO L. GONZALEZ 235</t>
+          <t>UNIVERSIDAD</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -7374,20 +7386,24 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>10-12-1994</t>
+          <t>18-09-1984</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CUBILLOSITZEL@GMAIL.COM</t>
+          <t>KMURILLO@UABCS.MX</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>11-02-2026 16:24:22</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>18-02-2026 16:45:58</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O52" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7405,17 +7421,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>11-02-2026 16:38:56</t>
+          <t>18-02-2026 16:49:17</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>11-02-2026 16:38:17</t>
+          <t>18-02-2026 16:48:16</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -7425,7 +7441,7 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
@@ -7435,7 +7451,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26210522269110003031</t>
+          <t>26210522467350003478</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr"/>
@@ -7459,12 +7475,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>344516</t>
+          <t>345619</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>22333</t>
+          <t>87784</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7474,17 +7490,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>GABRIEL MARTIN</t>
+          <t>AZUL</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>GULUARTE</t>
+          <t>DOMINGUEZ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>BARAJAS</t>
+          <t>ESCAMILLA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7494,67 +7510,67 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>6121009849</t>
+          <t>6121480447</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>C AGROPECUARIA</t>
+          <t>CHAMETLA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>13-02-2000</t>
+          <t>28-01-1977</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>MARTINBARAJAS1302@GMAIL.COM</t>
+          <t>PLAYAZUL28@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>17-02-2026 15:10:23</t>
+          <t>22-02-2026 13:07:59</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>17-02-2026 15:16:36</t>
+          <t>22-02-2026 13:15:30</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>22-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>17-02-2026 15:16:14</t>
+          <t>22-02-2026 13:13:25</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -7564,7 +7580,7 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
@@ -7574,19 +7590,19 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26210522431100003417</t>
+          <t>26210522563650003675</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Cristopher Armando Serrato</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -7598,12 +7614,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>343761</t>
+          <t>343038</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>21578</t>
+          <t>20855</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7613,17 +7629,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>OSMAR ALEJANDRO</t>
+          <t xml:space="preserve">DOLORES ITZEL </t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LIERA </t>
+          <t xml:space="preserve">CUBILLOS </t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7633,39 +7649,35 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>6151559659</t>
+          <t>6121029534</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>CENTRO</t>
+          <t>C PABLO L. GONZALEZ 235</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>26-07-2001</t>
+          <t>10-12-1994</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>LIERAGOMEZOSMARALEJANDRO@GMAIL.COM</t>
+          <t>CUBILLOSITZEL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>14-02-2026 23:55:59</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>11-02-2026 16:24:22</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7683,17 +7695,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>20-02-2026 05:36:59</t>
+          <t>11-02-2026 16:38:56</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>20-02-2026 05:34:42</t>
+          <t>11-02-2026 16:38:17</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -7703,7 +7715,7 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -7713,14 +7725,10 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26210522509510003598</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26210522269110003031</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr">
         <is>
@@ -7729,24 +7737,24 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>342527</t>
+          <t>344230</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>20344</t>
+          <t>22047</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7756,17 +7764,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>DIANA</t>
+          <t>SERGIO ENRIQUE</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MADRID</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>BURQUEZ</t>
+          <t>ORDUÑO</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7776,63 +7784,67 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6242249486</t>
+          <t>6121770347</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>AYENDE #1720</t>
+          <t>C BAHIA DE SALINAS 89</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>15-05-1995</t>
+          <t>26-01-1989</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>DIANAMB_@HOTMAIL.COM</t>
+          <t>SHEKO84_26@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>10-02-2026 07:13:24</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+          <t>16-02-2026 17:42:13</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>10-02-2026 07:22:03</t>
+          <t>25-02-2026 15:36:45</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>25-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>10-02-2026 07:20:53</t>
+          <t>25-02-2026 15:36:06</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -7852,19 +7864,27 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26210522224130002896</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr"/>
-      <c r="Z55" t="inlineStr"/>
+          <t>26210522655670003952</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>VERONICA VIANEY LOYA CONTRERAS</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -7876,12 +7896,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>346048</t>
+          <t>342527</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>88213</t>
+          <t>20344</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7891,17 +7911,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADALBERTO ABIMAEL </t>
+          <t>DIANA</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ZAZUETA</t>
+          <t>MADRID</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>VEGA</t>
+          <t>BURQUEZ</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -7911,39 +7931,35 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6122191467</t>
+          <t>6242249486</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>C MANUEL ENCINAS 1353</t>
+          <t>AYENDE #1720</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>21-10-1992</t>
+          <t>15-05-1995</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>REBUILDNERVE@GMAIL.COM</t>
+          <t>DIANAMB_@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>23-02-2026 20:33:49</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>10-02-2026 07:13:24</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7961,17 +7977,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>23-02-2026 20:38:02</t>
+          <t>10-02-2026 07:22:03</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>23-02-2026 20:37:01</t>
+          <t>10-02-2026 07:20:53</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -7981,7 +7997,7 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
@@ -7991,7 +8007,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26210522601920003802</t>
+          <t>26210522224130002896</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr"/>
@@ -8003,24 +8019,24 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>344873</t>
+          <t>342701</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>22690</t>
+          <t>20518</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8030,17 +8046,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>KARLA ROXANA</t>
+          <t>SUMIKO MARIA</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>MURILLO</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t>AGUIRRE</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8050,14 +8066,10 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>6121532789</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>UNIVERSIDAD</t>
-        </is>
-      </c>
+          <t>6121220205</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -8065,64 +8077,56 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>18-09-1984</t>
+          <t>07-04-2013</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>KMURILLO@UABCS.MX</t>
+          <t>SUMIJOAGUIRREFISHER@GMAIL.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>18-02-2026 16:45:58</t>
+          <t>10-02-2026 16:22:22</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>18-02-2026 16:49:17</t>
+          <t>10-02-2026 16:28:08</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>18-02-2026 16:48:16</t>
-        </is>
-      </c>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8130,14 +8134,14 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26210522467350003478</t>
+          <t>26210522236680002929</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
@@ -8154,12 +8158,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>342701</t>
+          <t>343761</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>20518</t>
+          <t>21578</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8169,17 +8173,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SUMIKO MARIA</t>
+          <t>OSMAR ALEJANDRO</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t xml:space="preserve"> LIERA </t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>AGUIRRE</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8189,67 +8193,79 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>6121220205</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>6151559659</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>CENTRO</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>07-04-2013</t>
+          <t>26-07-2001</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>SUMIJOAGUIRREFISHER@GMAIL.COM</t>
+          <t>LIERAGOMEZOSMARALEJANDRO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>10-02-2026 16:22:22</t>
+          <t>14-02-2026 23:55:59</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>10-02-2026 16:28:08</t>
+          <t>20-02-2026 05:36:59</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T58" t="inlineStr"/>
+          <t>20-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>20-02-2026 05:34:42</t>
+        </is>
+      </c>
       <c r="U58" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr"/>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W58" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8257,24 +8273,28 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>26210522236680002929</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr"/>
+          <t>26210522509510003598</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -8416,12 +8436,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>346045</t>
+          <t>343754</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>88210</t>
+          <t>21571</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8431,17 +8451,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">LIZBETH </t>
+          <t>ERNESTO</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>PIÑUELAS</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANTIAGO </t>
+          <t>ROSALES</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -8451,39 +8471,35 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>6121701231</t>
+          <t>6241578514</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>C MANUEL ENCINAS 1353</t>
+          <t>PEDRO MATIAS GONI 353</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>10-12-1997</t>
+          <t>07-11-1978</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>LIZPISA94@GMAIL.COM</t>
+          <t>NETOGR78@GMAIL.COM</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>23-02-2026 20:23:38</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>14-02-2026 18:11:53</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8501,29 +8517,29 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>23-02-2026 20:32:15</t>
+          <t>14-02-2026 18:11:54</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>23-02-2026 20:31:30</t>
+          <t>14-02-2026 18:11:54</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="W60" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8531,7 +8547,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>26210522601760003801</t>
+          <t>26210522349800003253</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr"/>
@@ -8543,24 +8559,24 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>343251</t>
+          <t>346045</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>21068</t>
+          <t>88210</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8570,17 +8586,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>TAMARA</t>
+          <t xml:space="preserve">LIZBETH </t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>PIÑUELAS</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AGUIÑAGA</t>
+          <t xml:space="preserve">SANTIAGO </t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -8590,10 +8606,14 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>5541288966</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>6121701231</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>C MANUEL ENCINAS 1353</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -8601,56 +8621,64 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>21-12-2004</t>
+          <t>10-12-1997</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>TAMARA211204@GMAIL.COM</t>
+          <t>LIZPISA94@GMAIL.COM</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>12-02-2026 13:32:17</t>
+          <t>23-02-2026 20:23:38</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>12-02-2026 13:33:36</t>
+          <t>23-02-2026 20:32:15</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>23-02-2026 20:31:30</t>
+        </is>
+      </c>
       <c r="U61" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr"/>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W61" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8658,36 +8686,36 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>26210522293540003108</t>
+          <t>26210522601760003801</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="inlineStr"/>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>343379</t>
+          <t>343251</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>21196</t>
+          <t>21068</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8697,17 +8725,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>SARA BEATRIZ</t>
+          <t>TAMARA</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASTELLANOS </t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>AGUIÑAGA</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -8717,14 +8745,10 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>6122327477</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>C MELON 121</t>
-        </is>
-      </c>
+          <t>5541288966</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -8732,38 +8756,42 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>03-06-1981</t>
+          <t>21-12-2004</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>DRA.SARACASTELLANOS@GMAIL.COM</t>
+          <t>TAMARA211204@GMAIL.COM</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>12-02-2026 18:54:35</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
+          <t>12-02-2026 13:32:17</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>12-02-2026 18:58:52</t>
+          <t>12-02-2026 13:33:36</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -8771,21 +8799,13 @@
           <t>12-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>12-02-2026 18:58:05</t>
-        </is>
-      </c>
+      <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V62" t="inlineStr"/>
       <c r="W62" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8793,14 +8813,14 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>26210522303780003149</t>
+          <t>26210522293540003108</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
@@ -8817,12 +8837,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>343375</t>
+          <t>343379</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>21192</t>
+          <t>21196</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8832,17 +8852,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIO ALBERTO </t>
+          <t>SARA BEATRIZ</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ROSAS</t>
+          <t xml:space="preserve">CASTELLANOS </t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANRIQUEZ </t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -8852,7 +8872,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>6122343338</t>
+          <t>6122327477</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -8862,22 +8882,22 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>12-12-1977</t>
+          <t>03-06-1981</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>ROSASCASTELLANOS@GMAIL.COM</t>
+          <t>DRA.SARACASTELLANOS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>12-02-2026 18:48:15</t>
+          <t>12-02-2026 18:54:35</t>
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
@@ -8898,7 +8918,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>12-02-2026 18:53:02</t>
+          <t>12-02-2026 18:58:52</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -8908,7 +8928,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>12-02-2026 18:52:16</t>
+          <t>12-02-2026 18:58:05</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -8928,7 +8948,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>26210522303620003147</t>
+          <t>26210522303780003149</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr"/>
@@ -8952,12 +8972,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>344727</t>
+          <t>344366</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>22544</t>
+          <t>22183</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -8967,17 +8987,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>MARIA TERESA</t>
+          <t>REYNA ICELA</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>CADENA MATUS</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>QUEZADA</t>
+          <t>CADENA MATUS</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -8987,12 +9007,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>5578843819</t>
+          <t>6121971764</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>CENTRO</t>
+          <t>REGIDORES 113</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -9002,57 +9022,57 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>31-05-1969</t>
+          <t>22-08-1987</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>MARIATERESAPEREZQUEZADA@GMAIL.COM</t>
+          <t>REYNAICELACM@GMAIL.COM</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>18-02-2026 05:24:32</t>
+          <t>16-02-2026 23:34:26</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>19-02-2026 06:46:30</t>
+          <t>16-02-2026 23:34:27</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>19-02-2026 06:44:39</t>
+          <t>16-02-2026 23:34:27</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -9067,18 +9087,14 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>26210522487370003516</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26210522412010003364</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="inlineStr"/>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
@@ -9095,12 +9111,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>345078</t>
+          <t>343375</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>87243</t>
+          <t>21192</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9110,17 +9126,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA VICTORIA </t>
+          <t xml:space="preserve">MARIO ALBERTO </t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">BARRANCO </t>
+          <t>ROSAS</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASTRO </t>
+          <t xml:space="preserve">MANRIQUEZ </t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -9130,39 +9146,35 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>6123489475</t>
+          <t>6122343338</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>C MAGUEY 4551</t>
+          <t>C MELON 121</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>08-02-1994</t>
+          <t>12-12-1977</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>ANACSTRO@GMAIL.COM</t>
+          <t>ROSASCASTELLANOS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>19-02-2026 14:27:10</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>12-02-2026 18:48:15</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -9180,17 +9192,17 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>19-02-2026 14:32:01</t>
+          <t>12-02-2026 18:53:02</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>19-02-2026 14:31:19</t>
+          <t>12-02-2026 18:52:16</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -9210,7 +9222,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>26210522495380003538</t>
+          <t>26210522303620003147</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr"/>
@@ -9222,24 +9234,24 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>345136</t>
+          <t>346048</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>87301</t>
+          <t>88213</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9249,17 +9261,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>FRANCISCA CECILIA</t>
+          <t xml:space="preserve">ADALBERTO ABIMAEL </t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>BARRETO</t>
+          <t>ZAZUETA</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>BARRETO</t>
+          <t>VEGA</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -9269,67 +9281,79 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>6122148757</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>6122191467</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>C MANUEL ENCINAS 1353</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>22-11-1987</t>
+          <t>21-10-1992</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>BARRETOCECILIA925@GMAIL.COM</t>
+          <t>REBUILDNERVE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>19-02-2026 17:04:50</t>
+          <t>23-02-2026 20:33:49</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>19-02-2026 17:05:35</t>
+          <t>23-02-2026 20:38:02</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T66" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>23-02-2026 20:37:01</t>
+        </is>
+      </c>
       <c r="U66" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V66" t="inlineStr"/>
       <c r="W66" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9337,22 +9361,570 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>26210522500360003555</t>
+          <t>26210522601920003802</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="inlineStr"/>
       <c r="AA66" t="inlineStr">
         <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>346328</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>88493</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JORGE </t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RUIZ </t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GARCIA </t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>6122133679</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>PRIV AZURITA M2</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>12-06-1986</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>JM.AUTOSPA.LAPAZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>24-02-2026 20:03:17</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>24-02-2026 20:22:54</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>24-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>24-02-2026 20:07:54</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>26210522636910003900</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>344727</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>22544</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>MARIA TERESA</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>PEREZ</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>QUEZADA</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>5578843819</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>CENTRO</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>31-05-1969</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>MARIATERESAPEREZQUEZADA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>18-02-2026 05:24:32</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>19-02-2026 06:46:30</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>19-02-2026 06:44:39</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>26210522487370003516</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>Christian Jahassiel Castro Navarro</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>345078</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>87243</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANA VICTORIA </t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BARRANCO </t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CASTRO </t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>6123489475</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>C MAGUEY 4551</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>08-02-1994</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>ANACSTRO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>19-02-2026 14:27:10</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>19-02-2026 14:32:01</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>19-02-2026 14:31:19</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>26210522495380003538</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>345136</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>87301</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>FRANCISCA CECILIA</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>BARRETO</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>BARRETO</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>6122148757</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>22-11-1987</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>BARRETOCECILIA925@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>19-02-2026 17:04:50</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
           <t>899</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>19-02-2026 17:05:35</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>26210522500360003555</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
+      <c r="AC70" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__PASEO LA PAZ.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__PASEO LA PAZ.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC70"/>
+  <dimension ref="A1:AC72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1138,12 +1138,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>340279</t>
+          <t>322857</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18097</t>
+          <t>19796</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1153,17 +1153,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUZ ANGELICA </t>
+          <t>NAYELI</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOA </t>
+          <t>MARILES</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">VEGA </t>
+          <t>CORDERO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1173,12 +1173,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6121042102</t>
+          <t>6122343921</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>C MANUEL F MONTAÑO</t>
+          <t>PISTACHE 144</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1188,17 +1188,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>20-09-1980</t>
+          <t>23-12-1992</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>LICLOAVEGA20@GMAIL.COM</t>
+          <t>NAYUNOCHO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-02-2026 16:39:48</t>
+          <t>10-11-2025 12:13:22</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1219,17 +1219,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-02-2026 16:43:50</t>
+          <t>05-02-2026 15:40:20</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>02-02-2026 16:42:42</t>
+          <t>05-02-2026 15:40:02</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26210522017090002277</t>
+          <t>26210522108860002579</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Guillermo  Garcia De Alba Velazquez</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1273,12 +1273,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>340290</t>
+          <t>339939</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18108</t>
+          <t>17757</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1288,17 +1288,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CHRISTIAN ALEJANDRO </t>
+          <t>GABRIELA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CERVERA </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CERVANTES</t>
+          <t>OVALLE</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1308,32 +1308,32 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6122289427</t>
+          <t>6121390387</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>C POSEIDON 666</t>
+          <t>CERRO</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>14-11-2011</t>
+          <t>17-10-1997</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CHRISTIANCERV777@GMAIL.COM</t>
+          <t>OVALLEGABRIELA97@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-02-2026 16:52:38</t>
+          <t>02-02-2026 09:09:56</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-02-2026 16:58:16</t>
+          <t>02-02-2026 09:17:23</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>02-02-2026 16:57:36</t>
+          <t>02-02-2026 09:16:38</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26210522017700002281</t>
+          <t>26210522002720002245</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
@@ -1408,12 +1408,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>322857</t>
+          <t>340015</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>19796</t>
+          <t>17833</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NAYELI</t>
+          <t>MARIA FERNANDA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MARILES</t>
+          <t>AVILES</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CORDERO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1443,12 +1443,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6122343921</t>
+          <t>6121058570</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PISTACHE 144</t>
+          <t>CENTRO</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1458,17 +1458,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>23-12-1992</t>
+          <t>08-12-1997</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>NAYUNOCHO@GMAIL.COM</t>
+          <t>AVILESSANCHEZFERNANDA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>10-11-2025 12:13:22</t>
+          <t>02-02-2026 10:34:28</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1489,17 +1489,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>05-02-2026 15:40:20</t>
+          <t>03-02-2026 05:22:36</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>05-02-2026 15:40:02</t>
+          <t>03-02-2026 05:22:05</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1519,10 +1519,14 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26210522108860002579</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr"/>
+          <t>26210522027620002320</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1531,7 +1535,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Guillermo  Garcia De Alba Velazquez</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1543,12 +1547,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>340215</t>
+          <t>340279</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18033</t>
+          <t>18097</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1558,17 +1562,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRANCISCO JAVIER </t>
+          <t xml:space="preserve">LUZ ANGELICA </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANCHEZ </t>
+          <t xml:space="preserve">LOA </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>IZAGUIRRE</t>
+          <t xml:space="preserve">VEGA </t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1578,32 +1582,32 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6121370121</t>
+          <t>6121042102</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>C ISLA PATO 107</t>
+          <t>C MANUEL F MONTAÑO</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>26-03-1977</t>
+          <t>20-09-1980</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>FRANCISCO.SAN.IZA@GMAIL.COM</t>
+          <t>LICLOAVEGA20@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-02-2026 15:28:02</t>
+          <t>02-02-2026 16:39:48</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1614,7 +1618,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1624,7 +1628,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-02-2026 15:40:28</t>
+          <t>02-02-2026 16:43:50</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1634,7 +1638,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>02-02-2026 15:39:32</t>
+          <t>02-02-2026 16:42:42</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1654,7 +1658,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26210522014940002273</t>
+          <t>26210522017090002277</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
@@ -1678,12 +1682,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>341119</t>
+          <t>340290</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18937</t>
+          <t>18108</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1693,17 +1697,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">HANNIA MARIA </t>
+          <t xml:space="preserve">CHRISTIAN ALEJANDRO </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASTRO </t>
+          <t xml:space="preserve">CERVERA </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>CERVANTES</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1713,67 +1717,75 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6121543278</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>6122289427</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>C POSEIDON 666</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>25-01-2008</t>
+          <t>14-11-2011</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>HANNIATAY13@ICLOUD.COM</t>
+          <t>CHRISTIANCERV777@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>04-02-2026 17:46:50</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>02-02-2026 16:52:38</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>04-02-2026 17:47:55</t>
+          <t>02-02-2026 16:58:16</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>02-02-2026 16:57:36</t>
+        </is>
+      </c>
       <c r="U10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1781,19 +1793,19 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26210522083460002490</t>
+          <t>26210522017700002281</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1805,12 +1817,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>339939</t>
+          <t>295801</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>17757</t>
+          <t>93299</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1820,17 +1832,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>GABRIELA</t>
+          <t>MARIBEL</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t xml:space="preserve">PEREZ </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>OVALLE</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1840,12 +1852,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6121390387</t>
+          <t>6122147740</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>CERRO</t>
+          <t>CADIZ #367</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1855,20 +1867,24 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>17-10-1997</t>
+          <t>05-02-1982</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>OVALLEGABRIELA97@GMAIL.COM</t>
+          <t>MARIBEPZNZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-02-2026 09:09:56</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>02-06-2025 07:55:35</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -1886,17 +1902,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>02-02-2026 09:17:23</t>
+          <t>24-02-2026 10:40:21</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>24-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>02-02-2026 09:16:38</t>
+          <t>24-02-2026 10:38:54</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1906,7 +1922,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1916,7 +1932,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26210522002720002245</t>
+          <t>26210522615770003833</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
@@ -1928,24 +1944,24 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>340015</t>
+          <t>340353</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>17833</t>
+          <t>18171</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1955,17 +1971,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA</t>
+          <t xml:space="preserve">GIBERTO </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AVILES</t>
+          <t xml:space="preserve">MENDEZ </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t xml:space="preserve">HALE </t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1975,32 +1991,32 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6121058570</t>
+          <t>6121528946</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CENTRO</t>
+          <t>C CERRADA SANTA INES 890</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>08-12-1997</t>
+          <t>23-11-2001</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>AVILESSANCHEZFERNANDA@GMAIL.COM</t>
+          <t>GILBERTO.MEN20011@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>02-02-2026 10:34:28</t>
+          <t>02-02-2026 18:54:26</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2011,7 +2027,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -2021,17 +2037,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>03-02-2026 05:22:36</t>
+          <t>02-02-2026 18:58:19</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>03-02-2026 05:22:05</t>
+          <t>02-02-2026 18:58:00</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2051,14 +2067,10 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26210522027620002320</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26210522021420002304</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
@@ -2067,7 +2079,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2079,12 +2091,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>295801</t>
+          <t>340215</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>93299</t>
+          <t>18033</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2094,17 +2106,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MARIBEL</t>
+          <t xml:space="preserve">FRANCISCO JAVIER </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEREZ </t>
+          <t xml:space="preserve">SANCHEZ </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t>IZAGUIRRE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2114,39 +2126,35 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6122147740</t>
+          <t>6121370121</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CADIZ #367</t>
+          <t>C ISLA PATO 107</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>05-02-1982</t>
+          <t>26-03-1977</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>MARIBEPZNZ@GMAIL.COM</t>
+          <t>FRANCISCO.SAN.IZA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>02-06-2025 07:55:35</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>02-02-2026 15:28:02</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -2164,17 +2172,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>24-02-2026 10:40:21</t>
+          <t>02-02-2026 15:40:28</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>24-02-2026 10:38:54</t>
+          <t>02-02-2026 15:39:32</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2184,7 +2192,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2194,7 +2202,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26210522615770003833</t>
+          <t>26210522014940002273</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
@@ -2206,24 +2214,24 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>340353</t>
+          <t>332784</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18171</t>
+          <t>14805</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2233,17 +2241,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">GIBERTO </t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">MENDEZ </t>
+          <t>ROBLES</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">HALE </t>
+          <t>ARANDA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2253,12 +2261,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6121528946</t>
+          <t>5585803795</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>C CERRADA SANTA INES 890</t>
+          <t xml:space="preserve">PUEBLO NUEVO </t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2268,17 +2276,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>23-11-2001</t>
+          <t>04-03-1978</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>GILBERTO.MEN20011@GMAIL.COM</t>
+          <t>ALEJANDRO.ROBLESARANDA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-02-2026 18:54:26</t>
+          <t>07-01-2026 09:40:49</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2299,17 +2307,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>02-02-2026 18:58:19</t>
+          <t>03-02-2026 14:14:15</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>02-02-2026 18:58:00</t>
+          <t>03-02-2026 13:57:02</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2329,7 +2337,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26210522021420002304</t>
+          <t>26210522040850002349</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
@@ -2353,12 +2361,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>342188</t>
+          <t>336694</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20006</t>
+          <t>22420</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2368,17 +2376,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EDNA</t>
+          <t>ZULEMA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TAMAYO</t>
+          <t>HIGUERA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2388,12 +2396,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6123489545</t>
+          <t>6122380771</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>PRIV MARINA CENTRAL 117</t>
+          <t>CENTRO</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2403,17 +2411,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>02-04-1974</t>
+          <t>08-04-1983</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>EDNA_321@HOTMAIL.COM</t>
+          <t>ZULEMA@BAJASURREALTORS.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>09-02-2026 14:43:59</t>
+          <t>21-01-2026 10:28:18</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2424,7 +2432,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PROMO ENERO 12 MESES</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2434,17 +2442,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>11-02-2026 13:12:45</t>
+          <t>02-02-2026 09:06:56</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>28-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>11-02-2026 13:12:26</t>
+          <t>28-01-2026 09:24:49</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2454,7 +2462,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -2464,7 +2472,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26210522263830003013</t>
+          <t>26210522002210002243</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2472,11 +2480,7 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>CRISTINA AYLIN CHAVEZ GONZALEZ</t>
-        </is>
-      </c>
+      <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
           <t>499</t>
@@ -2774,12 +2778,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>341390</t>
+          <t>341797</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19208</t>
+          <t>19615</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2789,17 +2793,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FERNANDA JETSEL</t>
+          <t>SUSANA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">TAPIZ </t>
+          <t>PASALAGUA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2809,12 +2813,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6121007438</t>
+          <t>6121590135</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAN FERNANDO </t>
+          <t>PRIV PALO DE SANTA RITA 9</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2824,17 +2828,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>21-10-1985</t>
+          <t>06-02-1966</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>SINDICATO.JEC@GMAIL.COM</t>
+          <t>SIPHITYA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>05-02-2026 17:08:31</t>
+          <t>07-02-2026 10:52:31</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2855,17 +2859,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>05-02-2026 17:12:39</t>
+          <t>07-02-2026 11:37:55</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>07-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>05-02-2026 17:12:22</t>
+          <t>07-02-2026 11:37:04</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2885,10 +2889,14 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26210522112170002589</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr"/>
+          <t>26210522160000002733</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
@@ -2897,7 +2905,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2909,12 +2917,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>342520</t>
+          <t>339764</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20337</t>
+          <t>17582</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2924,17 +2932,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>JOSE EDUARDO</t>
+          <t xml:space="preserve">WILIAM ULISES </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>LIMOM</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2944,12 +2952,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6121196214</t>
+          <t>6691484335</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>DEL ESTRIBO</t>
+          <t xml:space="preserve">C VALTIERRA 324 </t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2959,17 +2967,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>03-01-1992</t>
+          <t>21-09-1990</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>LIMON.EDUARDO@HOTMAIL.COM</t>
+          <t>WIL_UCL@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>10-02-2026 06:36:49</t>
+          <t>01-02-2026 10:17:19</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2980,7 +2988,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2990,17 +2998,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>10-02-2026 06:41:55</t>
+          <t>01-02-2026 10:33:00</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>01-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>10-02-2026 06:41:25</t>
+          <t>01-02-2026 10:25:23</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3020,7 +3028,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26210522223420002894</t>
+          <t>26210521989080002222</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
@@ -3032,7 +3040,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Cristopher Armando Serrato</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3044,12 +3052,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>341986</t>
+          <t>342051</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19804</t>
+          <t>19869</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3059,17 +3067,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>KARLA ELIZABETH</t>
+          <t xml:space="preserve">CLAUDIA </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>BERLANGA</t>
+          <t>AGUAYO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CALDERON</t>
+          <t>OJEDA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3079,10 +3087,14 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5577876880</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>8123512800</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>CENTRO</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3090,17 +3102,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>22-05-2001</t>
+          <t>13-11-2002</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>BERLANGACALDERONELIZABETH22@GMAIL.COM</t>
+          <t>CLAUDIABEATRIZ.AGUAYO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>09-02-2026 04:13:10</t>
+          <t>09-02-2026 08:32:35</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3110,36 +3122,44 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>09-02-2026 04:15:04</t>
+          <t>11-02-2026 09:29:24</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr"/>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>11-02-2026 09:28:31</t>
+        </is>
+      </c>
       <c r="U20" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr"/>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W20" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3147,36 +3167,40 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26210522174170002753</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr"/>
+          <t>26210522260760002999</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>341797</t>
+          <t>341390</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19615</t>
+          <t>19208</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3186,17 +3210,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SUSANA</t>
+          <t>FERNANDA JETSEL</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PASALAGUA</t>
+          <t xml:space="preserve">TAPIZ </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3206,12 +3230,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6121590135</t>
+          <t>6121007438</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>PRIV PALO DE SANTA RITA 9</t>
+          <t xml:space="preserve">SAN FERNANDO </t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3221,17 +3245,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>06-02-1966</t>
+          <t>21-10-1985</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>SIPHITYA@GMAIL.COM</t>
+          <t>SINDICATO.JEC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>07-02-2026 10:52:31</t>
+          <t>05-02-2026 17:08:31</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3252,17 +3276,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>07-02-2026 11:37:55</t>
+          <t>05-02-2026 17:12:39</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>07-02-2026 11:37:04</t>
+          <t>05-02-2026 17:12:22</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3282,14 +3306,10 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26210522160000002733</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26210522112170002589</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
@@ -3298,7 +3318,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3310,12 +3330,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>342427</t>
+          <t>340286</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20244</t>
+          <t>18104</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3325,17 +3345,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICOLAS </t>
+          <t xml:space="preserve">AMY ANGELINE </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PERPULI</t>
+          <t xml:space="preserve">GUZMAN </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>VERDUGO</t>
+          <t xml:space="preserve">LOA </t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3345,67 +3365,75 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6121614567</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>6121220630</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C MANUEL F MONTOYA </t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>06-03-1973</t>
+          <t>20-01-2010</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>NICOLASPERPULIVERDUGO@HOTMAIL.COM</t>
+          <t>LICLOAVEGA200@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>09-02-2026 19:09:18</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>02-02-2026 16:44:59</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>09-02-2026 19:12:38</t>
+          <t>02-02-2026 16:47:48</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>09-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>02-02-2026 16:46:46</t>
+        </is>
+      </c>
       <c r="U22" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3413,14 +3441,14 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26210522209990002868</t>
+          <t>26210522017270002279</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3437,12 +3465,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>342684</t>
+          <t>340590</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20501</t>
+          <t>18408</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3452,17 +3480,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANTIAGO </t>
+          <t xml:space="preserve">ANA LAURA </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUEN </t>
+          <t xml:space="preserve">MEZA </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t>MUNDO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3472,67 +3500,75 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6122186206</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>6123520177</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ANDADOR LAS PALMERAS E 615</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>06-10-2008</t>
+          <t>06-07-2003</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>SANTIAGOCUEN23@GMAIL.COM</t>
+          <t>MANALAURA346@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>10-02-2026 15:52:34</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>03-02-2026 14:17:27</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>10-02-2026 15:55:25</t>
+          <t>03-02-2026 14:22:36</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr"/>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>03-02-2026 14:22:15</t>
+        </is>
+      </c>
       <c r="U23" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W23" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3540,14 +3576,14 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26210522235410002926</t>
+          <t>26210522041020002351</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3564,12 +3600,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>343254</t>
+          <t>341986</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21071</t>
+          <t>19804</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3579,17 +3615,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>JOUSY ISABELLA</t>
+          <t>KARLA ELIZABETH</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>BERLANGA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>CALDERON</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3599,7 +3635,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6391613622</t>
+          <t>5577876880</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3610,17 +3646,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>12-10-2003</t>
+          <t>22-05-2001</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>ISABELLAMENDOZAVV@OUTLOOK.COM</t>
+          <t>BERLANGACALDERONELIZABETH22@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>12-02-2026 13:36:03</t>
+          <t>09-02-2026 04:13:10</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3635,22 +3671,22 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>12-02-2026 13:37:01</t>
+          <t>09-02-2026 04:15:04</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -3667,36 +3703,36 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26210522293680003109</t>
+          <t>26210522174170002753</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Cristopher Armando Serrato</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>343458</t>
+          <t>340554</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>21275</t>
+          <t>18372</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3706,17 +3742,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>EDUARDO ALEXIS</t>
+          <t>JANNETT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>VEGA</t>
+          <t>CALDERON</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>VIEYRA</t>
+          <t>SCHCOLNICK</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3726,10 +3762,14 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6121677253</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>6121042182</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>CARRETERA AL NORTE KM 11 PRIV. LAS QUINTAS DEL MAR 7</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3737,56 +3777,60 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>08-04-1991</t>
+          <t>22-09-2004</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>EDUARDOVIEYRA06@GMAIL.COM</t>
+          <t>JANNETT.22099@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>13-02-2026 10:06:29</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>03-02-2026 13:02:59</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>13-02-2026 10:17:33</t>
+          <t>03-02-2026 13:08:32</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr"/>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>03-02-2026 13:07:59</t>
+        </is>
+      </c>
       <c r="U25" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr"/>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W25" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3794,19 +3838,19 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26210522318120003186</t>
+          <t>26210522039110002341</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3818,12 +3862,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>343509</t>
+          <t>340350</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21326</t>
+          <t>18168</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3833,17 +3877,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANDRA DELMA </t>
+          <t xml:space="preserve">LUIS MANUEL </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">OLIVARES </t>
+          <t>CASILLAS</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>VIVAR</t>
+          <t>HALE</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3853,32 +3897,32 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6121310729</t>
+          <t>6121975782</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>C OLMECAS 508</t>
+          <t xml:space="preserve">C GASPAR VELA </t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>16-04-1976</t>
+          <t>24-08-1999</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>SANDYPRICES.19@GMAIL.COM</t>
+          <t>LUISCASILLAS_19@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>13-02-2026 15:14:31</t>
+          <t>02-02-2026 18:42:38</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3889,7 +3933,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -3899,17 +3943,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>13-02-2026 15:17:56</t>
+          <t>02-02-2026 18:50:43</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>13-02-2026 15:17:37</t>
+          <t>02-02-2026 18:49:33</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3929,7 +3973,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26210522322300003205</t>
+          <t>26210522021200002303</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
@@ -3953,12 +3997,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>332784</t>
+          <t>342427</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>14805</t>
+          <t>20244</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3968,17 +4012,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t xml:space="preserve">NICOLAS </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ROBLES</t>
+          <t>PERPULI</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ARANDA</t>
+          <t>VERDUGO</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3988,14 +4032,10 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>5585803795</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PUEBLO NUEVO </t>
-        </is>
-      </c>
+          <t>6121614567</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4003,60 +4043,56 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>04-03-1978</t>
+          <t>06-03-1973</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>ALEJANDRO.ROBLESARANDA@GMAIL.COM</t>
+          <t>NICOLASPERPULIVERDUGO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>07-01-2026 09:40:49</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>09-02-2026 19:09:18</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>03-02-2026 14:14:15</t>
+          <t>09-02-2026 19:12:38</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>03-02-2026 13:57:02</t>
-        </is>
-      </c>
+          <t>09-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4064,14 +4100,14 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26210522040850002349</t>
+          <t>26210522209990002868</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -4088,12 +4124,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>336694</t>
+          <t>342684</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>22420</t>
+          <t>20501</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4103,17 +4139,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ZULEMA</t>
+          <t xml:space="preserve">SANTIAGO </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>HIGUERA</t>
+          <t xml:space="preserve">CUEN </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4123,75 +4159,67 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6122380771</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>CENTRO</t>
-        </is>
-      </c>
+          <t>6122186206</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>08-04-1983</t>
+          <t>06-10-2008</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>ZULEMA@BAJASURREALTORS.COM</t>
+          <t>SANTIAGOCUEN23@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>21-01-2026 10:28:18</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>10-02-2026 15:52:34</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>PROMO ENERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>02-02-2026 09:06:56</t>
+          <t>10-02-2026 15:55:25</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>28-02-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>28-01-2026 09:24:49</t>
-        </is>
-      </c>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4199,23 +4227,19 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26210522002210002243</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26210522235410002926</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4227,12 +4251,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>342051</t>
+          <t>341119</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19869</t>
+          <t>18937</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4242,17 +4266,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLAUDIA </t>
+          <t xml:space="preserve">HANNIA MARIA </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AGUAYO</t>
+          <t xml:space="preserve">CASTRO </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>OJEDA</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4262,14 +4286,10 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>8123512800</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>CENTRO</t>
-        </is>
-      </c>
+          <t>6121543278</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4277,17 +4297,17 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>13-11-2002</t>
+          <t>25-01-2008</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLAUDIABEATRIZ.AGUAYO@GMAIL.COM</t>
+          <t>HANNIATAY13@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>09-02-2026 08:32:35</t>
+          <t>04-02-2026 17:46:50</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4297,44 +4317,36 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>11-02-2026 09:29:24</t>
+          <t>04-02-2026 17:47:55</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>11-02-2026 09:28:31</t>
-        </is>
-      </c>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4342,23 +4354,19 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26210522260760002999</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26210522083460002490</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4370,12 +4378,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>342302</t>
+          <t>342490</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20120</t>
+          <t>20307</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4385,17 +4393,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">MELANIE </t>
+          <t>RENEE ALESSANDRA</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ALBAÑEZ</t>
+          <t xml:space="preserve">CESEÑA </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t xml:space="preserve">DAVIS </t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4405,14 +4413,10 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6643640599</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>AGUA DULCE 618</t>
-        </is>
-      </c>
+          <t>6122046111</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4420,38 +4424,42 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>01-05-1980</t>
+          <t>20-02-2007</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>ANIEALRO2020@GMAIL.COM</t>
+          <t>RENEEE777111@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>09-02-2026 17:06:10</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+          <t>09-02-2026 20:30:27</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>09-02-2026 17:08:49</t>
+          <t>09-02-2026 20:32:52</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -4459,21 +4467,13 @@
           <t>09-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>09-02-2026 17:08:25</t>
-        </is>
-      </c>
+      <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4481,14 +4481,14 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26210522200900002835</t>
+          <t>26210522213810002877</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -4505,12 +4505,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>340590</t>
+          <t>342302</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>18408</t>
+          <t>20120</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4520,17 +4520,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA LAURA </t>
+          <t xml:space="preserve">MELANIE </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEZA </t>
+          <t>ALBAÑEZ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MUNDO</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4540,12 +4540,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6123520177</t>
+          <t>6643640599</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>ANDADOR LAS PALMERAS E 615</t>
+          <t>AGUA DULCE 618</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4555,17 +4555,17 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>06-07-2003</t>
+          <t>01-05-1980</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>MANALAURA346@GMAIL.COM</t>
+          <t>ANIEALRO2020@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>03-02-2026 14:17:27</t>
+          <t>09-02-2026 17:06:10</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4586,17 +4586,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>03-02-2026 14:22:36</t>
+          <t>09-02-2026 17:08:49</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>03-02-2026 14:22:15</t>
+          <t>09-02-2026 17:08:25</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26210522041020002351</t>
+          <t>26210522200900002835</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
@@ -4640,12 +4640,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>339764</t>
+          <t>341114</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>17582</t>
+          <t>18932</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4655,17 +4655,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">WILIAM ULISES </t>
+          <t>HANNIA ZULETT GUADALUPE</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t xml:space="preserve">BURGOIN </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t xml:space="preserve">LUCERO </t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4675,75 +4675,67 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6691484335</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C VALTIERRA 324 </t>
-        </is>
-      </c>
+          <t>6121041819</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>21-09-1990</t>
+          <t>01-12-2008</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>WIL_UCL@HOTMAIL.COM</t>
+          <t>HANNIAZULETTBURGOIN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>01-02-2026 10:17:19</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>04-02-2026 17:38:34</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>01-02-2026 10:33:00</t>
+          <t>04-02-2026 17:42:38</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>01-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>01-02-2026 10:25:23</t>
-        </is>
-      </c>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4751,19 +4743,19 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26210521989080002222</t>
+          <t>26210522083170002489</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4775,12 +4767,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>340286</t>
+          <t>341783</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>18104</t>
+          <t>19601</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4790,17 +4782,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">AMY ANGELINE </t>
+          <t>ERNESTO</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUZMAN </t>
+          <t xml:space="preserve">GARZA </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOA </t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4810,32 +4802,32 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6121220630</t>
+          <t>8180747965</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">C MANUEL F MONTOYA </t>
+          <t>ENCINO #216</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>20-01-2010</t>
+          <t>27-10-1990</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>LICLOAVEGA200@GMAIL.COM</t>
+          <t>DRERNESTOGARZA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>02-02-2026 16:44:59</t>
+          <t>07-02-2026 10:19:47</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4846,7 +4838,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -4856,17 +4848,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>02-02-2026 16:47:48</t>
+          <t>11-02-2026 15:26:34</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>02-02-2026 16:46:46</t>
+          <t>11-02-2026 15:25:43</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4876,7 +4868,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -4886,11 +4878,19 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26210522017270002279</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
+          <t>26210522266420003021</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>VERONICA VIANEY LOYA CONTRERAS</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>499</t>
@@ -4910,12 +4910,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>342490</t>
+          <t>341785</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20307</t>
+          <t>19603</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4925,17 +4925,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>RENEE ALESSANDRA</t>
+          <t>DENIS ALEJANDRA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">CESEÑA </t>
+          <t>ESTRADA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAVIS </t>
+          <t>SANTACRUZ</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4945,10 +4945,14 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6122046111</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>8120018311</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ENCINO # 216</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4956,56 +4960,60 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>20-02-2007</t>
+          <t>01-09-1985</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>RENEEE777111@GMAIL.COM</t>
+          <t>ALESSANALESAN85@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>09-02-2026 20:30:27</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>07-02-2026 10:21:42</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>09-02-2026 20:32:52</t>
+          <t>11-02-2026 15:32:23</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr"/>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>11-02-2026 15:31:50</t>
+        </is>
+      </c>
       <c r="U34" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr"/>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W34" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5013,14 +5021,22 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26210522213810002877</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
+          <t>26210522266660003022</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>VERONICA VIANEY LOYA CONTRERAS</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -5037,12 +5053,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>340554</t>
+          <t>343166</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>18372</t>
+          <t>20983</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5052,17 +5068,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>JANNETT</t>
+          <t>MARIA FERNANDA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CALDERON</t>
+          <t>ACEVEDO</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SCHCOLNICK</t>
+          <t>RUVALCABA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5072,12 +5088,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6121042182</t>
+          <t>6121068152</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>CARRETERA AL NORTE KM 11 PRIV. LAS QUINTAS DEL MAR 7</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5087,17 +5103,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>22-09-2004</t>
+          <t>13-09-2003</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>JANNETT.22099@GMAIL.COM</t>
+          <t>FERNANDAACEV13@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>03-02-2026 13:02:59</t>
+          <t>12-02-2026 07:13:35</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -5118,17 +5134,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>03-02-2026 13:08:32</t>
+          <t>12-02-2026 07:18:27</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>03-02-2026 13:07:59</t>
+          <t>12-02-2026 07:17:45</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5148,7 +5164,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26210522039110002341</t>
+          <t>26210522287800003090</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
@@ -5160,7 +5176,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>Cristopher Armando Serrato</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5172,12 +5188,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>340350</t>
+          <t>342226</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>18168</t>
+          <t>20044</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5187,17 +5203,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIS MANUEL </t>
+          <t>ARIANY ROSALIA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CASILLAS</t>
+          <t>COTA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>HALE</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5207,32 +5223,32 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6121975782</t>
+          <t>6121692055</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">C GASPAR VELA </t>
+          <t>CALLE EL TRIUNFO #233</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>24-08-1999</t>
+          <t>08-10-1981</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>LUISCASILLAS_19@HOTMAIL.COM</t>
+          <t>ARIANY2C@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>02-02-2026 18:42:38</t>
+          <t>09-02-2026 15:54:22</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -5253,17 +5269,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>02-02-2026 18:50:43</t>
+          <t>10-02-2026 17:08:18</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>02-02-2026 18:49:33</t>
+          <t>10-02-2026 17:07:27</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -5283,11 +5299,19 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26210522021200002303</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
+          <t>26210522238630002941</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>VERONICA VIANEY LOYA CONTRERAS</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>499</t>
@@ -5307,12 +5331,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>341783</t>
+          <t>342230</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>19601</t>
+          <t>20048</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5322,17 +5346,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ERNESTO</t>
+          <t>ANA ARACELY</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARZA </t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>COTA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5342,75 +5366,67 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>8180747965</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>ENCINO #216</t>
-        </is>
-      </c>
+          <t>6121372111</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>27-10-1990</t>
+          <t>08-10-2008</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>DRERNESTOGARZA@GMAIL.COM</t>
+          <t>ARIANYR2C@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>07-02-2026 10:19:47</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>09-02-2026 15:59:56</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>11-02-2026 15:26:34</t>
+          <t>12-02-2026 16:08:25</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>11-02-2026 15:25:43</t>
-        </is>
-      </c>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5418,7 +5434,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26210522266420003021</t>
+          <t>26210522296870003118</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -5433,7 +5449,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -5450,12 +5466,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>341785</t>
+          <t>343508</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>19603</t>
+          <t>21325</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5465,17 +5481,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>DENIS ALEJANDRA</t>
+          <t xml:space="preserve">LUISA FERNANDA </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ESTRADA</t>
+          <t xml:space="preserve">MURILLO </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SANTACRUZ</t>
+          <t xml:space="preserve">OLIVARES </t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5485,12 +5501,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>8120018311</t>
+          <t>6122290863</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>ENCINO # 216</t>
+          <t>C OLMECAS 508</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5500,17 +5516,17 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>01-09-1985</t>
+          <t>19-12-2004</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>ALESSANALESAN85@GMAIL.COM</t>
+          <t>ISAFERNAN.19@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>07-02-2026 10:21:42</t>
+          <t>13-02-2026 15:03:03</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5521,7 +5537,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -5531,17 +5547,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>11-02-2026 15:32:23</t>
+          <t>13-02-2026 15:12:55</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>11-02-2026 15:31:50</t>
+          <t>13-02-2026 15:11:55</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -5551,7 +5567,7 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
@@ -5561,19 +5577,11 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26210522266660003022</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>VERONICA VIANEY LOYA CONTRERAS</t>
-        </is>
-      </c>
+          <t>26210522322150003203</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr">
         <is>
           <t>499</t>
@@ -5581,7 +5589,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5593,12 +5601,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>344965</t>
+          <t>344143</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>22782</t>
+          <t>21960</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5608,17 +5616,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE LUIS </t>
+          <t xml:space="preserve">ISABELLA </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SERRANO</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>TELLEZ</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5628,57 +5636,53 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6241750961</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>C HORBLENDA 918</t>
-        </is>
-      </c>
+          <t>6122133549</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>31-03-1997</t>
+          <t>04-06-2010</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>IAJOSELUIS@OUTLOOK.COM</t>
+          <t>CASTROISABELLA600@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>18-02-2026 20:42:50</t>
+          <t>16-02-2026 16:04:56</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>18-02-2026 20:49:56</t>
+          <t>18-02-2026 16:06:37</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -5686,21 +5690,13 @@
           <t>18-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>18-02-2026 20:48:57</t>
-        </is>
-      </c>
+      <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5708,14 +5704,22 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26210522477060003507</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
+          <t>26210522465650003472</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>VERONICA VIANEY LOYA CONTRERAS</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -5732,12 +5736,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>345189</t>
+          <t>344316</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>87354</t>
+          <t>22133</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5747,17 +5751,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>MARIA ELISA</t>
+          <t>MAYTE ANELIZ</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t xml:space="preserve">CUEVAS </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ALAMILLA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5767,14 +5771,10 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6121717456</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>C MELITOM ALBAÑEZ 45</t>
-        </is>
-      </c>
+          <t>6241717643</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5782,64 +5782,56 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>17-12-2012</t>
+          <t>02-01-2007</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>MARIAELISAHERNANDEZ@ICLOUD.COM</t>
+          <t>ANELIZCG07@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>19-02-2026 19:10:37</t>
+          <t>16-02-2026 18:53:41</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>19-02-2026 19:15:52</t>
+          <t>17-02-2026 14:17:50</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>19-02-2026 19:15:15</t>
-        </is>
-      </c>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5847,36 +5839,36 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26210522505670003580</t>
+          <t>26210522429100003408</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>341114</t>
+          <t>343827</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>18932</t>
+          <t>21644</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5886,17 +5878,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>HANNIA ZULETT GUADALUPE</t>
+          <t xml:space="preserve">KARLA ADRIANA </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">BURGOIN </t>
+          <t>MAYORAL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCERO </t>
+          <t>COTA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5906,10 +5898,14 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6121041819</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>6122145835</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>C JUAN SARABIA 725</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5917,56 +5913,60 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>01-12-2008</t>
+          <t>04-11-1987</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>HANNIAZULETTBURGOIN@GMAIL.COM</t>
+          <t>KARLAMC4.87@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>04-02-2026 17:38:34</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>15-02-2026 12:11:56</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>04-02-2026 17:42:38</t>
+          <t>15-02-2026 12:17:37</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr"/>
+          <t>15-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>15-02-2026 12:16:16</t>
+        </is>
+      </c>
       <c r="U41" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr"/>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W41" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5974,14 +5974,14 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26210522083170002489</t>
+          <t>26210522365310003259</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
@@ -5998,12 +5998,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>344143</t>
+          <t>342188</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>21960</t>
+          <t>20006</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6013,17 +6013,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISABELLA </t>
+          <t>EDNA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>TAMAYO</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6033,10 +6033,14 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6122133549</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>6123489545</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>PRIV MARINA CENTRAL 117</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6044,56 +6048,60 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>04-06-2010</t>
+          <t>02-04-1974</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CASTROISABELLA600@GMAIL.COM</t>
+          <t>EDNA_321@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>16-02-2026 16:04:56</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 14:43:59</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>18-02-2026 16:06:37</t>
+          <t>11-02-2026 13:12:45</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr"/>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>11-02-2026 13:12:26</t>
+        </is>
+      </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W42" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6101,7 +6109,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26210522465650003472</t>
+          <t>26210522263830003013</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -6111,17 +6119,17 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>VERONICA VIANEY LOYA CONTRERAS</t>
+          <t>CRISTINA AYLIN CHAVEZ GONZALEZ</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6133,12 +6141,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>344316</t>
+          <t>342527</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>22133</t>
+          <t>20344</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6148,17 +6156,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>MAYTE ANELIZ</t>
+          <t>DIANA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUEVAS </t>
+          <t>MADRID</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>BURQUEZ</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6168,10 +6176,14 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6241717643</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>6242249486</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>AYENDE #1720</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6179,56 +6191,60 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>02-01-2007</t>
+          <t>15-05-1995</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>ANELIZCG07@GMAIL.COM</t>
+          <t>DIANAMB_@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>16-02-2026 18:53:41</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 07:13:24</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>17-02-2026 14:17:50</t>
+          <t>10-02-2026 07:22:03</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>10-02-2026 07:20:53</t>
+        </is>
+      </c>
       <c r="U43" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr"/>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W43" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6236,19 +6252,19 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26210522429100003408</t>
+          <t>26210522224130002896</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -6260,12 +6276,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>343166</t>
+          <t>342701</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>20983</t>
+          <t>20518</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6275,17 +6291,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA</t>
+          <t>SUMIKO MARIA</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ACEVEDO</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>RUVALCABA</t>
+          <t>AGUIRRE</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6295,14 +6311,10 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6121068152</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>ROMA</t>
-        </is>
-      </c>
+          <t>6121220205</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6310,60 +6322,56 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>13-09-2003</t>
+          <t>07-04-2013</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>FERNANDAACEV13@GMAIL.COM</t>
+          <t>SUMIJOAGUIRREFISHER@GMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>12-02-2026 07:13:35</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>10-02-2026 16:22:22</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>12-02-2026 07:18:27</t>
+          <t>10-02-2026 16:28:08</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>12-02-2026 07:17:45</t>
-        </is>
-      </c>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6371,19 +6379,19 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26210522287800003090</t>
+          <t>26210522236680002929</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>Cristopher Armando Serrato</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -6395,12 +6403,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>343508</t>
+          <t>343038</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>21325</t>
+          <t>20855</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6410,17 +6418,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUISA FERNANDA </t>
+          <t xml:space="preserve">DOLORES ITZEL </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">MURILLO </t>
+          <t xml:space="preserve">CUBILLOS </t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">OLIVARES </t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6430,12 +6438,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6122290863</t>
+          <t>6121029534</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>C OLMECAS 508</t>
+          <t>C PABLO L. GONZALEZ 235</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6445,17 +6453,17 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>19-12-2004</t>
+          <t>10-12-1994</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>ISAFERNAN.19@GMAIL.COM</t>
+          <t>CUBILLOSITZEL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>13-02-2026 15:03:03</t>
+          <t>11-02-2026 16:24:22</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -6466,7 +6474,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -6476,17 +6484,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>13-02-2026 15:12:55</t>
+          <t>11-02-2026 16:38:56</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>13-02-2026 15:11:55</t>
+          <t>11-02-2026 16:38:17</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -6496,7 +6504,7 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
@@ -6506,7 +6514,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26210522322150003203</t>
+          <t>26210522269110003031</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr"/>
@@ -6657,12 +6665,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>342226</t>
+          <t>344935</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20044</t>
+          <t>22752</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6672,17 +6680,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ARIANY ROSALIA</t>
+          <t xml:space="preserve">JESUS ANTONIO </t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>COTA</t>
+          <t>MADRID</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>GURROLA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6692,75 +6700,67 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6121692055</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>CALLE EL TRIUNFO #233</t>
-        </is>
-      </c>
+          <t>6124408280</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>08-10-1981</t>
+          <t>23-04-1999</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>ARIANY2C@HOTMAIL.COM</t>
+          <t>JESUSMG230499@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>09-02-2026 15:54:22</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+          <t>18-02-2026 19:00:03</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>10-02-2026 17:08:18</t>
+          <t>18-02-2026 19:01:59</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>10-02-2026 17:07:27</t>
-        </is>
-      </c>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6768,22 +6768,14 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26210522238630002941</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>VERONICA VIANEY LOYA CONTRERAS</t>
-        </is>
-      </c>
+          <t>26210522474020003495</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
@@ -6800,12 +6792,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>344935</t>
+          <t>342520</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>22752</t>
+          <t>20337</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6815,17 +6807,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">JESUS ANTONIO </t>
+          <t>JOSE EDUARDO</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MADRID</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>GURROLA</t>
+          <t>LIMOM</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6835,10 +6827,14 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6124408280</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>6121196214</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>DEL ESTRIBO</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -6846,56 +6842,60 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>23-04-1999</t>
+          <t>03-01-1992</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>JESUSMG230499@ICLOUD.COM</t>
+          <t>LIMON.EDUARDO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>18-02-2026 19:00:03</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 06:36:49</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>18-02-2026 19:01:59</t>
+          <t>10-02-2026 06:41:55</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>10-02-2026 06:41:25</t>
+        </is>
+      </c>
       <c r="U48" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6903,19 +6903,19 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26210522474020003495</t>
+          <t>26210522223420002894</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Cristopher Armando Serrato</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -6927,12 +6927,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>343827</t>
+          <t>342920</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>21644</t>
+          <t>20737</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6942,17 +6942,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">KARLA ADRIANA </t>
+          <t>FERNANDO</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>MAYORAL</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>COTA</t>
+          <t>ORNELAS</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6962,32 +6962,32 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6122145835</t>
+          <t>6121870554</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>C JUAN SARABIA 725</t>
+          <t>LA CIMA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>04-11-1987</t>
+          <t>16-09-1975</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>KARLAMC4.87@GMAIL.COM</t>
+          <t>FERNANDOCRUZORNELAS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>15-02-2026 12:11:56</t>
+          <t>11-02-2026 09:39:30</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -7008,17 +7008,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>15-02-2026 12:17:37</t>
+          <t>11-02-2026 09:45:27</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>15-02-2026 12:16:16</t>
+          <t>11-02-2026 09:45:03</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -7038,7 +7038,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26210522365310003259</t>
+          <t>26210522260970003000</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -7062,12 +7062,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>344516</t>
+          <t>343251</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>22333</t>
+          <t>21068</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7077,17 +7077,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>GABRIEL MARTIN</t>
+          <t>TAMARA</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>GULUARTE</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>BARAJAS</t>
+          <t>AGUIÑAGA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7097,79 +7097,67 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6121009849</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>C AGROPECUARIA</t>
-        </is>
-      </c>
+          <t>5541288966</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>13-02-2000</t>
+          <t>21-12-2004</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>MARTINBARAJAS1302@GMAIL.COM</t>
+          <t>TAMARA211204@GMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>17-02-2026 15:10:23</t>
+          <t>12-02-2026 13:32:17</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>17-02-2026 15:16:36</t>
+          <t>12-02-2026 13:33:36</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>17-02-2026 15:16:14</t>
-        </is>
-      </c>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7177,14 +7165,14 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26210522431100003417</t>
+          <t>26210522293540003108</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
@@ -7201,12 +7189,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>342230</t>
+          <t>343379</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>20048</t>
+          <t>21196</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7216,17 +7204,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ANA ARACELY</t>
+          <t>SARA BEATRIZ</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t xml:space="preserve">CASTELLANOS </t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>COTA</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7236,10 +7224,14 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6121372111</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>6122327477</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>C MELON 121</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7247,42 +7239,38 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>08-10-2008</t>
+          <t>03-06-1981</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>ARIANYR2C@HOTMAIL.COM</t>
+          <t>DRA.SARACASTELLANOS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>09-02-2026 15:59:56</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>12-02-2026 18:54:35</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>12-02-2026 16:08:25</t>
+          <t>12-02-2026 18:58:52</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -7290,13 +7278,21 @@
           <t>12-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr"/>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>12-02-2026 18:58:05</t>
+        </is>
+      </c>
       <c r="U51" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr"/>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W51" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7304,22 +7300,14 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26210522296870003118</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>VERONICA VIANEY LOYA CONTRERAS</t>
-        </is>
-      </c>
+          <t>26210522303780003149</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
@@ -7336,12 +7324,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>344873</t>
+          <t>343761</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>22690</t>
+          <t>21578</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7351,17 +7339,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>KARLA ROXANA</t>
+          <t>OSMAR ALEJANDRO</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>MURILLO</t>
+          <t xml:space="preserve"> LIERA </t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7371,32 +7359,32 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6121532789</t>
+          <t>6151559659</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD</t>
+          <t>CENTRO</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>18-09-1984</t>
+          <t>26-07-2001</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>KMURILLO@UABCS.MX</t>
+          <t>LIERAGOMEZOSMARALEJANDRO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>18-02-2026 16:45:58</t>
+          <t>14-02-2026 23:55:59</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7421,17 +7409,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>18-02-2026 16:49:17</t>
+          <t>20-02-2026 05:36:59</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>20-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>18-02-2026 16:48:16</t>
+          <t>20-02-2026 05:34:42</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -7451,10 +7439,14 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26210522467350003478</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr"/>
+          <t>26210522509510003598</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr">
         <is>
@@ -7463,24 +7455,24 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>345619</t>
+          <t>343754</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>87784</t>
+          <t>21571</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7490,17 +7482,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>AZUL</t>
+          <t>ERNESTO</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>DOMINGUEZ</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ESCAMILLA</t>
+          <t>ROSALES</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7510,79 +7502,75 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>6121480447</t>
+          <t>6241578514</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>CHAMETLA</t>
+          <t>PEDRO MATIAS GONI 353</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>28-01-1977</t>
+          <t>07-11-1978</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>PLAYAZUL28@HOTMAIL.COM</t>
+          <t>NETOGR78@GMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>22-02-2026 13:07:59</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>14-02-2026 18:11:53</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>22-02-2026 13:15:30</t>
+          <t>14-02-2026 18:11:54</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>22-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>22-02-2026 13:13:25</t>
+          <t>14-02-2026 18:11:54</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="W53" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7590,19 +7578,19 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26210522563650003675</t>
+          <t>26210522349800003253</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Cristopher Armando Serrato</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -7614,12 +7602,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>343038</t>
+          <t>344516</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20855</t>
+          <t>22333</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7629,17 +7617,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">DOLORES ITZEL </t>
+          <t>GABRIEL MARTIN</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUBILLOS </t>
+          <t>GULUARTE</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>BARAJAS</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7649,35 +7637,39 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>6121029534</t>
+          <t>6121009849</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>C PABLO L. GONZALEZ 235</t>
+          <t>C AGROPECUARIA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>10-12-1994</t>
+          <t>13-02-2000</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>CUBILLOSITZEL@GMAIL.COM</t>
+          <t>MARTINBARAJAS1302@GMAIL.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>11-02-2026 16:24:22</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+          <t>17-02-2026 15:10:23</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O54" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7695,17 +7687,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>11-02-2026 16:38:56</t>
+          <t>17-02-2026 15:16:36</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>11-02-2026 16:38:17</t>
+          <t>17-02-2026 15:16:14</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -7725,7 +7717,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26210522269110003031</t>
+          <t>26210522431100003417</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr"/>
@@ -7749,12 +7741,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>344230</t>
+          <t>345619</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>22047</t>
+          <t>87784</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7764,17 +7756,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SERGIO ENRIQUE</t>
+          <t>AZUL</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>DOMINGUEZ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ORDUÑO</t>
+          <t>ESCAMILLA</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7784,32 +7776,32 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6121770347</t>
+          <t>6121480447</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>C BAHIA DE SALINAS 89</t>
+          <t>CHAMETLA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>26-01-1989</t>
+          <t>28-01-1977</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>SHEKO84_26@HOTMAIL.COM</t>
+          <t>PLAYAZUL28@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>16-02-2026 17:42:13</t>
+          <t>22-02-2026 13:07:59</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -7834,17 +7826,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>25-02-2026 15:36:45</t>
+          <t>22-02-2026 13:15:30</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
+          <t>22-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>25-02-2026 15:36:06</t>
+          <t>22-02-2026 13:13:25</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -7854,7 +7846,7 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
@@ -7864,19 +7856,11 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26210522655670003952</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>VERONICA VIANEY LOYA CONTRERAS</t>
-        </is>
-      </c>
+          <t>26210522563650003675</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr">
         <is>
           <t>649</t>
@@ -7884,7 +7868,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Cristopher Armando Serrato</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -7896,12 +7880,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>342527</t>
+          <t>343375</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>20344</t>
+          <t>21192</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7911,17 +7895,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>DIANA</t>
+          <t xml:space="preserve">MARIO ALBERTO </t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MADRID</t>
+          <t>ROSAS</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>BURQUEZ</t>
+          <t xml:space="preserve">MANRIQUEZ </t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -7931,32 +7915,32 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6242249486</t>
+          <t>6122343338</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>AYENDE #1720</t>
+          <t>C MELON 121</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>15-05-1995</t>
+          <t>12-12-1977</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>DIANAMB_@HOTMAIL.COM</t>
+          <t>ROSASCASTELLANOS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>10-02-2026 07:13:24</t>
+          <t>12-02-2026 18:48:15</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -7977,17 +7961,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>10-02-2026 07:22:03</t>
+          <t>12-02-2026 18:53:02</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>10-02-2026 07:20:53</t>
+          <t>12-02-2026 18:52:16</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -7997,7 +7981,7 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
@@ -8007,7 +7991,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26210522224130002896</t>
+          <t>26210522303620003147</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr"/>
@@ -8019,7 +8003,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -8031,12 +8015,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>342701</t>
+          <t>344873</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>20518</t>
+          <t>22690</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8046,17 +8030,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SUMIKO MARIA</t>
+          <t>KARLA ROXANA</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>MURILLO</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>AGUIRRE</t>
+          <t>VALDEZ</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8066,10 +8050,14 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>6121220205</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>6121532789</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -8077,56 +8065,64 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>07-04-2013</t>
+          <t>18-09-1984</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>SUMIJOAGUIRREFISHER@GMAIL.COM</t>
+          <t>KMURILLO@UABCS.MX</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>10-02-2026 16:22:22</t>
+          <t>18-02-2026 16:45:58</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>10-02-2026 16:28:08</t>
+          <t>18-02-2026 16:49:17</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T57" t="inlineStr"/>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>18-02-2026 16:48:16</t>
+        </is>
+      </c>
       <c r="U57" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr"/>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W57" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8134,14 +8130,14 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26210522236680002929</t>
+          <t>26210522467350003478</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
@@ -8158,12 +8154,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>343761</t>
+          <t>344366</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>21578</t>
+          <t>22183</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8173,17 +8169,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>OSMAR ALEJANDRO</t>
+          <t>REYNA ICELA</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LIERA </t>
+          <t>CADENA MATUS</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>CADENA MATUS</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8193,32 +8189,32 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>6151559659</t>
+          <t>6121971764</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>CENTRO</t>
+          <t>REGIDORES 113</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>26-07-2001</t>
+          <t>22-08-1987</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>LIERAGOMEZOSMARALEJANDRO@GMAIL.COM</t>
+          <t>REYNAICELACM@GMAIL.COM</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>14-02-2026 23:55:59</t>
+          <t>16-02-2026 23:34:26</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -8243,22 +8239,22 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>20-02-2026 05:36:59</t>
+          <t>16-02-2026 23:34:27</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>20-02-2026 05:34:42</t>
+          <t>16-02-2026 23:34:27</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -8273,14 +8269,10 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>26210522509510003598</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26210522412010003364</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr">
         <is>
@@ -8289,24 +8281,24 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>342920</t>
+          <t>344230</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>20737</t>
+          <t>22047</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8316,17 +8308,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>FERNANDO</t>
+          <t>SERGIO ENRIQUE</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ORNELAS</t>
+          <t>ORDUÑO</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -8336,12 +8328,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>6121870554</t>
+          <t>6121770347</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>LA CIMA</t>
+          <t>C BAHIA DE SALINAS 89</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -8351,48 +8343,52 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>16-09-1975</t>
+          <t>26-01-1989</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>FERNANDOCRUZORNELAS@GMAIL.COM</t>
+          <t>SHEKO84_26@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>11-02-2026 09:39:30</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
+          <t>16-02-2026 17:42:13</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>11-02-2026 09:45:27</t>
+          <t>25-02-2026 15:36:45</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>25-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>11-02-2026 09:45:03</t>
+          <t>25-02-2026 15:36:06</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -8402,7 +8398,7 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
@@ -8412,19 +8408,27 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>26210522260970003000</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr"/>
-      <c r="Z59" t="inlineStr"/>
+          <t>26210522655670003952</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>VERONICA VIANEY LOYA CONTRERAS</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -8436,12 +8440,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>343754</t>
+          <t>343254</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>21571</t>
+          <t>21071</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8451,17 +8455,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ERNESTO</t>
+          <t>JOUSY ISABELLA</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ROSALES</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -8471,75 +8475,67 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>6241578514</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>PEDRO MATIAS GONI 353</t>
-        </is>
-      </c>
+          <t>6391613622</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>07-11-1978</t>
+          <t>12-10-2003</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>NETOGR78@GMAIL.COM</t>
+          <t>ISABELLAMENDOZAVV@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>14-02-2026 18:11:53</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
+          <t>12-02-2026 13:36:03</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>14-02-2026 18:11:54</t>
+          <t>12-02-2026 13:37:01</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>14-02-2026 18:11:54</t>
-        </is>
-      </c>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
           <t>2</t>
         </is>
       </c>
+      <c r="V60" t="inlineStr"/>
       <c r="W60" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8547,19 +8543,19 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>26210522349800003253</t>
+          <t>26210522293680003109</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="inlineStr"/>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Cristopher Armando Serrato</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -8571,12 +8567,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>346045</t>
+          <t>343458</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>88210</t>
+          <t>21275</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8586,17 +8582,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">LIZBETH </t>
+          <t>EDUARDO ALEXIS</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>PIÑUELAS</t>
+          <t>VEGA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANTIAGO </t>
+          <t>VIEYRA</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -8606,14 +8602,10 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>6121701231</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>C MANUEL ENCINAS 1353</t>
-        </is>
-      </c>
+          <t>6121677253</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -8621,64 +8613,56 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>10-12-1997</t>
+          <t>08-04-1991</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>LIZPISA94@GMAIL.COM</t>
+          <t>EDUARDOVIEYRA06@GMAIL.COM</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>23-02-2026 20:23:38</t>
+          <t>13-02-2026 10:06:29</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>23-02-2026 20:32:15</t>
+          <t>13-02-2026 10:17:33</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>23-02-2026 20:31:30</t>
-        </is>
-      </c>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V61" t="inlineStr"/>
       <c r="W61" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8686,36 +8670,36 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>26210522601760003801</t>
+          <t>26210522318120003186</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="inlineStr"/>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>343251</t>
+          <t>343509</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>21068</t>
+          <t>21326</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8725,17 +8709,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>TAMARA</t>
+          <t xml:space="preserve">SANDRA DELMA </t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t xml:space="preserve">OLIVARES </t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AGUIÑAGA</t>
+          <t>VIVAR</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -8745,10 +8729,14 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>5541288966</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>6121310729</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>C OLMECAS 508</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -8756,56 +8744,60 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>21-12-2004</t>
+          <t>16-04-1976</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>TAMARA211204@GMAIL.COM</t>
+          <t>SANDYPRICES.19@GMAIL.COM</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>12-02-2026 13:32:17</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>13-02-2026 15:14:31</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>12-02-2026 13:33:36</t>
+          <t>13-02-2026 15:17:56</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T62" t="inlineStr"/>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>13-02-2026 15:17:37</t>
+        </is>
+      </c>
       <c r="U62" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr"/>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W62" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8813,19 +8805,19 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>26210522293540003108</t>
+          <t>26210522322300003205</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -8837,12 +8829,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>343379</t>
+          <t>346661</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>21196</t>
+          <t>88826</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8852,17 +8844,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SARA BEATRIZ</t>
+          <t xml:space="preserve">JOSE MARIA </t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASTELLANOS </t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>COTA</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -8872,35 +8864,39 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>6122327477</t>
+          <t>6121210045</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>C MELON 121</t>
+          <t>SANTA CLARA 137</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>03-06-1981</t>
+          <t>10-08-2004</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>DRA.SARACASTELLANOS@GMAIL.COM</t>
+          <t>JHO76525@GMAIL.COM</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>12-02-2026 18:54:35</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
+          <t>26-02-2026 10:16:45</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O63" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8908,27 +8904,27 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>12-02-2026 18:58:52</t>
+          <t>26-02-2026 10:33:02</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>26-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>12-02-2026 18:58:05</t>
+          <t>26-02-2026 10:28:15</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -8948,36 +8944,36 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>26210522303780003149</t>
+          <t>26210522679680004020</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="inlineStr"/>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>344366</t>
+          <t>346045</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>22183</t>
+          <t>88210</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -8987,17 +8983,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>REYNA ICELA</t>
+          <t xml:space="preserve">LIZBETH </t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>CADENA MATUS</t>
+          <t>PIÑUELAS</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CADENA MATUS</t>
+          <t xml:space="preserve">SANTIAGO </t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -9007,12 +9003,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>6121971764</t>
+          <t>6121701231</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>REGIDORES 113</t>
+          <t>C MANUEL ENCINAS 1353</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -9022,17 +9018,17 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>22-08-1987</t>
+          <t>10-12-1997</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>REYNAICELACM@GMAIL.COM</t>
+          <t>LIZPISA94@GMAIL.COM</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>16-02-2026 23:34:26</t>
+          <t>23-02-2026 20:23:38</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -9057,22 +9053,22 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>16-02-2026 23:34:27</t>
+          <t>23-02-2026 20:32:15</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>16-02-2026 23:34:27</t>
+          <t>23-02-2026 20:31:30</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -9087,7 +9083,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>26210522412010003364</t>
+          <t>26210522601760003801</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr"/>
@@ -9099,24 +9095,24 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>343375</t>
+          <t>344727</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>21192</t>
+          <t>22544</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9126,17 +9122,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIO ALBERTO </t>
+          <t>MARIA TERESA</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ROSAS</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANRIQUEZ </t>
+          <t>QUEZADA</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -9146,63 +9142,67 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>6122343338</t>
+          <t>5578843819</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>C MELON 121</t>
+          <t>CENTRO</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>12-12-1977</t>
+          <t>31-05-1969</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>ROSASCASTELLANOS@GMAIL.COM</t>
+          <t>MARIATERESAPEREZQUEZADA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>12-02-2026 18:48:15</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
+          <t>18-02-2026 05:24:32</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>12-02-2026 18:53:02</t>
+          <t>19-02-2026 06:46:30</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>12-02-2026 18:52:16</t>
+          <t>19-02-2026 06:44:39</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -9222,19 +9222,23 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>26210522303620003147</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr"/>
+          <t>26210522487370003516</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z65" t="inlineStr"/>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -9246,12 +9250,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>346048</t>
+          <t>345078</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>88213</t>
+          <t>87243</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9261,17 +9265,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADALBERTO ABIMAEL </t>
+          <t xml:space="preserve">ANA VICTORIA </t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ZAZUETA</t>
+          <t xml:space="preserve">BARRANCO </t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>VEGA</t>
+          <t xml:space="preserve">CASTRO </t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -9281,32 +9285,32 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>6122191467</t>
+          <t>6123489475</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>C MANUEL ENCINAS 1353</t>
+          <t>C MAGUEY 4551</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>21-10-1992</t>
+          <t>08-02-1994</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>REBUILDNERVE@GMAIL.COM</t>
+          <t>ANACSTRO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>23-02-2026 20:33:49</t>
+          <t>19-02-2026 14:27:10</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -9331,17 +9335,17 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>23-02-2026 20:38:02</t>
+          <t>19-02-2026 14:32:01</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>23-02-2026 20:37:01</t>
+          <t>19-02-2026 14:31:19</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -9361,7 +9365,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>26210522601920003802</t>
+          <t>26210522495380003538</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr"/>
@@ -9385,12 +9389,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>346328</t>
+          <t>345136</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>88493</t>
+          <t>87301</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9400,17 +9404,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">JORGE </t>
+          <t>FRANCISCA CECILIA</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">RUIZ </t>
+          <t>BARRETO</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t>BARRETO</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -9420,79 +9424,67 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>6122133679</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>PRIV AZURITA M2</t>
-        </is>
-      </c>
+          <t>6122148757</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>12-06-1986</t>
+          <t>22-11-1987</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>JM.AUTOSPA.LAPAZ@GMAIL.COM</t>
+          <t>BARRETOCECILIA925@GMAIL.COM</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>24-02-2026 20:03:17</t>
+          <t>19-02-2026 17:04:50</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>24-02-2026 20:22:54</t>
+          <t>19-02-2026 17:05:35</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>24-02-2026 20:07:54</t>
-        </is>
-      </c>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V67" t="inlineStr"/>
       <c r="W67" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9500,14 +9492,14 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>26210522636910003900</t>
+          <t>26210522500360003555</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="inlineStr"/>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
@@ -9524,12 +9516,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>344727</t>
+          <t>346663</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>22544</t>
+          <t>88828</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9539,17 +9531,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>MARIA TERESA</t>
+          <t>MARIA FERNANDA</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t xml:space="preserve">GONZALEZ </t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>QUEZADA</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -9559,14 +9551,10 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>5578843819</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>CENTRO</t>
-        </is>
-      </c>
+          <t>6121674092</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -9574,64 +9562,56 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>31-05-1969</t>
+          <t>08-05-2005</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>MARIATERESAPEREZQUEZADA@GMAIL.COM</t>
+          <t>FERNANDAGLEZM13@GMAIL.COM</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>18-02-2026 05:24:32</t>
+          <t>26-02-2026 10:35:53</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>19-02-2026 06:46:30</t>
+          <t>26-02-2026 10:38:17</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>19-02-2026 06:44:39</t>
-        </is>
-      </c>
+          <t>26-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V68" t="inlineStr"/>
       <c r="W68" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9639,18 +9619,14 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>26210522487370003516</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26210522679730004021</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="inlineStr"/>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
@@ -9667,12 +9643,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>345078</t>
+          <t>346328</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>87243</t>
+          <t>88493</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -9682,17 +9658,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA VICTORIA </t>
+          <t xml:space="preserve">JORGE </t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">BARRANCO </t>
+          <t xml:space="preserve">RUIZ </t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASTRO </t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -9702,32 +9678,32 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>6123489475</t>
+          <t>6122133679</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>C MAGUEY 4551</t>
+          <t>PRIV AZURITA M2</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>08-02-1994</t>
+          <t>12-06-1986</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>ANACSTRO@GMAIL.COM</t>
+          <t>JM.AUTOSPA.LAPAZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>19-02-2026 14:27:10</t>
+          <t>24-02-2026 20:03:17</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -9752,17 +9728,17 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>19-02-2026 14:32:01</t>
+          <t>24-02-2026 20:22:54</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>24-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>19-02-2026 14:31:19</t>
+          <t>24-02-2026 20:07:54</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -9782,7 +9758,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>26210522495380003538</t>
+          <t>26210522636910003900</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr"/>
@@ -9806,12 +9782,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>345136</t>
+          <t>346048</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>87301</t>
+          <t>88213</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -9821,17 +9797,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>FRANCISCA CECILIA</t>
+          <t xml:space="preserve">ADALBERTO ABIMAEL </t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>BARRETO</t>
+          <t>ZAZUETA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>BARRETO</t>
+          <t>VEGA</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -9841,67 +9817,79 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>6122148757</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>6122191467</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>C MANUEL ENCINAS 1353</t>
+        </is>
+      </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>22-11-1987</t>
+          <t>21-10-1992</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>BARRETOCECILIA925@GMAIL.COM</t>
+          <t>REBUILDNERVE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>19-02-2026 17:04:50</t>
+          <t>23-02-2026 20:33:49</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>19-02-2026 17:05:35</t>
+          <t>23-02-2026 20:38:02</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T70" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>23-02-2026 20:37:01</t>
+        </is>
+      </c>
       <c r="U70" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V70" t="inlineStr"/>
       <c r="W70" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9909,14 +9897,14 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>26210522500360003555</t>
+          <t>26210522601920003802</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="inlineStr"/>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
@@ -9925,6 +9913,284 @@
         </is>
       </c>
       <c r="AC70" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>344965</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>22782</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JOSE LUIS </t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>SERRANO</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>TELLEZ</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>6241750961</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>C HORBLENDA 918</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>31-03-1997</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>IAJOSELUIS@OUTLOOK.COM</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>18-02-2026 20:42:50</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>18-02-2026 20:49:56</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>18-02-2026 20:48:57</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>26210522477060003507</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr"/>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>Juan Pablo Rieke Campoy</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>345189</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>87354</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>MARIA ELISA</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HERNANDEZ </t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>ALAMILLA</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>6121717456</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>C MELITOM ALBAÑEZ 45</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>17-12-2012</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>MARIAELISAHERNANDEZ@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>19-02-2026 19:10:37</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>19-02-2026 19:15:52</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>19-02-2026 19:15:15</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>26210522505670003580</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__PASEO LA PAZ.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__PASEO LA PAZ.xlsx
@@ -1944,12 +1944,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>340353</t>
+          <t>341799</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>18171</t>
+          <t>19617</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1959,17 +1959,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">GIBERTO </t>
+          <t xml:space="preserve">MIGUEL ANGEL </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MENDEZ </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HALE </t>
+          <t>VICENT</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1979,12 +1979,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6121528946</t>
+          <t>6121590416</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>C CERRADA SANTA INES 890</t>
+          <t>PRIV PALO DE SANTA RITA 9</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1994,17 +1994,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>23-11-2001</t>
+          <t>30-10-1955</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>GILBERTO.MEN20011@GMAIL.COM</t>
+          <t>MHVICENT@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>02-02-2026 18:54:26</t>
+          <t>07-02-2026 10:56:26</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2025,17 +2025,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>02-02-2026 18:58:19</t>
+          <t>07-02-2026 11:33:16</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>07-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>02-02-2026 18:58:00</t>
+          <t>07-02-2026 11:32:27</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2055,10 +2055,14 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26210522021420002304</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr"/>
+          <t>26210522159870002732</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
@@ -2067,7 +2071,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2079,12 +2083,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>341799</t>
+          <t>340353</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19617</t>
+          <t>18171</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2094,17 +2098,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGUEL ANGEL </t>
+          <t xml:space="preserve">GIBERTO </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t xml:space="preserve">MENDEZ </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>VICENT</t>
+          <t xml:space="preserve">HALE </t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2114,12 +2118,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6121590416</t>
+          <t>6121528946</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>PRIV PALO DE SANTA RITA 9</t>
+          <t>C CERRADA SANTA INES 890</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2129,17 +2133,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>30-10-1955</t>
+          <t>23-11-2001</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>MHVICENT@GMAIL.COM</t>
+          <t>GILBERTO.MEN20011@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>07-02-2026 10:56:26</t>
+          <t>02-02-2026 18:54:26</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2160,17 +2164,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>07-02-2026 11:33:16</t>
+          <t>02-02-2026 18:58:19</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>07-02-2026 11:32:27</t>
+          <t>02-02-2026 18:58:00</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2190,14 +2194,10 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26210522159870002732</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26210522021420002304</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2770,12 +2770,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>342427</t>
+          <t>332784</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20244</t>
+          <t>14805</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2785,17 +2785,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">NICOLAS </t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PERPULI</t>
+          <t>ROBLES</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>VERDUGO</t>
+          <t>ARANDA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2805,10 +2805,14 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6121614567</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>5585803795</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUEBLO NUEVO </t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2816,56 +2820,60 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>06-03-1973</t>
+          <t>04-03-1978</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>NICOLASPERPULIVERDUGO@HOTMAIL.COM</t>
+          <t>ALEJANDRO.ROBLESARANDA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>09-02-2026 19:09:18</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>07-01-2026 09:40:49</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>09-02-2026 19:12:38</t>
+          <t>03-02-2026 14:14:15</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>09-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr"/>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>03-02-2026 13:57:02</t>
+        </is>
+      </c>
       <c r="U18" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2873,14 +2881,14 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26210522209990002868</t>
+          <t>26210522040850002349</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2897,12 +2905,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>332784</t>
+          <t>336694</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14805</t>
+          <t>22420</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2912,17 +2920,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t>ZULEMA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ROBLES</t>
+          <t>HIGUERA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ARANDA</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2932,32 +2940,32 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>5585803795</t>
+          <t>6122380771</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">PUEBLO NUEVO </t>
+          <t>CENTRO</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>04-03-1978</t>
+          <t>08-04-1983</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>ALEJANDRO.ROBLESARANDA@GMAIL.COM</t>
+          <t>ZULEMA@BAJASURREALTORS.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>07-01-2026 09:40:49</t>
+          <t>21-01-2026 10:28:18</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2968,7 +2976,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PROMO ENERO 12 MESES</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2978,17 +2986,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>03-02-2026 14:14:15</t>
+          <t>02-02-2026 09:06:56</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>28-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>03-02-2026 13:57:02</t>
+          <t>28-01-2026 09:24:49</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3008,10 +3016,14 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26210522040850002349</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr"/>
+          <t>26210522002210002243</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
@@ -3020,7 +3032,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3108,7 +3120,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -3154,7 +3166,7 @@
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -3171,12 +3183,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>336694</t>
+          <t>342427</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>22420</t>
+          <t>20244</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3186,17 +3198,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ZULEMA</t>
+          <t xml:space="preserve">NICOLAS </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>HIGUERA</t>
+          <t>PERPULI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>VERDUGO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3206,75 +3218,67 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6122380771</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>CENTRO</t>
-        </is>
-      </c>
+          <t>6121614567</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>08-04-1983</t>
+          <t>06-03-1973</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>ZULEMA@BAJASURREALTORS.COM</t>
+          <t>NICOLASPERPULIVERDUGO@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>21-01-2026 10:28:18</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>09-02-2026 19:09:18</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>PROMO ENERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>02-02-2026 09:06:56</t>
+          <t>09-02-2026 19:12:38</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>28-02-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>28-01-2026 09:24:49</t>
-        </is>
-      </c>
+          <t>09-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3282,23 +3286,19 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26210522002210002243</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26210522209990002868</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3437,12 +3437,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>343254</t>
+          <t>340590</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21071</t>
+          <t>18408</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3452,17 +3452,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>JOUSY ISABELLA</t>
+          <t xml:space="preserve">ANA LAURA </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t xml:space="preserve">MEZA </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>MUNDO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3472,10 +3472,14 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6391613622</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>6123520177</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ANDADOR LAS PALMERAS E 615</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3483,56 +3487,60 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>12-10-2003</t>
+          <t>06-07-2003</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>ISABELLAMENDOZAVV@OUTLOOK.COM</t>
+          <t>MANALAURA346@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>12-02-2026 13:36:03</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>03-02-2026 14:17:27</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>12-02-2026 13:37:01</t>
+          <t>03-02-2026 14:22:36</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr"/>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>03-02-2026 14:22:15</t>
+        </is>
+      </c>
       <c r="U23" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W23" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3540,19 +3548,19 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26210522293680003109</t>
+          <t>26210522041020002351</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Cristopher Armando Serrato</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3564,12 +3572,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>339764</t>
+          <t>343254</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>17582</t>
+          <t>21071</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3579,17 +3587,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">WILIAM ULISES </t>
+          <t>JOUSY ISABELLA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3599,75 +3607,67 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6691484335</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C VALTIERRA 324 </t>
-        </is>
-      </c>
+          <t>6391613622</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>21-09-1990</t>
+          <t>12-10-2003</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>WIL_UCL@HOTMAIL.COM</t>
+          <t>ISABELLAMENDOZAVV@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>01-02-2026 10:17:19</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>12-02-2026 13:36:03</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>01-02-2026 10:33:00</t>
+          <t>12-02-2026 13:37:01</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>01-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>01-02-2026 10:25:23</t>
-        </is>
-      </c>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3675,19 +3675,19 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26210521989080002222</t>
+          <t>26210522293680003109</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>Cristopher Armando Serrato</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3699,12 +3699,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>340590</t>
+          <t>339764</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>18408</t>
+          <t>17582</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3714,17 +3714,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA LAURA </t>
+          <t xml:space="preserve">WILIAM ULISES </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEZA </t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MUNDO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3734,32 +3734,32 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6123520177</t>
+          <t>6691484335</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ANDADOR LAS PALMERAS E 615</t>
+          <t xml:space="preserve">C VALTIERRA 324 </t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>06-07-2003</t>
+          <t>21-09-1990</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>MANALAURA346@GMAIL.COM</t>
+          <t>WIL_UCL@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>03-02-2026 14:17:27</t>
+          <t>01-02-2026 10:17:19</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -3780,17 +3780,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>03-02-2026 14:22:36</t>
+          <t>01-02-2026 10:33:00</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>01-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>03-02-2026 14:22:15</t>
+          <t>01-02-2026 10:25:23</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26210522041020002351</t>
+          <t>26210521989080002222</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -4231,12 +4231,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>341797</t>
+          <t>340350</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19615</t>
+          <t>18168</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4246,17 +4246,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SUSANA</t>
+          <t xml:space="preserve">LUIS MANUEL </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PASALAGUA</t>
+          <t>CASILLAS</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>HALE</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4266,32 +4266,32 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6121590135</t>
+          <t>6121975782</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>PRIV PALO DE SANTA RITA 9</t>
+          <t xml:space="preserve">C GASPAR VELA </t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>06-02-1966</t>
+          <t>24-08-1999</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>SIPHITYA@GMAIL.COM</t>
+          <t>LUISCASILLAS_19@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>07-02-2026 10:52:31</t>
+          <t>02-02-2026 18:42:38</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4312,17 +4312,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>07-02-2026 11:37:55</t>
+          <t>02-02-2026 18:50:43</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>07-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>07-02-2026 11:37:04</t>
+          <t>02-02-2026 18:49:33</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4342,14 +4342,10 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26210522160000002733</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26210522021200002303</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
@@ -4358,7 +4354,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4370,12 +4366,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>340350</t>
+          <t>341797</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>18168</t>
+          <t>19615</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4385,17 +4381,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIS MANUEL </t>
+          <t>SUSANA</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CASILLAS</t>
+          <t>PASALAGUA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>HALE</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4405,32 +4401,32 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6121975782</t>
+          <t>6121590135</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">C GASPAR VELA </t>
+          <t>PRIV PALO DE SANTA RITA 9</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>24-08-1999</t>
+          <t>06-02-1966</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>LUISCASILLAS_19@HOTMAIL.COM</t>
+          <t>SIPHITYA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>02-02-2026 18:42:38</t>
+          <t>07-02-2026 10:52:31</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4451,17 +4447,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>02-02-2026 18:50:43</t>
+          <t>07-02-2026 11:37:55</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>07-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>02-02-2026 18:49:33</t>
+          <t>07-02-2026 11:37:04</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4481,10 +4477,14 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26210522021200002303</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr"/>
+          <t>26210522160000002733</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -5057,12 +5057,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>341986</t>
+          <t>341783</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>19804</t>
+          <t>19601</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5072,17 +5072,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>KARLA ELIZABETH</t>
+          <t>ERNESTO</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>BERLANGA</t>
+          <t xml:space="preserve">GARZA </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CALDERON</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5092,67 +5092,75 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>5577876880</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>8180747965</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ENCINO #216</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>22-05-2001</t>
+          <t>27-10-1990</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>BERLANGACALDERONELIZABETH22@GMAIL.COM</t>
+          <t>DRERNESTOGARZA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>09-02-2026 04:13:10</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>07-02-2026 10:19:47</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>09-02-2026 04:15:04</t>
+          <t>11-02-2026 15:26:34</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr"/>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>11-02-2026 15:25:43</t>
+        </is>
+      </c>
       <c r="U35" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr"/>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W35" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5160,36 +5168,44 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26210522174170002753</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
+          <t>26210522266420003021</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>VERONICA VIANEY LOYA CONTRERAS</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>342490</t>
+          <t>341785</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20307</t>
+          <t>19603</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5199,17 +5215,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>RENEE ALESSANDRA</t>
+          <t>DENIS ALEJANDRA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">CESEÑA </t>
+          <t>ESTRADA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAVIS </t>
+          <t>SANTACRUZ</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5219,10 +5235,14 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6122046111</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>8120018311</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ENCINO # 216</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5230,56 +5250,60 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>20-02-2007</t>
+          <t>01-09-1985</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>RENEEE777111@GMAIL.COM</t>
+          <t>ALESSANALESAN85@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>09-02-2026 20:30:27</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>07-02-2026 10:21:42</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>09-02-2026 20:32:52</t>
+          <t>11-02-2026 15:32:23</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr"/>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>11-02-2026 15:31:50</t>
+        </is>
+      </c>
       <c r="U36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr"/>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W36" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5287,14 +5311,22 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26210522213810002877</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
+          <t>26210522266660003022</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>VERONICA VIANEY LOYA CONTRERAS</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -5311,12 +5343,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>344965</t>
+          <t>341986</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>22782</t>
+          <t>19804</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5326,17 +5358,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE LUIS </t>
+          <t>KARLA ELIZABETH</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SERRANO</t>
+          <t>BERLANGA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>TELLEZ</t>
+          <t>CALDERON</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5346,79 +5378,67 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6241750961</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>C HORBLENDA 918</t>
-        </is>
-      </c>
+          <t>5577876880</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>31-03-1997</t>
+          <t>22-05-2001</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>IAJOSELUIS@OUTLOOK.COM</t>
+          <t>BERLANGACALDERONELIZABETH22@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>18-02-2026 20:42:50</t>
+          <t>09-02-2026 04:13:10</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>18-02-2026 20:49:56</t>
+          <t>09-02-2026 04:15:04</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>18-02-2026 20:48:57</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5426,36 +5446,36 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26210522477060003507</t>
+          <t>26210522174170002753</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>345189</t>
+          <t>344143</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>87354</t>
+          <t>21960</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5465,17 +5485,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>MARIA ELISA</t>
+          <t xml:space="preserve">ISABELLA </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ALAMILLA</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5485,14 +5505,10 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6121717456</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>C MELITOM ALBAÑEZ 45</t>
-        </is>
-      </c>
+          <t>6122133549</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5500,64 +5516,56 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>17-12-2012</t>
+          <t>04-06-2010</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>MARIAELISAHERNANDEZ@ICLOUD.COM</t>
+          <t>CASTROISABELLA600@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>19-02-2026 19:10:37</t>
+          <t>16-02-2026 16:04:56</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>19-02-2026 19:15:52</t>
+          <t>18-02-2026 16:06:37</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>19-02-2026 19:15:15</t>
-        </is>
-      </c>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5565,36 +5573,44 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26210522505670003580</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
+          <t>26210522465650003472</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>VERONICA VIANEY LOYA CONTRERAS</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>344143</t>
+          <t>344965</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>21960</t>
+          <t>22782</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5604,17 +5620,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISABELLA </t>
+          <t xml:space="preserve">JOSE LUIS </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>SERRANO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>TELLEZ</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5624,53 +5640,57 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6122133549</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>6241750961</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>C HORBLENDA 918</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>04-06-2010</t>
+          <t>31-03-1997</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CASTROISABELLA600@GMAIL.COM</t>
+          <t>IAJOSELUIS@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>16-02-2026 16:04:56</t>
+          <t>18-02-2026 20:42:50</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>18-02-2026 16:06:37</t>
+          <t>18-02-2026 20:49:56</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -5678,13 +5698,21 @@
           <t>18-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr"/>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>18-02-2026 20:48:57</t>
+        </is>
+      </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W39" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5692,22 +5720,14 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26210522465650003472</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>VERONICA VIANEY LOYA CONTRERAS</t>
-        </is>
-      </c>
+          <t>26210522477060003507</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -5724,12 +5744,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>341114</t>
+          <t>345189</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>18932</t>
+          <t>87354</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5739,17 +5759,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>HANNIA ZULETT GUADALUPE</t>
+          <t>MARIA ELISA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">BURGOIN </t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCERO </t>
+          <t>ALAMILLA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5759,10 +5779,14 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6121041819</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>6121717456</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>C MELITOM ALBAÑEZ 45</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5770,56 +5794,64 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>01-12-2008</t>
+          <t>17-12-2012</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>HANNIAZULETTBURGOIN@GMAIL.COM</t>
+          <t>MARIAELISAHERNANDEZ@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>04-02-2026 17:38:34</t>
+          <t>19-02-2026 19:10:37</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>04-02-2026 17:42:38</t>
+          <t>19-02-2026 19:15:52</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr"/>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>19-02-2026 19:15:15</t>
+        </is>
+      </c>
       <c r="U40" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr"/>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W40" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5827,36 +5859,36 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26210522083170002489</t>
+          <t>26210522505670003580</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>341783</t>
+          <t>342490</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>19601</t>
+          <t>20307</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5866,17 +5898,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ERNESTO</t>
+          <t>RENEE ALESSANDRA</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARZA </t>
+          <t xml:space="preserve">CESEÑA </t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t xml:space="preserve">DAVIS </t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5886,75 +5918,67 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>8180747965</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>ENCINO #216</t>
-        </is>
-      </c>
+          <t>6122046111</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>27-10-1990</t>
+          <t>20-02-2007</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>DRERNESTOGARZA@GMAIL.COM</t>
+          <t>RENEEE777111@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>07-02-2026 10:19:47</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+          <t>09-02-2026 20:30:27</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>11-02-2026 15:26:34</t>
+          <t>09-02-2026 20:32:52</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>11-02-2026 15:25:43</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5962,22 +5986,14 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26210522266420003021</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>VERONICA VIANEY LOYA CONTRERAS</t>
-        </is>
-      </c>
+          <t>26210522213810002877</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
@@ -5994,12 +6010,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>341785</t>
+          <t>341114</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>19603</t>
+          <t>18932</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6009,17 +6025,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DENIS ALEJANDRA</t>
+          <t>HANNIA ZULETT GUADALUPE</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ESTRADA</t>
+          <t xml:space="preserve">BURGOIN </t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SANTACRUZ</t>
+          <t xml:space="preserve">LUCERO </t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6029,14 +6045,10 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>8120018311</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>ENCINO # 216</t>
-        </is>
-      </c>
+          <t>6121041819</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6044,60 +6056,56 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>01-09-1985</t>
+          <t>01-12-2008</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>ALESSANALESAN85@GMAIL.COM</t>
+          <t>HANNIAZULETTBURGOIN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>07-02-2026 10:21:42</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+          <t>04-02-2026 17:38:34</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>11-02-2026 15:32:23</t>
+          <t>04-02-2026 17:42:38</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>11-02-2026 15:31:50</t>
-        </is>
-      </c>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6105,22 +6113,14 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26210522266660003022</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>VERONICA VIANEY LOYA CONTRERAS</t>
-        </is>
-      </c>
+          <t>26210522083170002489</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
@@ -6137,12 +6137,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>342302</t>
+          <t>344316</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20120</t>
+          <t>22133</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6152,17 +6152,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">MELANIE </t>
+          <t>MAYTE ANELIZ</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ALBAÑEZ</t>
+          <t xml:space="preserve">CUEVAS </t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6172,14 +6172,10 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6643640599</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>AGUA DULCE 618</t>
-        </is>
-      </c>
+          <t>6241717643</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6187,60 +6183,56 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>01-05-1980</t>
+          <t>02-01-2007</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>ANIEALRO2020@GMAIL.COM</t>
+          <t>ANELIZCG07@GMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>09-02-2026 17:06:10</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+          <t>16-02-2026 18:53:41</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>09-02-2026 17:08:49</t>
+          <t>17-02-2026 14:17:50</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>09-02-2026 17:08:25</t>
-        </is>
-      </c>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6248,14 +6240,14 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26210522200900002835</t>
+          <t>26210522429100003408</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
@@ -6272,12 +6264,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>344316</t>
+          <t>342302</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>22133</t>
+          <t>20120</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6287,17 +6279,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>MAYTE ANELIZ</t>
+          <t xml:space="preserve">MELANIE </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUEVAS </t>
+          <t>ALBAÑEZ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6307,10 +6299,14 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6241717643</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>6643640599</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>AGUA DULCE 618</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6318,56 +6314,60 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>02-01-2007</t>
+          <t>01-05-1980</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>ANELIZCG07@GMAIL.COM</t>
+          <t>ANIEALRO2020@GMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>16-02-2026 18:53:41</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 17:06:10</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>17-02-2026 14:17:50</t>
+          <t>09-02-2026 17:08:49</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>09-02-2026 17:08:25</t>
+        </is>
+      </c>
       <c r="U44" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr"/>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W44" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6375,14 +6375,14 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26210522429100003408</t>
+          <t>26210522200900002835</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
@@ -6399,12 +6399,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>342230</t>
+          <t>342226</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20048</t>
+          <t>20044</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6414,17 +6414,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ANA ARACELY</t>
+          <t>ARIANY ROSALIA</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>COTA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>COTA</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6434,10 +6434,14 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6121372111</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>6121692055</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>CALLE EL TRIUNFO #233</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6445,56 +6449,60 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>08-10-2008</t>
+          <t>08-10-1981</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>ARIANYR2C@HOTMAIL.COM</t>
+          <t>ARIANY2C@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>09-02-2026 15:59:56</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 15:54:22</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>12-02-2026 16:08:25</t>
+          <t>10-02-2026 17:08:18</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>10-02-2026 17:07:27</t>
+        </is>
+      </c>
       <c r="U45" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr"/>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W45" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6502,7 +6510,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26210522296870003118</t>
+          <t>26210522238630002941</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -6517,7 +6525,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
@@ -6534,12 +6542,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>342226</t>
+          <t>342230</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>20044</t>
+          <t>20048</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6549,19 +6557,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ARIANY ROSALIA</t>
+          <t>ANA ARACELY</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
+          <t>FLORES</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t>COTA</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>CARDENAS</t>
-        </is>
-      </c>
       <c r="G46" t="inlineStr">
         <is>
           <t>52</t>
@@ -6569,14 +6577,10 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6121692055</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>CALLE EL TRIUNFO #233</t>
-        </is>
-      </c>
+          <t>6121372111</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6584,60 +6588,56 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>08-10-1981</t>
+          <t>08-10-2008</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>ARIANY2C@HOTMAIL.COM</t>
+          <t>ARIANYR2C@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>09-02-2026 15:54:22</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
+          <t>09-02-2026 15:59:56</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>10-02-2026 17:08:18</t>
+          <t>12-02-2026 16:08:25</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>10-02-2026 17:07:27</t>
-        </is>
-      </c>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26210522238630002941</t>
+          <t>26210522296870003118</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
@@ -6677,12 +6677,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>343166</t>
+          <t>344935</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20983</t>
+          <t>22752</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6692,17 +6692,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA</t>
+          <t xml:space="preserve">JESUS ANTONIO </t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ACEVEDO</t>
+          <t>MADRID</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>RUVALCABA</t>
+          <t>GURROLA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6712,75 +6712,67 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6121068152</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>ROMA</t>
-        </is>
-      </c>
+          <t>6124408280</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>13-09-2003</t>
+          <t>23-04-1999</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>FERNANDAACEV13@GMAIL.COM</t>
+          <t>JESUSMG230499@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>12-02-2026 07:13:35</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+          <t>18-02-2026 19:00:03</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>12-02-2026 07:18:27</t>
+          <t>18-02-2026 19:01:59</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>12-02-2026 07:17:45</t>
-        </is>
-      </c>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6788,19 +6780,19 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26210522287800003090</t>
+          <t>26210522474020003495</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>Cristopher Armando Serrato</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -6812,12 +6804,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>344935</t>
+          <t>343166</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>22752</t>
+          <t>20983</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6827,17 +6819,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">JESUS ANTONIO </t>
+          <t>MARIA FERNANDA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MADRID</t>
+          <t>ACEVEDO</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>GURROLA</t>
+          <t>RUVALCABA</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6847,67 +6839,75 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6124408280</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>6121068152</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>ROMA</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>23-04-1999</t>
+          <t>13-09-2003</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>JESUSMG230499@ICLOUD.COM</t>
+          <t>FERNANDAACEV13@GMAIL.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>18-02-2026 19:00:03</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>12-02-2026 07:13:35</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>18-02-2026 19:01:59</t>
+          <t>12-02-2026 07:18:27</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr"/>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>12-02-2026 07:17:45</t>
+        </is>
+      </c>
       <c r="U48" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6915,19 +6915,19 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26210522474020003495</t>
+          <t>26210522287800003090</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Cristopher Armando Serrato</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -6939,12 +6939,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>343508</t>
+          <t>345619</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>21325</t>
+          <t>87784</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6954,17 +6954,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUISA FERNANDA </t>
+          <t>AZUL</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">MURILLO </t>
+          <t>DOMINGUEZ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">OLIVARES </t>
+          <t>ESCAMILLA</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6974,12 +6974,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6122290863</t>
+          <t>6121480447</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>C OLMECAS 508</t>
+          <t>CHAMETLA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6989,48 +6989,52 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>19-12-2004</t>
+          <t>28-01-1977</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>ISAFERNAN.19@GMAIL.COM</t>
+          <t>PLAYAZUL28@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>13-02-2026 15:03:03</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
+          <t>22-02-2026 13:07:59</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>13-02-2026 15:12:55</t>
+          <t>22-02-2026 13:15:30</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>22-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>13-02-2026 15:11:55</t>
+          <t>22-02-2026 13:13:25</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -7050,19 +7054,19 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26210522322150003203</t>
+          <t>26210522563650003675</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>Cristopher Armando Serrato</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -7074,12 +7078,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>345619</t>
+          <t>343508</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>87784</t>
+          <t>21325</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7089,17 +7093,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>AZUL</t>
+          <t xml:space="preserve">LUISA FERNANDA </t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>DOMINGUEZ</t>
+          <t xml:space="preserve">MURILLO </t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>ESCAMILLA</t>
+          <t xml:space="preserve">OLIVARES </t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7109,12 +7113,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6121480447</t>
+          <t>6122290863</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>CHAMETLA</t>
+          <t>C OLMECAS 508</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -7124,52 +7128,48 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>28-01-1977</t>
+          <t>19-12-2004</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>PLAYAZUL28@HOTMAIL.COM</t>
+          <t>ISAFERNAN.19@GMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>22-02-2026 13:07:59</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>13-02-2026 15:03:03</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>22-02-2026 13:15:30</t>
+          <t>13-02-2026 15:12:55</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>22-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>22-02-2026 13:13:25</t>
+          <t>13-02-2026 15:11:55</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -7189,19 +7189,19 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26210522563650003675</t>
+          <t>26210522322150003203</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>Cristopher Armando Serrato</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -7340,12 +7340,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>343827</t>
+          <t>343038</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>21644</t>
+          <t>20855</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7355,17 +7355,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">KARLA ADRIANA </t>
+          <t xml:space="preserve">DOLORES ITZEL </t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>MAYORAL</t>
+          <t xml:space="preserve">CUBILLOS </t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>COTA</t>
+          <t>SILVA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6122145835</t>
+          <t>6121029534</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>C JUAN SARABIA 725</t>
+          <t>C PABLO L. GONZALEZ 235</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -7390,17 +7390,17 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>04-11-1987</t>
+          <t>10-12-1994</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>KARLAMC4.87@GMAIL.COM</t>
+          <t>CUBILLOSITZEL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>15-02-2026 12:11:56</t>
+          <t>11-02-2026 16:24:22</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -7421,17 +7421,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>15-02-2026 12:17:37</t>
+          <t>11-02-2026 16:38:56</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>15-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>15-02-2026 12:16:16</t>
+          <t>11-02-2026 16:38:17</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26210522365310003259</t>
+          <t>26210522269110003031</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr"/>
@@ -7757,12 +7757,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>343038</t>
+          <t>343827</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>20855</t>
+          <t>21644</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7772,17 +7772,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">DOLORES ITZEL </t>
+          <t xml:space="preserve">KARLA ADRIANA </t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUBILLOS </t>
+          <t>MAYORAL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>COTA</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6121029534</t>
+          <t>6122145835</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>C PABLO L. GONZALEZ 235</t>
+          <t>C JUAN SARABIA 725</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7807,17 +7807,17 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>10-12-1994</t>
+          <t>04-11-1987</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>CUBILLOSITZEL@GMAIL.COM</t>
+          <t>KARLAMC4.87@GMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>11-02-2026 16:24:22</t>
+          <t>15-02-2026 12:11:56</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -7838,17 +7838,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>11-02-2026 16:38:56</t>
+          <t>15-02-2026 12:17:37</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>15-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>11-02-2026 16:38:17</t>
+          <t>15-02-2026 12:16:16</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26210522269110003031</t>
+          <t>26210522365310003259</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr"/>
@@ -7892,12 +7892,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>343379</t>
+          <t>343761</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>21196</t>
+          <t>21578</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7907,17 +7907,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SARA BEATRIZ</t>
+          <t>OSMAR ALEJANDRO</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASTELLANOS </t>
+          <t xml:space="preserve"> LIERA </t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -7927,35 +7927,39 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6122327477</t>
+          <t>6151559659</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>C MELON 121</t>
+          <t>CENTRO</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>03-06-1981</t>
+          <t>26-07-2001</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>DRA.SARACASTELLANOS@GMAIL.COM</t>
+          <t>LIERAGOMEZOSMARALEJANDRO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>12-02-2026 18:54:35</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
+          <t>14-02-2026 23:55:59</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O56" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7973,17 +7977,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>12-02-2026 18:58:52</t>
+          <t>20-02-2026 05:36:59</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>20-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>12-02-2026 18:58:05</t>
+          <t>20-02-2026 05:34:42</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -8003,10 +8007,14 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26210522303780003149</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr"/>
+          <t>26210522509510003598</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr">
         <is>
@@ -8015,24 +8023,24 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>344230</t>
+          <t>343379</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>22047</t>
+          <t>21196</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8042,17 +8050,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SERGIO ENRIQUE</t>
+          <t>SARA BEATRIZ</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t xml:space="preserve">CASTELLANOS </t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>ORDUÑO</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8062,67 +8070,63 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>6121770347</t>
+          <t>6122327477</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>C BAHIA DE SALINAS 89</t>
+          <t>C MELON 121</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>26-01-1989</t>
+          <t>03-06-1981</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>SHEKO84_26@HOTMAIL.COM</t>
+          <t>DRA.SARACASTELLANOS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>16-02-2026 17:42:13</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>12-02-2026 18:54:35</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>25-02-2026 15:36:45</t>
+          <t>12-02-2026 18:58:52</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>25-02-2026 15:36:06</t>
+          <t>12-02-2026 18:58:05</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -8132,7 +8136,7 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -8142,22 +8146,14 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26210522655670003952</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>VERONICA VIANEY LOYA CONTRERAS</t>
-        </is>
-      </c>
+          <t>26210522303780003149</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
@@ -8174,12 +8170,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>343761</t>
+          <t>343754</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>21578</t>
+          <t>21571</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8189,17 +8185,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>OSMAR ALEJANDRO</t>
+          <t>ERNESTO</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve"> LIERA </t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>ROSALES</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8209,12 +8205,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>6151559659</t>
+          <t>6241578514</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>CENTRO</t>
+          <t>PEDRO MATIAS GONI 353</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -8224,24 +8220,20 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>26-07-2001</t>
+          <t>07-11-1978</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>LIERAGOMEZOSMARALEJANDRO@GMAIL.COM</t>
+          <t>NETOGR78@GMAIL.COM</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>14-02-2026 23:55:59</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>14-02-2026 18:11:53</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8259,29 +8251,29 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>20-02-2026 05:36:59</t>
+          <t>14-02-2026 18:11:54</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
+          <t>14-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>20-02-2026 05:34:42</t>
+          <t>14-02-2026 18:11:54</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="W58" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8289,14 +8281,10 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>26210522509510003598</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26210522349800003253</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr">
         <is>
@@ -8305,24 +8293,24 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>343754</t>
+          <t>342920</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>21571</t>
+          <t>20737</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8332,17 +8320,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ERNESTO</t>
+          <t>FERNANDO</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ROSALES</t>
+          <t>ORNELAS</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -8352,12 +8340,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>6241578514</t>
+          <t>6121870554</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>PEDRO MATIAS GONI 353</t>
+          <t>LA CIMA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -8367,17 +8355,17 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>07-11-1978</t>
+          <t>16-09-1975</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>NETOGR78@GMAIL.COM</t>
+          <t>FERNANDOCRUZORNELAS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>14-02-2026 18:11:53</t>
+          <t>11-02-2026 09:39:30</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -8398,27 +8386,27 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>14-02-2026 18:11:54</t>
+          <t>11-02-2026 09:45:27</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>14-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>14-02-2026 18:11:54</t>
+          <t>11-02-2026 09:45:03</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
@@ -8428,7 +8416,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>26210522349800003253</t>
+          <t>26210522260970003000</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr"/>
@@ -8440,7 +8428,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -8452,12 +8440,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>342920</t>
+          <t>343251</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>20737</t>
+          <t>21068</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8467,17 +8455,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>FERNANDO</t>
+          <t>TAMARA</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ORNELAS</t>
+          <t>AGUIÑAGA</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -8487,75 +8475,67 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>6121870554</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>LA CIMA</t>
-        </is>
-      </c>
+          <t>5541288966</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>16-09-1975</t>
+          <t>21-12-2004</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>FERNANDOCRUZORNELAS@GMAIL.COM</t>
+          <t>TAMARA211204@GMAIL.COM</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>11-02-2026 09:39:30</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
+          <t>12-02-2026 13:32:17</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>11-02-2026 09:45:27</t>
+          <t>12-02-2026 13:33:36</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>11-02-2026 09:45:03</t>
-        </is>
-      </c>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V60" t="inlineStr"/>
       <c r="W60" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8563,19 +8543,19 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>26210522260970003000</t>
+          <t>26210522293540003108</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="inlineStr"/>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -8587,12 +8567,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>343251</t>
+          <t>346661</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>21068</t>
+          <t>88826</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8602,17 +8582,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>TAMARA</t>
+          <t xml:space="preserve">JOSE MARIA </t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AGUIÑAGA</t>
+          <t>COTA</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -8622,28 +8602,32 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>5541288966</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>6121210045</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>SANTA CLARA 137</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>21-12-2004</t>
+          <t>10-08-2004</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>TAMARA211204@GMAIL.COM</t>
+          <t>JHO76525@GMAIL.COM</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>12-02-2026 13:32:17</t>
+          <t>26-02-2026 10:16:45</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -8653,12 +8637,12 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -8668,21 +8652,29 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>12-02-2026 13:33:36</t>
+          <t>26-02-2026 10:33:02</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr"/>
+          <t>26-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>26-02-2026 10:28:15</t>
+        </is>
+      </c>
       <c r="U61" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr"/>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W61" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8690,7 +8682,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>26210522293540003108</t>
+          <t>26210522679680004020</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr"/>
@@ -8702,24 +8694,24 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>346661</t>
+          <t>346891</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>88826</t>
+          <t>89056</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8729,17 +8721,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE MARIA </t>
+          <t>ALBA PATRICIA</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>COTA</t>
+          <t>DUARTE</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -8749,37 +8741,37 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>6121210045</t>
+          <t>6124447099</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>SANTA CLARA 137</t>
+          <t>C ARQUITECTURA MZA 13</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>10-08-2004</t>
+          <t>15-10-1992</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>JHO76525@GMAIL.COM</t>
+          <t>DUARTEALBAA.9225@GMAIL.COM</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>26-02-2026 10:16:45</t>
+          <t>27-02-2026 09:47:34</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -8789,27 +8781,27 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>26-02-2026 10:33:02</t>
+          <t>27-02-2026 09:55:51</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>26-03-2026 23:59:59</t>
+          <t>27-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>26-02-2026 10:28:15</t>
+          <t>27-02-2026 09:54:09</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -8829,14 +8821,14 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>26210522679680004020</t>
+          <t>26210522708080004100</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
@@ -8853,12 +8845,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>346891</t>
+          <t>344321</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>89056</t>
+          <t>22138</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8868,17 +8860,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ALBA PATRICIA</t>
+          <t>NOELIA ANAID</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>ARAIZA</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>DUARTE</t>
+          <t>ALBAÑEZ</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -8888,14 +8880,10 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>6124447099</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>C ARQUITECTURA MZA 13</t>
-        </is>
-      </c>
+          <t>6121498018</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -8903,64 +8891,56 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>15-10-1992</t>
+          <t>25-05-2007</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>DUARTEALBAA.9225@GMAIL.COM</t>
+          <t>NOELIAANAIDARAIZA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>27-02-2026 09:47:34</t>
+          <t>16-02-2026 18:57:53</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>27-02-2026 09:55:51</t>
+          <t>16-02-2026 18:59:47</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>27-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>27-02-2026 09:54:09</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V63" t="inlineStr"/>
       <c r="W63" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8968,36 +8948,36 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>26210522708080004100</t>
+          <t>26210522406620003354</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="inlineStr"/>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>344321</t>
+          <t>344230</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>22138</t>
+          <t>22047</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -9007,17 +8987,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NOELIA ANAID</t>
+          <t>SERGIO ENRIQUE</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ARAIZA</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>ALBAÑEZ</t>
+          <t>ORDUÑO</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -9027,28 +9007,32 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>6121498018</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>6121770347</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>C BAHIA DE SALINAS 89</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>25-05-2007</t>
+          <t>26-01-1989</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>NOELIAANAIDARAIZA@GMAIL.COM</t>
+          <t>SHEKO84_26@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>16-02-2026 18:57:53</t>
+          <t>16-02-2026 17:42:13</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -9058,36 +9042,44 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>16-02-2026 18:59:47</t>
+          <t>25-02-2026 15:36:45</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T64" t="inlineStr"/>
+          <t>25-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>25-02-2026 15:36:06</t>
+        </is>
+      </c>
       <c r="U64" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V64" t="inlineStr"/>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W64" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -9095,14 +9087,22 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>26210522406620003354</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr"/>
-      <c r="Z64" t="inlineStr"/>
+          <t>26210522655670003952</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>VERONICA VIANEY LOYA CONTRERAS</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
@@ -9119,12 +9119,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>343375</t>
+          <t>344516</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>21192</t>
+          <t>22333</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9134,17 +9134,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIO ALBERTO </t>
+          <t>GABRIEL MARTIN</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ROSAS</t>
+          <t>GULUARTE</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANRIQUEZ </t>
+          <t>BARAJAS</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -9154,12 +9154,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>6122343338</t>
+          <t>6121009849</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>C MELON 121</t>
+          <t>C AGROPECUARIA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -9169,20 +9169,24 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>12-12-1977</t>
+          <t>13-02-2000</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>ROSASCASTELLANOS@GMAIL.COM</t>
+          <t>MARTINBARAJAS1302@GMAIL.COM</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>12-02-2026 18:48:15</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
+          <t>17-02-2026 15:10:23</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O65" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -9200,17 +9204,17 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>12-02-2026 18:53:02</t>
+          <t>17-02-2026 15:16:36</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>12-02-2026 18:52:16</t>
+          <t>17-02-2026 15:16:14</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -9220,7 +9224,7 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
@@ -9230,7 +9234,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>26210522303620003147</t>
+          <t>26210522431100003417</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr"/>
@@ -9254,12 +9258,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>344366</t>
+          <t>343375</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>22183</t>
+          <t>21192</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9269,17 +9273,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>REYNA ICELA</t>
+          <t xml:space="preserve">MARIO ALBERTO </t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>CADENA MATUS</t>
+          <t>ROSAS</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CADENA MATUS</t>
+          <t xml:space="preserve">MANRIQUEZ </t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -9289,39 +9293,35 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>6121971764</t>
+          <t>6122343338</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>REGIDORES 113</t>
+          <t>C MELON 121</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>22-08-1987</t>
+          <t>12-12-1977</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>REYNAICELACM@GMAIL.COM</t>
+          <t>ROSASCASTELLANOS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>16-02-2026 23:34:26</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>12-02-2026 18:48:15</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -9339,22 +9339,22 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>16-02-2026 23:34:27</t>
+          <t>12-02-2026 18:53:02</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>16-02-2026 23:34:27</t>
+          <t>12-02-2026 18:52:16</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -9369,7 +9369,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>26210522412010003364</t>
+          <t>26210522303620003147</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr"/>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -9393,12 +9393,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>344516</t>
+          <t>344366</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>22333</t>
+          <t>22183</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9408,17 +9408,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>GABRIEL MARTIN</t>
+          <t>REYNA ICELA</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>GULUARTE</t>
+          <t>CADENA MATUS</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>BARAJAS</t>
+          <t>CADENA MATUS</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -9428,32 +9428,32 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>6121009849</t>
+          <t>6121971764</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>C AGROPECUARIA</t>
+          <t>REGIDORES 113</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>13-02-2000</t>
+          <t>22-08-1987</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>MARTINBARAJAS1302@GMAIL.COM</t>
+          <t>REYNAICELACM@GMAIL.COM</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>17-02-2026 15:10:23</t>
+          <t>16-02-2026 23:34:26</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -9478,27 +9478,27 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>17-02-2026 15:16:36</t>
+          <t>16-02-2026 23:34:27</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>17-02-2026 15:16:14</t>
+          <t>16-02-2026 23:34:27</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>26210522431100003417</t>
+          <t>26210522412010003364</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr"/>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
@@ -9532,12 +9532,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>345768</t>
+          <t>344873</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>87933</t>
+          <t>22690</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9547,17 +9547,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANDRA </t>
+          <t>KARLA ROXANA</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ESCOBAR</t>
+          <t>MURILLO</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>VALDEZ</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -9567,12 +9567,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>6148590790</t>
+          <t>6121532789</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>MINA LA PAZ 16713</t>
+          <t>UNIVERSIDAD</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -9582,17 +9582,17 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>22-07-1988</t>
+          <t>18-09-1984</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>ESCOBARSARITO@GMAIL.COM</t>
+          <t>KMURILLO@UABCS.MX</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>23-02-2026 13:19:14</t>
+          <t>18-02-2026 16:45:58</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -9617,17 +9617,17 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>27-02-2026 19:49:56</t>
+          <t>18-02-2026 16:49:17</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>27-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>27-02-2026 19:47:22</t>
+          <t>18-02-2026 16:48:16</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -9647,19 +9647,11 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>26200522725200002577</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>MARIO ANDRE FIGUEROA RUIZ</t>
-        </is>
-      </c>
+          <t>26210522467350003478</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
       <c r="AA68" t="inlineStr">
         <is>
           <t>499</t>
@@ -9667,24 +9659,24 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>345784</t>
+          <t>345768</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>87949</t>
+          <t>87933</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -9694,12 +9686,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>JANETH</t>
+          <t xml:space="preserve">SANDRA </t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> RIVAS </t>
+          <t>ESCOBAR</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -9714,12 +9706,12 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>6141647304</t>
+          <t>6148590790</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>CALLE NAYARITH 21</t>
+          <t>MINA LA PAZ 16713</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -9729,17 +9721,17 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>22-07-1997</t>
+          <t>22-07-1988</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>CCRVS1323@GMAIL.COM</t>
+          <t>ESCOBARSARITO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>23-02-2026 13:49:05</t>
+          <t>23-02-2026 13:19:14</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -9764,7 +9756,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>27-02-2026 19:57:55</t>
+          <t>27-02-2026 19:49:56</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -9774,7 +9766,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>27-02-2026 19:57:31</t>
+          <t>27-02-2026 19:47:22</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -9784,7 +9776,7 @@
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
@@ -9794,7 +9786,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>26200522725330002578</t>
+          <t>26200522725200002577</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
@@ -9826,12 +9818,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>344873</t>
+          <t>345784</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>22690</t>
+          <t>87949</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -9841,17 +9833,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>KARLA ROXANA</t>
+          <t>JANETH</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MURILLO</t>
+          <t xml:space="preserve"> RIVAS </t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t>X</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -9861,12 +9853,12 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>6121532789</t>
+          <t>6141647304</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD</t>
+          <t>CALLE NAYARITH 21</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9876,17 +9868,17 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>18-09-1984</t>
+          <t>22-07-1997</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>KMURILLO@UABCS.MX</t>
+          <t>CCRVS1323@GMAIL.COM</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>18-02-2026 16:45:58</t>
+          <t>23-02-2026 13:49:05</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -9911,17 +9903,17 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>18-02-2026 16:49:17</t>
+          <t>27-02-2026 19:57:55</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>27-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>18-02-2026 16:48:16</t>
+          <t>27-02-2026 19:57:31</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -9931,7 +9923,7 @@
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W70" t="inlineStr">
@@ -9941,11 +9933,19 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>26210522467350003478</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr"/>
-      <c r="Z70" t="inlineStr"/>
+          <t>26200522725330002578</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>MARIO ANDRE FIGUEROA RUIZ</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>499</t>
@@ -9953,7 +9953,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>Juan Pablo Rieke Campoy</t>
+          <t>Ivonne Hernandez Rivera</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
@@ -9965,12 +9965,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>346048</t>
+          <t>346328</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>88213</t>
+          <t>88493</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -9980,17 +9980,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADALBERTO ABIMAEL </t>
+          <t xml:space="preserve">JORGE </t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ZAZUETA</t>
+          <t xml:space="preserve">RUIZ </t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>VEGA</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -10000,12 +10000,12 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>6122191467</t>
+          <t>6122133679</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>C MANUEL ENCINAS 1353</t>
+          <t>PRIV AZURITA M2</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -10015,17 +10015,17 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>21-10-1992</t>
+          <t>12-06-1986</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>REBUILDNERVE@GMAIL.COM</t>
+          <t>JM.AUTOSPA.LAPAZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>23-02-2026 20:33:49</t>
+          <t>24-02-2026 20:03:17</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -10050,17 +10050,17 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>23-02-2026 20:38:02</t>
+          <t>24-02-2026 20:22:54</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>24-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>23-02-2026 20:37:01</t>
+          <t>24-02-2026 20:07:54</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -10080,7 +10080,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>26210522601920003802</t>
+          <t>26210522636910003900</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr"/>
@@ -10104,12 +10104,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>345136</t>
+          <t>346048</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>87301</t>
+          <t>88213</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -10119,17 +10119,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>FRANCISCA CECILIA</t>
+          <t xml:space="preserve">ADALBERTO ABIMAEL </t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>BARRETO</t>
+          <t>ZAZUETA</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>BARRETO</t>
+          <t>VEGA</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -10139,67 +10139,79 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>6122148757</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>6122191467</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>C MANUEL ENCINAS 1353</t>
+        </is>
+      </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>22-11-1987</t>
+          <t>21-10-1992</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>BARRETOCECILIA925@GMAIL.COM</t>
+          <t>REBUILDNERVE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>19-02-2026 17:04:50</t>
+          <t>23-02-2026 20:33:49</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>19-02-2026 17:05:35</t>
+          <t>23-02-2026 20:38:02</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T72" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>23-02-2026 20:37:01</t>
+        </is>
+      </c>
       <c r="U72" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V72" t="inlineStr"/>
       <c r="W72" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10207,14 +10219,14 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>26210522500360003555</t>
+          <t>26210522601920003802</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="inlineStr"/>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
@@ -10231,12 +10243,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>344727</t>
+          <t>345136</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>22544</t>
+          <t>87301</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -10246,17 +10258,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>MARIA TERESA</t>
+          <t>FRANCISCA CECILIA</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>BARRETO</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>QUEZADA</t>
+          <t>BARRETO</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -10266,14 +10278,10 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>5578843819</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>CENTRO</t>
-        </is>
-      </c>
+          <t>6122148757</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -10281,17 +10289,17 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>31-05-1969</t>
+          <t>22-11-1987</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>MARIATERESAPEREZQUEZADA@GMAIL.COM</t>
+          <t>BARRETOCECILIA925@GMAIL.COM</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>18-02-2026 05:24:32</t>
+          <t>19-02-2026 17:04:50</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -10301,22 +10309,22 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>19-02-2026 06:46:30</t>
+          <t>19-02-2026 17:05:35</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -10324,21 +10332,13 @@
           <t>19-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>19-02-2026 06:44:39</t>
-        </is>
-      </c>
+      <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V73" t="inlineStr"/>
       <c r="W73" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10346,40 +10346,36 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>26210522487370003516</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26210522500360003555</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="inlineStr"/>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>346328</t>
+          <t>346045</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>88493</t>
+          <t>88210</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -10389,17 +10385,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">JORGE </t>
+          <t xml:space="preserve">LIZBETH </t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">RUIZ </t>
+          <t>PIÑUELAS</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t xml:space="preserve">SANTIAGO </t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -10409,32 +10405,32 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>6122133679</t>
+          <t>6121701231</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>PRIV AZURITA M2</t>
+          <t>C MANUEL ENCINAS 1353</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>12-06-1986</t>
+          <t>10-12-1997</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>JM.AUTOSPA.LAPAZ@GMAIL.COM</t>
+          <t>LIZPISA94@GMAIL.COM</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>24-02-2026 20:03:17</t>
+          <t>23-02-2026 20:23:38</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -10459,17 +10455,17 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>24-02-2026 20:22:54</t>
+          <t>23-02-2026 20:32:15</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>24-02-2026 20:07:54</t>
+          <t>23-02-2026 20:31:30</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -10489,7 +10485,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>26210522636910003900</t>
+          <t>26210522601760003801</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr"/>
@@ -10513,12 +10509,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>345078</t>
+          <t>344727</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>87243</t>
+          <t>22544</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -10528,17 +10524,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA VICTORIA </t>
+          <t>MARIA TERESA</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">BARRANCO </t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASTRO </t>
+          <t>QUEZADA</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -10548,12 +10544,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>6123489475</t>
+          <t>5578843819</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>C MAGUEY 4551</t>
+          <t>CENTRO</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -10563,42 +10559,42 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>08-02-1994</t>
+          <t>31-05-1969</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>ANACSTRO@GMAIL.COM</t>
+          <t>MARIATERESAPEREZQUEZADA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>19-02-2026 14:27:10</t>
+          <t>18-02-2026 05:24:32</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>19-02-2026 14:32:01</t>
+          <t>19-02-2026 06:46:30</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -10608,7 +10604,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>19-02-2026 14:31:19</t>
+          <t>19-02-2026 06:44:39</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -10628,36 +10624,40 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>26210522495380003538</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr"/>
+          <t>26210522487370003516</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z75" t="inlineStr"/>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>346045</t>
+          <t>346663</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>88210</t>
+          <t>88828</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -10667,17 +10667,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">LIZBETH </t>
+          <t>MARIA FERNANDA</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>PIÑUELAS</t>
+          <t xml:space="preserve">GONZALEZ </t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANTIAGO </t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -10687,14 +10687,10 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>6121701231</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>C MANUEL ENCINAS 1353</t>
-        </is>
-      </c>
+          <t>6121674092</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -10702,64 +10698,56 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>10-12-1997</t>
+          <t>08-05-2005</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>LIZPISA94@GMAIL.COM</t>
+          <t>FERNANDAGLEZM13@GMAIL.COM</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>23-02-2026 20:23:38</t>
+          <t>26-02-2026 10:35:53</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>23-02-2026 20:32:15</t>
+          <t>26-02-2026 10:38:17</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>23-02-2026 20:31:30</t>
-        </is>
-      </c>
+          <t>26-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr"/>
       <c r="U76" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V76" t="inlineStr"/>
       <c r="W76" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10767,36 +10755,36 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>26210522601760003801</t>
+          <t>26210522679730004021</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="inlineStr"/>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>346663</t>
+          <t>345078</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>88828</t>
+          <t>87243</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -10806,17 +10794,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA</t>
+          <t xml:space="preserve">ANA VICTORIA </t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONZALEZ </t>
+          <t xml:space="preserve">BARRANCO </t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t xml:space="preserve">CASTRO </t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -10826,10 +10814,14 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>6121674092</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>6123489475</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>C MAGUEY 4551</t>
+        </is>
+      </c>
       <c r="J77" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -10837,56 +10829,64 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>08-05-2005</t>
+          <t>08-02-1994</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>FERNANDAGLEZM13@GMAIL.COM</t>
+          <t>ANACSTRO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>26-02-2026 10:35:53</t>
+          <t>19-02-2026 14:27:10</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>26-02-2026 10:38:17</t>
+          <t>19-02-2026 14:32:01</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>26-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T77" t="inlineStr"/>
+          <t>19-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>19-02-2026 14:31:19</t>
+        </is>
+      </c>
       <c r="U77" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V77" t="inlineStr"/>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W77" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -10894,24 +10894,24 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>26210522679730004021</t>
+          <t>26210522495380003538</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="inlineStr"/>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__PASEO LA PAZ.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__PASEO LA PAZ.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -856,12 +856,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347807</t>
+          <t>348090</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89972</t>
+          <t>90255</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -871,17 +871,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">OSCAR DE JESUS </t>
+          <t>PERLA YAMELY</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">AVILES </t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -891,32 +891,32 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6121833306</t>
+          <t>6122342275</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>C AZTECAS 562</t>
+          <t>C VILLA LAETITIA 316</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>20-04-1986</t>
+          <t>22-05-1987</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>AVILESTORRESOSCARDEJESUS@GMAIL.COM</t>
+          <t>YAMELYGLEZ@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-03-2026 18:19:26</t>
+          <t>03-03-2026 15:41:32</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -941,17 +941,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 18:25:23</t>
+          <t>03-03-2026 15:46:24</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>02-03-2026 18:23:41</t>
+          <t>03-03-2026 15:45:50</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26210522811830004287</t>
+          <t>26210522844800004364</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
@@ -987,6 +987,284 @@
         </is>
       </c>
       <c r="AC4" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>347807</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>89972</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSCAR DE JESUS </t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AVILES </t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>TORRES</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>6121833306</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>C AZTECAS 562</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>20-04-1986</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>AVILESTORRESOSCARDEJESUS@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:19:26</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:25:23</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:23:41</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>26210522811830004287</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>348084</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>90249</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MITZI JAQUELIN</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZAZUETA </t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDINA </t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>3314282828</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>OAXACA 370</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>28-10-1998</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>MITZI.ZAZUETA.M@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>03-03-2026 15:27:52</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>03-03-2026 15:38:07</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>03-03-2026 15:37:20</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>26210522844480004363</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__PASEO LA PAZ.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__PASEO LA PAZ.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>347884</t>
+          <t>217127</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>90049</t>
+          <t>14635</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">JULIA VICTORIA </t>
+          <t>ITZEL NAHOMY</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>LUPERCIO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCERO </t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6121770622</t>
+          <t>6121761511</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>C VILLA MIRAKI 149</t>
+          <t>C SANTA ANA 1213</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -628,52 +628,52 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>07-05-2008</t>
+          <t>18-05-2004</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>JULIAVICTORIALUCERO@GMAIL.COM</t>
+          <t>NAHOMYLUPERCIO18@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>02-03-2026 19:49:13</t>
+          <t>29-01-2024 11:08:06</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02-03-2026 19:55:34</t>
+          <t>04-03-2026 15:26:33</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>02-03-2026 19:55:05</t>
+          <t>04-03-2026 15:25:21</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -693,14 +693,22 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26210522818280004310</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
+          <t>26210522885090004475</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>VERONICA VIANEY LOYA CONTRERAS</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -856,12 +864,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>348090</t>
+          <t>347401</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>90255</t>
+          <t>89566</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -871,17 +879,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PERLA YAMELY</t>
+          <t>LILIA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -891,12 +899,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6122342275</t>
+          <t>6121571433</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>C VILLA LAETITIA 316</t>
+          <t>REVOLUCION #1910</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -906,17 +914,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>22-05-1987</t>
+          <t>06-04-1970</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>YAMELYGLEZ@ICLOUD.COM</t>
+          <t>LOAALE@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>03-03-2026 15:41:32</t>
+          <t>02-03-2026 06:09:50</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -941,17 +949,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>03-03-2026 15:46:24</t>
+          <t>04-03-2026 06:13:55</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>03-03-2026 15:45:50</t>
+          <t>04-03-2026 06:13:02</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -961,7 +969,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -971,11 +979,19 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26210522844800004364</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+          <t>26210522865670004436</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Guillermo Velazquez Garcia de Alba</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>549</t>
@@ -983,12 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -1134,12 +1150,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>348084</t>
+          <t>348090</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>90249</t>
+          <t>90255</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1149,17 +1165,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MITZI JAQUELIN</t>
+          <t>PERLA YAMELY</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAZUETA </t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEDINA </t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1169,12 +1185,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3314282828</t>
+          <t>6122342275</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>OAXACA 370</t>
+          <t>C VILLA LAETITIA 316</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1184,17 +1200,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>28-10-1998</t>
+          <t>22-05-1987</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>MITZI.ZAZUETA.M@HOTMAIL.COM</t>
+          <t>YAMELYGLEZ@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>03-03-2026 15:27:52</t>
+          <t>03-03-2026 15:41:32</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1219,7 +1235,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>03-03-2026 15:38:07</t>
+          <t>03-03-2026 15:46:24</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1229,7 +1245,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>03-03-2026 15:37:20</t>
+          <t>03-03-2026 15:45:50</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1239,7 +1255,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1249,7 +1265,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26210522844480004363</t>
+          <t>26210522844800004364</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -1265,6 +1281,665 @@
         </is>
       </c>
       <c r="AC6" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>348773</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>90938</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JESUS IVAN </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RUIZ</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>FLORES</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>6121688845</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>21-08-2001</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>IVANFLORESCIV@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>05-03-2026 17:42:55</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>05-03-2026 17:44:17</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>05-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>26210522924890004584</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>348084</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>90249</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>MITZI JAQUELIN</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ZAZUETA </t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEDINA </t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>3314282828</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>OAXACA 370</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>28-10-1998</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>MITZI.ZAZUETA.M@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>03-03-2026 15:27:52</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>03-03-2026 15:38:07</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>03-03-2026 15:37:20</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>26210522844480004363</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>347884</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>90049</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JULIA VICTORIA </t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RODRIGUEZ </t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUCERO </t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>6121770622</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>C VILLA MIRAKI 149</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>07-05-2008</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>JULIAVICTORIALUCERO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:49:13</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:55:34</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:55:05</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>26210522818280004310</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>348551</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>90716</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CAROLINA </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GONZALEZ </t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TENA </t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>6121209365</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>29-05-2000</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>CAROLINAGONZALEZTNA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:01:21</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:02:41</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>04-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>26210522892810004499</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>348553</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>90718</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ENRIQUE </t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>FERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ALVARADO</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>6151035404</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>02-09-1997</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>EN.FERNANDEZ@UABC.MX</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:04:01</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:06:06</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>04-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>26210522893100004500</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__PASEO LA PAZ.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__PASEO LA PAZ.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>217127</t>
+          <t>346787</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14635</t>
+          <t>88952</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ITZEL NAHOMY</t>
+          <t xml:space="preserve">BARBARA </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LUPERCIO</t>
+          <t xml:space="preserve">ZARATE </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>OROZCO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6121761511</t>
+          <t>6121574684</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>C SANTA ANA 1213</t>
+          <t>C MELITON ALBAÑEZ 45</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -628,17 +628,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>18-05-2004</t>
+          <t>03-01-1982</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>NAHOMYLUPERCIO18@GMAIL.COM</t>
+          <t>BARBYMAYDEY@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>29-01-2024 11:08:06</t>
+          <t>26-02-2026 17:48:36</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -663,17 +663,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>04-03-2026 15:26:33</t>
+          <t>06-03-2026 17:17:38</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>05-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>04-03-2026 15:25:21</t>
+          <t>06-03-2026 17:16:13</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -693,19 +693,11 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26210522885090004475</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>VERONICA VIANEY LOYA CONTRERAS</t>
-        </is>
-      </c>
+          <t>26210522956030004656</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
           <t>549</t>
@@ -725,12 +717,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>347872</t>
+          <t>217127</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>90037</t>
+          <t>14635</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -740,17 +732,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIXA JUDITH </t>
+          <t>ITZEL NAHOMY</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>LUPERCIO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PEREA</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -760,12 +752,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6121034767</t>
+          <t>6121761511</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>C POSEIDON 624</t>
+          <t>C SANTA ANA 1213</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -775,52 +767,52 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>05-07-2001</t>
+          <t>18-05-2004</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>DANIXASOTOPEREA@GMAIL.COM</t>
+          <t>NAHOMYLUPERCIO18@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>02-03-2026 19:36:43</t>
+          <t>29-01-2024 11:08:06</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 19:52:01</t>
+          <t>04-03-2026 15:26:33</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>02-03-2026 19:45:26</t>
+          <t>04-03-2026 15:25:21</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -840,14 +832,22 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26210522818200004309</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
+          <t>26210522885090004475</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>VERONICA VIANEY LOYA CONTRERAS</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1150,12 +1150,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>348090</t>
+          <t>347884</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>90255</t>
+          <t>90049</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PERLA YAMELY</t>
+          <t xml:space="preserve">JULIA VICTORIA </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t xml:space="preserve">LUCERO </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6122342275</t>
+          <t>6121770622</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>C VILLA LAETITIA 316</t>
+          <t>C VILLA MIRAKI 149</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1200,52 +1200,52 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>22-05-1987</t>
+          <t>07-05-2008</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>YAMELYGLEZ@ICLOUD.COM</t>
+          <t>JULIAVICTORIALUCERO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>03-03-2026 15:41:32</t>
+          <t>02-03-2026 19:49:13</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>03-03-2026 15:46:24</t>
+          <t>02-03-2026 19:55:34</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>03-03-2026 15:45:50</t>
+          <t>02-03-2026 19:55:05</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1265,14 +1265,14 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26210522844800004364</t>
+          <t>26210522818280004310</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>348773</t>
+          <t>348084</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90938</t>
+          <t>90249</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1304,17 +1304,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">JESUS IVAN </t>
+          <t>MITZI JAQUELIN</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t xml:space="preserve">ZAZUETA </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t xml:space="preserve">MEDINA </t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1324,67 +1324,79 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6121688845</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>3314282828</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>OAXACA 370</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>21-08-2001</t>
+          <t>28-10-1998</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>IVANFLORESCIV@HOTMAIL.COM</t>
+          <t>MITZI.ZAZUETA.M@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>05-03-2026 17:42:55</t>
+          <t>03-03-2026 15:27:52</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>05-03-2026 17:44:17</t>
+          <t>03-03-2026 15:38:07</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>05-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>03-03-2026 15:37:20</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W7" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1392,14 +1404,14 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26210522924890004584</t>
+          <t>26210522844480004363</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1416,12 +1428,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>348084</t>
+          <t>348090</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>90249</t>
+          <t>90255</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1431,17 +1443,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MITZI JAQUELIN</t>
+          <t>PERLA YAMELY</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAZUETA </t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEDINA </t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1451,12 +1463,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3314282828</t>
+          <t>6122342275</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>OAXACA 370</t>
+          <t>C VILLA LAETITIA 316</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1466,17 +1478,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>28-10-1998</t>
+          <t>22-05-1987</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>MITZI.ZAZUETA.M@HOTMAIL.COM</t>
+          <t>YAMELYGLEZ@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>03-03-2026 15:27:52</t>
+          <t>03-03-2026 15:41:32</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1501,17 +1513,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>03-03-2026 15:38:07</t>
+          <t>03-03-2026 15:46:24</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>03-03-2026 15:37:20</t>
+          <t>03-03-2026 15:45:50</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1521,7 +1533,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1531,7 +1543,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26210522844480004363</t>
+          <t>26210522844800004364</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1555,12 +1567,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347884</t>
+          <t>347872</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>90049</t>
+          <t>90037</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1570,17 +1582,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">JULIA VICTORIA </t>
+          <t xml:space="preserve">DANIXA JUDITH </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCERO </t>
+          <t>PEREA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1590,12 +1602,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6121770622</t>
+          <t>6121034767</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>C VILLA MIRAKI 149</t>
+          <t>C POSEIDON 624</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1605,17 +1617,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>07-05-2008</t>
+          <t>05-07-2001</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>JULIAVICTORIALUCERO@GMAIL.COM</t>
+          <t>DANIXASOTOPEREA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 19:49:13</t>
+          <t>02-03-2026 19:36:43</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1640,17 +1652,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-03-2026 19:55:34</t>
+          <t>02-03-2026 19:52:01</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>02-03-2026 19:55:05</t>
+          <t>02-03-2026 19:45:26</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1670,7 +1682,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26210522818280004310</t>
+          <t>26210522818200004309</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
@@ -1694,12 +1706,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>348551</t>
+          <t>348553</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>90716</t>
+          <t>90718</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1709,17 +1721,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAROLINA </t>
+          <t xml:space="preserve">ENRIQUE </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONZALEZ </t>
+          <t>FERNANDEZ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">TENA </t>
+          <t>ALVARADO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1729,28 +1741,28 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6121209365</t>
+          <t>6151035404</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>29-05-2000</t>
+          <t>02-09-1997</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CAROLINAGONZALEZTNA@GMAIL.COM</t>
+          <t>EN.FERNANDEZ@UABC.MX</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>04-03-2026 18:01:21</t>
+          <t>04-03-2026 18:04:01</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1775,12 +1787,12 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>04-03-2026 18:02:41</t>
+          <t>04-03-2026 18:06:06</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>04-06-2026 23:59:59</t>
+          <t>03-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1797,7 +1809,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26210522892810004499</t>
+          <t>26210522893100004500</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
@@ -1821,12 +1833,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>348553</t>
+          <t>348551</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90718</t>
+          <t>90716</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1836,17 +1848,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENRIQUE </t>
+          <t xml:space="preserve">CAROLINA </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FERNANDEZ</t>
+          <t xml:space="preserve">GONZALEZ </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ALVARADO</t>
+          <t xml:space="preserve">TENA </t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1856,28 +1868,28 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6151035404</t>
+          <t>6121209365</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>02-09-1997</t>
+          <t>29-05-2000</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>EN.FERNANDEZ@UABC.MX</t>
+          <t>CAROLINAGONZALEZTNA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>04-03-2026 18:04:01</t>
+          <t>04-03-2026 18:01:21</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1902,12 +1914,12 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>04-03-2026 18:06:06</t>
+          <t>04-03-2026 18:02:41</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>04-06-2026 23:59:59</t>
+          <t>03-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1924,7 +1936,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26210522893100004500</t>
+          <t>26210522892810004499</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
@@ -1940,6 +1952,260 @@
         </is>
       </c>
       <c r="AC11" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>348773</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>90938</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JESUS IVAN </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RUIZ</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>FLORES</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>6121688845</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>21-08-2001</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>IVANFLORESCIV@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>05-03-2026 17:42:55</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>05-03-2026 17:44:17</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>04-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>26210522924890004584</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>348995</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>91160</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>JENNIFER</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SOLIS</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>BERNAL</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>5569105371</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>26-05-2003</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>SOLISBERNALJENNIFER3@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>06-03-2026 17:26:05</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>07-03-2026 13:32:29</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>06-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>26210522975760004698</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__PASEO LA PAZ.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__PASEO LA PAZ.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC13"/>
+  <dimension ref="A1:AC34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>346787</t>
+          <t>217127</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>88952</t>
+          <t>14635</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BARBARA </t>
+          <t>ITZEL NAHOMY</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZARATE </t>
+          <t>LUPERCIO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>OROZCO</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6121574684</t>
+          <t>6121761511</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>C MELITON ALBAÑEZ 45</t>
+          <t>C SANTA ANA 1213</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -628,17 +628,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>03-01-1982</t>
+          <t>18-05-2004</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>BARBYMAYDEY@ICLOUD.COM</t>
+          <t>NAHOMYLUPERCIO18@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>26-02-2026 17:48:36</t>
+          <t>29-01-2024 11:08:06</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -663,17 +663,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>06-03-2026 17:17:38</t>
+          <t>04-03-2026 15:26:33</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>06-03-2026 17:16:13</t>
+          <t>04-03-2026 15:25:21</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -693,11 +693,19 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26210522956030004656</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
+          <t>26210522885090004475</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>VERONICA VIANEY LOYA CONTRERAS</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>549</t>
@@ -717,12 +725,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>217127</t>
+          <t>340782</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14635</t>
+          <t>18600</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -732,17 +740,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ITZEL NAHOMY</t>
+          <t>CAROLINA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LUPERCIO</t>
+          <t xml:space="preserve">CASTRO </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t xml:space="preserve">COTA </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -752,14 +760,10 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6121761511</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>C SANTA ANA 1213</t>
-        </is>
-      </c>
+          <t>6121683063</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -767,32 +771,32 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>18-05-2004</t>
+          <t>19-04-1982</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>NAHOMYLUPERCIO18@GMAIL.COM</t>
+          <t>CAROLCASTRO_27@LIVE.COM.MX</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>29-01-2024 11:08:06</t>
+          <t>03-02-2026 18:20:32</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -802,29 +806,21 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>04-03-2026 15:26:33</t>
+          <t>18-03-2026 15:11:59</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>04-03-2026 15:25:21</t>
-        </is>
-      </c>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -832,7 +828,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26210522885090004475</t>
+          <t>26210523294190005455</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -864,12 +860,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347401</t>
+          <t>318230</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89566</t>
+          <t>15727</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -879,17 +875,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LILIA</t>
+          <t>MARIANN VICTORIA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>ROLDAN</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>CONTRERAS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -899,14 +895,10 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6121571433</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>REVOLUCION #1910</t>
-        </is>
-      </c>
+          <t>6121837034</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -914,32 +906,32 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>06-04-1970</t>
+          <t>25-09-2010</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>LOAALE@HOTMAIL.COM</t>
+          <t>MARIANVROLD_@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-03-2026 06:09:50</t>
+          <t>11-10-2025 10:45:14</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -949,29 +941,21 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>04-03-2026 06:13:55</t>
+          <t>09-03-2026 18:16:05</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>04-03-2026 06:13:02</t>
-        </is>
-      </c>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -979,7 +963,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26210522865670004436</t>
+          <t>26210523021670004793</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -989,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Guillermo Velazquez Garcia de Alba</t>
+          <t>CRISTINA AYLIN CHAVEZ GONZALEZ</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,24 +983,24 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347807</t>
+          <t>346787</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89972</t>
+          <t>88952</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1026,17 +1010,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">OSCAR DE JESUS </t>
+          <t xml:space="preserve">BARBARA </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AVILES </t>
+          <t xml:space="preserve">ZARATE </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>OROZCO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1046,32 +1030,32 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6121833306</t>
+          <t>6121574684</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>C AZTECAS 562</t>
+          <t>C MELITON ALBAÑEZ 45</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>20-04-1986</t>
+          <t>03-01-1982</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>AVILESTORRESOSCARDEJESUS@GMAIL.COM</t>
+          <t>BARBYMAYDEY@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-03-2026 18:19:26</t>
+          <t>26-02-2026 17:48:36</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1096,17 +1080,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 18:25:23</t>
+          <t>06-03-2026 17:17:38</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>05-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>02-03-2026 18:23:41</t>
+          <t>06-03-2026 17:16:13</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1116,7 +1100,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1126,7 +1110,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26210522811830004287</t>
+          <t>26210522956030004656</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
@@ -1150,12 +1134,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347884</t>
+          <t>347401</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>90049</t>
+          <t>89566</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1165,17 +1149,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">JULIA VICTORIA </t>
+          <t>LILIA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCERO </t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1185,12 +1169,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6121770622</t>
+          <t>6121571433</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>C VILLA MIRAKI 149</t>
+          <t>REVOLUCION #1910</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1200,52 +1184,52 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>07-05-2008</t>
+          <t>06-04-1970</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>JULIAVICTORIALUCERO@GMAIL.COM</t>
+          <t>LOAALE@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-03-2026 19:49:13</t>
+          <t>02-03-2026 06:09:50</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 19:55:34</t>
+          <t>04-03-2026 06:13:55</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>02-03-2026 19:55:05</t>
+          <t>04-03-2026 06:13:02</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1255,7 +1239,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1265,36 +1249,44 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26210522818280004310</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
+          <t>26210522865670004436</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Guillermo Velazquez Garcia de Alba</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>348084</t>
+          <t>347884</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90249</t>
+          <t>90049</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1304,17 +1296,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MITZI JAQUELIN</t>
+          <t xml:space="preserve">JULIA VICTORIA </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAZUETA </t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEDINA </t>
+          <t xml:space="preserve">LUCERO </t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1324,12 +1316,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3314282828</t>
+          <t>6121770622</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>OAXACA 370</t>
+          <t>C VILLA MIRAKI 149</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1339,52 +1331,52 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>28-10-1998</t>
+          <t>07-05-2008</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>MITZI.ZAZUETA.M@HOTMAIL.COM</t>
+          <t>JULIAVICTORIALUCERO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>03-03-2026 15:27:52</t>
+          <t>02-03-2026 19:49:13</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>03-03-2026 15:38:07</t>
+          <t>02-03-2026 19:55:34</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>03-03-2026 15:37:20</t>
+          <t>02-03-2026 19:55:05</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1394,7 +1386,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1404,14 +1396,14 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26210522844480004363</t>
+          <t>26210522818280004310</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1428,12 +1420,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>348090</t>
+          <t>347807</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>90255</t>
+          <t>89972</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1443,17 +1435,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PERLA YAMELY</t>
+          <t xml:space="preserve">OSCAR DE JESUS </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t xml:space="preserve">AVILES </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1463,32 +1455,32 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6122342275</t>
+          <t>6121833306</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>C VILLA LAETITIA 316</t>
+          <t>C AZTECAS 562</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>22-05-1987</t>
+          <t>20-04-1986</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>YAMELYGLEZ@ICLOUD.COM</t>
+          <t>AVILESTORRESOSCARDEJESUS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>03-03-2026 15:41:32</t>
+          <t>02-03-2026 18:19:26</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1513,17 +1505,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>03-03-2026 15:46:24</t>
+          <t>02-03-2026 18:25:23</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>03-03-2026 15:45:50</t>
+          <t>02-03-2026 18:23:41</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1543,7 +1535,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26210522844800004364</t>
+          <t>26210522811830004287</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1706,12 +1698,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>348553</t>
+          <t>348090</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>90718</t>
+          <t>90255</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1721,17 +1713,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENRIQUE </t>
+          <t>PERLA YAMELY</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FERNANDEZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ALVARADO</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1741,67 +1733,79 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6151035404</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>6122342275</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>C VILLA LAETITIA 316</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>02-09-1997</t>
+          <t>22-05-1987</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>EN.FERNANDEZ@UABC.MX</t>
+          <t>YAMELYGLEZ@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>04-03-2026 18:04:01</t>
+          <t>03-03-2026 15:41:32</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>04-03-2026 18:06:06</t>
+          <t>03-03-2026 15:46:24</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>03-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>03-03-2026 15:45:50</t>
+        </is>
+      </c>
       <c r="U10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1809,14 +1813,14 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26210522893100004500</t>
+          <t>26210522844800004364</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1833,12 +1837,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>348551</t>
+          <t>348324</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90716</t>
+          <t>90489</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1848,17 +1852,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAROLINA </t>
+          <t xml:space="preserve">RODOLFO </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONZALEZ </t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">TENA </t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1868,67 +1872,79 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6121209365</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>6121881551</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>CALLE # 3</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>29-05-2000</t>
+          <t>21-01-1971</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CAROLINAGONZALEZTNA@GMAIL.COM</t>
+          <t>CGALAPAZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>04-03-2026 18:01:21</t>
+          <t>04-03-2026 06:48:12</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>04-03-2026 18:02:41</t>
+          <t>09-03-2026 08:12:11</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>03-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr"/>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>09-03-2026 08:02:31</t>
+        </is>
+      </c>
       <c r="U11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1936,14 +1952,22 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26210522892810004499</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
+          <t>26210523000020004734</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Guillermo Velazquez Garcia de Alba</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1960,12 +1984,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>348773</t>
+          <t>348322</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>90938</t>
+          <t>90487</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1975,17 +1999,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">JESUS IVAN </t>
+          <t xml:space="preserve">YUKIKO </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>ARIAS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1995,67 +2019,79 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6121688845</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>6122026071</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>CALLE# 3</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>21-08-2001</t>
+          <t>23-06-1987</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>IVANFLORESCIV@HOTMAIL.COM</t>
+          <t>YUKIKOARIAS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>05-03-2026 17:42:55</t>
+          <t>04-03-2026 06:43:22</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>05-03-2026 17:44:17</t>
+          <t>09-03-2026 08:17:11</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>04-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr"/>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>09-03-2026 08:16:44</t>
+        </is>
+      </c>
       <c r="U12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2063,14 +2099,22 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26210522924890004584</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
+          <t>26210523000180004735</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Guillermo Velazquez Garcia de Alba</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -2087,12 +2131,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>348995</t>
+          <t>348084</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>91160</t>
+          <t>90249</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2102,17 +2146,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>JENNIFER</t>
+          <t>MITZI JAQUELIN</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SOLIS</t>
+          <t xml:space="preserve">ZAZUETA </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>BERNAL</t>
+          <t xml:space="preserve">MEDINA </t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2122,10 +2166,14 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5569105371</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>3314282828</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>OAXACA 370</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2133,56 +2181,64 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>26-05-2003</t>
+          <t>28-10-1998</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>SOLISBERNALJENNIFER3@GMAIL.COM</t>
+          <t>MITZI.ZAZUETA.M@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>06-03-2026 17:26:05</t>
+          <t>03-03-2026 15:27:52</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>07-03-2026 13:32:29</t>
+          <t>03-03-2026 15:38:07</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>06-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>03-03-2026 15:37:20</t>
+        </is>
+      </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W13" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2190,22 +2246,2769 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26210522975760004698</t>
+          <t>26210522844480004363</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>348553</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>90718</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ENRIQUE </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>FERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ALVARADO</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>6151035404</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>02-09-1997</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>EN.FERNANDEZ@UABC.MX</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:04:01</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:06:06</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>03-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>26210522893100004500</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>348681</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>90846</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CLAUDIA YANET</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> MEDELLIN</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> MARTINEZ</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>6121768652</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>30-10-1978</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>ATNDH.ISSSTEHG@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>05-03-2026 12:15:38</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>18-03-2026 14:09:39</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>26210523292300005450</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>CRISTINA AYLIN CHAVEZ GONZALEZ</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>348773</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>90938</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JESUS IVAN </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RUIZ</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>FLORES</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>6121688845</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>21-08-2001</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>IVANFLORESCIV@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>05-03-2026 17:42:55</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>05-03-2026 17:44:17</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>04-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>26210522924890004584</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>348551</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>90716</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CAROLINA </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GONZALEZ </t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TENA </t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>6121209365</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>29-05-2000</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>CAROLINAGONZALEZTNA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:01:21</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:02:41</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>03-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>26210522892810004499</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>348995</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>91160</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>JENNIFER</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>SOLIS</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>BERNAL</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>5569105371</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>26-05-2003</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>SOLISBERNALJENNIFER3@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>06-03-2026 17:26:05</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>899</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>07-03-2026 13:32:29</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>06-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>26210522975760004698</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>349634</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>91799</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>JESUS EDUARDO</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>CORONADO</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SOLIS</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>3222622231</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>C OLEAJE 290</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>05-04-2009</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>JESUSCORONADO1209@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:55:07</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:57:49</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:57:19</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>26210523025010004805</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>349643</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>91808</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ALEXSA PAULET</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>BELTRAN</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GUTIERREZ </t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>6122324179</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>18-11-2008</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>ALEXSAPAULETBELTRANMORA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>09-03-2026 19:04:02</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>09-03-2026 19:05:11</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>26210523025690004807</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>349621</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>91786</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VIRGINIA</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>CORONADO</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SOLIS</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>6122500220</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>C OLEAJE 290</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>16-11-1991</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>VIRGINIACORONADO1209@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:43:37</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:53:31</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:51:27</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>26210523024640004803</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>349596</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>91761</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ALAN ALEXANDER</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>ARREOLA</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>PEREZ</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>6123484570</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>14-08-2009</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>ALAN.09AP28@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:12:45</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>12-03-2026 16:46:17</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>26210523126850005063</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>350435</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>92599</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AZUL JOHANA </t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BENITEZ </t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DOMINGUEZ </t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>7531651551</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>12-05-1996</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>ANYA12270213@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>12-03-2026 18:30:32</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>12-03-2026 18:32:25</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>11-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>26210523131670005075</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>350190</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>92355</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANGEL ENRIQUE </t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JORDAN </t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MADERA </t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>6121545813</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>29-07-2004</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>FECA362@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>11-03-2026 18:09:43</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>11-03-2026 18:10:47</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>10-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>26210523098170004990</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>351715</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>93879</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JOHANN EMIR </t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DAVIS </t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>CARBALLO</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>6122182276</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>23-06-2008</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>JEMIRS@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>17-03-2026 20:25:14</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>19-03-2026 19:37:43</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>18-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>26210523341920005574</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>VERONICA VIANEY LOYA CONTRERAS</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>351912</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>94076</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>JOSE ANTONIO</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>SOSA</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>9622915521</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>29-07-2003</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>JOSEANTONIOSOSALOPEZ26@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>18-03-2026 17:40:04</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>18-03-2026 17:41:09</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>26210523300070005469</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>352135</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>94299</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANGEL DE JESUS </t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>SILVA</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2227397462</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>C DE LA NORIA 459-B</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>27-01-2000</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>ANGELDEJESUSSILVA61@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>19-03-2026 16:41:16</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>19-03-2026 16:53:56</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>18-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>19-03-2026 16:52:23</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>26210523333450005550</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>351913</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>94077</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ESLIN DANIEL</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOMEZ </t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PEREZ </t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>6692359001</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>09-09-1999</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>EDANIEL909@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>18-03-2026 17:42:35</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>18-03-2026 17:43:30</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>26210523300250005470</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>352212</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>94376</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OLIVIA </t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>LARA</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>CASTILLO</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>6121530603</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>AGINGANDU LT 10</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>27-12-1980</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>LARACASTILLOLIVIA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>19-03-2026 20:01:32</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>19-03-2026 20:10:12</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>18-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>19-03-2026 20:09:26</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>26210523343270005577</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>352216</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>94380</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VALENTINA ISABEL</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>ESPINOZA</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>LARA</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>6122038086</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>23-11-2008</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>VALESPINOZALARA08@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>19-03-2026 20:07:14</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>19-03-2026 20:10:12</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>18-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>26210523343270005577</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>351713</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>93877</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KHAZEL </t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>MAGAÑA</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BARAJAS </t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>6121409077</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>08-11-2008</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>KHAZELITO08@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>17-03-2026 20:22:24</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>19-03-2026 19:39:17</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>18-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>26210523342010005575</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>VERONICA VIANEY LOYA CONTRERAS</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>352014</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>94178</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GABRIEL </t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>VALENCIA</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>LUCERO</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>6121006899</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C TEOTIHUACAN </t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>14-06-2002</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>GABRIELVALENCIALUCERO07@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>18-03-2026 20:58:14</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>18-03-2026 21:05:19</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>18-03-2026 21:04:30</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>26210523310820005509</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>352220</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>94384</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>JESUS ALBERTO</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>CASTANEDO</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>6122121070</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>C PERU 340</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>15-04-1969</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>1JCASTANEDO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>19-03-2026 20:15:21</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>19-03-2026 20:20:34</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>18-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>19-03-2026 20:19:39</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>26210523343810005580</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>352222</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>94386</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARIA DE LOS ANGELES </t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>GUILLEN</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PEÑALOZA </t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>6122200244</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>28-07-1981</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>MARI32.9P@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>19-03-2026 20:18:42</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>19-03-2026 20:20:34</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>18-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>26210523343810005580</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__PASEO LA PAZ.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__PASEO LA PAZ.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC34"/>
+  <dimension ref="A1:AC54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -725,12 +725,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>340782</t>
+          <t>245455</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18600</t>
+          <t>42960</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -740,17 +740,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CAROLINA</t>
+          <t xml:space="preserve">GABRIEL </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASTRO </t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">COTA </t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -760,28 +760,28 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6121683063</t>
+          <t>6122208009</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>19-04-1982</t>
+          <t>16-04-2010</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CAROLCASTRO_27@LIVE.COM.MX</t>
+          <t>GABRIELGARCIAROMERO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>03-02-2026 18:20:32</t>
+          <t>12-07-2024 17:28:46</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -806,12 +806,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>18-03-2026 15:11:59</t>
+          <t>24-03-2026 19:18:58</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>17-04-2026 23:59:59</t>
+          <t>23-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26210523294190005455</t>
+          <t>26210523481800005887</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -836,11 +836,7 @@
           <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>VERONICA VIANEY LOYA CONTRERAS</t>
-        </is>
-      </c>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
           <t>549</t>
@@ -860,12 +856,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>318230</t>
+          <t>259929</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15727</t>
+          <t>57433</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -875,17 +871,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MARIANN VICTORIA</t>
+          <t>YOHANA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ROLDAN</t>
+          <t>MURILLO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CONTRERAS</t>
+          <t>SALAS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -895,7 +891,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6121837034</t>
+          <t>6122338187</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -906,17 +902,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>25-09-2010</t>
+          <t>08-08-2006</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>MARIANVROLD_@GMAIL.COM</t>
+          <t>CBZDCOCO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>11-10-2025 10:45:14</t>
+          <t>30-09-2024 20:18:20</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -941,12 +937,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>09-03-2026 18:16:05</t>
+          <t>30-03-2026 14:58:24</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
+          <t>29-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -963,19 +959,11 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26210523021670004793</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>CRISTINA AYLIN CHAVEZ GONZALEZ</t>
-        </is>
-      </c>
+          <t>26020523631090002632</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
           <t>549</t>
@@ -995,12 +983,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>346787</t>
+          <t>340782</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>88952</t>
+          <t>18600</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1010,17 +998,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">BARBARA </t>
+          <t>CAROLINA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZARATE </t>
+          <t xml:space="preserve">CASTRO </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>OROZCO</t>
+          <t xml:space="preserve">COTA </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1030,14 +1018,10 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6121574684</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>C MELITON ALBAÑEZ 45</t>
-        </is>
-      </c>
+          <t>6121683063</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1045,32 +1029,32 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>03-01-1982</t>
+          <t>19-04-1982</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>BARBYMAYDEY@ICLOUD.COM</t>
+          <t>CAROLCASTRO_27@LIVE.COM.MX</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>26-02-2026 17:48:36</t>
+          <t>03-02-2026 18:20:32</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1080,29 +1064,21 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>06-03-2026 17:17:38</t>
+          <t>18-03-2026 15:11:59</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>06-03-2026 17:16:13</t>
-        </is>
-      </c>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1110,11 +1086,19 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26210522956030004656</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+          <t>26210523294190005455</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>VERONICA VIANEY LOYA CONTRERAS</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>549</t>
@@ -1122,24 +1106,24 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347401</t>
+          <t>338272</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89566</t>
+          <t>16090</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1149,17 +1133,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LILIA</t>
+          <t>CARLA VICTORIA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>SILVESTRE</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1169,14 +1153,10 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6121571433</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>REVOLUCION #1910</t>
-        </is>
-      </c>
+          <t>9921415133</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1184,64 +1164,56 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>06-04-1970</t>
+          <t>20-11-1996</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>LOAALE@HOTMAIL.COM</t>
+          <t>CARLAVICTORIASILVESTREPEREZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-03-2026 06:09:50</t>
+          <t>27-01-2026 08:10:06</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>2 MESES X $ 1250</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>625</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>04-03-2026 06:13:55</t>
+          <t>30-03-2026 09:04:37</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>04-03-2026 06:13:02</t>
-        </is>
-      </c>
+          <t>29-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1249,7 +1221,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26210522865670004436</t>
+          <t>26210523621020006219</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1264,29 +1236,29 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Christian Jahassiel Castro Navarro</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347884</t>
+          <t>318230</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90049</t>
+          <t>15727</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1296,17 +1268,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">JULIA VICTORIA </t>
+          <t>MARIANN VICTORIA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>ROLDAN</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCERO </t>
+          <t>CONTRERAS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1316,14 +1288,10 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6121770622</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>C VILLA MIRAKI 149</t>
-        </is>
-      </c>
+          <t>6121837034</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1331,64 +1299,56 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>07-05-2008</t>
+          <t>25-09-2010</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>JULIAVICTORIALUCERO@GMAIL.COM</t>
+          <t>MARIANVROLD_@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 19:49:13</t>
+          <t>11-10-2025 10:45:14</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-03-2026 19:55:34</t>
+          <t>09-03-2026 18:16:05</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>02-03-2026 19:55:05</t>
-        </is>
-      </c>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1396,14 +1356,22 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26210522818280004310</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
+          <t>26210523021670004793</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>CRISTINA AYLIN CHAVEZ GONZALEZ</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1420,12 +1388,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347807</t>
+          <t>346787</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89972</t>
+          <t>88952</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1435,17 +1403,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">OSCAR DE JESUS </t>
+          <t xml:space="preserve">BARBARA </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">AVILES </t>
+          <t xml:space="preserve">ZARATE </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>OROZCO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1455,32 +1423,32 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6121833306</t>
+          <t>6121574684</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>C AZTECAS 562</t>
+          <t>C MELITON ALBAÑEZ 45</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>20-04-1986</t>
+          <t>03-01-1982</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>AVILESTORRESOSCARDEJESUS@GMAIL.COM</t>
+          <t>BARBYMAYDEY@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 18:19:26</t>
+          <t>26-02-2026 17:48:36</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1505,17 +1473,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 18:25:23</t>
+          <t>06-03-2026 17:17:38</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>05-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>02-03-2026 18:23:41</t>
+          <t>06-03-2026 17:16:13</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1525,7 +1493,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1535,7 +1503,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26210522811830004287</t>
+          <t>26210522956030004656</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1559,12 +1527,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347872</t>
+          <t>347401</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>90037</t>
+          <t>89566</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1574,17 +1542,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIXA JUDITH </t>
+          <t>LILIA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PEREA</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1594,12 +1562,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6121034767</t>
+          <t>6121571433</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>C POSEIDON 624</t>
+          <t>REVOLUCION #1910</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1609,52 +1577,52 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>05-07-2001</t>
+          <t>06-04-1970</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>DANIXASOTOPEREA@GMAIL.COM</t>
+          <t>LOAALE@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 19:36:43</t>
+          <t>02-03-2026 06:09:50</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-03-2026 19:52:01</t>
+          <t>04-03-2026 06:13:55</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>02-03-2026 19:45:26</t>
+          <t>04-03-2026 06:13:02</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1664,7 +1632,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1674,36 +1642,44 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26210522818200004309</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
+          <t>26210522865670004436</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Guillermo Velazquez Garcia de Alba</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>348090</t>
+          <t>347872</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>90255</t>
+          <t>90037</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1713,17 +1689,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PERLA YAMELY</t>
+          <t xml:space="preserve">DANIXA JUDITH </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t>PEREA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1733,12 +1709,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6122342275</t>
+          <t>6121034767</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>C VILLA LAETITIA 316</t>
+          <t>C POSEIDON 624</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1748,52 +1724,52 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>22-05-1987</t>
+          <t>05-07-2001</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>YAMELYGLEZ@ICLOUD.COM</t>
+          <t>DANIXASOTOPEREA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>03-03-2026 15:41:32</t>
+          <t>02-03-2026 19:36:43</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>03-03-2026 15:46:24</t>
+          <t>02-03-2026 19:52:01</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>03-03-2026 15:45:50</t>
+          <t>02-03-2026 19:45:26</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1813,14 +1789,14 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26210522844800004364</t>
+          <t>26210522818200004309</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1837,12 +1813,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>348324</t>
+          <t>347884</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90489</t>
+          <t>90049</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1852,17 +1828,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODOLFO </t>
+          <t xml:space="preserve">JULIA VICTORIA </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t xml:space="preserve">LUCERO </t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1872,67 +1848,67 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6121881551</t>
+          <t>6121770622</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>CALLE # 3</t>
+          <t>C VILLA MIRAKI 149</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>21-01-1971</t>
+          <t>07-05-2008</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CGALAPAZ@GMAIL.COM</t>
+          <t>JULIAVICTORIALUCERO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>04-03-2026 06:48:12</t>
+          <t>02-03-2026 19:49:13</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>09-03-2026 08:12:11</t>
+          <t>02-03-2026 19:55:34</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>09-03-2026 08:02:31</t>
+          <t>02-03-2026 19:55:05</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1952,22 +1928,14 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26210523000020004734</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Guillermo Velazquez Garcia de Alba</t>
-        </is>
-      </c>
+          <t>26210522818280004310</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -2119,24 +2087,24 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>348084</t>
+          <t>347807</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>90249</t>
+          <t>89972</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2146,17 +2114,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MITZI JAQUELIN</t>
+          <t xml:space="preserve">OSCAR DE JESUS </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZAZUETA </t>
+          <t xml:space="preserve">AVILES </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEDINA </t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2166,32 +2134,32 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3314282828</t>
+          <t>6121833306</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>OAXACA 370</t>
+          <t>C AZTECAS 562</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>28-10-1998</t>
+          <t>20-04-1986</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>MITZI.ZAZUETA.M@HOTMAIL.COM</t>
+          <t>AVILESTORRESOSCARDEJESUS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>03-03-2026 15:27:52</t>
+          <t>02-03-2026 18:19:26</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2216,17 +2184,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>03-03-2026 15:38:07</t>
+          <t>02-03-2026 18:25:23</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>03-03-2026 15:37:20</t>
+          <t>02-03-2026 18:23:41</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2236,7 +2204,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2246,7 +2214,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26210522844480004363</t>
+          <t>26210522811830004287</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
@@ -2270,12 +2238,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>348553</t>
+          <t>348324</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>90718</t>
+          <t>90489</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2285,17 +2253,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENRIQUE </t>
+          <t xml:space="preserve">RODOLFO </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FERNANDEZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ALVARADO</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2305,10 +2273,14 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6151035404</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>6121881551</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>CALLE # 3</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2316,56 +2288,64 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>02-09-1997</t>
+          <t>21-01-1971</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>EN.FERNANDEZ@UABC.MX</t>
+          <t>CGALAPAZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>04-03-2026 18:04:01</t>
+          <t>04-03-2026 06:48:12</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>04-03-2026 18:06:06</t>
+          <t>09-03-2026 08:12:11</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>03-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr"/>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>09-03-2026 08:02:31</t>
+        </is>
+      </c>
       <c r="U14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W14" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2373,14 +2353,22 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26210522893100004500</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
+          <t>26210523000020004734</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Guillermo Velazquez Garcia de Alba</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -2397,12 +2385,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>348681</t>
+          <t>348553</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90846</t>
+          <t>90718</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2412,17 +2400,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CLAUDIA YANET</t>
+          <t xml:space="preserve">ENRIQUE </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MEDELLIN</t>
+          <t>FERNANDEZ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MARTINEZ</t>
+          <t>ALVARADO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2432,33 +2420,33 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6121768652</t>
+          <t>6151035404</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>30-10-1978</t>
+          <t>02-09-1997</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>ATNDH.ISSSTEHG@GMAIL.COM</t>
+          <t>EN.FERNANDEZ@UABC.MX</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>05-03-2026 12:15:38</t>
+          <t>04-03-2026 18:04:01</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -2468,28 +2456,28 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>18-03-2026 14:09:39</t>
+          <t>04-03-2026 18:06:06</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>17-04-2026 23:59:59</t>
+          <t>03-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V15" t="inlineStr"/>
@@ -2500,22 +2488,14 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26210523292300005450</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>CRISTINA AYLIN CHAVEZ GONZALEZ</t>
-        </is>
-      </c>
+          <t>26210522893100004500</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2532,12 +2512,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>348773</t>
+          <t>348681</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90938</t>
+          <t>90846</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2547,17 +2527,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">JESUS IVAN </t>
+          <t>CLAUDIA YANET</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t xml:space="preserve"> MEDELLIN</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t xml:space="preserve"> MARTINEZ</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2567,33 +2547,33 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6121688845</t>
+          <t>6121768652</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>21-08-2001</t>
+          <t>30-10-1978</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>IVANFLORESCIV@HOTMAIL.COM</t>
+          <t>ATNDH.ISSSTEHG@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>05-03-2026 17:42:55</t>
+          <t>05-03-2026 12:15:38</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2603,28 +2583,28 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>05-03-2026 17:44:17</t>
+          <t>18-03-2026 14:09:39</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>04-06-2026 23:59:59</t>
+          <t>17-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V16" t="inlineStr"/>
@@ -2635,14 +2615,22 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26210522924890004584</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
+          <t>26210523292300005450</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>CRISTINA AYLIN CHAVEZ GONZALEZ</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2659,12 +2647,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>348551</t>
+          <t>348773</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>90716</t>
+          <t>90938</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2674,17 +2662,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">CAROLINA </t>
+          <t xml:space="preserve">JESUS IVAN </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">GONZALEZ </t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">TENA </t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2694,28 +2682,28 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6121209365</t>
+          <t>6121688845</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>29-05-2000</t>
+          <t>21-08-2001</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CAROLINAGONZALEZTNA@GMAIL.COM</t>
+          <t>IVANFLORESCIV@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>04-03-2026 18:01:21</t>
+          <t>05-03-2026 17:42:55</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2740,12 +2728,12 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>04-03-2026 18:02:41</t>
+          <t>05-03-2026 17:44:17</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>03-06-2026 23:59:59</t>
+          <t>04-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -2762,7 +2750,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26210522892810004499</t>
+          <t>26210522924890004584</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
@@ -2786,12 +2774,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>348995</t>
+          <t>348090</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>91160</t>
+          <t>90255</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2801,17 +2789,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>JENNIFER</t>
+          <t>PERLA YAMELY</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SOLIS</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>BERNAL</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2821,10 +2809,14 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5569105371</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>6122342275</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>C VILLA LAETITIA 316</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2832,56 +2824,64 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>26-05-2003</t>
+          <t>22-05-1987</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>SOLISBERNALJENNIFER3@GMAIL.COM</t>
+          <t>YAMELYGLEZ@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>06-03-2026 17:26:05</t>
+          <t>03-03-2026 15:41:32</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>07-03-2026 13:32:29</t>
+          <t>03-03-2026 15:46:24</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>06-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>03-03-2026 15:45:50</t>
+        </is>
+      </c>
       <c r="U18" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2889,36 +2889,36 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26210522975760004698</t>
+          <t>26210522844800004364</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>349634</t>
+          <t>348084</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>91799</t>
+          <t>90249</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2928,17 +2928,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>JESUS EDUARDO</t>
+          <t>MITZI JAQUELIN</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CORONADO</t>
+          <t xml:space="preserve">ZAZUETA </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SOLIS</t>
+          <t xml:space="preserve">MEDINA </t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2948,67 +2948,67 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3222622231</t>
+          <t>3314282828</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>C OLEAJE 290</t>
+          <t>OAXACA 370</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>05-04-2009</t>
+          <t>28-10-1998</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>JESUSCORONADO1209@ICLOUD.COM</t>
+          <t>MITZI.ZAZUETA.M@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>09-03-2026 18:55:07</t>
+          <t>03-03-2026 15:27:52</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>09-03-2026 18:57:49</t>
+          <t>03-03-2026 15:38:07</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>09-03-2026 18:57:19</t>
+          <t>03-03-2026 15:37:20</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -3028,36 +3028,36 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26210523025010004805</t>
+          <t>26210522844480004363</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Pablo Rieke Campoy</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>349643</t>
+          <t>348995</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>91808</t>
+          <t>91160</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3067,17 +3067,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ALEXSA PAULET</t>
+          <t>JENNIFER</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>BELTRAN</t>
+          <t>SOLIS</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUTIERREZ </t>
+          <t>BERNAL</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6122324179</t>
+          <t>5569105371</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3098,22 +3098,22 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>18-11-2008</t>
+          <t>26-05-2003</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>ALEXSAPAULETBELTRANMORA@GMAIL.COM</t>
+          <t>SOLISBERNALJENNIFER3@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>09-03-2026 19:04:02</t>
+          <t>06-03-2026 17:26:05</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -3123,28 +3123,28 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>09-03-2026 19:05:11</t>
+          <t>07-03-2026 13:32:29</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
+          <t>06-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V20" t="inlineStr"/>
@@ -3155,14 +3155,14 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26210523025690004807</t>
+          <t>26210522975760004698</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -3179,12 +3179,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>349621</t>
+          <t>349634</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>91786</t>
+          <t>91799</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VIRGINIA</t>
+          <t>JESUS EDUARDO</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6122500220</t>
+          <t>3222622231</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3224,22 +3224,22 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>16-11-1991</t>
+          <t>05-04-2009</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>VIRGINIACORONADO1209@GMAIL.COM</t>
+          <t>JESUSCORONADO1209@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>09-03-2026 18:43:37</t>
+          <t>09-03-2026 18:55:07</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>09-03-2026 18:53:31</t>
+          <t>09-03-2026 18:57:49</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>09-03-2026 18:51:27</t>
+          <t>09-03-2026 18:57:19</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26210523024640004803</t>
+          <t>26210523025010004805</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
@@ -3318,12 +3318,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>349596</t>
+          <t>349643</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>91761</t>
+          <t>91808</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3333,17 +3333,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ALAN ALEXANDER</t>
+          <t>ALEXSA PAULET</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ARREOLA</t>
+          <t>BELTRAN</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t xml:space="preserve">GUTIERREZ </t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3353,28 +3353,28 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6123484570</t>
+          <t>6122324179</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>14-08-2009</t>
+          <t>18-11-2008</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>ALAN.09AP28@GMAIL.COM</t>
+          <t>ALEXSAPAULETBELTRANMORA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>09-03-2026 18:12:45</t>
+          <t>09-03-2026 19:04:02</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>12-03-2026 16:46:17</t>
+          <t>09-03-2026 19:05:11</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>11-04-2026 23:59:59</t>
+          <t>08-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26210523126850005063</t>
+          <t>26210523025690004807</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
@@ -3445,12 +3445,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>350435</t>
+          <t>349621</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>92599</t>
+          <t>91786</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3460,17 +3460,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">AZUL JOHANA </t>
+          <t>VIRGINIA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">BENITEZ </t>
+          <t>CORONADO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">DOMINGUEZ </t>
+          <t>SOLIS</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3480,10 +3480,14 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>7531651551</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>6122500220</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>C OLEAJE 290</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3491,17 +3495,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>12-05-1996</t>
+          <t>16-11-1991</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>ANYA12270213@GMAIL.COM</t>
+          <t>VIRGINIACORONADO1209@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>12-03-2026 18:30:32</t>
+          <t>09-03-2026 18:43:37</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3511,36 +3515,44 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>12-03-2026 18:32:25</t>
+          <t>09-03-2026 18:53:31</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>11-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr"/>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>09-03-2026 18:51:27</t>
+        </is>
+      </c>
       <c r="U23" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W23" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3548,14 +3560,14 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26210523131670005075</t>
+          <t>26210523024640004803</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3572,12 +3584,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>350190</t>
+          <t>348551</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>92355</t>
+          <t>90716</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3587,17 +3599,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANGEL ENRIQUE </t>
+          <t xml:space="preserve">CAROLINA </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">JORDAN </t>
+          <t xml:space="preserve">GONZALEZ </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">MADERA </t>
+          <t xml:space="preserve">TENA </t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3607,28 +3619,28 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6121545813</t>
+          <t>6121209365</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>29-07-2004</t>
+          <t>29-05-2000</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>FECA362@GMAIL.COM</t>
+          <t>CAROLINAGONZALEZTNA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>11-03-2026 18:09:43</t>
+          <t>04-03-2026 18:01:21</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3643,28 +3655,28 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>11-03-2026 18:10:47</t>
+          <t>04-03-2026 18:02:41</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>10-04-2026 23:59:59</t>
+          <t>03-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V24" t="inlineStr"/>
@@ -3675,14 +3687,14 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26210523098170004990</t>
+          <t>26210522892810004499</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -3699,12 +3711,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>351715</t>
+          <t>350435</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>93879</t>
+          <t>92599</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3714,17 +3726,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOHANN EMIR </t>
+          <t xml:space="preserve">AZUL JOHANA </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAVIS </t>
+          <t xml:space="preserve">BENITEZ </t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CARBALLO</t>
+          <t xml:space="preserve">DOMINGUEZ </t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3734,31 +3746,35 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6122182276</t>
+          <t>7531651551</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>23-06-2008</t>
+          <t>12-05-1996</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>JEMIRS@GMAIL.COM</t>
+          <t>ANYA12270213@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>17-03-2026 20:25:14</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>12-03-2026 18:30:32</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -3766,22 +3782,22 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>19-03-2026 19:37:43</t>
+          <t>12-03-2026 18:32:25</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>18-06-2026 23:59:59</t>
+          <t>11-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -3798,22 +3814,14 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26210523341920005574</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>VERONICA VIANEY LOYA CONTRERAS</t>
-        </is>
-      </c>
+          <t>26210523131670005075</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -3830,12 +3838,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>351912</t>
+          <t>351713</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>94076</t>
+          <t>93877</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3845,17 +3853,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>JOSE ANTONIO</t>
+          <t xml:space="preserve">KHAZEL </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SOSA</t>
+          <t>MAGAÑA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t xml:space="preserve">BARAJAS </t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3865,7 +3873,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>9622915521</t>
+          <t>6121409077</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3876,24 +3884,20 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>29-07-2003</t>
+          <t>08-11-2008</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>JOSEANTONIOSOSALOPEZ26@GMAIL.COM</t>
+          <t>KHAZELITO08@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>18-03-2026 17:40:04</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>17-03-2026 20:22:24</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -3901,22 +3905,22 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>TRIMESTRE ESTUDIANTE</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>500</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>18-03-2026 17:41:09</t>
+          <t>19-03-2026 19:39:17</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>17-04-2026 23:59:59</t>
+          <t>18-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
@@ -3933,14 +3937,22 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26210523300070005469</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
+          <t>26210523342010005575</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>VERONICA VIANEY LOYA CONTRERAS</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -3957,12 +3969,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>352135</t>
+          <t>351772</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>94299</t>
+          <t>93936</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3972,17 +3984,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANGEL DE JESUS </t>
+          <t xml:space="preserve">JESUS IGNACIO </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SILVA</t>
+          <t>INZUNZA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t xml:space="preserve">TAMAYO </t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3992,12 +4004,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2227397462</t>
+          <t>6121595587</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>C DE LA NORIA 459-B</t>
+          <t>CAPELLA #102</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4007,17 +4019,17 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>27-01-2000</t>
+          <t>22-08-1972</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>ANGELDEJESUSSILVA61@GMAIL.COM</t>
+          <t>IGNACIOINZUNZAMX@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>19-03-2026 16:41:16</t>
+          <t>18-03-2026 09:14:57</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -4032,27 +4044,27 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>19-03-2026 16:53:56</t>
+          <t>21-03-2026 08:02:30</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>18-04-2026 23:59:59</t>
+          <t>19-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>19-03-2026 16:52:23</t>
+          <t>20-03-2026 10:23:41</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4072,36 +4084,44 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26210523333450005550</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
+          <t>26210523388340005653</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>Guillermo Velazquez Garcia de Alba</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>351913</t>
+          <t>352212</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>94077</t>
+          <t>94376</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4111,17 +4131,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ESLIN DANIEL</t>
+          <t xml:space="preserve">OLIVIA </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">GOMEZ </t>
+          <t>LARA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">PEREZ </t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4131,10 +4151,14 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6692359001</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>6121530603</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>AGINGANDU LT 10</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4142,17 +4166,17 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>09-09-1999</t>
+          <t>27-12-1980</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>EDANIEL909@ICLOUD.COM</t>
+          <t>LARACASTILLOLIVIA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>18-03-2026 17:42:35</t>
+          <t>19-03-2026 20:01:32</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4162,36 +4186,44 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>999</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>18-03-2026 17:43:30</t>
+          <t>19-03-2026 20:10:12</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>17-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr"/>
+          <t>18-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>19-03-2026 20:09:26</t>
+        </is>
+      </c>
       <c r="U28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr"/>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W28" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4199,36 +4231,36 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26210523300250005470</t>
+          <t>26210523343270005577</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>352212</t>
+          <t>352216</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>94376</t>
+          <t>94380</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4238,19 +4270,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">OLIVIA </t>
+          <t>VALENTINA ISABEL</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
+          <t>ESPINOZA</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t>LARA</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>CASTILLO</t>
-        </is>
-      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>52</t>
@@ -4258,42 +4290,34 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6121530603</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>AGINGANDU LT 10</t>
-        </is>
-      </c>
+          <t>6122038086</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>27-12-1980</t>
+          <t>23-11-2008</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>LARACASTILLOLIVIA@GMAIL.COM</t>
+          <t>VALESPINOZALARA08@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>19-03-2026 20:01:32</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>19-03-2026 20:07:14</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4303,7 +4327,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -4316,21 +4340,13 @@
           <t>18-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>19-03-2026 20:09:26</t>
-        </is>
-      </c>
+      <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4345,7 +4361,7 @@
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -4362,12 +4378,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>352216</t>
+          <t>349596</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>94380</t>
+          <t>91761</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4377,17 +4393,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VALENTINA ISABEL</t>
+          <t>ALAN ALEXANDER</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>ARREOLA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>LARA</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4397,31 +4413,35 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6122038086</t>
+          <t>6123484570</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>23-11-2008</t>
+          <t>14-08-2009</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>VALESPINOZALARA08@GMAIL.COM</t>
+          <t>ALAN.09AP28@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>19-03-2026 20:07:14</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+          <t>09-03-2026 18:12:45</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
       <c r="O30" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -4429,22 +4449,22 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>19-03-2026 20:10:12</t>
+          <t>12-03-2026 16:46:17</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>18-04-2026 23:59:59</t>
+          <t>11-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
@@ -4461,14 +4481,14 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26210523343270005577</t>
+          <t>26210523126850005063</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -4485,12 +4505,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>351713</t>
+          <t>351912</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>93877</t>
+          <t>94076</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4500,17 +4520,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">KHAZEL </t>
+          <t>JOSE ANTONIO</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>MAGAÑA</t>
+          <t>SOSA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">BARAJAS </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4520,7 +4540,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6121409077</t>
+          <t>9622915521</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4531,20 +4551,24 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>08-11-2008</t>
+          <t>29-07-2003</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>KHAZELITO08@GMAIL.COM</t>
+          <t>JOSEANTONIOSOSALOPEZ26@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>17-03-2026 20:22:24</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>18-03-2026 17:40:04</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr">
         <is>
           <t>Sin contrato</t>
@@ -4552,22 +4576,22 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>TRIMESTRE ESTUDIANTE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>19-03-2026 19:39:17</t>
+          <t>18-03-2026 17:41:09</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>18-06-2026 23:59:59</t>
+          <t>17-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T31" t="inlineStr"/>
@@ -4584,22 +4608,14 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26210523342010005575</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>VERONICA VIANEY LOYA CONTRERAS</t>
-        </is>
-      </c>
+          <t>26210523300070005469</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -4616,12 +4632,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>352014</t>
+          <t>351534</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>94178</t>
+          <t>93698</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4631,17 +4647,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">GABRIEL </t>
+          <t>GEMA LETICIA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>LUCERO</t>
+          <t>JACOBO</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4651,37 +4667,37 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6121006899</t>
+          <t>6121318359</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">C TEOTIHUACAN </t>
+          <t>EUCALIPTO #210</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>14-06-2002</t>
+          <t>23-09-1987</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>GABRIELVALENCIALUCERO07@GMAIL.COM</t>
+          <t>GEMMITA29@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>18-03-2026 20:58:14</t>
+          <t>17-03-2026 15:08:42</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -4691,27 +4707,27 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>999</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>18-03-2026 21:05:19</t>
+          <t>23-03-2026 13:36:50</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>17-04-2026 23:59:59</t>
+          <t>22-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>18-03-2026 21:04:30</t>
+          <t>23-03-2026 13:35:40</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4721,7 +4737,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -4731,14 +4747,22 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26210523310820005509</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
+          <t>26210523426270005749</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>VERONICA VIANEY LOYA CONTRERAS</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -4755,12 +4779,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>352220</t>
+          <t>351739</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>94384</t>
+          <t>93903</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4770,17 +4794,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>JESUS ALBERTO</t>
+          <t>EDGAR OMAR</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CASTANEDO</t>
+          <t>MONTIEL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>HIGUERA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4790,12 +4814,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6122121070</t>
+          <t>6121411204</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>C PERU 340</t>
+          <t>ZEOLITA S/N</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4805,22 +4829,22 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>15-04-1969</t>
+          <t>09-05-1999</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1JCASTANEDO@GMAIL.COM</t>
+          <t>MONTIELE8@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>19-03-2026 20:15:21</t>
+          <t>18-03-2026 05:24:14</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -4830,27 +4854,27 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>19-03-2026 20:20:34</t>
+          <t>20-03-2026 05:23:05</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>18-04-2026 23:59:59</t>
+          <t>19-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>19-03-2026 20:19:39</t>
+          <t>20-03-2026 05:22:22</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4860,7 +4884,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -4870,145 +4894,2813 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26210523343810005580</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
+          <t>26210523346940005588</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>Guillermo Velazquez Garcia de Alba</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Christian Jahassiel Castro Navarro</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>351677</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>93841</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JUAN ANDRES </t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>BARRETO</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>VALENCIA</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>6121776260</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>C. PUMITA S/N</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>09-05-1995</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>JUANRKANDRES@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>17-03-2026 19:17:29</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>24-03-2026 21:36:49</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>23-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>24-03-2026 21:35:59</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>26210523487060005906</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>CRISTINA AYLIN CHAVEZ GONZALEZ</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>Natalia Rangel Gavilan</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>351679</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>93843</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALONDRA </t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>ESTRADA</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>6121832286</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>10-08-1996</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>17-03-2026 19:18:41</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>24-03-2026 21:36:49</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>23-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>26210523487060005906</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>CRISTINA AYLIN CHAVEZ GONZALEZ</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>351913</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>94077</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ESLIN DANIEL</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GOMEZ </t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PEREZ </t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>6692359001</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>09-09-1999</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>EDANIEL909@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>18-03-2026 17:42:35</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>18-03-2026 17:43:30</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>26210523300250005470</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>350190</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>92355</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANGEL ENRIQUE </t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JORDAN </t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MADERA </t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>6121545813</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>29-07-2004</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>FECA362@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>11-03-2026 18:09:43</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>11-03-2026 18:10:47</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>10-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>26210523098170004990</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>352653</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>94817</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>JESUS ANIBAL</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>ESPINOZA</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COTA </t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>6121696144</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C AGUIGANDU </t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>13-07-1981</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>JESUSANIBALESPPINOZACOTA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>23-03-2026 07:16:20</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>23-03-2026 09:31:55</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>23-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>23-03-2026 09:29:40</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>26210523420280005731</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>VERONICA VIANEY LOYA CONTRERAS</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>Christian Jahassiel Castro Navarro</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>352014</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>94178</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GABRIEL </t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>VALENCIA</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>LUCERO</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>6121006899</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C TEOTIHUACAN </t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>14-06-2002</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>GABRIELVALENCIALUCERO07@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>18-03-2026 20:58:14</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>18-03-2026 21:05:19</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>18-03-2026 21:04:30</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>26210523310820005509</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>353138</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>95302</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NICOLE ALEXA</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>MANRIQUEZ</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>6122291761</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>27-09-2005</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>ALEXA2MANRIQUEZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>24-03-2026 16:47:15</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>24-03-2026 16:50:11</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>23-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>26210523472140005863</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>353322</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>95486</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>DANIELA MONSERRAT</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>TENORIO</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIRANDA </t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>6121997821</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>C DRAKKAR 204</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>11-08-1995</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>DANYELAMTM@OUTLOOK.COM</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>25-03-2026 13:17:28</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>25-03-2026 13:25:25</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>24-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>25-03-2026 13:24:49</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>26210523501060005935</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>353820</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>95984</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GEMMA IRAIS </t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CAMACHO </t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>TALAMANTES</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>6121562076</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>SAN JUAN 203</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>17-12-1987</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>DIFSANTAFE@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>27-03-2026 18:53:51</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>27-03-2026 18:58:53</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>26-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>27-03-2026 18:57:10</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>26210523573240006132</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>353837</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>96001</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>JORGE</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>VEGA</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>ORTIZ</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>6671507538</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>FRANCISCO JAVIER MINA 810</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>06-02-1975</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>JORGEVEGAORG@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>27-03-2026 20:12:38</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>27-03-2026 20:17:13</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>26-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>27-03-2026 20:16:12</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>26210523575760006136</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>Guillermo  Garcia De Alba Velazquez</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>353278</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>95442</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LEONARDO</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>JIMENEZ</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>ARMENTA</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>6124309077</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>14-07-2002</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>LEOYOULONE@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>25-03-2026 08:30:25</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>25-03-2026 08:35:39</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>24-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>26210523495890005916</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>353512</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>95676</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>DAVID ANTONIO</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAMIREZ</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>QUIROZ</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>6121407986</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>12-06-1993</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>DAVID120325@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>26-03-2026 09:45:04</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>26-03-2026 09:46:32</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>25-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>26210523530490006009</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>Christian Jahassiel Castro Navarro</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>353276</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>95440</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>DEMIAN YAMIL</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>MAYORAL</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>NARVAEZ</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>5510585391</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>C BONAMPAK</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>05-06-2003</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>DEMINIOM@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>25-03-2026 08:25:31</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>25-03-2026 08:35:39</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>24-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>25-03-2026 08:32:29</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>26210523495890005916</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>353509</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>95673</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>KARLA MELISSA</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>YEE</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>VELASCO</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>6122023492</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>03-08-1992</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>MELYEE92@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>26-03-2026 09:39:48</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>26-03-2026 09:41:38</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>25-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>26210523530350006008</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>Christian Jahassiel Castro Navarro</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>353847</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>96011</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YESSICA </t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>LARA</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>BARRIENTOS</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>6121365893</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>23-12-1976</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>YESS_LARA@YAHOO.COM.MX</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>28-03-2026 06:42:01</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>28-03-2026 06:54:42</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>27-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>26210523588720006142</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>Christian Jahassiel Castro Navarro</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>352220</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>94384</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>JESUS ALBERTO</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>CASTANEDO</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>6122121070</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>C PERU 340</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>15-04-1969</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>1JCASTANEDO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>19-03-2026 20:15:21</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>19-03-2026 20:20:34</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>18-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>19-03-2026 20:19:39</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>26210523343810005580</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>352222</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>94386</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>PASEO LA PAZ</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t xml:space="preserve">MARIA DE LOS ANGELES </t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>GUILLEN</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t xml:space="preserve">PEÑALOZA </t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>6122200244</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
         <is>
           <t>Femenino</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>28-07-1981</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>MARI32.9P@GMAIL.COM</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>19-03-2026 20:18:42</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr">
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
         <is>
           <t>Sin contrato</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>19-03-2026 20:20:34</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>18-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr">
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr">
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr">
         <is>
           <t>Sucursal</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>26210523343810005580</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="inlineStr">
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
+      <c r="AB50" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>351715</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>93879</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JOHANN EMIR </t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DAVIS </t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>CARBALLO</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>6122182276</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>23-06-2008</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>JEMIRS@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>17-03-2026 20:25:14</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>TRIMESTRE ESTUDIANTE</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>19-03-2026 19:37:43</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>18-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>26210523341920005574</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>VERONICA VIANEY LOYA CONTRERAS</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>352135</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>94299</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANGEL DE JESUS </t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>SILVA</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2227397462</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>C DE LA NORIA 459-B</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>27-01-2000</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>ANGELDEJESUSSILVA61@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>19-03-2026 16:41:16</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>19-03-2026 16:53:56</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>18-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>19-03-2026 16:52:23</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>26210523333450005550</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>Juan Pablo Rieke Campoy</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>353414</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>95578</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>SANJUANA</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MORALES </t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>ANDRADE</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>6122297928</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>QUETZALCOATL</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>09-07-2009</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>SANJUANANDRADE@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>25-03-2026 18:21:36</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>25-03-2026 18:23:37</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>24-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>25-03-2026 18:22:50</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>26210523511600005969</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>352754</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>94918</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>PASEO LA PAZ</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LAURO ROLANDO YAIR</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>MAZO</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>ESPINOZA</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>6121192001</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>28-01-1986</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>CHESKKY2886@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>23-03-2026 13:15:15</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>23-03-2026 13:36:50</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>22-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>26210523426270005749</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>
